--- a/mc2/result/excel/engram_new.xlsx
+++ b/mc2/result/excel/engram_new.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25714" windowHeight="12634"/>
+    <workbookView windowWidth="25714" windowHeight="12634" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="level0" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2198" uniqueCount="910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2198" uniqueCount="912">
   <si>
     <t>fetchcase_name</t>
   </si>
@@ -2393,10 +2393,16 @@
     <t>exception_indices_range_exceed_ID901</t>
   </si>
   <si>
+    <t>['int8']</t>
+  </si>
+  <si>
     <t>[[10000, 20000], [30000, 40000], [50000, 60000], [70000, 80000]]</t>
   </si>
   <si>
     <t>exception_fetch_num_exceed_32_ID902</t>
+  </si>
+  <si>
+    <t>[[10240000000, 128]]</t>
   </si>
   <si>
     <t>[[2016, 2707, 400, 3897, 1164, 209, 2225, 1964, 509, 3554, 3621, 1012, 1340, 2609, 1636, 2594, 2367, 4088, 3724, 379, 4089, 1820, 738, 3837, 1539, 2350, 2638, 1690, 1748, 2926, 3293, 1647, 3130, 831, 639, 952, 1981, 116, 748, 3210, 3163, 3741, 224, 1152, 976, 1283, 1058, 2547, 3659, 3150], [2025, 1266, 1543, 2750, 3671, 110, 1895, 3864, 2004, 2933, 2634, 3869, 3088, 627, 1237, 3307, 881, 575, 3352, 1582, 1916, 3091, 1016, 258, 36, 3954, 1905, 3424, 1804, 2298, 2352, 2810, 1102, 473, 2468, 785, 2955, 3964, 2595, 263, 2689, 512, 2095, 728, 107, 3768, 537, 1058, 953, 2289], [548, 1410, 3016, 2248, 1625, 2555, 3147, 3472, 3254, 218, 1027, 870, 537, 2405, 1065, 3487, 201, 3077, 2889, 3288, 130, 32, 1703, 1525, 2472, 2963, 3414, 2963, 1547, 3987, 2250, 2182, 2139, 1163, 3331, 4031, 1638, 122, 324, 4036, 79, 2689, 3130, 755, 3762, 2818, 1318, 176, 4070, 357], [3386, 1024, 3658, 2997, 2545, 785, 915, 756, 2974, 2096, 1615, 3065, 2608, 2151, 1389, 1850, 98, 846, 750, 1160, 3699, 2534, 1264, 2882, 199, 2335, 123, 979, 3616, 2693, 2751, 1010, 3697, 1425, 3630, 3855, 1883, 2799, 2752, 1103, 2260, 151, 120, 2137, 1708, 1421, 930, 924, 113, 3350]]</t>
@@ -2772,7 +2778,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2783,13 +2789,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3242,28 +3241,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3272,118 +3274,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -12488,6 +12487,12 @@
   <sheetPr/>
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="7" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="2" width="27.8738738738739" customWidth="1"/>
+    <col min="3" max="3" width="12.5855855855856" customWidth="1"/>
+    <col min="4" max="4" width="15.8198198198198" customWidth="1"/>
+    <col min="5" max="5" width="67.7927927927928" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
@@ -12520,13 +12525,13 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>787</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -12537,10 +12542,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>790</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -12549,7 +12554,7 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -12560,7 +12565,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -12572,7 +12577,7 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -12583,19 +12588,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -12606,10 +12611,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B6" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -12618,7 +12623,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -12629,7 +12634,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -12641,7 +12646,7 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -12652,10 +12657,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B8" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -12664,7 +12669,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -12710,7 +12715,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -12722,7 +12727,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -12733,7 +12738,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -12745,7 +12750,7 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="F3">
         <v>8</v>
@@ -12756,7 +12761,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -12768,7 +12773,7 @@
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="F4">
         <v>16</v>
@@ -12779,10 +12784,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B5" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -12791,7 +12796,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -12802,11 +12807,11 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
+        <v>814</v>
+      </c>
+      <c r="B6" t="s">
         <v>812</v>
       </c>
-      <c r="B6" t="s">
-        <v>810</v>
-      </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
@@ -12814,7 +12819,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -12825,10 +12830,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B7" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
@@ -12837,7 +12842,7 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="F7">
         <v>16</v>
@@ -12848,7 +12853,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B8" t="s">
         <v>63</v>
@@ -12860,7 +12865,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -12871,7 +12876,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B9" t="s">
         <v>63</v>
@@ -12883,7 +12888,7 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -12894,7 +12899,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B10" t="s">
         <v>63</v>
@@ -12906,7 +12911,7 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="F10">
         <v>16</v>
@@ -12917,10 +12922,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B11" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -12929,7 +12934,7 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="F11">
         <v>4</v>
@@ -12940,10 +12945,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B12" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -12952,7 +12957,7 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="F12">
         <v>8</v>
@@ -12963,10 +12968,10 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B13" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -12975,7 +12980,7 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="F13">
         <v>16</v>
@@ -12986,7 +12991,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B14" t="s">
         <v>94</v>
@@ -12998,7 +13003,7 @@
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F14">
         <v>4</v>
@@ -13009,7 +13014,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B15" t="s">
         <v>172</v>
@@ -13021,7 +13026,7 @@
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="F15">
         <v>4</v>
@@ -13032,10 +13037,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B16" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
@@ -13044,7 +13049,7 @@
         <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="F16">
         <v>4</v>
@@ -13055,7 +13060,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B17" t="s">
         <v>94</v>
@@ -13067,7 +13072,7 @@
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F17">
         <v>8</v>
@@ -13078,7 +13083,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B18" t="s">
         <v>172</v>
@@ -13090,7 +13095,7 @@
         <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="F18">
         <v>8</v>
@@ -13101,10 +13106,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B19" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
@@ -13113,7 +13118,7 @@
         <v>10</v>
       </c>
       <c r="E19" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="F19">
         <v>8</v>
@@ -13124,7 +13129,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B20" t="s">
         <v>190</v>
@@ -13136,7 +13141,7 @@
         <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -13147,7 +13152,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B21" t="s">
         <v>193</v>
@@ -13159,7 +13164,7 @@
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -13170,10 +13175,10 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B22" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
@@ -13182,7 +13187,7 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="F22">
         <v>4</v>
@@ -13193,7 +13198,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B23" t="s">
         <v>190</v>
@@ -13205,7 +13210,7 @@
         <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="F23">
         <v>8</v>
@@ -13216,7 +13221,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B24" t="s">
         <v>193</v>
@@ -13228,7 +13233,7 @@
         <v>10</v>
       </c>
       <c r="E24" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="F24">
         <v>8</v>
@@ -13239,10 +13244,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B25" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
@@ -13251,7 +13256,7 @@
         <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="F25">
         <v>8</v>
@@ -13262,7 +13267,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B26" t="s">
         <v>94</v>
@@ -13274,7 +13279,7 @@
         <v>10</v>
       </c>
       <c r="E26" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -13285,7 +13290,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B27" t="s">
         <v>172</v>
@@ -13297,7 +13302,7 @@
         <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="F27">
         <v>4</v>
@@ -13308,10 +13313,10 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B28" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
@@ -13320,7 +13325,7 @@
         <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="F28">
         <v>4</v>
@@ -13331,7 +13336,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B29" t="s">
         <v>94</v>
@@ -13343,7 +13348,7 @@
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="F29">
         <v>8</v>
@@ -13354,7 +13359,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B30" t="s">
         <v>172</v>
@@ -13366,7 +13371,7 @@
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="F30">
         <v>8</v>
@@ -13377,10 +13382,10 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B31" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
@@ -13389,7 +13394,7 @@
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="F31">
         <v>8</v>
@@ -13400,7 +13405,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B32" t="s">
         <v>190</v>
@@ -13412,7 +13417,7 @@
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="F32">
         <v>4</v>
@@ -13423,7 +13428,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B33" t="s">
         <v>193</v>
@@ -13435,7 +13440,7 @@
         <v>10</v>
       </c>
       <c r="E33" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="F33">
         <v>4</v>
@@ -13446,10 +13451,10 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B34" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -13458,7 +13463,7 @@
         <v>10</v>
       </c>
       <c r="E34" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="F34">
         <v>4</v>
@@ -13469,7 +13474,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B35" t="s">
         <v>190</v>
@@ -13481,7 +13486,7 @@
         <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="F35">
         <v>8</v>
@@ -13492,7 +13497,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B36" t="s">
         <v>193</v>
@@ -13504,7 +13509,7 @@
         <v>10</v>
       </c>
       <c r="E36" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="F36">
         <v>8</v>
@@ -13515,10 +13520,10 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B37" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
@@ -13527,7 +13532,7 @@
         <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="F37">
         <v>8</v>
@@ -13538,7 +13543,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B38" t="s">
         <v>24</v>
@@ -13550,7 +13555,7 @@
         <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="F38">
         <v>32</v>
@@ -13561,7 +13566,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B39" t="s">
         <v>24</v>
@@ -13573,7 +13578,7 @@
         <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="F39">
         <v>64</v>
@@ -13584,7 +13589,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B40" t="s">
         <v>56</v>
@@ -13596,7 +13601,7 @@
         <v>10</v>
       </c>
       <c r="E40" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F40">
         <v>32</v>
@@ -13607,7 +13612,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B41" t="s">
         <v>56</v>
@@ -13619,7 +13624,7 @@
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F41">
         <v>64</v>
@@ -13630,7 +13635,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B42" t="s">
         <v>24</v>
@@ -13642,7 +13647,7 @@
         <v>10</v>
       </c>
       <c r="E42" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="F42">
         <v>32</v>
@@ -13653,7 +13658,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B43" t="s">
         <v>24</v>
@@ -13665,7 +13670,7 @@
         <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="F43">
         <v>64</v>
@@ -13676,7 +13681,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B44" t="s">
         <v>56</v>
@@ -13688,7 +13693,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="F44">
         <v>32</v>
@@ -13699,7 +13704,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B45" t="s">
         <v>56</v>
@@ -13711,7 +13716,7 @@
         <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="F45">
         <v>64</v>
@@ -13722,10 +13727,10 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B46" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
@@ -13734,7 +13739,7 @@
         <v>10</v>
       </c>
       <c r="E46" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="F46">
         <v>8</v>
@@ -13745,10 +13750,10 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B47" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -13757,7 +13762,7 @@
         <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="F47">
         <v>8</v>
@@ -13768,10 +13773,10 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B48" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
@@ -13780,7 +13785,7 @@
         <v>10</v>
       </c>
       <c r="E48" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="F48">
         <v>4</v>
@@ -13791,10 +13796,10 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B49" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
@@ -13803,7 +13808,7 @@
         <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="F49">
         <v>8</v>
@@ -13814,10 +13819,10 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B50" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
@@ -13826,7 +13831,7 @@
         <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="F50">
         <v>2</v>
@@ -13837,10 +13842,10 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B51" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C51" t="s">
         <v>13</v>
@@ -13849,7 +13854,7 @@
         <v>10</v>
       </c>
       <c r="E51" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="F51">
         <v>4</v>

--- a/mc2/result/excel/engram_new.xlsx
+++ b/mc2/result/excel/engram_new.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25714" windowHeight="12634" activeTab="3"/>
+    <workbookView windowWidth="25714" windowHeight="12634"/>
   </bookViews>
   <sheets>
     <sheet name="level0" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
     <t>[(-5, 5)]</t>
   </si>
   <si>
-    <t>[[386, 315, 315, 175, 315, 304, 259, 301, 63, 334, 314, 156, 451, 36, 266, 193, 293, 200, 400, 110, 172, 490], [504, 412, 403, 36, 91, 17, 270, 14, 99, 23, 476, 204, 233, 147, 492]]</t>
+    <t>[[203], [387, 417]]</t>
   </si>
   <si>
     <t>h128_ws2_ne256_idx512_infp16_outfp16_ID002</t>
@@ -74,7 +74,7 @@
     <t>['fp16']</t>
   </si>
   <si>
-    <t>[[132, 81, 288, 182, 456, 198, 16, 254, 130, 301, 475, 50, 208, 226, 122, 174, 155, 509, 345, 393], [398, 7, 46, 196, 103, 51, 149, 462, 488, 349, 361, 386, 31, 459, 300, 440, 419, 88, 500, 367, 447, 207, 92, 401]]</t>
+    <t>[[227, 285, 96, 446, 248, 42, 133, 167, 288], [1587, 1853]]</t>
   </si>
   <si>
     <t>h128_ws2_ne256_idx512_infp32_outfp32_ID003</t>
@@ -83,7 +83,7 @@
     <t>['fp32']</t>
   </si>
   <si>
-    <t>[[98, 358, 408, 384, 493, 155, 290, 443, 221, 277, 151, 18, 273, 386, 494, 309, 499, 7, 179], [210, 266, 289, 147, 221, 349, 239, 430, 456, 378, 371, 370, 226, 33, 474, 188, 163, 345, 443, 46, 399, 164, 255, 425, 32]]</t>
+    <t>[[227, 458, 414, 343, 463, 303, 1703, 1982], [63]]</t>
   </si>
   <si>
     <t>h128_ws2_ne128_idx256_small_inbf16_outbf16_ID004</t>
@@ -92,13 +92,13 @@
     <t>[[128, 128]]</t>
   </si>
   <si>
-    <t>[[197, 134, 209, 211, 156, 95, 119, 179, 24, 35, 163, 27, 218, 229, 22, 88, 242, 19, 34, 132, 92, 250, 85, 136, 239, 151], [109, 117, 114, 118, 57, 190, 255, 233, 123, 189]]</t>
+    <t>[[193, 215, 63, 155, 379, 242, 147], [96]]</t>
   </si>
   <si>
     <t>h128_ws2_ne128_idx256_small_infp16_outfp16_ID005</t>
   </si>
   <si>
-    <t>[[148], [92, 89, 231, 20, 239, 86, 224, 108, 144, 2, 124, 186, 215, 235, 179, 169, 50]]</t>
+    <t>[[409, 308, 184, 332, 213, 46, 57, 98], [303, 485, 403, 1974, 609]]</t>
   </si>
   <si>
     <t>h128_ws2_ne1024_inbf16_outbf16_ID006</t>
@@ -107,73 +107,73 @@
     <t>[[1024, 128]]</t>
   </si>
   <si>
-    <t>[[374, 221, 82, 1086, 211, 849, 78, 418, 123, 1725, 233, 382, 325, 985, 40, 228, 354, 15, 1983, 280, 410], [390, 682, 453, 295, 385, 417, 1686, 453]]</t>
+    <t>[[455, 331, 215, 1145, 73, 31], [51, 2025, 2017, 269, 94]]</t>
   </si>
   <si>
     <t>h128_ws4_ne1024_inbf16_outbf16_ID007</t>
   </si>
   <si>
-    <t>[[474, 1685, 20, 320, 69, 327, 118, 15, 1111, 387, 392, 258, 421, 340, 68, 83, 220, 989, 326, 318, 290, 430, 245, 2360, 1738, 98, 502, 423, 2703], [263, 245, 758, 383, 454, 179, 61, 35, 48, 4019, 1387, 74, 482], [407, 1290, 209, 501, 109, 475, 2047, 151, 37, 93, 175, 479, 18, 105, 221, 119, 421, 361, 406, 176, 1644, 489, 421, 2228, 1494, 2105, 384, 143, 153, 189], [91, 344, 102, 558, 129, 342, 433, 262, 440, 3037, 1954, 459, 148, 457, 225, 500, 39, 3874, 235, 444, 336, 1328, 263]]</t>
+    <t>[[179], [182, 59, 55, 291, 34], [194], [658, 60, 1925, 302]]</t>
   </si>
   <si>
     <t>h128_ws8_ne1024_inbf16_outbf16_ID008</t>
   </si>
   <si>
-    <t>[[227, 346, 245, 294, 212, 319, 3064, 467, 471, 177, 350, 252, 371, 501, 232, 96, 7866, 109, 225, 122, 3537, 118, 5019, 6392, 175, 247, 195, 5736], [6837], [150, 122, 367, 129, 458, 210, 5197, 478, 989, 311], [2638, 458], [130, 7222, 460, 2259, 46, 205, 5103, 315, 239, 146, 5532, 133, 417, 246, 38, 89, 423, 143, 114, 35], [98, 24, 427, 326, 3507, 231, 119, 102, 5778, 206, 3322], [365, 232, 7455, 6178, 453, 152, 303, 2492, 201, 433, 217, 224], [48, 11, 4617, 218, 354]]</t>
+    <t>[[1424, 105, 146, 1723, 1725, 12, 336, 497, 42], [106, 1281, 99, 230], [236, 724, 461, 131, 469, 331], [375, 426, 49, 248, 307, 512, 463], [227, 44, 2007, 492, 88, 162, 356, 297], [322, 81], [147], [211]]</t>
   </si>
   <si>
     <t>h128_ws16_ne1024_inbf16_outbf16_ID009</t>
   </si>
   <si>
-    <t>[[185, 470, 233, 491, 2473, 12200, 443, 0, 13393, 476, 3689, 305, 65, 502, 14061, 282, 485, 99, 190, 440, 49, 312, 491, 129], [390, 15321, 309, 8], [14394, 441, 8081, 881, 215, 200, 272, 438, 240, 381, 476, 212, 81, 254, 9871, 431, 212, 433, 506, 309], [379, 216, 374, 9037, 387], [14808, 1, 484, 353, 333, 4607, 430, 183, 443, 7319, 474, 87, 212, 497, 103, 345, 498, 10154, 483, 14648, 428, 167], [311, 255, 511, 216, 10545, 3360, 137, 252, 429], [475, 425, 298, 452, 325, 8, 118, 450, 6638, 434, 385, 17, 14068, 351, 3471, 125, 15675, 32, 156, 10970, 50, 66, 147], [4708], [199, 253, 9282, 492, 341, 292, 38, 13736, 162, 238, 179, 10534, 356, 238, 1365, 312, 11114, 235, 450, 512, 72, 364, 310, 352, 119, 351, 511, 11268], [112, 10571, 446, 505, 447, 464, 478, 74, 293, 102, 409, 406, 494, 4864, 10767, 417, 98, 15, 425, 2110, 6484, 140, 437, 288, 7644, 471, 102, 286, 253, 363], [12685, 481, 1, 11256, 2289, 396, 315, 344, 144, 51, 201, 316, 53, 374], [458, 323, 148, 10364, 443, 15348, 459, 361, 333, 6533, 210, 100, 229, 103, 54, 311, 805, 209, 227, 12, 321, 484, 7829, 83, 7368, 448], [310, 381, 499, 14266, 141, 488, 14416, 132, 101, 2148, 485], [215, 260, 85, 477, 461, 409, 5574, 11454, 146, 387], [162, 131, 172, 6229, 194, 78, 411, 378, 441, 507, 234, 4283, 96, 78, 430, 413, 326, 2949, 354, 452, 5662, 10048, 230, 99, 286, 99, 379, 15903, 178], [680, 396, 486, 64, 262, 254, 488, 278, 14887, 313, 38, 5874]]</t>
+    <t>[[80, 490, 855], [244, 91, 201, 505, 101, 475, 138, 1237, 795], [469, 956, 176], [312, 424, 348, 455, 324, 143, 350, 321], [252, 1383], [281, 378, 407, 1625, 302], [144, 185, 333, 415, 234, 278], [62, 57], [466, 54, 1423, 309, 1955, 46, 1649, 215], [38, 1185, 489, 223, 10, 134, 94, 987, 36, 437], [122, 143, 1655, 368, 744, 18, 288], [292, 112, 289, 70], [452], [282, 1601, 446, 489, 217], [433], [78, 1549, 262, 272]]</t>
   </si>
   <si>
     <t>h128_ws2_ne1024_infp16_outfp16_ID010</t>
   </si>
   <si>
-    <t>[[103, 274, 395, 620, 3, 620, 1253, 1671, 445, 190, 305, 245, 1049, 380, 127, 54, 32, 68, 264, 135, 250, 98], [412, 1280, 337, 305, 336, 451, 351, 72, 1346, 373, 159, 431, 79, 692, 353, 1171]]</t>
+    <t>[[1018, 421, 169, 210, 365, 1691, 402, 378, 15, 293], [178, 2016, 444]]</t>
   </si>
   <si>
     <t>h128_ws4_ne1024_infp16_outfp16_ID011</t>
   </si>
   <si>
-    <t>[[194, 364, 467, 175, 454, 376, 271, 294, 500, 2314, 26, 129, 1888, 284, 66, 232, 2466, 495, 480, 345, 280, 94, 173, 329, 2071, 3921, 3367, 474], [479, 506, 367, 41, 116, 253, 265, 391, 1491, 3838, 175, 279, 364, 478, 172, 3216, 2213], [1611, 169, 369, 107, 211, 98, 326, 89, 3603, 190, 251, 3464, 233, 3500, 204, 496, 314, 43, 100, 24], [265, 2889, 14, 213, 270, 198, 1833, 255, 402, 161, 145, 44, 438, 2148, 3528, 486, 51, 2324, 423, 211, 501, 391, 199]]</t>
+    <t>[[425, 453, 454, 1041, 477, 389], [1231, 441, 359, 20, 161, 274, 170, 2024, 457, 486], [94, 205, 192], [482, 182]]</t>
   </si>
   <si>
     <t>h128_ws8_ne1024_infp16_outfp16_ID012</t>
   </si>
   <si>
-    <t>[[2781, 323, 2826, 7310, 493, 27, 408, 138, 404, 343, 3, 508, 329, 111, 5400, 482, 21, 479, 355, 103, 448, 239, 6737, 472, 210], [476, 406, 143, 67, 49, 200, 5, 0, 640, 430, 166, 4001, 3189], [264, 3982], [86, 46, 326, 214, 198, 65, 152, 96, 2074, 276, 7971, 424, 73, 59, 4161, 173, 6795, 406, 271], [178, 315, 370, 289, 492, 463, 290, 131, 361, 311, 179, 284, 383, 427, 6964, 4601, 3119, 5779, 471, 363, 71, 7845, 202, 296, 511, 8041, 234, 78, 485, 278], [2500, 375, 495, 375, 278, 70, 590, 39, 356, 532, 51], [374, 192, 407, 103, 209, 118, 2432, 7862, 214, 219, 360, 499, 381, 5954, 390], [470, 360, 35, 61, 2845, 70, 94, 396, 53, 7017, 452, 20, 383, 470, 507, 82, 1702, 270, 261, 501, 242, 7150, 237, 3605, 361, 275, 1076, 108]]</t>
+    <t>[[414, 31, 443, 204, 451, 410], [1490, 230, 1504, 171, 399, 1660, 1499, 293], [182, 1067, 664, 231], [205, 64, 243, 344, 415, 365, 157, 54, 29], [149, 124, 35, 276], [347, 10, 1562, 104, 295, 403, 290, 309, 178], [1944, 229, 1818, 461, 363, 138, 823, 191, 1956], [442, 458, 365]]</t>
   </si>
   <si>
     <t>h128_ws16_ne1024_infp16_outfp16_ID013</t>
   </si>
   <si>
-    <t>[[4206, 339, 6815, 502, 7003, 9611, 309, 485, 495, 241, 33, 142, 147, 499, 272, 305], [34, 416, 397, 25, 432, 7276, 5623, 14, 1706, 125, 88, 475, 378, 159, 5216, 11, 176, 493, 465, 8, 2983, 343, 258, 189], [206, 223, 114, 8163, 416], [18, 6220, 276, 348, 391, 50, 437, 170, 11573, 134, 501, 16113], [9803, 1160, 372, 774, 199, 507, 194, 478, 28, 78, 77], [13740, 474, 462, 442, 39, 485, 94, 162, 89, 1759, 226, 222, 171, 5215, 320, 172, 16132, 5275, 82, 68, 463], [355, 14997, 1197, 1474, 108, 389, 29, 41, 238, 12, 200, 202, 435, 333, 417, 438, 60, 1290, 501, 102, 7328, 174, 268, 451, 352], [305, 12283, 7875, 69, 294, 4629, 358, 257, 316, 92, 512, 54, 172, 14, 2568, 10940, 22, 112, 207, 493, 4691, 344, 371, 94, 237, 174, 12445, 279, 65, 177, 255], [14594, 21, 124, 195, 1478, 283, 366, 81, 318, 205, 249, 43, 70, 312, 368, 9033, 127, 7979, 6767, 429, 101, 14920, 494, 190, 275, 156, 305, 153, 255, 85], [100, 13064, 42, 485, 407, 275, 3684, 298, 121, 237, 176, 228, 219, 9098, 2587, 10, 250, 162, 498, 354, 140, 299, 6246, 236, 7680, 8, 357, 224, 212], [3789, 129, 332, 259, 140, 327, 13919, 11973, 309, 453, 231, 169, 155], [12439, 249, 353, 381, 369, 12917, 484, 62, 458, 343, 493, 249, 74, 256, 368, 7536, 78, 4257, 12811, 14696, 387, 454, 23, 413, 493, 469], [220, 284, 1691, 335, 310, 74, 389, 33, 318, 494, 287, 133, 3155, 191, 7765, 139, 328, 147, 387, 985, 3703, 264, 74], [512, 10004, 4204, 509, 168, 172, 16, 417], [11225, 481, 233, 56, 203, 15696, 308, 429, 88, 188, 231, 34, 355, 170, 96, 506, 436, 197, 436, 7097, 15267, 6302], [12077, 118, 140, 509]]</t>
+    <t>[[189, 28, 57, 265, 339, 457, 72, 304], [363, 207, 152], [123, 1499, 185, 302, 205, 1092, 370], [1589, 263, 512, 446, 297, 332, 371, 433], [74, 342, 74], [249, 380, 1127, 277, 48], [445, 328, 428, 1744], [113], [213, 416, 200, 35, 414], [49, 39, 384, 5, 1617, 47, 481, 460], [257, 293, 244, 90, 108, 344, 431, 81], [56, 25, 89, 381, 356, 160, 416, 146], [667, 971, 302], [383, 29, 373, 1147, 323, 493, 26, 276, 134, 1610], [509, 318, 252, 187], [200, 1796, 417, 230, 424, 217, 1894, 374, 370, 29]]</t>
   </si>
   <si>
     <t>h128_ws2_ne1024_infp32_outfp32_ID014</t>
   </si>
   <si>
-    <t>[[1553, 74, 234, 194, 54, 48, 465, 8, 231, 1353, 398, 400, 1260, 124, 1655, 260], [1022, 1229, 245, 446, 42, 1438, 444, 422, 159, 1673, 360, 74, 407, 208, 239, 235, 262, 444, 155, 119, 1491, 144, 444, 245, 176, 212, 1260, 67, 1105, 153, 362]]</t>
+    <t>[[261, 440, 178, 502, 428, 106, 221, 152, 146], [252, 251, 285, 501, 433, 342]]</t>
   </si>
   <si>
     <t>h128_ws4_ne1024_infp32_outfp32_ID015</t>
   </si>
   <si>
-    <t>[[259, 199, 324, 120, 449, 1386, 467, 241, 161, 426, 89, 385, 2503, 304, 3881, 2311, 262], [300, 182, 1061, 122, 50, 136, 440, 465, 2732, 76, 436, 463, 94, 1799, 416, 3731, 572, 374, 63, 353, 379, 501], [407, 2161, 2327, 238, 340, 176], [3696, 465, 62, 135, 451, 3722, 44, 341]]</t>
+    <t>[[499, 412], [314, 10, 113, 1527, 1537], [237, 311, 389, 70, 289, 264], [427, 731, 6, 10, 230, 482]]</t>
   </si>
   <si>
     <t>h128_ws8_ne1024_infp32_outfp32_ID016</t>
   </si>
   <si>
-    <t>[[428, 257, 284, 338, 343, 4467, 349, 2173, 645, 370, 7870, 257, 190, 394, 194, 329, 380, 33], [350, 294, 175, 4297, 6007, 53, 7266, 297, 330, 220, 226, 315, 4353, 232, 184, 497, 322, 11, 398, 298, 492, 37, 1681], [126, 312, 4005, 1458, 218, 493, 92, 392, 836, 206, 188, 108, 151, 198], [12, 7676, 275, 240, 3151, 347, 1037, 117, 469, 249, 286, 503, 350, 164, 376, 362, 253, 298, 224, 204, 162, 1233, 148, 6497, 483, 4174, 334, 178, 18], [138, 157, 429, 116, 7906, 495, 930, 1049, 321, 171, 237, 231, 103, 202, 26, 194, 7853, 185, 466, 280, 479, 223, 5109, 39, 2329, 78, 94], [202, 284, 166, 5664, 29, 5375, 278, 136, 130, 30, 233, 6953, 29, 330, 4099, 152], [407, 3282, 203, 455, 68, 5081, 273, 4243, 139, 963, 464, 287, 329, 178, 70, 429, 167, 317, 288, 960, 290, 179], [2265]]</t>
+    <t>[[358, 176, 66, 505, 489, 405], [512, 275, 371, 341, 248, 287, 467, 240, 351, 141], [386, 196, 449, 188, 305], [1124, 1312], [447, 176, 405, 407, 226, 13], [1711, 407], [48, 311, 182, 253, 218, 236, 502, 1792], [505, 57, 436, 447, 191, 205, 366, 512]]</t>
   </si>
   <si>
     <t>h128_ws16_ne1024_infp32_outfp32_ID017</t>
   </si>
   <si>
-    <t>[[651, 381, 379, 357, 501], [510, 2718, 440, 175, 7, 40, 456, 4741, 469, 461, 460, 503, 305, 2, 167, 255, 7318, 427, 7707, 102, 246, 2426, 91], [27, 246, 376, 409, 11813, 287, 11339, 494, 221, 12723, 303, 4294, 342, 265, 460, 298], [4423, 482, 231, 154, 4521, 197, 393, 9316, 92, 327, 413], [5346, 7448, 22, 39, 475, 35, 50, 410, 317, 329, 21, 299, 363, 365, 325, 95, 331, 18, 198, 8869, 9308, 16251, 318, 450, 15, 6583, 446, 281], [119, 239, 351, 64, 86, 216, 9951, 6042, 198], [15667, 430, 295, 371, 370, 470, 407, 2318, 283, 108, 61, 473, 15312, 136, 497], [587, 476, 383], [12602, 14324, 85, 367, 107, 295, 243, 434], [334, 124, 192, 262, 103, 365, 11345, 437, 15212, 468], [6426, 452, 236, 164, 188, 183, 483, 164, 213, 7764, 182, 7686], [6568], [105, 172, 3114, 143, 313, 3, 7510, 41, 330, 484, 119, 473, 471, 2239, 370, 400, 14914, 126, 296], [178, 392, 459, 481, 15273, 111, 6912, 113, 14836, 500, 109, 13219, 38, 12929, 432, 417, 394, 317, 345, 14985, 3648, 317, 205, 385, 302, 249, 286, 400, 141, 26, 380], [505, 4859, 117, 8, 123, 14303, 130, 426, 406, 114, 13555, 317, 445], [393, 249, 293, 329, 335, 55, 174, 208, 8904, 385, 233, 412, 3712, 317, 294, 220, 220, 327, 130, 7043, 6368, 14931]]</t>
+    <t>[[1387, 97, 105, 10, 490, 1585, 492, 268], [477, 1512, 1818, 461, 121, 208, 151, 393, 110], [500, 27], [205, 754, 273, 50, 129, 507, 487, 580, 1966], [326, 226, 342], [315], [157, 1724, 450, 372, 383, 1124], [223, 63, 97, 54, 408, 258, 384, 1446, 109], [233], [55, 185, 1975, 603, 98], [1187, 123, 299, 224, 209, 91, 153, 1692, 391, 410], [467, 123, 407, 34, 291, 125, 303, 347], [385, 325, 197, 289, 52, 444], [105, 81], [298, 400], [150, 1657, 15, 329, 177, 134, 120, 254]]</t>
   </si>
   <si>
     <t>h64_ws2_ne1024_inbf16_outbf16_ID018</t>
@@ -182,19 +182,19 @@
     <t>[[1024, 64]]</t>
   </si>
   <si>
-    <t>[[1273, 68, 98], [26, 210, 332, 30, 1076, 28, 13, 146, 113, 495, 446, 360, 307, 1104, 690, 378, 1191, 1563, 204, 86, 133, 406, 377, 55, 407]]</t>
+    <t>[[405, 226, 325, 192, 1992, 222, 116], [181, 395, 440, 1729, 373, 732, 326]]</t>
   </si>
   <si>
     <t>h64_ws4_ne1024_inbf16_outbf16_ID019</t>
   </si>
   <si>
-    <t>[[103, 506, 77, 425, 3158, 372, 463, 264, 3174, 3929, 315, 510, 142, 253, 90], [305, 2596, 0, 35, 211, 444, 412, 299, 360, 315, 35, 389, 2579, 503, 252, 156, 397, 543, 1907], [1024, 94], [1489, 93, 474, 172, 16, 198, 49, 482, 390, 253, 1422, 176, 457, 2586, 309, 4, 2719, 301, 53, 92, 461, 478, 3986]]</t>
+    <t>[[104], [234, 1116, 397, 231], [359, 190, 296, 486, 124], [195, 409, 173, 56, 299, 1431, 110, 304]]</t>
   </si>
   <si>
     <t>h64_ws8_ne1024_inbf16_outbf16_ID020</t>
   </si>
   <si>
-    <t>[[174, 8118, 396, 317, 35, 482, 6773, 210, 194, 4489, 298, 98, 333, 238, 485, 3012, 480, 242, 333, 294, 207, 6716, 15, 424], [199, 12, 474, 171, 140, 53, 2584, 20, 5520, 5], [403, 1878, 335, 39, 344, 228, 4395, 507, 354, 51, 309, 1041, 56, 447, 342, 3101, 111, 470, 485, 1014, 391, 211, 7], [181, 5368, 319, 2, 93, 710, 397, 157, 28, 1695, 428, 456, 428, 83, 89, 401, 431, 127, 78, 8014, 7296, 377], [120, 176, 436, 122, 5717, 195, 7979, 478, 229, 71, 6222, 295, 462, 68], [66, 3, 221, 44, 4834], [96, 27, 160, 317, 499, 6231, 251, 511, 493, 1979, 433, 868], [5161]]</t>
+    <t>[[416, 303], [374, 283, 1351], [47], [189, 128, 399, 94, 1, 231, 114, 129, 343, 382], [199], [141, 184], [1566, 424], [161, 115, 1826, 114, 167, 272, 176, 359, 137]]</t>
   </si>
   <si>
     <t>h256_ws2_ne1024_inbf16_outbf16_ID021</t>
@@ -203,19 +203,19 @@
     <t>[[1024, 256]]</t>
   </si>
   <si>
-    <t>[[418, 15, 235, 284, 234, 108, 104, 262, 113, 2030, 43, 301, 62, 164, 1442, 149, 262, 930, 360, 832], [1658, 200, 327, 276, 106, 162, 107, 326, 564]]</t>
+    <t>[[252, 1608, 441, 343, 468, 434, 1874, 555, 6], [1478, 100, 381, 458]]</t>
   </si>
   <si>
     <t>h256_ws4_ne1024_inbf16_outbf16_ID022</t>
   </si>
   <si>
-    <t>[[195, 3749, 237, 374, 310, 342, 214, 24, 2771, 3436, 242, 243, 282, 3372, 193, 387], [195, 280, 196, 1022, 482, 119, 3276, 25, 2885, 2, 504, 45, 313, 295, 1280, 235, 2449, 3834, 144, 151, 3301, 15, 393, 439, 353, 31, 284, 267, 178, 204, 192, 369], [66, 511, 322, 364, 193, 429, 384, 198, 53, 391, 1723, 30, 443, 796, 348, 255, 169, 478, 105, 152, 144, 2068, 490, 128, 3189, 805, 3662, 146], [475, 3221, 99]]</t>
+    <t>[[370, 401, 70], [57, 495, 385, 156, 466, 827], [323, 132, 482, 494, 116, 102, 1010, 137, 118, 359], [445, 340, 342, 177, 87, 218, 158, 93, 37, 272]]</t>
   </si>
   <si>
     <t>h256_ws8_ne1024_inbf16_outbf16_ID023</t>
   </si>
   <si>
-    <t>[[144, 49, 229, 386, 108, 388, 347, 83, 97, 365, 263, 509, 412, 376, 1127, 189, 322, 7491, 500, 360, 7092, 5529, 619, 322, 71, 3581, 5958, 434, 246, 162, 114, 129], [87, 21, 113, 417, 3467, 1027, 3953, 464, 220, 495, 411, 363, 209, 156], [267, 326, 95, 184, 382, 5954, 7164], [159, 95, 632, 181, 2990, 208, 113, 253, 510], [151, 410, 55, 227, 7725, 279, 7161, 430, 353, 270, 3172, 427, 399, 198, 342, 7667, 384], [3008, 379], [96, 291, 335, 3535, 6536, 243, 3696, 392, 258, 400, 321, 221, 3, 73, 370, 368, 187, 419, 240, 3682, 120, 254, 7065, 369, 45, 69, 63, 3251, 232], [190, 308, 231, 197, 278, 1505, 2374, 44, 470, 275, 40, 195, 87, 7473, 487]]</t>
+    <t>[[490, 1377, 430, 369, 425, 273, 107, 173], [210, 270, 474, 343], [213, 119, 306, 504, 1456, 422, 233, 964], [484], [148, 379, 274, 451], [783, 340, 376], [64, 318, 450, 1225], [434, 422, 297, 116, 1572, 85]]</t>
   </si>
   <si>
     <t>h512_ws2_ne1024_inbf16_outbf16_ID024</t>
@@ -224,73 +224,73 @@
     <t>[[1024, 512]]</t>
   </si>
   <si>
-    <t>[[272, 236, 365, 1916, 29, 352, 295, 16, 202, 618, 501, 1969, 158, 454, 248, 54, 276, 114, 33, 448, 1479, 27, 1908, 44, 248, 148, 2021, 806, 45, 262, 210, 199], [467, 47, 1381, 459, 306, 696, 82, 21, 192, 46, 1204, 1841, 302, 1565, 262, 125, 452, 1164, 267, 264, 0, 95, 28, 274, 454, 60, 461, 844, 16, 75, 91]]</t>
+    <t>[[399], [103, 375, 1991, 378, 99, 144]]</t>
   </si>
   <si>
     <t>h512_ws4_ne1024_inbf16_outbf16_ID025</t>
   </si>
   <si>
-    <t>[[2721, 439, 246, 17, 538, 312], [151, 67, 537, 159, 63, 1506, 167, 388, 376, 481, 26, 43, 1189, 88, 3732, 363, 372, 105, 184, 293, 233, 3906, 353, 346], [68, 47, 458, 2077, 302, 258, 2979, 250, 100, 215], [194, 1255, 810, 138, 426, 322, 361, 9, 3247, 237, 263, 234, 51, 965, 17, 233, 322, 36, 125, 324]]</t>
+    <t>[[211, 235, 256, 324], [790, 72, 347, 212, 1887, 128, 8, 39], [329], [253, 338, 37, 37, 371, 515, 373]]</t>
   </si>
   <si>
     <t>h512_ws8_ne1024_inbf16_outbf16_ID026</t>
   </si>
   <si>
-    <t>[[3682, 471, 190, 95, 502, 396, 335, 823, 373, 18, 5782, 198, 65, 63, 205], [115, 246, 411, 231, 2229, 2373, 170, 90, 317, 194, 6956, 372, 7813, 72, 184, 59, 200, 246, 151, 357, 500, 7929, 288, 6475, 400, 256, 444, 495], [209, 86, 110, 5074, 285, 481, 316, 262, 351, 443, 7695, 5924, 230], [457, 420, 150, 136, 6232, 376, 200, 4704, 244, 452, 7900, 353, 101, 341, 86, 241, 7803, 403, 8013, 237, 59], [317, 306, 13, 368, 227, 182, 19, 195, 562, 1044, 431, 4286, 326, 399], [119, 92, 1810, 415, 235, 1, 236, 1329, 85, 358, 447, 10, 210, 415, 2143, 227, 432, 1959, 120], [7970, 94, 421, 385, 379, 344, 4590, 472, 5977, 334, 400, 2109, 92, 197, 214, 263, 2539, 113, 175, 4911, 126, 122, 53, 193, 355, 419], [6816, 167, 2567, 7222, 204, 312, 370, 314, 456, 453, 487, 7607, 2620, 25, 420, 251, 136, 69, 198, 451, 98, 147]]</t>
+    <t>[[1057], [227, 426, 328, 115, 361, 248, 303], [1881], [178, 155, 387, 402, 2019, 342, 397, 191, 490, 282], [437, 45, 102, 161, 92, 44, 268], [336, 234, 98, 57, 140, 60, 467, 196, 506, 101], [89, 250, 1530, 18, 376], [1374]]</t>
   </si>
   <si>
     <t>h64_ws2_ne1024_infp16_outfp16_ID027</t>
   </si>
   <si>
-    <t>[[348, 149, 267, 633, 141, 1801, 383, 4, 95, 32, 168, 442, 700, 376, 481], [1531, 166, 217, 322, 279, 415, 1111, 32, 484, 253, 1195, 420, 63, 174, 163, 222, 819, 451]]</t>
+    <t>[[85], [1519, 421, 1594, 53, 260, 282, 1919, 90, 707]]</t>
   </si>
   <si>
     <t>h64_ws4_ne1024_infp16_outfp16_ID028</t>
   </si>
   <si>
-    <t>[[426, 111, 338, 3135, 249, 3920, 145, 271], [5, 151, 432, 637, 30, 1966, 285, 76, 387, 180, 5, 357, 269, 4019, 344, 912, 217, 496, 474, 20], [262, 704, 310, 106, 250, 189, 122, 150, 81, 443, 326, 3899, 9, 297, 371, 140, 172, 1271, 798, 3617, 240], [60, 274, 434, 431, 275, 35, 834, 231, 237, 296, 2828, 53, 30, 119, 2982]]</t>
+    <t>[[259, 202, 395, 26, 87, 958, 79, 322], [361], [148, 307, 394, 121, 468, 92, 812, 139, 187, 480], [114, 412]]</t>
   </si>
   <si>
     <t>h64_ws8_ne1024_infp16_outfp16_ID029</t>
   </si>
   <si>
-    <t>[[5351, 495, 55], [50, 192, 447, 271, 3156, 8080, 56, 305, 140, 342, 80, 4791, 2964, 56, 36, 171], [288, 240, 8, 399, 88, 206, 5575, 4711, 284, 1879, 446, 46, 21, 181, 434, 452, 282, 4057, 174, 230, 310, 484, 1363, 296], [3225, 401, 201, 235, 4670, 325, 61, 85], [2039, 284, 439, 128, 243, 425, 199, 14, 8089, 121, 487, 37, 169, 4039, 501], [1617, 42, 38, 119], [4741, 43, 378, 222, 235, 203, 10, 6, 6534, 161, 1540], [397, 72, 97, 2678, 1070, 78, 480, 414, 4195, 163, 399, 82, 394]]</t>
+    <t>[[167, 448, 1040, 355, 103, 280, 493, 462, 764, 918], [18], [29], [364, 136, 258], [1046, 33], [915, 7], [52], [223, 375, 450]]</t>
   </si>
   <si>
     <t>h256_ws2_ne1024_infp16_outfp16_ID030</t>
   </si>
   <si>
-    <t>[[1280, 189, 307, 558, 363, 309, 372, 463, 228, 164, 1416, 175, 1161, 370, 167, 92, 813, 1838, 351, 47, 38, 448, 506, 173, 433, 351], [454, 268, 265, 1949, 221, 299, 250, 1298, 266, 481, 183, 376, 353, 305, 1703]]</t>
+    <t>[[161], [1439, 1559, 1321, 460]]</t>
   </si>
   <si>
     <t>h256_ws4_ne1024_infp16_outfp16_ID031</t>
   </si>
   <si>
-    <t>[[2072, 1113, 192, 347, 482, 152, 174], [383, 265, 14, 210, 348, 1256, 1852, 65, 179, 175], [284, 2110, 215, 402, 92, 398, 247, 123, 184, 86, 1866, 353, 249, 2374], [161, 352, 3443, 106, 261, 122, 21, 42, 4052, 398, 340, 2921, 432, 43, 404, 84, 2439, 342, 467]]</t>
+    <t>[[36, 322, 382, 283, 407, 57, 190, 188, 34, 216], [34], [111, 482, 1715, 359, 366, 370, 52, 119], [502, 235, 294, 215]]</t>
   </si>
   <si>
     <t>h256_ws8_ne1024_infp16_outfp16_ID032</t>
   </si>
   <si>
-    <t>[[247, 265, 384, 350, 3720, 1, 51, 219, 8003, 413, 351, 66, 4940, 219, 8], [355, 136, 331, 3853, 261, 37, 185, 21, 6032, 213, 331, 2660, 481, 2232, 100, 275], [4365, 49, 149, 328, 512], [39, 480, 22, 3, 91, 6450, 248, 7952, 348, 232, 67, 2035], [369, 6225, 511, 267, 4592, 246, 241, 1161, 5046, 229, 453, 121, 491, 225, 8000, 323, 400, 437, 203, 183, 301], [506, 243, 260, 310, 2, 393, 372, 413, 186, 6921, 336, 107, 232, 194, 6566, 90, 4105, 37, 116, 2462, 117, 71, 475, 313, 148, 475, 3775, 4968, 357], [66, 152, 173, 328, 2876, 3175, 265, 256, 249, 106, 333, 425, 7370, 234, 261, 3505, 30, 319, 362, 1452, 161, 397, 122, 319, 6036, 360], [251, 461, 5280, 91, 310, 421, 7701, 335, 7294, 4, 17]]</t>
+    <t>[[435, 346, 291, 57, 547, 390, 377], [566, 39, 271, 258, 45], [39, 131, 593, 478, 291, 471, 480], [184], [395, 364], [101, 487, 16, 248], [499, 331, 132], [62, 225, 446, 404, 172, 1382, 321]]</t>
   </si>
   <si>
     <t>h512_ws2_ne1024_infp16_outfp16_ID033</t>
   </si>
   <si>
-    <t>[[1513, 1482, 464, 29, 306, 452, 83, 402, 1992, 118, 1137, 465, 442, 300, 293, 18, 383], [898, 326, 429, 252, 478, 163, 863]]</t>
+    <t>[[469, 652, 237, 385], [169, 161, 61]]</t>
   </si>
   <si>
     <t>h512_ws4_ne1024_infp16_outfp16_ID034</t>
   </si>
   <si>
-    <t>[[259, 394, 3763, 198, 2965, 294], [94, 440, 346, 3442, 13, 186, 331, 126, 426, 29, 2863, 339, 386, 247, 358, 1355, 3029, 11, 468, 3679, 3042, 360, 500, 179, 141, 220, 174], [226, 313, 1395, 227, 50, 1836, 491, 363, 1521, 239, 292, 252, 476, 2395, 384, 48, 110, 105, 1684, 490, 195, 203, 138, 323, 487, 140, 469, 1439, 348, 237, 738, 507], [102, 363, 174, 204, 470, 1856, 336, 739, 3399, 62, 335, 467]]</t>
+    <t>[[87], [239, 237], [18, 292, 238], [131, 226, 103, 1661, 1453, 1238, 267, 1188]]</t>
   </si>
   <si>
     <t>h512_ws8_ne1024_infp16_outfp16_ID035</t>
   </si>
   <si>
-    <t>[[497, 226, 243, 180, 4170, 116, 146, 74, 186, 239, 199, 2687, 44, 184, 166, 4659, 25, 493, 223, 4228, 222, 504, 313, 5750, 295, 226, 3126], [281, 126, 142, 232, 428, 219, 246, 224, 403, 88, 4710, 7409, 279, 3085, 175, 123, 385, 2096, 6182, 308, 506, 315, 465, 153], [501, 422, 358, 258, 220, 400, 39, 333, 255, 228, 56, 1641, 409, 310, 318, 37, 378, 2534, 130, 6321, 175, 1824, 98, 1946, 189], [342, 55, 359, 491, 67, 51, 5967, 211, 4390, 289, 376, 450, 7485], [381, 73, 4387, 416, 323, 1337, 113, 163, 462, 6980, 373], [2503, 438, 231, 338], [4736, 144, 53, 228, 409], [439, 1591]]</t>
+    <t>[[161, 389, 236, 8, 311, 346, 163, 398], [159, 306, 202, 93, 2042, 351, 983, 410], [421, 53, 266, 397, 464], [2, 170], [204, 82, 238, 138, 338], [59, 1926, 453, 57, 394, 192, 24, 356, 127], [122, 1967, 208, 1227, 347, 1, 372, 443], [158, 462, 1419, 292, 330, 458, 279, 337, 48, 472]]</t>
   </si>
   <si>
     <t>h128_ws2_ne512_inbf16_outbf16_ID036</t>
@@ -299,7 +299,7 @@
     <t>[[512, 128]]</t>
   </si>
   <si>
-    <t>[[166, 483, 429, 882, 142, 122, 559, 379, 227, 87, 998, 255, 11, 88, 79, 933, 142, 409], [858, 755, 133, 55, 82, 233, 344, 27, 185, 104, 367, 53, 84, 330, 462, 259, 168, 440, 598, 905, 823, 378, 33]]</t>
+    <t>[[91, 40, 470, 365, 108, 269, 259], [133, 641, 380]]</t>
   </si>
   <si>
     <t>h128_ws2_ne2048_inbf16_outbf16_ID037</t>
@@ -308,7 +308,7 @@
     <t>[[2048, 128]]</t>
   </si>
   <si>
-    <t>[[1577, 278, 366, 151], [64, 23, 9, 106, 328, 498, 32, 344, 348, 226, 2810, 424, 2175, 330, 3968, 2362, 239, 5, 453, 1226, 87, 196, 309, 409, 41]]</t>
+    <t>[[505, 47], [293]]</t>
   </si>
   <si>
     <t>h128_ws2_ne4096_inbf16_outbf16_ID038</t>
@@ -317,97 +317,97 @@
     <t>[[4096, 128]]</t>
   </si>
   <si>
-    <t>[[180, 445, 345, 381, 3826, 310, 107, 101, 36, 5573, 385, 75, 333, 7813, 308], [222, 5790, 398, 176]]</t>
+    <t>[[154, 502], [480]]</t>
   </si>
   <si>
     <t>h128_ws4_ne512_inbf16_outbf16_ID039</t>
   </si>
   <si>
-    <t>[[140, 355, 1156, 228], [1394, 488, 1195, 128, 60, 1403, 410, 61, 420, 179, 219, 249, 342, 34, 399, 83, 492, 97, 209, 982, 667, 232, 385, 95, 1094, 183, 125, 138], [367, 440, 384, 462, 203, 955, 23, 301, 66, 137, 659, 163, 683, 407, 1575, 126, 385, 53, 924, 23, 280, 331, 432], [40, 1880, 1426, 1889, 67, 474, 125, 92, 177, 1396, 138, 389, 262, 51, 15, 353, 1402, 299, 284, 1957, 1033, 229, 152, 93, 418, 316, 206, 320, 215, 208, 80]]</t>
+    <t>[[102, 414, 843], [52, 384, 316], [103, 125, 405, 240, 62, 730, 85, 218, 110], [79, 299, 314, 347, 1212, 1, 332, 260, 111]]</t>
   </si>
   <si>
     <t>h128_ws4_ne2048_inbf16_outbf16_ID040</t>
   </si>
   <si>
-    <t>[[7647, 5007, 84, 396, 226, 362, 164, 6190, 430, 134, 280, 7780, 460, 9, 368, 140, 475], [177, 251, 1557, 104, 450, 5362, 173, 309, 370, 311, 396, 8007, 308, 44, 6305, 474], [4539, 7234, 235, 2353, 60, 1109, 174, 76, 418, 246, 5071, 92, 445, 220, 174, 5, 337, 2269, 223, 257, 279, 49, 21, 181, 226, 394, 88, 474, 377], [213, 5441, 309, 494, 204, 346, 289, 454, 1167, 442]]</t>
+    <t>[[241, 280, 272, 314, 180], [1285, 248, 303, 67, 1351, 512, 46, 340, 59, 382], [230, 397, 480, 369, 287, 59, 510, 391, 218, 402], [256]]</t>
   </si>
   <si>
     <t>h128_ws4_ne4096_inbf16_outbf16_ID041</t>
   </si>
   <si>
-    <t>[[392, 2827, 180, 510, 487, 260, 7345, 253, 121, 152, 328, 14963, 263, 11554, 415, 162], [41, 136, 214, 329, 429, 155, 484, 321, 347, 6320, 12498, 874, 226, 164, 504, 417, 363, 173, 1345], [190, 267, 437, 289, 502, 16134, 16054, 428, 348, 291, 9, 64, 12078, 305, 9630, 2986, 239, 85, 122, 87, 238], [179, 15240, 110, 25, 2281, 221]]</t>
+    <t>[[391, 90, 80, 219, 468, 91, 113, 143], [200, 55, 399, 487, 369, 412, 35, 495, 117, 1251], [284, 1863], [355, 1116, 386, 354, 291, 488]]</t>
   </si>
   <si>
     <t>h128_ws8_ne512_inbf16_outbf16_ID042</t>
   </si>
   <si>
-    <t>[[110, 174, 426, 172, 392, 77, 256, 366, 185, 492, 3890, 846, 241, 3400, 37, 376, 457, 490, 97, 339, 131, 371, 432, 2993, 2366], [14, 3870, 2768, 260, 404, 341, 362, 2955, 161, 435, 155, 62], [250, 2459, 339, 1989, 2936, 255, 165, 213, 407, 418, 129], [437, 485, 1911, 235, 359, 74, 398, 336, 38, 2347, 72, 434, 240, 505, 3452, 3658, 40, 416, 207, 402, 330, 166, 3061, 444, 169, 3090, 280, 365, 1391, 56, 58], [228, 332, 104, 137, 18, 1404, 308, 207, 408, 467, 748, 1035, 1046, 348, 365, 162, 1853, 438, 497, 300, 511, 457, 411, 427, 1063, 336, 53], [343, 815, 1789, 137, 181, 32, 38, 4087, 50, 2492, 319, 432, 355, 512, 130, 195, 475, 299, 321, 170, 169, 1168, 163], [48, 3552, 1420, 242, 0, 176, 377, 369, 325, 104, 407, 255, 480, 546], [360, 1158, 127, 187, 3, 3578, 31, 213, 386, 3, 85, 2451, 397, 297, 301, 42, 508, 394, 2289, 812, 2226, 113, 268, 398, 381, 195, 274, 332, 429, 249]]</t>
+    <t>[[57, 1126, 301, 493], [176, 498, 67, 437, 481, 211, 108, 328], [99, 345, 1366, 48, 382, 206, 212, 203, 212, 322], [183, 203, 254, 606, 165, 109, 470, 1807, 296], [402, 357, 254, 226, 1120, 197], [179, 343, 256, 365, 27, 515, 431, 193], [81, 349, 391, 337], [280, 376, 156, 263, 955]]</t>
   </si>
   <si>
     <t>h128_ws8_ne2048_inbf16_outbf16_ID043</t>
   </si>
   <si>
-    <t>[[399, 349, 28, 390, 476, 5087, 139, 455, 249, 12, 245, 136, 436, 4756, 180, 383, 12200, 3041, 147], [7531, 32, 495, 6488, 6619, 211, 487, 12946, 323, 17, 221, 215, 3, 138, 116, 462, 97, 259, 408, 434], [0, 4633], [474, 433, 220, 353, 222, 5697, 57, 86, 150, 836, 1634, 164, 437, 5452, 152, 14, 329, 480, 464, 2017, 459, 7663, 128, 72, 366, 430], [378, 477, 407, 342, 362, 14398, 213, 12340, 441, 191, 389, 498, 169, 1034, 97, 126, 627], [62, 441, 0, 8230], [308, 11070, 47, 4389, 242, 147, 102, 1, 331, 155, 84, 15389, 415, 274, 278, 469, 308, 141, 6273, 333, 125, 36, 205, 11149, 113, 491, 396, 5761], [14976, 349, 249, 152, 58, 149, 328, 16012, 4171, 333, 474, 54, 299, 13441, 91, 86, 302, 14695, 160, 61, 244]]</t>
+    <t>[[484, 228, 1172, 270, 237, 258, 88, 326, 297, 301], [35, 70, 1870, 84, 66, 739, 267, 222, 286, 1140], [92, 1607], [239, 386, 277, 118], [281, 483, 142, 400, 407], [1595, 54, 344, 104, 463, 1960, 226, 287], [283], [440, 404, 53, 400, 1276, 93]]</t>
   </si>
   <si>
     <t>h128_ws8_ne4096_inbf16_outbf16_ID044</t>
   </si>
   <si>
-    <t>[[309, 212, 90, 22169, 256, 365, 254, 448, 316, 357, 207, 32, 137, 488, 17463, 442, 15045, 274, 264, 8534, 19880, 10, 339, 14, 21809, 233, 166, 479, 219, 27518, 389, 187], [305, 294, 182, 135, 61, 294, 5374, 150, 468, 456, 35, 192, 300, 273, 451, 472, 29645, 15219, 478, 32, 7753, 313, 6930, 6229, 187, 281, 153, 133, 275, 449], [281, 172, 229, 486, 88, 314, 427, 323, 269, 104, 30037, 11946, 2178], [999, 327, 158, 371, 12, 397, 91, 482, 84, 264, 377, 66, 208, 24340, 31, 99, 384, 382, 11765, 32342, 24227, 182, 325, 242], [10872, 4436, 235, 63, 141, 365, 332, 458, 508, 48, 6182, 113], [184, 145, 454, 16319, 29947, 17704, 212, 265, 446, 149, 26841, 70, 412, 496, 358, 224], [459, 15747, 147, 154, 483, 2836], [18501, 375, 246, 107]]</t>
+    <t>[[458, 40, 1924, 139], [25, 338, 190, 290, 294, 198, 233, 253, 1816], [250], [431, 57, 442, 247, 270, 353], [38, 44, 366], [1172, 87, 35, 318, 13, 45, 213, 100, 188], [298, 280, 321, 148, 124, 145, 279, 98], [308, 204, 361, 35, 512, 365, 1578, 1250, 465]]</t>
   </si>
   <si>
     <t>h128_ws2_ne512_infp16_outfp16_ID045</t>
   </si>
   <si>
-    <t>[[306, 457, 733, 728, 181, 60, 342, 299, 53, 184], [602, 42, 249]]</t>
+    <t>[[440], [118, 334, 1480, 170, 181, 237, 333, 359]]</t>
   </si>
   <si>
     <t>h128_ws2_ne2048_infp16_outfp16_ID046</t>
   </si>
   <si>
-    <t>[[495, 468, 116, 255, 511, 3212, 398, 2238, 323, 424, 375, 1412, 113, 1722, 81, 56, 121, 33, 476, 287, 119, 82, 268, 859, 475, 328, 393, 453, 67, 1050, 3454], [1951, 238, 372, 130, 350, 131, 89, 103, 256, 322, 359, 46, 2148, 190, 628, 221, 498, 236, 504, 2979]]</t>
+    <t>[[506, 373, 806, 604, 1842, 77, 200, 334], [409, 139, 105, 110, 147, 311, 116, 813, 1325, 457]]</t>
   </si>
   <si>
     <t>h128_ws2_ne4096_infp16_outfp16_ID047</t>
   </si>
   <si>
-    <t>[[504, 126, 474, 4642, 6, 144, 323, 3942, 3599, 331, 3, 210, 94, 371, 154, 1923], [191, 324, 11, 243, 5647, 436, 3873, 1381, 71, 92, 218, 334, 398, 175, 181, 360, 436, 148, 300, 761, 189, 7403, 511, 372]]</t>
+    <t>[[266, 481], [255, 120, 76]]</t>
   </si>
   <si>
     <t>h128_ws4_ne512_infp16_outfp16_ID048</t>
   </si>
   <si>
-    <t>[[235, 350, 503, 487, 286, 754, 341, 438, 704, 222, 1187, 420, 200, 961, 725, 441, 493, 321, 399, 208, 308, 348, 251, 114, 406, 212, 475, 1979], [1619, 158, 397, 119, 453, 1851, 246, 258, 98, 174, 1951], [305, 283, 1339, 488, 541, 325, 38, 386, 336, 28], [379, 235, 415, 1386, 510, 5, 478, 1653, 227]]</t>
+    <t>[[216, 1861, 202, 82, 224], [422, 138], [946, 14, 54, 475, 1296, 1527, 32, 1748], [287, 595, 67, 420, 22]]</t>
   </si>
   <si>
     <t>h128_ws4_ne2048_infp16_outfp16_ID049</t>
   </si>
   <si>
-    <t>[[105, 3845, 338, 247, 327, 180, 5545, 468, 304, 299, 287, 71, 2752, 268], [308, 243, 439, 77, 265, 80, 106, 470, 225, 6921, 212, 69, 185, 1642, 924, 246, 3018, 1603, 463, 221, 296, 262, 944, 183, 315, 377, 89, 460, 405], [6598, 232, 172], [4414, 405, 363, 3687, 187, 296, 186, 419]]</t>
+    <t>[[640, 343, 1046, 53, 117, 754, 214, 405, 47, 1604], [499, 382, 348, 418, 350, 540, 136, 439, 294], [23, 319, 357, 28, 666, 29, 236, 511, 693], [507, 747, 108, 254]]</t>
   </si>
   <si>
     <t>h128_ws4_ne4096_infp16_outfp16_ID050</t>
   </si>
   <si>
-    <t>[[7544, 255, 502, 278, 204, 21, 9949, 11856, 244, 68, 340, 13991, 360, 206, 117, 296], [8195, 403, 400, 11347, 262, 233], [476, 7712, 160, 13479, 10529, 477, 87, 14349, 333, 283, 15520, 259, 224, 478, 482, 11366, 355, 389, 406, 377, 102, 167, 488, 33, 504, 300, 380, 233, 45], [176, 9431, 104]]</t>
+    <t>[[1370, 356, 701, 863, 33, 438], [1742, 100, 486, 426, 330, 204, 402, 498, 846], [353, 846, 366, 363, 297], [380]]</t>
   </si>
   <si>
     <t>h128_ws8_ne512_infp16_outfp16_ID051</t>
   </si>
   <si>
-    <t>[[445, 461, 2500, 1776, 930, 306, 294, 173, 339, 4, 434], [92, 52, 1421, 145, 499, 764, 357, 178, 93, 1629, 266, 973, 372, 456, 289, 93, 177, 342, 38, 88, 142, 134, 227, 1730, 125], [170, 3692, 119, 19, 438, 429, 483, 1021, 187, 266, 7, 471, 2467, 155, 286], [524, 184], [196, 173, 144, 2783, 2809, 486, 324, 348, 245, 3981, 2746, 232, 473, 166, 20, 78, 155, 3212, 353, 370, 102, 340], [328, 472, 3999, 90, 383, 3937, 277, 89, 299, 233, 206, 382, 3912], [499, 107, 84, 494, 425, 395, 203, 108, 2398, 3120, 3647, 98], [2563, 305, 2543, 248, 277, 127, 61, 2180, 8, 500, 176, 91, 19, 408, 401, 119, 85, 298, 1110]]</t>
+    <t>[[273], [132, 453, 455, 182, 416, 200, 431, 160], [480, 471, 64, 1035, 456], [1991, 17, 304, 514, 425, 178, 21, 430, 30], [484, 76, 1359, 53, 179, 233], [97, 492, 332, 188], [207, 428, 125, 89], [196, 424, 38, 57]]</t>
   </si>
   <si>
     <t>h128_ws8_ne2048_infp16_outfp16_ID052</t>
   </si>
   <si>
-    <t>[[3808, 283, 213, 301, 113, 27, 461, 188, 4183, 326], [438, 100, 323, 251, 264, 419, 7223, 4845, 397, 331, 447, 2437, 63], [316, 6, 412, 1180, 7153, 231, 113, 254, 14123, 208, 102, 4012, 422, 510, 376, 96, 121, 241, 193, 2732, 27, 432, 203, 1417, 303, 231, 83, 28, 421], [282, 283, 34, 688, 120, 186, 105, 242, 285, 411, 283, 394, 64, 4529, 394, 230, 285, 152, 267, 7446, 417, 13789, 6, 1402, 8693, 129, 426, 503], [144, 3390, 405, 112, 106, 43, 394, 479, 137, 213, 2025, 12106, 397, 3649, 368, 4127, 100, 356, 250, 202, 330, 205, 6986, 87, 123, 429, 450, 222, 476, 296], [324, 11322, 68, 281, 414, 72, 367, 19, 77, 6597, 456, 283, 254, 195, 175, 279, 4747, 222, 1173, 497], [115, 13295], [83, 97, 3397]]</t>
+    <t>[[126, 497, 268], [480], [302, 1900, 448, 133, 377], [90, 152, 266], [232], [121, 192, 299, 359, 83, 932, 431], [504, 647, 160, 300], [406, 47, 308, 457]]</t>
   </si>
   <si>
     <t>h128_ws8_ne4096_infp16_outfp16_ID053</t>
   </si>
   <si>
-    <t>[[135, 26195, 86, 0, 12, 496, 17689, 396, 214, 32, 45, 32059, 339, 158, 252], [314, 272, 23081, 12950, 469, 309, 48, 344, 306, 12361, 329, 104, 316, 65, 260, 229, 32, 394, 280, 422, 312, 10574, 291, 36, 23642, 380, 1027, 90], [81, 31944, 9, 321, 286, 194, 29177, 244, 240, 36], [32, 213, 53, 317, 279, 317, 11534, 133, 7176, 195, 448, 7068, 488, 56], [61, 32364, 5419, 295, 276, 12, 332, 31919, 226, 306, 266, 30764, 24, 297, 313, 103, 326, 209, 288, 219, 485, 310, 21835, 489, 194], [310, 223, 16, 437, 2, 456, 96, 142, 118, 135, 12462, 302, 142, 149, 23148, 27092, 391, 292, 471, 397, 417, 23678, 81, 165, 304, 168, 20570, 29882, 496, 13757, 168, 327], [25099, 358], [457, 442, 331, 133, 1269, 12194, 157, 27707, 267, 9, 14817, 152, 94, 354, 292, 117, 300, 29108, 420, 56, 269]]</t>
+    <t>[[370, 237, 429, 88, 511, 199], [417, 60], [474, 257, 192], [840, 258, 110, 83, 191, 1132], [326, 449, 1042], [374, 1024, 2037, 319, 297, 444, 1773], [392, 480, 232, 427, 38, 446, 317], [355, 367, 1493, 492, 378, 357, 32, 217, 1573]]</t>
   </si>
   <si>
     <t>fetch_num</t>
@@ -416,133 +416,133 @@
     <t>h128_ws2_idx2048_inbf16_outbf16_ID201</t>
   </si>
   <si>
-    <t>[[1102, 907, 214, 337, 158, 343, 183, 222, 434, 631, 354, 83, 493, 104, 1014, 169, 400, 74, 455], [509, 129, 378, 389, 1246, 604, 484, 467, 192, 350, 1006, 326, 1932, 1185, 126, 203, 265, 201, 332, 205, 300, 279]]</t>
+    <t>[[146, 445, 501], [1976, 506, 508, 92, 206]]</t>
   </si>
   <si>
     <t>h128_ws4_idx4096_inbf16_outbf16_ID202</t>
   </si>
   <si>
-    <t>[[184, 137, 15, 391, 39, 1005, 277, 185, 343, 3718, 332, 1564, 126, 439, 412, 228, 524, 144, 319, 399, 440, 110, 27, 508, 392, 2090, 1293], [345, 81, 1913, 173, 217, 120, 5, 301, 340, 1547, 192, 461, 200, 337, 1579], [498, 2613, 173, 2617, 36, 307, 319, 1505, 285, 337, 123, 229, 2740, 379, 391, 409, 238], [99, 405, 344, 385, 3589, 345, 1353, 363, 1741, 100, 445, 0, 274, 9, 827, 481, 1603, 418, 417, 120, 260, 482]]</t>
+    <t>[[84], [133, 274, 275, 167, 1743, 1302, 361, 73, 217], [384, 1194, 372, 238, 142, 52, 176, 106], [218]]</t>
   </si>
   <si>
     <t>h128_ws8_idx8192_inbf16_outbf16_ID203</t>
   </si>
   <si>
-    <t>[[344, 10, 123, 362, 180, 5518, 1355, 32, 437, 45, 171, 1112, 176, 86, 309, 210, 437, 220, 475, 82, 6599, 278, 4970], [319, 473, 319, 41, 175, 423, 364, 452, 479, 162, 416, 98, 6562, 81, 25, 7911, 2154, 240, 329, 4527, 490, 2215, 2188, 210, 491, 179, 315, 405], [72, 53, 292, 21, 309, 439, 6670, 315, 1468, 421, 482, 5144, 419, 5911, 459, 132, 138, 138, 504, 155, 3355, 351, 303, 249, 274], [4871, 56, 188, 460, 27, 460, 290, 395, 6254, 47, 144, 169, 3, 360, 436, 412, 343, 174, 6520, 1377, 341, 29, 175, 317, 264, 4038, 126, 2366, 491], [16, 2987, 2674, 505, 3195, 350, 476, 351, 507, 153, 433, 20, 153, 170, 68], [11, 2521, 232, 287, 185, 370, 512, 162, 192, 113, 184, 174, 324, 5723, 217, 341, 3139, 6600, 288, 235], [31, 188, 4147, 1002, 78, 2447, 92, 8, 463, 6111, 386, 373, 267, 66, 5496, 128, 121, 178, 195, 119, 18, 239, 434, 432, 326, 38, 3415], [276, 261, 4, 127, 363, 109, 308, 453, 244, 20, 8048, 3757, 23, 3936, 389, 68, 435, 10, 86, 108, 419, 49, 7869, 374, 3380, 6847, 349, 194, 124, 164]]</t>
+    <t>[[300, 58, 64, 160, 243, 1549, 127, 307, 491], [87, 256, 402, 424, 219, 445, 148, 277, 160], [173, 398, 437, 1049, 262, 103, 362, 131, 287, 49], [471, 38, 407], [277, 1249, 412, 219, 429], [136, 359, 290, 135, 512, 171, 19, 137, 250], [134, 35, 1420, 282, 274], [104, 822, 1510, 103, 44, 1147, 94]]</t>
   </si>
   <si>
     <t>h128_ws16_idx16384_inbf16_outbf16_ID204</t>
   </si>
   <si>
-    <t>[[8687, 377, 446, 504, 6940, 8300, 194, 442, 143, 504, 60, 88, 269, 94, 98, 5855, 392, 231, 132, 439, 10069, 420, 12520, 7825, 321, 18, 321, 377, 477, 27, 408, 287], [378, 5810, 71, 4508, 1258, 291, 183, 277, 403, 474, 417, 113, 344, 6337, 3, 495, 49, 53, 317], [207, 458, 15160, 366, 225, 10901, 104, 447, 389, 9387, 396, 283, 1054, 69, 8197, 398, 287, 447, 355, 228, 25, 509, 336, 103, 32, 438, 13184, 136, 431], [158, 287, 312, 13256, 8], [490, 200, 15747, 242, 346, 320, 11372, 362, 13413, 454, 64, 2625, 280, 12650, 70, 454, 474, 504, 292, 11776, 369, 275, 419, 263, 312, 1615, 0, 418, 83, 4, 369], [78, 2602, 118, 242, 5264, 351, 227, 308, 172, 333, 19, 402, 224, 112, 5354, 424, 200, 507, 138, 219, 9196, 269, 410, 5146], [407, 357, 407, 197, 14619, 201, 372, 329, 272, 13500, 14216], [843, 174, 454, 401, 270, 445, 35, 331, 219, 11409, 16342, 422, 2, 219], [344, 366, 13464, 2127, 308, 15, 168, 320, 46, 459, 195, 194, 912, 5956, 384, 475, 105, 430, 469, 10188, 239, 229, 399, 5082, 312, 25, 379, 435], [289, 450, 351, 2529, 493, 225, 214, 41, 247, 15, 382, 9102, 121, 433, 10096], [9696, 135, 216, 133, 122, 5791, 278, 198, 82, 152, 77, 500, 28, 8616, 85, 4, 6812, 165, 158, 2787, 405, 368, 93], [12, 421, 164, 259, 101, 46, 512, 457, 160, 496, 341, 382, 160, 37, 1791, 11320, 458, 504, 0, 13328, 8687, 7180, 2660, 339, 311, 445], [159, 2954, 287, 484, 450, 371, 301, 14077, 337, 362, 389, 2537, 13484, 342, 307, 500, 372], [402, 3191, 117, 317], [444, 192, 10828, 9364, 258, 137], [458, 66, 15072, 6240, 199, 12857, 266, 274, 189, 287, 479, 50]]</t>
+    <t>[[1069], [131, 484, 849, 334], [224, 305, 1738, 249, 433], [239, 637, 454, 325, 446, 118, 125, 1770], [167, 6, 407, 12], [184, 65], [366, 454, 471, 183, 24, 1871, 1300, 1492, 330], [416, 255, 506, 461], [335], [391, 1776, 484, 71, 291, 430, 1892], [390, 376, 2016, 1350, 52, 276, 65, 478, 279], [486, 172, 312, 960, 196, 438, 195], [425, 153, 351, 902, 240, 731, 160, 27, 397, 1495], [16, 22, 11, 83, 439, 498, 204, 215, 157, 1332], [94, 1372], [441, 185, 37, 1236, 2040]]</t>
   </si>
   <si>
     <t>h128_ws2_idx2048_infp16_outfp16_ID205</t>
   </si>
   <si>
-    <t>[[160, 486, 64, 573, 239, 173, 484, 300, 1657, 502, 1204, 107, 12, 195, 148, 331, 1285, 1], [1927]]</t>
+    <t>[[1538, 472, 388, 339, 402, 1717, 361, 488, 269, 353], [1810, 392, 437, 209, 61]]</t>
   </si>
   <si>
     <t>h128_ws4_idx4096_infp16_outfp16_ID206</t>
   </si>
   <si>
-    <t>[[267, 249, 392, 389, 2653, 354, 327, 1415, 2244, 400, 447, 47, 397, 64, 339, 19, 442, 391, 1258, 781, 486, 747, 462, 40, 475, 306], [3536, 450, 53, 340, 2900, 100, 460, 2036, 1545, 187, 28, 417, 220, 479, 498, 320, 33, 396, 348, 108], [183, 43, 252, 269, 495, 3453, 250, 442, 267, 378, 508, 43, 3827, 3957, 248, 456, 1074, 353, 349, 411, 1011, 227, 505, 393, 228], [415, 130, 94, 103, 440, 252, 1268, 333, 272, 496, 1111, 333, 2122, 63, 490, 498, 1389, 326, 832, 73, 266, 322, 56, 134, 111, 4041, 2080, 248, 173, 170, 370]]</t>
+    <t>[[158, 1008, 475, 301, 248, 371, 159, 1078], [305], [1292, 444, 6, 1935], [323, 227, 159, 359, 240, 166]]</t>
   </si>
   <si>
     <t>h128_ws8_idx8192_infp16_outfp16_ID207</t>
   </si>
   <si>
-    <t>[[284, 185, 6911, 134, 4066, 7308, 402, 436, 11, 87, 476, 5019, 80, 485, 12, 463, 40, 392, 385, 2368, 185, 291, 2563, 89, 371, 290, 357, 447, 502, 407], [46, 1742, 392, 148, 354, 38, 3552, 146, 180, 231], [464, 3034, 195, 423, 280, 302, 109, 25, 184, 4974, 455, 65, 442, 269, 5257, 264, 102, 4622], [4795, 72, 132, 407, 14, 411, 56, 4752, 177, 1698, 181, 451, 4012, 258, 462, 127, 368, 467, 473, 152, 272, 10, 256, 8009, 247], [192, 170, 240, 235, 6078, 63, 38, 5779, 400], [431, 2462], [149, 4554, 218], [342, 66, 7025, 308, 4627, 225, 197]]</t>
+    <t>[[1598, 403, 68, 444, 311], [65, 220, 146, 114, 111, 442, 63], [417, 201, 113], [236, 248, 146, 419, 198, 445, 1200, 138, 267, 64], [415, 107, 221, 1053], [200, 66, 213, 1762, 295, 455, 387], [16, 399, 147, 105, 347, 286, 458, 467, 118, 137], [9, 1917, 377, 1773, 452]]</t>
   </si>
   <si>
     <t>h128_ws16_idx16384_infp16_outfp16_ID208</t>
   </si>
   <si>
-    <t>[[227, 112, 2573, 77, 472, 424, 10728, 205, 259], [333, 325, 15, 39, 16, 15763, 54, 3068, 116, 97, 391, 15519, 245, 65, 229], [373, 387, 506, 11093, 473, 221, 55, 16123, 280, 196, 12351, 512, 332, 1707, 437, 326, 12, 291, 387, 500, 7911, 327, 40, 194, 1530, 205], [452, 144, 489, 77, 2889, 422, 420, 426, 226, 6116, 286, 376, 6, 7091, 400, 16145, 37, 22, 382], [454, 1704, 8334, 41, 7610, 328, 469, 8, 33, 203, 13755, 9, 201, 275, 371, 193, 460, 112], [4664, 29, 44, 436, 486, 427, 178, 6153, 490, 494, 161, 194, 9821, 14463, 131, 429, 6683, 451, 394, 271, 90, 30, 15024, 254, 1628, 275, 263, 484, 74, 193, 368, 350], [6026, 4126, 11, 256, 49, 310, 28, 123, 11235, 153, 57, 222], [15169, 18, 250, 380, 311, 372, 175, 6351, 4667, 186, 27, 387, 221, 13773, 44, 222], [406, 320, 55, 83, 11707], [349, 94, 477, 390, 12177, 311, 153, 500, 402, 375, 170, 215, 474, 5749, 8291, 14227, 296, 1653, 406, 266, 189, 4193, 91, 245, 435, 432, 375, 344], [81, 63, 262, 12493, 14314, 461, 490, 190, 9516, 280, 63, 445, 73, 143], [494, 492, 221, 222, 118, 169, 377, 214, 11856, 440, 4144, 275, 448, 410, 275, 65, 413, 337, 397, 267, 486, 16378, 1071, 154, 2330], [407, 81, 456, 190, 3231, 42, 500, 8981, 117, 2006, 358, 260, 161, 7671, 310, 512, 508, 162, 312, 356, 14064, 16237, 412, 53, 82, 156, 402, 386, 236, 7465, 81], [11780, 274, 2533, 277, 390, 454, 131, 7567, 420, 321, 450, 1709, 358, 3812, 485, 143, 408, 36, 294, 505, 141, 52, 198, 22, 3325, 164, 440, 99, 295], [1356, 30, 90, 44, 6, 383, 3713, 107], [156, 2012, 257, 71]]</t>
+    <t>[[216, 466], [218], [24, 495], [102, 1703, 1520, 123, 191, 143, 436, 253], [45, 26, 310, 262], [394], [390, 255, 455, 337, 1293, 187, 190], [270, 11], [126], [383, 96, 189, 12], [192, 658, 1560, 157, 929], [470, 1436, 486, 63], [330, 104, 924, 242, 252, 1950, 262], [458, 363, 1768], [2007, 161, 156, 1342, 1933, 137, 1807], [412, 78, 112, 314, 182, 333, 85, 226]]</t>
   </si>
   <si>
     <t>h128_ws2_idx2048_infp32_outfp32_ID209</t>
   </si>
   <si>
-    <t>[[196, 370, 180, 1950, 84, 1797], [198, 90, 253, 338, 290, 502, 1171, 238, 179, 428, 257, 286, 457, 1603, 389, 19, 403, 243, 120, 860, 539, 453, 428, 936, 28]]</t>
+    <t>[[440, 35], [372, 238, 235, 179, 168, 441]]</t>
   </si>
   <si>
     <t>h128_ws4_idx4096_infp32_outfp32_ID210</t>
   </si>
   <si>
-    <t>[[408, 349, 354, 3164, 51, 54, 206, 2071, 177, 185, 329, 1641, 401, 37, 457, 410, 1539, 466, 2803, 268, 463, 222, 1485, 432, 3247, 13, 136, 495, 203, 296, 379], [3377, 77, 68, 2498, 320, 296, 235, 3933, 29, 396, 378, 245, 371, 194, 40, 452, 289, 157, 257, 2257, 3630], [310, 290, 244, 1089, 365, 488, 348, 180, 2421, 345], [291, 2093]]</t>
+    <t>[[307, 378], [229, 344, 419], [939, 1901, 392, 187, 35, 470, 420, 167, 167], [439, 430, 300, 169, 471, 533, 445]]</t>
   </si>
   <si>
     <t>h128_ws8_idx8192_infp32_outfp32_ID211</t>
   </si>
   <si>
-    <t>[[83, 233, 444, 3498, 6281, 147, 475, 248, 4446, 7337, 512, 369, 1347, 137, 125, 2973, 58, 382, 461, 307, 171, 89, 300, 416, 80, 222, 397], [64, 284, 510, 509, 237, 148, 349, 28, 465, 7858, 53, 266, 314, 37, 6606, 426, 5253, 400, 3746, 135, 85, 118, 118, 3194], [150, 164, 7656, 347, 507, 3966, 434, 399, 481, 138, 101, 457, 57, 6632, 228], [2868, 160, 5855, 472, 278, 185, 71], [7050, 372, 2463, 381, 5194, 19, 172, 263, 354, 403, 161], [312, 445, 500, 2047, 176, 94, 92, 239, 428, 450, 3879, 388, 147, 276, 164, 215, 252, 941, 483, 95, 2367, 89, 3003, 4818, 445, 474], [1011, 174, 437, 17], [271, 274, 405, 5445, 447, 276, 303, 24, 315, 347, 5334, 148, 112, 3638, 3993, 269, 98]]</t>
+    <t>[[377, 924, 480, 162, 459, 103, 509, 477, 13], [117, 14, 137, 78, 478, 112, 567, 258, 120], [19, 308, 311, 180, 509, 394, 162, 441, 233, 188], [168], [305], [1196, 96, 416, 351, 113, 126, 142, 536, 63], [10, 439, 74, 135, 86, 385, 381, 446, 93], [261, 142, 211, 91, 1860, 113]]</t>
   </si>
   <si>
     <t>h128_ws16_idx16384_infp32_outfp32_ID212</t>
   </si>
   <si>
-    <t>[[184, 371, 53, 237, 155, 493, 2702, 18, 255, 905, 482, 246, 16130, 365], [274, 2737], [12534], [60, 416, 5710, 12829, 350, 442, 318, 373, 5077, 101, 308, 396, 450, 85, 140, 13755, 400, 383, 472, 66, 10768, 213, 269, 213], [3759, 504, 176, 180, 1330, 248, 256, 387, 298, 11463, 134, 93, 428, 383, 1359, 11, 472, 1, 27, 418, 359, 31, 2584, 9422, 129, 418, 247, 354], [152, 334, 221, 300, 5889, 12875, 374], [275, 305, 11602, 4, 291, 38, 277, 249, 29, 255, 487, 250, 352, 8807, 10842, 307, 243, 298, 14508, 480, 456, 403, 383, 193, 335, 374, 289, 7675, 450, 4145], [285, 14166, 483, 63, 227, 7578, 167, 286, 342, 443, 255, 227, 89, 455, 10388, 264, 440, 163, 349, 2217, 293, 8, 334, 366, 333, 159, 136, 172, 206, 9929, 6153, 6040], [3478, 96, 24, 471, 424, 16270, 453, 161, 370], [221, 265, 553], [138, 491, 179, 4675, 8999, 32, 367, 20], [251, 432, 283, 209, 4091], [390, 298, 285, 92, 6125, 43, 410, 1436, 322, 316, 278, 118, 373, 67, 242, 30, 12761, 172, 96, 353, 221, 15617, 338, 13550, 287, 415, 4342, 3724, 484, 443, 19], [166, 363, 12328, 9163, 385, 302], [4310, 82, 359, 240, 347, 450, 2148, 107, 370, 7202, 420, 144], [292, 420, 11422, 420, 195, 312, 402, 3329, 1280, 230, 302, 464, 25, 9, 66, 419, 142, 845]]</t>
+    <t>[[926, 76, 283, 36, 87, 479, 121, 475, 285], [414, 363, 20, 177, 1946, 435], [1625, 476], [62, 355], [366, 252, 245], [445, 375, 1990, 95, 414, 140, 1138, 442], [274, 444, 495, 473, 185, 575, 330, 428, 221], [457, 124, 183, 482, 506, 116, 202, 1367, 1888], [355, 45, 445, 79, 350, 507, 1760, 80], [409, 258, 508, 188, 92, 424, 216, 343, 1046], [417, 1740, 283, 393, 296, 498, 1538], [65, 350, 68, 215, 263], [36, 175, 44, 345], [103, 436, 251, 65, 170], [1464], [61, 408, 452, 58, 211, 181]]</t>
   </si>
   <si>
     <t>h128_ws2_idx256_small_inbf16_outbf16_ID213</t>
   </si>
   <si>
-    <t>[[170, 35, 119, 223, 140, 148, 176, 44, 169, 32, 157, 76], [213, 255, 44, 112, 104, 43, 48, 57, 212, 112, 185, 214, 18, 212]]</t>
+    <t>[[403, 438, 136, 1420, 98], [124, 326, 738, 511, 207, 154, 1370, 6]]</t>
   </si>
   <si>
     <t>h128_ws2_idx512_small_inbf16_outbf16_ID214</t>
   </si>
   <si>
-    <t>[[466, 183, 460, 101, 63, 282, 114, 103, 509, 18, 345, 268, 303, 446, 474, 426, 367], [16, 191, 74, 433, 189, 35, 113, 64, 489, 133, 174, 292, 362, 367, 403, 55, 107, 263, 233, 270, 315, 477, 101, 104]]</t>
+    <t>[[102, 155, 436, 381, 187], [48, 1669, 132, 293, 215, 226, 441, 156, 333]]</t>
   </si>
   <si>
     <t>h128_ws4_idx512_small_inbf16_outbf16_ID215</t>
   </si>
   <si>
-    <t>[[134, 370, 85], [174, 126, 271, 473, 171, 485, 423, 364, 8, 244, 287, 155, 83], [44, 342, 428, 229, 33, 402, 417, 267, 139, 284, 479, 378, 47, 272, 330, 361, 439, 309, 262, 329, 209, 477, 349, 360, 213], [86, 248]]</t>
+    <t>[[200, 1380, 355, 413], [331, 408, 748, 243, 221, 1476, 297, 393], [58, 250, 173, 1234], [259, 500, 366, 483, 27, 121, 223, 417, 151]]</t>
   </si>
   <si>
     <t>h128_ws4_idx1024_small_inbf16_outbf16_ID216</t>
   </si>
   <si>
-    <t>[[169, 76, 804, 504, 244, 336, 64, 616, 465, 560, 637, 55, 363, 806, 315, 507, 194, 418, 312, 189, 126, 370, 76, 323, 413, 27, 755, 500, 275, 347, 113, 772], [156, 621, 455, 284, 224], [360, 47, 379, 109, 310, 123, 188, 170, 885, 565, 482, 602, 703, 434, 322, 45, 337, 228, 117, 38, 7, 217, 446, 282, 878, 264, 710, 382], [395, 13, 891, 965, 208, 379]]</t>
+    <t>[[892, 160, 468, 257, 353, 144, 398, 354, 129, 466], [456, 1074, 2034, 26, 1713, 7, 396], [97, 249, 124, 282, 507, 227, 252, 325], [440]]</t>
   </si>
   <si>
     <t>h128_ws2_idx256_small_infp16_outfp16_ID217</t>
   </si>
   <si>
-    <t>[[9, 157, 82, 181, 58, 116, 175, 155, 32, 52, 8, 245, 29, 98, 64, 155, 151, 171, 236, 168, 53, 32, 36, 224, 2, 209], [104, 223, 226, 191, 179, 96, 204, 35, 166, 164, 182, 46, 55, 117, 163, 191, 21, 5, 211, 16, 206, 117, 11, 93, 45]]</t>
+    <t>[[193, 427, 232], [143, 260, 122]]</t>
   </si>
   <si>
     <t>h128_ws2_idx512_small_infp16_outfp16_ID218</t>
   </si>
   <si>
-    <t>[[133, 320, 361], [290, 220, 395, 402, 149, 476, 140, 189, 447, 381, 417, 18, 338, 453, 174, 431, 340, 236, 347, 215, 509, 458, 369, 418, 202, 356, 454, 28, 290, 375]]</t>
+    <t>[[379, 793], [140, 419, 33, 41, 214, 422, 433, 391, 384, 23]]</t>
   </si>
   <si>
     <t>h128_ws4_idx512_small_infp16_outfp16_ID219</t>
   </si>
   <si>
-    <t>[[58, 358, 453, 42, 376, 422, 264, 119, 403, 392, 377, 228, 183, 420, 3], [108, 359, 491, 503, 244, 128, 138, 506, 480, 286, 137, 367, 1, 281], [372, 64, 244, 452, 8, 166, 474, 429, 37, 366, 175, 375, 486, 112, 264, 133, 478, 13, 225, 94], [360]]</t>
+    <t>[[850, 28], [54], [440, 324, 384, 383, 896, 507], [26, 86, 270, 134, 35, 76, 279, 121, 419]]</t>
   </si>
   <si>
     <t>h128_ws4_idx1024_small_infp16_outfp16_ID220</t>
   </si>
   <si>
-    <t>[[341, 291, 867, 139, 322, 26, 289, 460, 227, 83, 178, 769, 52, 279, 327, 500, 852, 689, 153, 78, 136, 411, 361, 945, 83, 54, 52, 267, 840], [829, 27, 752, 338, 66, 365, 336, 480, 509, 32, 22, 630, 316, 123, 157, 201, 501, 51, 932, 606, 471, 426, 236, 76, 410, 207, 476, 815], [231, 550, 965, 118, 365, 579, 14, 331, 53, 33, 263, 344, 510, 155, 20, 80, 21, 631, 52, 446, 413, 416, 825, 85, 320, 804, 187, 6, 344, 666, 358, 358], [228, 427, 372, 117, 420, 611, 445, 14, 195, 272, 453, 585, 583, 47, 756, 460, 397, 332, 361]]</t>
+    <t>[[341, 343, 1139, 455, 459, 1440, 1719, 4, 433, 26], [248, 311, 325, 114, 78, 35], [328, 417, 346, 502], [316, 429, 361, 292, 256, 323]]</t>
   </si>
   <si>
     <t>h128_ws4_idx8192_large_inbf16_outbf16_ID221</t>
   </si>
   <si>
-    <t>[[354, 336, 129, 460, 4350, 272, 3, 4855, 704, 499, 472, 286, 7250, 473, 441, 150, 136, 242, 113, 281, 2876, 484, 96], [5371, 441, 7374, 219, 3110, 277, 236, 406, 370, 1070, 336, 342, 420, 342, 4148, 42, 997, 237, 460, 108, 185, 267, 370, 177, 76, 322], [508, 316, 400, 212, 264, 496, 441, 3860, 359, 45, 216, 345, 320, 7845, 343, 6950, 7711, 6092, 177, 349, 356], [163, 269, 387, 439, 215, 327, 46, 138, 240, 477, 227, 79, 55, 386, 175, 7748, 6534, 352, 7277, 391, 4584, 236, 174, 299, 197, 462, 40, 2369, 6839, 5665, 445]]</t>
+    <t>[[58, 336, 93, 491, 133, 270, 457, 355, 1956, 165], [1774], [436, 501], [70]]</t>
   </si>
   <si>
     <t>h128_ws4_idx16384_large_inbf16_outbf16_ID222</t>
   </si>
   <si>
-    <t>[[3716, 14487, 248, 24, 416, 420, 240, 20, 202, 508], [5214, 214, 369, 270, 38, 155, 459, 279, 340, 14302, 157, 341, 429, 4783, 430, 14712], [185, 14, 159, 6319, 9551, 443, 354, 267, 315, 37, 229, 12407, 964, 425, 462, 332, 440], [88, 11478, 420, 38, 15092, 95, 303]]</t>
+    <t>[[652, 265, 82, 1159], [217, 285, 258, 26, 154, 374, 238], [376, 509], [194, 326, 90, 988, 178, 250, 23, 20, 1202]]</t>
   </si>
   <si>
     <t>h128_ws4_idx32768_large_inbf16_outbf16_ID223</t>
@@ -551,43 +551,43 @@
     <t>[[8192, 128]]</t>
   </si>
   <si>
-    <t>[[85, 207, 137, 268, 22285, 5, 32600, 285, 409, 459, 83, 1403, 150, 227, 508], [381, 101, 9105], [2686, 120, 288, 262, 69, 1329, 214, 275, 31, 348, 299, 210, 27992, 15192, 493, 30309, 76, 384, 172, 213, 256, 336, 304], [401, 81, 67, 262, 506, 322, 78, 4661, 17658, 76, 201, 13591, 264, 281, 51, 10715]]</t>
+    <t>[[1490, 1062, 414, 1146, 422], [264, 509], [319, 328, 18, 217, 322, 204, 381], [321, 1980, 92, 357]]</t>
   </si>
   <si>
     <t>h128_ws8_idx16384_large_inbf16_outbf16_ID224</t>
   </si>
   <si>
-    <t>[[141, 9867], [502, 9559, 472, 14, 2714, 152, 364, 281, 14928, 480, 30, 374, 172, 287, 327, 79, 500, 1179, 330, 512, 84, 5182, 6990, 32, 86, 80, 98, 173, 202], [9, 441, 5894, 3172, 216, 6450, 2750, 417, 279, 163, 242, 490, 505, 83, 304, 387, 414, 126, 116, 307, 11779, 283, 9077, 30, 283, 161, 238, 353, 240, 329], [15684, 107, 353, 199, 408], [16, 234, 191, 88, 280, 285, 37, 420, 292, 4, 415, 186, 139, 15512, 10735, 2097, 393, 10242, 13282, 264, 156], [45, 14078, 377, 85, 168, 458, 5684, 357, 6491, 189, 212], [465, 153, 87, 9666, 304, 425, 59, 133, 370, 15216], [6680, 314, 473, 95, 162, 9890, 341, 286, 486, 1, 4008, 211, 469, 55, 211, 40, 327, 12, 267, 306, 122, 7559, 8264]]</t>
+    <t>[[1587, 12, 1589], [1729], [434, 356, 330], [316, 1748, 92, 440, 124, 355, 247], [129, 6, 110, 487, 335, 430, 128], [241, 511, 16, 389, 490, 462], [91], [505, 215, 450]]</t>
   </si>
   <si>
     <t>h128_ws8_idx32768_large_inbf16_outbf16_ID225</t>
   </si>
   <si>
-    <t>[[4677, 475, 5912, 440, 381, 241, 2894, 469, 81, 83, 329, 320, 16, 316, 379, 235, 5295, 51, 272, 2842, 130, 74, 14011, 348, 44, 342, 317, 274, 433], [40, 358, 507, 476, 138, 430, 214, 13961, 419, 19287, 483, 371, 75, 130, 88, 273, 484, 280, 18413, 246, 233, 230, 17922, 17344, 74], [191, 405, 8655, 5, 48, 30609, 61, 178, 351, 192, 38, 1237, 13388, 237, 451, 152, 88, 130], [161, 6061, 17286, 37, 162, 136, 229, 13529, 396, 19490, 130, 135, 310, 434, 38, 397, 178, 33, 348, 14175, 465, 207, 12], [467, 125, 385, 466, 479, 16, 7288, 349, 104, 209, 404, 254, 14419, 10878, 281, 494, 510, 340, 286, 10798, 25297], [500, 497, 81, 494, 386, 13812, 11912, 208, 296, 443, 28409, 395, 317], [224, 181, 25116, 15988, 483, 20, 199, 415, 271, 421, 275, 22251, 464, 281, 61], [65, 422, 17019, 400, 24619, 18391, 873, 335, 334, 461, 359, 502, 174, 499, 137, 440]]</t>
+    <t>[[280, 133, 5], [338, 396, 264, 261, 477, 318, 85], [4, 527, 390, 314, 382, 119], [143, 471, 399, 405, 1802, 1963, 113], [167, 21, 397, 323, 455], [54, 430, 336, 1], [2, 599], [176, 460, 1945, 126, 307]]</t>
   </si>
   <si>
     <t>h128_ws8_idx65536_large_inbf16_outbf16_ID226</t>
   </si>
   <si>
-    <t>[[30064, 326, 458, 473, 175, 181, 56, 77, 331, 120, 76, 418, 7, 150, 66, 64659, 53541, 152, 45844, 354, 9412, 224, 57], [1, 449, 26752, 81, 34959, 25882, 316, 278, 19, 409, 112, 86, 40728, 120, 395, 392, 363, 62, 177, 34806, 91, 212, 55655, 355, 404, 160, 24366, 490, 14, 269, 58, 320], [50212], [23108, 6, 231, 192, 104], [190, 480, 52802, 343, 281, 26696, 146, 221, 260, 118, 5873, 498, 339, 238, 203, 39627], [325, 384, 351, 462, 459, 11930, 53, 345, 131, 363, 43138, 23375, 122, 111, 63125, 497, 51, 131, 269, 339, 8784, 495], [270, 357, 38, 24, 438, 361, 134, 87, 160, 62280, 100, 170, 253, 451, 59222, 63980, 226, 172, 295, 317, 61430, 99, 20203, 195, 42, 57611], [147, 27636, 291, 86, 412, 367, 42281, 438, 5750, 494, 64, 6, 230]]</t>
+    <t>[[95, 334], [389, 973, 167, 259, 1640], [140, 485, 462, 5, 10, 230], [175, 177], [67, 101, 137, 373, 488], [13, 249, 73, 35, 336, 183, 265], [1918, 3, 445], [497, 185]]</t>
   </si>
   <si>
     <t>h128_ws16_idx32768_large_inbf16_outbf16_ID227</t>
   </si>
   <si>
-    <t>[[402, 426, 82, 440, 505, 441, 13788, 18673, 179, 7453, 291, 303, 267], [241, 386, 143, 23622, 5, 13195, 46, 174, 1, 303, 311, 4, 468, 15, 428, 388, 29960, 92, 28853, 17191, 372], [21770, 10837, 417, 401, 246, 444, 21225, 463, 495, 394, 358, 236, 288, 308, 169], [26527, 381, 191, 490, 279], [105, 215, 73, 380, 13354, 114, 31306, 31966, 457, 379, 402], [83, 332, 351, 4934, 24871, 6559, 505, 419, 498, 493, 410, 74, 96, 311, 6, 96, 475, 18901, 9086, 4871, 505, 117, 217, 172, 21, 65, 276, 321], [488, 134, 380, 411, 339, 27353, 188, 409, 430, 665], [423, 313, 389, 6227], [177, 52, 158, 365, 234, 64, 505, 336, 9568, 260, 358, 64, 447, 279, 10902, 280, 30598, 424, 28014, 303, 484, 76, 5981], [371, 38, 442, 31340, 228, 247, 309, 1, 230, 242, 316, 15993, 3959, 169, 472, 13, 23178], [189, 309, 30613], [38, 433, 14296, 481, 453, 32, 487, 353, 12425, 22260, 301, 479, 233, 3717, 254, 360], [346, 233, 207, 5909, 3784, 183, 498, 425], [169, 467, 392, 21072, 68, 143, 29614, 433, 43, 445, 485, 364, 379, 41, 15463, 340, 80, 436, 328, 28832, 11245, 275, 177, 304], [6489, 361, 20061, 218, 4025, 511, 177, 327, 299, 21, 160, 203, 40, 162, 374, 398, 17, 8, 229, 310, 168, 82, 11739, 743, 20930, 175, 318, 14610, 109, 365, 354], [7810, 0, 318, 488, 17817, 195, 431, 489, 506]]</t>
+    <t>[[28, 130, 124, 319, 25], [1448, 176, 1], [365], [70, 67, 138, 298, 320, 402, 85], [362], [1726, 235], [69, 1174, 423, 151], [333], [409, 1835, 428, 189, 92], [288, 1007, 2, 124, 416, 298], [1504, 353, 1531, 476, 1185, 143, 363, 119, 399], [186, 22, 206, 81, 252, 104], [186, 260, 452, 483, 209, 402, 504, 219, 143, 216], [164, 205, 196, 687, 1288], [224, 44, 340, 4, 127, 191, 288, 508], [190, 202, 507, 1515]]</t>
   </si>
   <si>
     <t>h128_ws16_idx65536_large_inbf16_outbf16_ID228</t>
   </si>
   <si>
-    <t>[[427, 319, 30, 103, 59829, 390, 399, 48, 26511, 3368, 21626, 270, 12999, 478, 54654, 395, 394, 269, 231, 311, 242, 262, 43480, 93, 281, 145, 7, 44, 476, 184, 308, 254], [47460, 392, 447, 473, 325], [27731, 354, 355], [300, 417, 18671, 190, 509, 45468, 217, 424, 472, 363, 53999, 324, 213, 464, 178], [248, 250, 153, 435, 472, 2295, 288, 236, 38337, 324, 448, 148, 19621, 77], [34741, 480, 386, 196, 447, 469, 227, 269, 15517, 192, 420, 270, 341, 47, 399, 38336, 321, 496, 404, 433, 321, 61658, 289, 59, 17047], [106, 173, 298, 86, 10, 62741, 425, 3783, 296, 159, 273, 157, 333, 54, 47248, 248, 450, 506, 58663], [492, 506, 452, 28261, 30975, 9, 9218, 314, 30871, 245, 353, 240, 189, 48, 23408, 89, 35565, 408, 111, 191, 73, 323, 508, 207, 373, 39111, 379, 62, 490, 412, 334], [203, 50109, 447, 450, 274, 100, 464, 39537, 122, 19, 26715, 53853, 134, 354, 310, 101, 246, 466, 8989, 74, 347, 332, 752, 498, 444, 390], [52, 385, 182, 405, 438, 219, 449, 328, 3769, 357, 50452, 215, 169, 317, 492, 33, 264, 65, 27874, 68, 274, 139, 14059, 232, 103, 23630, 185, 3, 2546], [191, 243, 120, 68, 380, 65, 22379, 46943, 329, 49, 20426, 288, 253], [118, 1731, 35, 136, 56792, 315], [238, 63, 380, 202, 59226, 19567, 439, 499, 398, 317, 138, 62876, 509, 489, 460, 166, 38924, 313, 4905, 168, 414, 368, 353, 213, 204, 135, 56113], [479, 361, 394, 42913, 134, 251, 102, 75, 38937, 283, 290, 3426, 288, 79, 408, 353, 43352, 200, 337, 8, 11840, 362, 495], [378, 226, 55697, 64431, 169, 52396, 282, 151, 82, 207, 125, 23], [149, 39532, 154, 200, 487, 192, 327, 17910, 13750, 340, 434, 197, 39, 31, 400, 385, 431, 61895, 402, 375, 38607, 66, 211, 273, 333, 46316, 82, 469]]</t>
+    <t>[[30, 366, 255, 498, 614], [201, 171, 992, 106], [697, 118, 429], [59, 149, 55], [535, 282, 486, 958, 40, 372, 44, 378], [425, 2042, 95, 135, 494, 236, 280, 121, 27, 460], [356, 398, 289, 66, 115, 102, 417, 341, 443, 469], [403, 464, 111, 355, 490, 324, 160, 483, 254, 186], [378, 25, 76, 257, 195, 1886, 249], [34, 136, 594, 334, 397, 420], [435, 312], [90, 496, 512, 1386, 355, 307, 151, 105, 135, 486], [422, 310, 85, 430, 35], [1794, 8], [1084, 481], [210, 71, 354, 1336, 439, 406]]</t>
   </si>
   <si>
     <t>h128_ws16_idx131072_large_inbf16_outbf16_ID229</t>
   </si>
   <si>
-    <t>[[25947, 445, 33799, 411, 405, 226, 342, 185, 216, 411, 14, 485, 91680, 98, 14960, 405, 279, 377, 108, 235], [42650, 309, 289, 425, 256, 208, 482, 95550, 69630, 388, 48, 443, 19965, 423, 278, 55, 56, 418, 42, 125795, 235, 194, 469, 409], [356, 159, 713, 86507, 44, 286, 495, 424, 96], [64005, 60, 46447, 298, 372, 295], [210, 118423, 327, 38, 435, 458, 420, 284, 407, 62223, 447, 111575, 48431, 193, 246, 368, 368, 142, 323, 431, 96, 11860, 289, 172, 268, 107368], [505, 94, 83945, 354, 473, 12690, 53, 389, 446, 81036, 197, 505, 114179, 246, 18, 189, 376, 290, 343, 43005, 469, 21424, 286, 28, 78, 279, 446, 136, 369], [347, 73511, 37, 310, 77, 340, 29313], [71, 106941, 417, 354, 178, 106143, 382, 216, 23, 326, 9, 510, 47091, 68961, 492, 355, 484, 294], [303, 196, 120453, 32647, 209, 207, 467, 246, 479, 138, 355, 38698, 222, 97], [192, 486, 341, 69637, 15, 204, 107515, 407, 79367, 266, 448, 251, 111277, 305, 0, 160, 6, 318, 195, 181, 377, 107663, 192, 99, 93841, 57569, 281, 289, 122, 386, 176], [58213, 7080, 123, 401, 24117, 102, 479, 193, 92, 481, 349, 12, 401, 507, 106, 63822, 449], [282, 96484, 395, 425], [297, 72496, 425, 1857, 83, 125, 259, 47, 38122, 53, 431, 205, 390, 494, 278, 401, 162, 185, 11630], [406, 506, 88888, 189, 368, 408, 42144, 287, 452, 338, 286, 509, 117, 452, 113, 3769, 65412, 195, 432, 16220, 352, 246, 87], [26094, 471, 413], [71359, 456, 80, 95, 478, 375, 61393, 214, 349, 101, 109, 33765, 3, 62, 25, 53, 37095, 134, 105050, 83, 125, 362]]</t>
+    <t>[[160, 433, 323, 209, 58, 6, 476, 302], [455, 113, 398], [459, 41, 1069, 85, 337], [410], [245, 180, 445, 836], [149, 354, 389, 239], [467, 364, 278, 243, 323], [145, 21, 1465, 320, 397, 133, 406, 1368], [256, 345, 384, 509, 371, 134, 334], [66, 119, 186, 451, 447, 25, 160, 171, 303], [13, 122, 652, 118, 266, 173], [225, 70, 277, 97], [275, 152, 356], [1343, 645, 155, 332, 1244, 470, 274], [438, 389, 392, 80, 294, 188, 982], [207, 464, 427, 149, 63, 2028, 165, 129]]</t>
   </si>
   <si>
     <t>h256_ws4_idx8192_large_inbf16_outbf16_ID230</t>
@@ -596,7 +596,7 @@
     <t>[[2048, 256]]</t>
   </si>
   <si>
-    <t>[[2360, 151, 369, 432, 178, 8085, 440, 301, 2, 238, 191, 2320], [382, 344, 172, 3712, 160, 4861, 80, 241, 448, 504, 3478], [5510], [130, 1749, 107, 419, 255, 6958, 127, 289, 17, 24, 2148, 503, 466, 8132, 122, 271, 28, 111, 376, 494, 4889, 188]]</t>
+    <t>[[2004, 1496, 189], [323, 456, 39, 254, 373, 1618], [260, 431, 233, 381, 432, 1041, 85, 328], [325, 487, 328]]</t>
   </si>
   <si>
     <t>h256_ws4_idx16384_large_inbf16_outbf16_ID231</t>
@@ -605,7 +605,7 @@
     <t>[[4096, 256]]</t>
   </si>
   <si>
-    <t>[[329, 61, 7376], [49, 4593, 289, 461, 118, 349, 332, 27, 246, 829, 16222, 199, 219, 88, 403, 354, 241, 4180, 5897, 175, 179, 293, 9293, 360, 397, 301, 46, 26, 12477, 320, 387], [396, 242, 189, 204, 755, 29, 227, 6565, 423, 148, 11742, 3, 2326, 106, 522, 458, 232, 76, 434, 21, 7824, 6833, 31, 120, 102, 205, 166, 432, 188, 499, 31, 445], [493, 423, 4640, 18, 320, 5433, 424, 319, 450, 371, 8752, 216, 313, 139, 100, 510, 399, 8571, 273]]</t>
+    <t>[[185], [430, 76], [229, 1667, 446, 290], [64, 37, 166, 409, 469, 424, 324]]</t>
   </si>
   <si>
     <t>h256_ws4_idx32768_large_inbf16_outbf16_ID232</t>
@@ -614,295 +614,295 @@
     <t>[[8192, 256]]</t>
   </si>
   <si>
-    <t>[[446, 98, 235, 501, 56, 219, 24333, 24358], [475, 433, 12235, 178, 30738, 6711, 11, 478, 66, 281, 465, 449, 13581, 232, 460, 152, 79, 490, 92, 12518, 202], [195, 232, 226, 11, 34, 369, 18904, 273, 375, 235, 322, 5246, 32749, 326, 405, 152, 5, 168, 468, 284, 122, 417, 420, 29230, 263, 168, 3847, 32109], [338, 128, 4, 160, 411, 348, 352, 19189, 7217, 23, 3, 168, 483, 7290, 70, 359, 413, 22921, 367, 270, 7, 23, 8436, 8, 403, 28487, 95, 490, 305]]</t>
+    <t>[[1589], [350, 1350, 483, 359, 92], [53, 2024, 306, 414], [389, 18, 424, 437]]</t>
   </si>
   <si>
     <t>h256_ws8_idx16384_large_inbf16_outbf16_ID233</t>
   </si>
   <si>
-    <t>[[195, 97, 142, 15062, 32, 13305, 92, 204, 11338, 196, 382, 5916, 155, 367, 269, 6446, 491, 404, 333, 311, 96], [370, 264, 36, 227, 440, 332, 498, 119, 379, 59, 13597, 392, 487, 310, 164, 3236, 3857, 55, 9545], [9023, 363, 140, 273, 226, 466, 5968, 106, 1446, 468, 461], [352, 8529, 9015, 512, 122, 255, 315, 15191, 5696, 351, 379, 75, 128, 489, 7831, 257, 420, 434, 4, 43, 168, 211, 148, 241, 39, 3879, 490, 178, 79, 125], [238, 141, 252, 14859, 12449, 484, 133, 479, 229, 134, 9934, 403, 36], [430, 230, 257, 120, 450, 491, 4035, 357, 118, 185, 5501, 7716, 81, 469, 423, 446, 412, 244, 3795, 86, 415, 371, 1669, 352, 313, 14093], [501, 474, 105, 433, 3165], [339, 177, 420, 180, 125, 214, 153, 110, 184, 11957, 83, 1784, 14605, 316, 119, 7854, 49]]</t>
+    <t>[[99, 469, 258, 314, 149, 493, 1339, 358, 370], [7, 210, 463], [962, 9, 271, 1408, 1597, 1225, 447, 260, 40], [359, 325, 286, 386], [1130, 324, 405, 96, 390, 191, 1606, 167, 426], [475, 243, 421, 603, 456, 16, 118, 143], [251, 505, 877, 397], [508, 493, 477, 19, 259]]</t>
   </si>
   <si>
     <t>h256_ws8_idx32768_large_inbf16_outbf16_ID234</t>
   </si>
   <si>
-    <t>[[20014, 472, 214, 149, 85, 53, 468, 464, 198, 14326, 11057, 343], [11, 437, 186, 66, 28, 1356, 457, 380, 66, 53, 470, 7355, 17717, 1761, 151, 242, 509, 4, 471, 15107, 439, 145, 155, 152, 26709, 452, 287, 7522, 363, 428, 216, 121], [18129, 427, 299, 219, 391, 29, 113, 342, 241, 5239, 448, 431, 14826, 316, 359, 375, 21591, 324, 219, 48, 3887, 0, 397, 416, 22125, 206], [150, 1142, 120, 98, 288, 361, 47, 13703, 242, 383, 60, 328, 61, 71, 27128, 350, 9317, 29646, 501, 353, 22, 409], [432, 92, 391, 115, 285, 9202, 43, 13240, 72, 490], [318, 11338], [83, 188, 379, 222, 401, 17748, 431, 492, 20548, 418, 25783, 26983, 393, 350, 271, 39, 221, 20739, 103, 17129, 465, 449, 233, 382, 396, 473, 507], [33, 31320, 497, 38, 13952, 336]]</t>
+    <t>[[34, 199], [273, 16, 117, 225, 155, 752, 1856, 275], [285, 145, 24, 243, 1889, 354], [440, 166, 332, 508, 282, 1196, 290, 37, 71, 140], [124], [1399, 297, 79, 244, 101, 54, 171, 49, 468, 1777], [337, 511, 74], [1658, 349, 230, 109, 955, 510, 138, 427]]</t>
   </si>
   <si>
     <t>h256_ws8_idx65536_large_inbf16_outbf16_ID235</t>
   </si>
   <si>
-    <t>[[19664, 370, 36872, 403, 116, 134, 383, 204, 450], [365, 6370, 391, 384, 298, 317, 265, 337, 23361, 145, 332, 440, 268, 63, 37252, 206, 50844, 40], [244, 28346, 438, 125, 425], [471, 436, 496, 355, 436, 29776, 137, 388, 56309, 473, 48592, 244, 44285, 228, 422, 307, 381, 353, 115, 322, 160, 5972, 34262, 159, 19, 75, 208, 480], [455, 41620], [150, 264, 30792, 50, 64, 129, 29791, 224, 15497, 158, 161, 117, 371, 193, 147, 4, 323, 256, 379, 13, 52, 41739, 63563, 272], [10558, 410, 417, 343, 18615, 277], [244, 34, 438, 64329, 12747, 157, 324, 424, 36, 361, 281, 138, 131, 142, 25719, 126, 106, 339, 3558, 433, 469, 10, 3753, 277, 10553, 99, 115]]</t>
+    <t>[[153, 1038, 56, 179, 185], [216, 244, 2028, 278, 362], [449, 125, 466, 110, 490, 1777, 506, 1624, 461], [820, 1059, 598, 1038], [411], [1640, 268, 235, 1913, 333, 145, 1417, 270, 491, 300], [29, 447, 455, 474, 510, 391, 1798, 298], [631, 427, 786, 33, 471, 348]]</t>
   </si>
   <si>
     <t>h256_ws16_idx32768_large_inbf16_outbf16_ID236</t>
   </si>
   <si>
-    <t>[[21681, 108, 141], [12634, 162, 170, 466, 182, 141, 121, 29203, 204, 73, 437, 14787, 493], [353, 376, 418, 364, 3292, 373, 21044, 285, 13693, 382, 163, 498, 317, 5062, 26, 323, 201, 48, 66, 3906, 454], [5853, 146, 273, 380, 185, 89, 22375, 234, 30879, 53, 323, 209, 207, 157, 5816, 449, 144, 104], [38, 203, 17, 484, 213, 7, 372, 23549, 244, 299, 30, 167, 31, 25120, 445, 27630, 265, 26115, 148], [24517], [8292, 311, 14360, 18, 243, 163, 217, 490, 509], [8680, 370, 21936, 277, 72, 141, 143, 310, 22, 271, 267, 510, 368, 330, 26732, 360, 153, 8053, 46, 322], [198, 18, 158, 53, 4562, 7424, 324, 504, 281, 12, 11229, 53, 233, 161, 8229, 48], [27749, 409, 15400, 426, 50, 222, 205], [472, 408, 27045, 375, 458, 436, 20424, 501], [1115, 13965, 458, 15, 125, 512, 316, 9, 357, 285, 496, 6286, 210, 37, 505], [11606, 10, 477, 32438, 313, 13649, 15, 4, 0, 213, 43, 498, 113, 308, 52, 155, 186, 114, 2097, 223, 10356, 396], [14539, 195, 282, 134, 235, 82, 20399, 220, 169, 125], [78, 306, 22607, 125, 294, 105, 465, 347, 18143, 155, 375, 20817, 152, 143, 170, 9138, 112], [11102, 222, 169, 123, 27753, 491, 196, 23610, 34, 83, 160, 8363, 300, 478, 326, 132, 143, 507, 179, 456, 240, 223, 48, 120, 299, 21195, 24120, 465]]</t>
+    <t>[[1549, 289, 88, 196, 242, 366, 379, 98, 461], [110, 723, 1934, 310, 425, 13], [75, 9, 1], [271, 284], [404, 409, 512, 354, 103, 248, 341, 495, 453, 533], [1502, 249], [188, 121], [504, 453, 15, 457, 202, 179, 1453], [169], [1204, 461, 277, 20, 449, 372, 437, 54], [178], [354, 26], [51, 388, 347, 472, 408], [15, 331, 726], [84, 227, 1337, 60, 404, 469, 160, 508, 1134], [40, 439, 158]]</t>
   </si>
   <si>
     <t>h256_ws16_idx65536_large_inbf16_outbf16_ID237</t>
   </si>
   <si>
-    <t>[[290, 203, 67, 368, 47, 105, 34646, 20, 23521, 149, 432, 15138], [373, 475, 37, 17890, 325, 226, 320, 45631, 419, 443, 365, 439, 27, 63689], [148, 300, 10724, 469, 302, 282, 22486, 62, 300], [466, 389, 52624, 2, 122, 247, 233, 414, 26999, 385, 80, 295, 227, 442, 481, 57, 63453, 451, 486, 157, 50101, 39874, 54342, 218, 267, 495, 287], [26392, 226, 325, 237, 100, 93, 199, 354, 201, 432, 39838, 84, 320, 32532, 420, 391, 172, 392, 16330, 404, 304, 10070, 503, 433, 37475, 498], [241, 146, 391, 75, 81, 322, 1, 116, 40335, 44, 495, 493, 301, 55635, 285, 37062, 59689, 38], [427, 68, 443, 22924, 290, 88, 177, 48384, 40265, 32, 481], [389, 54390, 15779, 463, 64844, 287, 217, 162, 32271, 502, 28, 209, 319, 226, 378, 81, 164], [301, 35666, 127, 463, 35, 88, 59856, 351, 223, 316], [266, 36030, 133, 295, 331, 432, 477, 5569, 75, 188, 159, 324, 29, 66, 21831], [392, 297, 165, 204, 94, 208, 50283, 48100], [380, 21, 65392, 101, 132, 104, 142, 280, 13561, 32925, 46851, 264, 400, 249, 172, 286, 90, 195, 342, 407, 247, 321, 134, 474, 65514], [24095, 32, 35600, 255, 308, 439, 107, 207, 127, 234, 339, 383, 318, 465, 346, 338, 244, 259, 14, 187, 182, 79, 56211, 58, 505, 409, 4230, 561, 4621], [226, 269, 12658, 331], [24677, 500, 337, 214, 213, 440, 180, 273, 118, 16327, 103, 38, 18794, 28345, 404, 167, 145, 300, 256, 34582, 21, 53], [19184, 39]]</t>
+    <t>[[116], [196, 2028, 505, 43, 421, 342], [374, 99, 271, 299, 14, 69], [275, 345, 149, 458, 79, 292, 326, 15, 233, 238], [323, 1401, 205, 352, 1816, 462, 100, 476, 400], [174, 257, 103, 302, 469, 222, 1379, 271], [7, 368, 475, 147, 197, 226, 105], [227, 114, 1700, 264, 432, 24, 370, 387, 37, 407], [67, 463], [963, 95, 305], [181, 1360, 84, 556, 441, 1887, 320, 1926, 730, 427], [366], [59, 367, 377, 446, 104, 1598, 799, 224, 437, 244], [1937, 262, 230, 199, 313, 250, 16], [455, 216, 175, 191, 225, 324, 48, 182, 213, 278], [1758]]</t>
   </si>
   <si>
     <t>h256_ws16_idx131072_large_inbf16_outbf16_ID238</t>
   </si>
   <si>
-    <t>[[100, 124, 262, 125621, 88, 114584, 239, 503, 510, 127515, 56, 183, 288, 343, 435, 96414], [322, 306, 85421, 88, 435, 747], [164, 102, 417, 387, 34984, 76, 167, 11, 95462, 63258, 183, 82], [405, 135, 446, 433, 68849, 504, 48, 204, 232, 36, 395, 5180, 109943, 231, 102, 8, 70424, 120, 338, 228, 103043], [58, 22, 3541, 346, 332, 64934, 469, 399, 357, 362, 332, 252, 66540, 109783, 72351, 467, 238, 0, 267, 177, 331, 465], [321, 358, 15437, 120456, 322, 87, 295, 26, 9693, 24, 13, 383, 126370, 46531, 238, 23, 18137, 66139, 319, 363, 202, 444, 121, 352, 67, 380, 200, 253, 2, 290, 335, 460], [13433, 18, 8, 201, 408, 114, 28, 190, 88685, 249, 397, 130, 46229, 273, 499, 226, 6, 326, 263, 117868], [107521, 300, 30245, 171, 402, 116464, 0, 62, 483, 91, 149, 313, 347, 153], [53544], [487, 47293, 256, 435, 63894, 20, 178, 372, 65, 30081, 159], [168, 467, 455, 69, 233, 217, 284, 228, 62150, 106, 90, 300, 329, 149, 191, 405, 287, 456, 107053, 124959, 5, 86, 364, 131, 105, 101276, 67538, 198, 188, 25219], [232, 72, 149, 374, 146, 141, 19, 69194, 460, 458, 109, 12332, 235, 13363, 101110, 265, 307, 30], [99, 197, 58080], [67430, 112], [275, 262, 7, 231, 24907, 5346, 365], [367, 201, 27906, 217, 488, 11351, 96294, 499, 143, 354, 497, 245, 473, 444, 286, 119, 217, 345, 41180, 419, 124936, 8, 195, 264, 77417, 432, 83]]</t>
+    <t>[[1971, 227, 304, 383], [176, 6, 409, 507, 367], [76, 1933, 102, 308, 223, 70], [153, 141, 349, 1532, 421, 68], [232, 229], [61, 3, 394, 504, 480, 134, 121, 337], [264, 381, 228, 199, 467, 41, 284, 1406, 317, 478], [78, 76, 179, 1113, 1741, 187, 342, 6, 499], [1257, 496, 230, 115], [184, 482, 81], [316, 493, 405, 22, 407, 55], [154, 197, 3, 195], [389, 419, 16, 46], [2], [307, 348, 121, 321, 204, 491, 488], [1427, 341, 1615, 352, 510, 49]]</t>
   </si>
   <si>
     <t>h128_ws4_idx8192_large_infp16_outfp16_ID239</t>
   </si>
   <si>
-    <t>[[351, 14, 2514, 120, 164, 367, 362, 1638, 128, 635, 23, 250, 280, 378, 289], [350, 2806, 135, 276, 5883, 309], [185, 225, 17, 389, 10, 347, 310, 333, 6000, 348, 110, 7500, 5625, 16, 472, 454, 3, 23, 237, 3905, 187, 294, 155, 202, 7770, 6781, 511, 15, 454], [6614, 304, 222, 6048, 261, 509, 159, 433, 200, 350, 6938, 160]]</t>
+    <t>[[239, 428, 1795, 366, 501], [28, 122, 217], [472, 101, 482], [389, 177, 469, 345, 503, 1817, 415, 193, 44]]</t>
   </si>
   <si>
     <t>h128_ws4_idx16384_large_infp16_outfp16_ID240</t>
   </si>
   <si>
-    <t>[[672, 233, 467, 374, 302, 260, 123, 124, 459, 309, 119, 10362, 439, 13289], [9787, 74, 45, 343, 485, 396, 140, 14186, 434, 119, 481, 17, 164, 429, 7233], [376, 327, 481, 8514, 1023, 498, 68, 249, 376, 103, 312, 151, 11301, 264, 13695, 264, 174, 29, 383, 307, 349, 447, 450, 5486], [112, 15459, 9785, 375, 415, 13617, 1173, 54, 354, 10206, 137, 297, 192, 326, 477, 454, 25, 259, 381, 399, 226]]</t>
+    <t>[[374, 435, 142, 424, 298], [1728], [995, 1783, 1007, 330, 1350], [394, 433, 300, 301, 1252, 1569, 1353, 551, 435, 731]]</t>
   </si>
   <si>
     <t>h128_ws4_idx32768_large_infp16_outfp16_ID241</t>
   </si>
   <si>
-    <t>[[236, 42, 355, 12243, 182, 106, 2054, 363, 423, 18918, 373, 216, 292, 217, 411, 41, 412, 32, 115, 284, 233, 27559, 432, 721], [60, 15246, 143, 411, 47, 7369, 369, 16986, 322, 365, 436, 277, 460, 408, 27197, 84, 511, 69, 228], [41, 265, 4818, 97, 456, 0, 415, 66, 195, 8416], [114, 72, 327, 491, 21, 366, 15848, 9591]]</t>
+    <t>[[488, 204, 263, 144, 409, 223, 511, 117, 1897, 2029], [313, 50, 121, 512, 109, 394], [69, 1282], [413, 31, 337, 187, 423]]</t>
   </si>
   <si>
     <t>h128_ws8_idx16384_large_infp16_outfp16_ID242</t>
   </si>
   <si>
-    <t>[[507, 494, 9561, 47, 100, 9020, 4, 29, 166], [8513, 396, 407, 352, 445, 6956, 304, 288, 38, 3965, 454], [324, 32, 311, 365, 190, 4882, 9466, 348, 409, 348], [27, 11303, 150, 303, 1016, 48, 6235, 240, 195, 140, 293, 128, 474, 65, 159, 270, 385, 8538, 130, 362, 244, 208, 131, 123, 4436, 109, 8228], [48, 14234, 243, 297, 153, 13021, 468, 284, 8871, 124, 401, 332, 8587, 431, 365, 280, 4885, 432, 133, 263, 220, 326, 197, 82, 359, 224, 1542, 81, 474], [48, 97, 276, 8161], [15310, 498, 6, 505, 470, 398, 3225], [206, 9590, 466, 13100, 458, 423, 256, 437, 64, 340, 109, 984, 502, 107, 273, 14001, 53, 11507, 32, 348, 335, 460]]</t>
+    <t>[[1144, 1076, 422, 95, 53, 146, 422, 488, 144], [125, 1855, 393], [224, 508, 47, 246, 256, 58], [387, 1957, 56, 308, 471, 443, 429, 15, 138, 289], [491, 300, 302, 76, 233, 1144, 272, 446, 229], [439, 64, 491, 240, 417, 506, 150, 488], [261, 172, 339, 243, 68, 144, 232], [27, 1175, 229, 66, 220, 397, 487, 390, 368, 1260]]</t>
   </si>
   <si>
     <t>h128_ws8_idx32768_large_infp16_outfp16_ID243</t>
   </si>
   <si>
-    <t>[[10, 105, 78, 107, 48, 10638, 3402, 361], [405, 269, 6030, 357, 443, 7272, 360, 57, 211, 30213, 465, 151, 477, 63, 31119, 473, 387, 118, 8823, 70, 89, 474, 9595, 265, 275, 394], [347, 107, 414, 14017, 147, 384, 47, 20939, 248, 487, 22201, 188, 126, 48, 5149, 81, 218], [28, 122, 24331, 367, 166, 2835, 105, 505, 250, 15752, 462, 24691, 246, 378, 447, 1835, 162, 446, 295, 166, 252, 274], [26750, 290, 23, 31303, 51, 152, 18851, 509, 131, 352, 130, 188, 13574, 331, 361, 389, 181, 2], [10, 337, 60, 6359, 16312, 324], [403, 2377, 9998, 103, 188, 264, 195, 215, 356], [8809, 421, 27046, 111, 27, 425, 89, 375, 4536, 167, 112, 326, 379, 32094, 329, 400]]</t>
+    <t>[[391, 443, 152, 315, 345, 203, 60, 146], [413, 663], [228, 294, 939, 117, 102, 459, 250], [345, 492, 250, 468, 311, 432], [484, 91, 1265, 490, 138], [4, 107, 109, 1939, 474, 102], [259, 464, 361, 1550, 1328, 42, 158, 938, 430, 443], [335, 93, 225, 406, 430]]</t>
   </si>
   <si>
     <t>h128_ws8_idx65536_large_infp16_outfp16_ID244</t>
   </si>
   <si>
-    <t>[[410, 331, 285, 50078, 512, 252, 51, 44594, 322, 465, 9076, 29234, 224, 452, 18, 17, 171, 186, 46964, 229, 228, 34, 425, 21086, 288, 121], [10, 47, 63399, 237, 247, 72, 260, 64602, 23050, 53, 365], [450, 40045, 307, 208, 207, 357, 395, 213, 103, 432, 4, 36, 489, 21652, 53, 43, 49728, 216, 4707, 0, 384, 52, 37117, 253, 272, 252, 31261, 3142, 468, 381, 458, 89], [46822, 154, 231, 8, 4, 35, 315, 22221, 453, 196], [406, 176, 7345, 13737, 50131, 493, 414, 507, 332, 383, 401, 84, 287, 469, 63], [328, 283, 486, 4617, 486, 335, 101, 16572, 83, 476, 65433, 498, 103, 289, 95, 62, 36892, 110, 451, 158, 115, 502, 351, 135, 100, 394, 30009, 252, 64290, 331], [57, 49651, 13], [24202, 61, 511, 248, 179, 267, 6102, 100, 358, 28649, 33, 118, 277, 455, 438, 144, 230, 64637, 2635, 33, 114, 225]]</t>
+    <t>[[263, 437, 474, 35, 356, 84, 192, 473, 511], [463, 442, 146, 1235, 59, 446, 1920], [12, 210, 1330], [408, 498, 156, 46], [171, 1456, 920, 261, 120, 811, 201, 1648, 27, 366], [115, 43, 428, 444, 278], [280, 196, 132, 315, 501, 462, 278, 39, 221, 297], [268, 1932, 54, 428, 377, 213]]</t>
   </si>
   <si>
     <t>h128_ws16_idx32768_large_infp16_outfp16_ID245</t>
   </si>
   <si>
-    <t>[[131, 65, 406, 456, 353, 351, 28291, 32688, 51, 138, 2, 374, 12665, 429, 111, 156, 119, 91, 4383, 30272, 328, 192, 218, 45, 201, 29803, 381, 126, 491, 7041, 431], [112, 308, 8836, 257, 429, 270, 427, 193, 12039, 451, 489, 65, 10108, 147, 27, 127, 137, 29497, 9140, 309, 78, 288], [401, 403, 234, 324, 306, 28114, 200, 386, 13, 32052, 355, 210, 24742, 207, 28565, 487, 49, 120, 157], [77, 58, 9613], [173, 440, 64, 27339, 9941, 33, 227, 346, 335, 447, 376, 28956, 266, 201, 187, 180, 2010], [13479, 395, 478, 0, 175, 277, 16369, 203, 183, 96, 417, 496, 256, 259, 174, 11, 176, 425, 29069, 45, 299, 6053, 2449, 355, 316], [170, 365, 316, 6426], [495, 51, 86, 30040, 442, 425, 181, 403, 212, 291, 377, 8310, 257, 168, 138, 3878, 132, 8257, 257, 429, 457, 419, 11513, 96, 268, 24212], [28050, 20289, 317, 97, 250, 187], [472, 4099, 217, 20802, 290, 502, 68], [14665, 486, 6706, 276, 294, 18013, 83, 244, 494, 348, 40], [259, 91, 15599, 125, 80, 140, 60, 16806, 75], [394, 61, 206, 74, 508, 447, 456, 465, 151, 451, 10269, 455, 395, 281, 181, 257, 234, 492, 29113, 82, 143, 2366, 32619, 28, 176, 367, 25657, 223, 72, 31020], [510, 12202, 12, 268, 151, 335, 16, 21325, 468, 437, 12491, 243], [71, 196, 209, 388, 464, 500, 13420, 431, 44, 23727, 139, 87, 35, 387, 4444, 488, 414, 332, 505, 23546], [79, 32222, 132, 84, 148, 90, 191, 260, 6, 18650, 294, 266, 34, 15797, 458, 4, 13080, 143, 195, 11780, 350]]</t>
+    <t>[[799, 62, 275], [423, 182, 488, 242, 44, 319, 133, 378, 660], [187, 20, 78, 510, 453, 14, 336, 1293, 587], [171, 130, 281, 72, 1503], [359], [374, 220, 352, 1896, 100, 318], [268, 238, 962, 1893, 447, 108, 114, 471, 320, 13], [329, 373, 194, 48, 85, 242, 52, 38], [489, 355, 74, 67, 420, 38, 21, 432], [345, 471, 298, 117, 359, 286, 241, 103], [788, 208, 185, 1275, 217], [506, 1695, 1404, 241, 405, 35, 1780, 179, 218], [310, 322, 156], [406, 459, 380, 8, 15], [110, 417, 70], [26, 82, 279, 6, 861, 1791, 464, 87, 237]]</t>
   </si>
   <si>
     <t>h128_ws16_idx65536_large_infp16_outfp16_ID246</t>
   </si>
   <si>
-    <t>[[97, 39, 313, 265, 51959, 175, 280, 463, 12083, 84, 90, 171, 213, 421, 20668, 58965, 175, 305], [291, 8482], [32, 64, 306, 54, 217, 60164, 2425, 23527, 358, 75, 176, 321], [39145, 499, 195], [263, 398, 445, 415, 18318, 304, 398, 78, 23353, 320, 309, 234, 35345, 12651, 348, 125, 147, 503, 316], [142, 23733, 25003, 136, 418, 25085, 122, 148, 358, 38831, 319, 463, 361, 343, 20, 105, 21137, 49, 330, 247, 124, 81, 387, 172, 237], [249, 406, 437, 54274, 20175, 461, 4652, 432, 265, 264, 124, 294, 291, 198, 37, 486, 61176, 164, 79, 228, 290, 385, 395, 51579, 58, 199, 122, 26672, 76, 402], [424, 175, 446, 51, 285, 277, 46424, 42, 490, 73, 11469, 30351, 63826, 449, 76, 296, 329], [313, 80, 2160, 26941, 194, 1218, 15330, 386, 164, 454, 50, 155, 4899, 23, 51163, 71, 380, 353, 253, 157, 335, 503, 51, 214, 409, 271, 294], [478, 116, 399, 500, 417, 157, 58127, 245, 48017, 246, 331, 273, 469, 43397, 355], [50049, 441, 485, 209, 331, 451, 136, 319, 33410, 29620, 15258, 270, 64644, 53887, 59, 211, 432, 387, 253, 238, 456, 488, 79, 26, 78, 53018, 368, 137, 232, 109, 387], [187, 510, 266, 506, 145, 62801, 45, 144, 35398, 44, 305, 31179, 64060, 118, 373, 453, 180, 359, 417, 170, 36604, 443, 477, 59], [371, 230, 50572, 174, 152, 17263, 41589, 87, 326, 142, 226, 469, 489, 404], [9, 340, 15581, 99, 395, 234, 213, 278, 18707], [45, 12859, 470, 236, 496, 460, 63, 2301, 455, 55786, 248, 244, 178, 95, 91, 58425, 432, 132, 188, 268, 22263, 183, 214], [311, 450, 33396, 34420, 257, 222, 30980, 198, 161, 456, 426, 10485, 163, 398, 495, 185]]</t>
+    <t>[[258], [85, 70, 129, 923, 54, 108, 574, 84], [1268, 505, 428, 465, 191], [354, 100, 1886], [426, 929, 400, 44, 253, 52, 80, 317, 349], [446, 263, 1452, 1409], [263, 360], [234, 495, 139], [402, 71, 353], [244], [273, 78, 275, 744, 44, 472, 300, 389], [406, 160, 68], [186, 381, 56, 1526, 890, 293, 1426], [1296, 647, 506, 275, 419, 398, 936], [398, 351, 1015, 102, 28, 550, 163, 105, 321, 275], [62, 386, 179, 51, 52, 394, 356, 245, 243]]</t>
   </si>
   <si>
     <t>h128_ws16_idx131072_large_infp16_outfp16_ID247</t>
   </si>
   <si>
-    <t>[[155, 100169, 74, 214, 276, 132, 58859, 318, 489, 124706, 493, 225, 357, 355, 218, 270, 100843], [384, 113803, 387, 463, 435, 266, 38, 93297, 345, 53, 52348, 85, 101, 466, 23, 130, 238, 42099, 256, 126, 146, 283, 122944, 141, 92], [88, 480, 244, 347, 120, 254, 154, 19, 96, 327, 184, 123707, 1945, 181, 4378, 339, 54, 76337, 14, 66726, 245, 170, 493], [32445, 124700, 361, 147, 124513, 368, 457, 69442, 33178, 499, 403, 12, 84, 268, 66163, 30, 486, 452, 187, 154, 366, 131, 232, 342, 174, 284, 452], [507, 67091, 410, 496, 39, 104174, 286, 438, 94, 232, 384, 269, 12616, 407, 8446, 313, 417, 296, 490, 509, 42924, 16], [79893, 401, 453, 438, 313], [422, 419, 452, 219, 126937, 397, 373, 422, 443, 181, 140, 171, 358, 257, 272, 69163, 146, 466, 232, 6, 95302, 404, 11378, 50494, 82611, 3448, 492, 110, 107, 206, 263], [73434, 232, 495, 360, 168, 22, 29824, 66039, 123281, 395, 36419, 144, 25031, 217, 451, 31, 384, 310, 193, 277, 121, 100, 350, 51779, 265, 420, 498, 330, 121, 443, 176, 385], [194, 3, 209, 83679, 216, 373, 357, 309, 422, 451, 74481, 127150, 55], [316, 136, 142, 321, 67792, 8, 84, 161, 119387, 413, 478, 46564, 20, 222, 36374, 32, 41, 109, 257], [511, 287, 475, 19, 395, 124696, 74606, 109785, 493, 194, 153, 465, 47, 22666, 111470, 464, 156, 366, 117, 232, 89], [174, 121909, 505, 375, 58492, 139, 66, 147, 63618, 209, 116, 74, 179, 429, 405, 332, 229, 302, 464, 473, 427, 55, 35886, 54, 123, 96825, 145, 13102, 122], [102128], [376, 77729, 442, 281, 71666, 295, 422, 42704, 409, 75808, 312, 218, 479, 375, 164, 505, 190, 72655, 64, 345, 89555, 190, 191, 503, 116, 373, 135, 497], [305, 92670, 273], [7918, 19890, 137, 53, 376, 147, 77]]</t>
+    <t>[[199, 324, 168, 26, 193, 1065, 798, 7, 172, 51], [203, 1411, 194, 660, 450, 1514, 453, 480], [506, 386, 1877, 48, 458, 289, 394, 351], [532, 84, 274, 210, 161], [381, 92, 27, 197, 494, 202, 26, 260], [426, 376, 446], [512, 440, 311, 357, 219, 45, 305, 234, 55], [495, 494, 302, 82, 212, 83, 1674, 119, 436, 239], [126], [1874, 958, 421], [1184, 292], [121, 222], [294, 103, 488, 143, 215, 230, 435, 505], [41, 244, 434], [390, 375, 416, 312, 146, 425, 349, 316, 1628], [113, 413, 366, 449, 1362]]</t>
   </si>
   <si>
     <t>h256_ws4_idx8192_large_infp16_outfp16_ID248</t>
   </si>
   <si>
-    <t>[[93, 1296, 4160, 259, 23, 3320, 110, 146, 14, 326, 402, 423, 1789, 278, 393, 10, 131, 165, 207, 3458, 59, 4461, 185, 97, 158, 325, 326], [348, 4539, 300, 511, 349, 458, 433, 361, 77, 3748, 1592, 1217, 14, 40, 8085, 437, 238, 5707, 29, 305, 249, 363, 483, 167, 88, 223, 162, 411], [174, 376, 200, 2077, 167, 83, 493, 6721, 30, 42, 3037, 446, 263, 152, 350, 379, 384, 458, 7839, 423, 306, 567, 138], [494, 2466, 174, 154, 390, 484, 167, 264, 36, 2622, 306, 4081, 280, 4423, 142, 18, 81, 210, 467]]</t>
+    <t>[[76, 1111, 918, 1842, 254], [52, 391, 141, 352, 289, 261], [349, 503, 506, 368, 367], [131, 472, 1404, 203, 25, 195, 1268, 292, 294]]</t>
   </si>
   <si>
     <t>h256_ws4_idx16384_large_infp16_outfp16_ID249</t>
   </si>
   <si>
-    <t>[[223, 480, 467, 7919, 356, 406, 474, 47, 8438, 360, 367, 331, 96, 245, 69, 450, 207, 208, 307, 105, 9510, 415, 318, 160, 3812, 270, 105, 365, 5869, 7313], [14412, 6, 63, 19, 5015, 462, 277, 222, 490, 485, 480, 380, 5762, 207, 559, 46, 290], [234, 8651, 301, 161], [115, 509, 173, 188, 323, 291, 94, 73, 15943, 70, 3402, 211, 246, 284, 11356]]</t>
+    <t>[[1898, 156, 58, 267, 188, 323], [486, 308], [389], [470, 494, 379, 902, 409, 831, 204]]</t>
   </si>
   <si>
     <t>h256_ws4_idx32768_large_infp16_outfp16_ID250</t>
   </si>
   <si>
-    <t>[[14441, 412, 238, 412, 114, 1739, 4, 75, 437, 83, 409, 318, 20118, 430, 670, 312, 442, 288, 45, 9521, 47, 221, 40, 484, 210, 104, 10264, 52], [55, 2869, 130, 43, 19296, 230, 5579, 355, 463, 22892, 490, 220, 313, 29970, 162, 133, 341, 355, 398, 19, 474], [251, 325, 400, 179, 299, 305, 28595, 17753, 479, 254, 13896, 308, 108, 59, 23472, 183, 75, 398, 60, 87, 30823, 454, 458, 66, 27478, 220, 423, 283, 187], [185, 234, 486, 61, 30263, 1691, 28014, 98, 480, 489, 23, 20245, 212, 16, 483, 485, 146, 304]]</t>
+    <t>[[274, 320, 137, 1439, 91, 4, 422, 215], [259, 1087, 396], [433, 321, 116, 156, 227], [373, 119, 320, 465]]</t>
   </si>
   <si>
     <t>h256_ws8_idx16384_large_infp16_outfp16_ID251</t>
   </si>
   <si>
-    <t>[[308, 13440], [446, 164, 438, 456, 418, 501, 359, 4177, 104, 170, 480, 5157, 213, 2513, 403, 233, 290, 274, 358, 3139, 502, 188, 222, 215, 6616, 5254], [7928, 1516, 333, 16271, 298, 138, 15, 199, 477, 464, 209, 115, 170, 505, 428, 381, 325, 211, 324, 10174, 440, 492, 203, 141, 377, 7723, 453, 9952, 333, 481], [67, 4455, 42, 8953, 273, 399, 242, 14806, 299, 38, 443, 98], [60, 6850, 218, 392, 156, 11561, 237, 264], [354, 1, 14306, 147, 14655, 469, 45, 364, 53, 44, 266, 172, 399, 284, 206, 275, 11464, 13053, 97, 16267, 92, 475, 94, 49, 2321, 36, 255, 391, 241], [166, 157, 370, 8315, 48, 15197], [202, 133, 494, 14930, 258, 425, 127, 7686, 16301, 128, 280, 421, 473, 339, 481]]</t>
+    <t>[[465], [173, 504, 205, 1559], [248, 30, 25, 457], [194, 4, 172, 249], [364, 395], [117, 153, 488, 371, 347, 213, 107, 40, 310, 128], [1483, 168, 1441, 206, 103], [1227, 1611, 185, 441, 259]]</t>
   </si>
   <si>
     <t>h256_ws8_idx32768_large_infp16_outfp16_ID252</t>
   </si>
   <si>
-    <t>[[438, 279, 31596, 295, 434], [304, 2, 454, 294, 422, 450, 45, 370, 24180, 143, 8903, 370, 10306, 456, 14431, 340, 13, 302, 384, 14814, 14, 189, 414, 47, 32506, 290, 188, 74, 256], [23088, 172, 358, 141, 26924, 206, 57, 45, 289, 23766, 10302, 136, 23032, 202, 358, 427, 110, 251, 132, 159, 13, 54], [33, 55, 268, 389, 179, 13413, 128, 20988, 49, 281, 271, 191, 489, 483, 431, 49, 472, 12, 971, 16655, 4368, 330, 157, 113, 281], [289, 5460, 79, 290, 15492, 301, 142, 488], [146, 213, 18588, 403, 370, 130, 26616, 409, 405, 35, 336, 8571, 222, 29635, 381, 320], [145, 9014, 448, 98, 380, 9271], [27432, 370, 287]]</t>
+    <t>[[297, 74, 1995], [221, 346], [427, 192], [168, 29, 345, 59], [68, 26, 1948, 508, 484], [330, 138, 459], [640], [267, 425]]</t>
   </si>
   <si>
     <t>h256_ws8_idx65536_large_infp16_outfp16_ID253</t>
   </si>
   <si>
-    <t>[[464, 199, 151, 16542, 55569, 99, 24064, 289, 110, 300, 410], [315, 293, 194, 433, 20879, 162, 366, 402, 267, 26812], [302, 294, 325, 443, 358, 38, 141, 420, 399, 132, 124, 36502, 214, 497, 128, 59, 57545, 5666, 31358, 5855, 95], [148, 308, 497, 318, 507, 38806, 107, 36707, 7072, 432, 320, 127, 112, 95, 508, 296, 38, 62898, 2295, 173, 403, 69, 38, 43], [434, 288, 130, 347, 44907, 414, 159, 247, 390, 59111, 34, 196, 243, 106, 9422], [502, 206, 309, 23699, 65, 25, 252, 9935, 34150, 79, 459, 306], [51679, 166, 329, 40671, 198, 1, 64361, 437, 129, 29704, 335, 130, 433, 192, 33, 259, 385, 197, 111, 505, 48, 270, 302, 19594, 59, 96, 16010, 93], [323, 134, 126, 336, 33038, 421, 388, 124, 385, 26583, 52181, 235, 176, 476, 5158, 378, 425, 432, 403, 331, 348, 2268]]</t>
+    <t>[[509, 456, 42, 160, 262, 500, 1541, 131], [988, 196, 496, 247, 195, 458], [75], [418, 130, 242, 10, 220, 49], [598, 82, 196], [163, 303, 233, 16, 353, 486, 384], [510, 20, 370, 241, 249, 69], [276, 280]]</t>
   </si>
   <si>
     <t>h256_ws16_idx32768_large_infp16_outfp16_ID254</t>
   </si>
   <si>
-    <t>[[419, 17, 11331, 23878, 488, 14742, 112, 423, 465, 138, 219, 64, 316], [119, 268, 29184, 32, 15393, 413, 392, 14849, 301, 499, 33, 376, 126, 31271, 273, 16907, 264, 479, 104, 162, 508, 7874, 506, 323, 99, 127, 148, 4, 206, 8494, 84], [284, 6, 234, 253, 262, 597, 84, 503, 3712, 87], [127, 491, 303, 6912, 58, 130, 432, 10727, 3416, 133, 418, 452, 9311, 385, 390, 291, 142, 210, 297, 0, 292, 358, 428, 16230, 503], [15, 11682, 442], [113, 8479, 381, 232], [395, 367, 500, 311, 4086, 408, 423, 473, 24, 432, 170, 18382, 24391, 445, 1, 314, 210, 7999, 498], [440, 172, 140, 318, 141, 464, 6337, 20310, 295, 61, 1720, 26178, 28, 328, 62, 392], [135, 12646, 197, 353, 502], [234, 326, 24250, 183, 293, 27720, 84, 160, 357, 204, 394, 377, 370, 389, 2382], [292, 327, 390, 28, 23624, 197, 125, 377, 504, 422, 266, 123, 27254, 48, 25149, 5600, 135, 267, 22978, 165, 29, 1853, 295, 458, 314, 419, 21, 121], [19174, 120, 247, 22408, 163, 227], [452, 329, 262, 71, 451, 1635, 417, 440, 77, 916, 14262, 466, 336, 477, 93, 148, 27842, 210, 249, 7814, 259, 51, 331], [329, 88, 13578, 118, 487, 4278, 425, 359, 55, 86, 252, 265, 171, 14496], [108, 263, 30106, 231, 188, 183, 1481, 326], [15613, 142]]</t>
+    <t>[[27, 146, 450], [179, 372], [56, 143, 351, 147, 230, 360, 30], [842, 305, 351, 9, 752, 1889, 433], [535, 4, 20, 433, 475, 546], [334, 1599, 183, 1515, 20, 131, 113], [282], [268, 274, 441, 430, 83, 1881, 1523], [393, 447, 226, 480, 216, 86, 453, 9], [89, 83, 313, 393, 438, 89], [36], [1347, 312, 673, 350, 459, 1135, 425, 192, 1521], [462, 1722, 500, 287, 346], [229, 267, 491, 379, 142, 916, 1328, 97], [437, 21, 317], [480, 649, 376, 241, 253, 366, 431, 180]]</t>
   </si>
   <si>
     <t>h256_ws16_idx65536_large_infp16_outfp16_ID255</t>
   </si>
   <si>
-    <t>[[33374, 17767, 358, 12, 239, 135, 496, 33, 23442, 172, 81, 469, 477, 282, 177, 448, 193, 45549, 127], [383, 147, 131, 100, 119, 240, 269, 56771, 492, 302, 176, 7373, 278, 107, 34, 100, 157, 53896, 250, 56689, 372, 460, 15725, 339, 316, 205, 99, 5022, 74, 496], [31349, 74, 56, 106, 189, 509, 2484, 430, 165, 393, 110, 32, 183, 23120, 62939, 2375, 404, 485, 297, 336, 351, 397, 350], [6082, 410, 373, 51, 148, 502, 35269, 174, 426, 482], [494, 336, 312, 35344, 7792, 372, 273, 512, 28657, 332, 187], [39260, 457, 28969, 57, 48, 458], [24464, 197, 113, 1917, 225, 382, 197, 358, 355, 321, 1563, 13574, 37, 168, 101, 117], [247, 379, 21364, 156, 400, 201, 9, 284, 63203, 395, 394, 61688, 300, 388, 473, 294, 504, 11142, 454, 1, 8860, 384], [156, 291, 117, 170, 60580, 17178, 270, 401, 171, 85, 32, 36182, 307, 294, 4298, 95, 372, 195, 3167, 102, 223], [297, 27488, 511], [13085, 4618, 422, 398, 1751, 138, 422, 196, 439, 108, 80, 170], [433, 16290, 25827, 512, 153, 165, 409, 367, 202, 269, 192, 30877, 13, 268, 36, 402, 178, 506, 13712, 375, 170, 48508, 141, 275, 78, 43295, 251, 113], [155, 444, 336, 5444], [83, 217, 51049, 442, 227, 498, 108, 343, 244, 482, 100, 96, 511, 43344, 5, 329, 257, 415, 60467, 8000, 109, 142, 356, 20034, 156, 60403], [11, 161, 8646, 269, 394, 31493, 447, 125], [4838]]</t>
+    <t>[[401, 100, 410, 5, 370, 148, 387, 338, 359, 198], [295, 260, 1624, 500, 262, 76], [1348, 169, 37, 363, 318, 299, 200, 232], [176, 311, 405, 84, 96, 108, 97, 460], [327, 322, 799, 365, 40, 196, 347, 280, 475, 215], [225, 490, 171, 252, 167], [504, 48, 350, 1625, 1975, 294, 4, 475, 196], [189, 367, 294], [372, 493], [427, 103], [229, 358, 70, 315, 1878, 290], [423, 408, 14, 439], [377, 421, 17, 202, 927, 348, 330], [306, 206], [56, 21, 152, 155, 143, 316], [108, 174]]</t>
   </si>
   <si>
     <t>h256_ws16_idx131072_large_infp16_outfp16_ID256</t>
   </si>
   <si>
-    <t>[[147, 252, 24, 435, 353, 62111, 60722, 73713, 301, 50186, 349, 80, 125804, 442, 205, 501, 117, 1312, 78, 10, 154, 320, 310, 145, 510, 463], [403, 161, 316, 460, 354, 127866, 418, 248, 38623, 378, 493, 112566, 46468, 437, 351, 401, 426, 138, 223, 466], [489, 114445, 505, 16045, 217, 444, 489, 292, 41273, 2, 26318, 69, 289, 498, 202, 355, 72164, 101, 246, 15, 22, 100977, 249, 133, 110, 192, 212, 83, 456], [41075, 276, 27036, 249, 49, 182, 142, 64539, 313, 432, 197, 18916, 496, 412, 430, 237, 201, 110], [239, 171, 94478, 330, 74, 77, 245, 222, 226, 512, 222, 179, 127275, 312, 86, 134, 3750, 269, 116883, 410, 80991, 208, 470, 438], [339, 341, 75237], [215, 31, 248, 10141, 80866, 43, 31, 37, 48, 20756, 269, 73, 501, 95, 461, 423, 197, 125220, 82], [92, 5, 17905, 369, 16746, 351, 227, 476, 254, 85498, 257, 148, 403, 361, 385, 104421, 72975, 225, 2, 142, 112, 119552, 64, 159, 295, 391, 463], [474, 129884, 171, 512, 54925, 128, 91, 105473, 54, 204, 455, 16101, 415, 95, 296, 261, 120, 23, 479, 414, 255, 429, 15270, 392, 403], [274, 22676], [311, 174, 162, 163, 235, 102588, 219, 61746, 329, 71350, 136, 46], [480, 409, 7810, 86], [426, 66, 113, 59100, 338, 270, 273, 94, 128345], [63, 252, 221, 88704, 34], [135, 2, 349, 44, 127495, 313, 315, 237, 233, 277, 19132, 113, 509, 55366, 32403, 485, 180, 173, 209, 275, 11392, 79, 464], [119864]]</t>
+    <t>[[1673, 228], [152, 138, 372], [318, 11, 373], [449, 73, 385, 190, 221], [345, 1928, 466, 485, 28, 72], [298, 413, 339, 406, 461, 497, 93, 340, 296], [174, 63, 419, 827, 512], [48, 15], [392, 413, 446], [931, 346, 299, 226, 186], [424, 361, 67, 444, 1673, 146, 185, 9, 413], [415], [47, 409, 306, 3], [252, 49, 63, 37, 434, 217, 374, 203, 486, 440], [304, 31, 272, 82], [196, 244, 572, 327]]</t>
   </si>
   <si>
     <t>h64_ws2_idx2048_inbf16_outbf16_ID257</t>
   </si>
   <si>
-    <t>[[396, 547], [174, 239, 359, 1191, 305, 627, 167, 96, 466, 294, 270, 185, 444, 703, 485, 316, 1314, 149, 1665, 422, 125, 328, 296, 146]]</t>
+    <t>[[245], [23, 392, 1702, 94]]</t>
   </si>
   <si>
     <t>h64_ws4_idx4096_inbf16_outbf16_ID258</t>
   </si>
   <si>
-    <t>[[3363, 179, 306, 235, 1540, 500, 165, 111, 273, 256, 244, 265, 292, 354, 170, 269, 3160, 163, 538, 417, 2, 1420, 44, 375], [198, 51, 132, 155, 3793, 99, 104, 3192], [1711, 63, 113], [485, 509, 146, 246, 3383, 294, 455, 369, 728, 397, 854, 236]]</t>
+    <t>[[417, 497], [246, 327], [8, 271, 72, 400, 299, 1900, 13, 204, 118, 152], [407, 231, 201, 49, 468]]</t>
   </si>
   <si>
     <t>h64_ws8_idx8192_inbf16_outbf16_ID259</t>
   </si>
   <si>
-    <t>[[171, 5935, 440, 178, 382, 1, 486, 347, 415, 469, 2769, 2761, 136, 33, 8, 5903, 229, 29, 341, 213, 434, 485, 197, 5556, 5273, 181, 318, 418], [60, 113, 169, 2357, 317, 234, 3, 345, 4990, 102, 399, 427, 27, 6660, 143, 179, 334, 5830, 2392, 466, 37, 378, 507], [91, 420, 5152, 331, 2804, 190, 508, 150, 393, 2174, 7199, 419, 502, 144, 270, 95], [295, 423, 453, 462, 330, 259, 314, 40, 6282, 2337], [2644, 70, 228, 154, 172, 352, 633, 5935, 119, 203, 168, 480, 143, 478], [6863, 430, 322, 5310, 330, 203, 276, 308, 187, 161, 237, 269, 1829, 30, 7511, 265, 234, 269, 394, 154, 434, 418, 5691, 408], [7867], [114, 392, 4896, 251, 421, 7385, 455, 2798, 400, 100, 238, 322, 383, 114, 321, 3, 282, 477, 365, 8116, 5820, 298, 482, 430, 503, 168, 319, 219, 7565]]</t>
+    <t>[[219, 315], [247, 217, 470, 431, 84, 99, 476, 216, 344], [381, 237, 322, 449, 376], [193, 274, 441, 377], [136, 353, 208, 338, 530, 1648, 430, 458], [781, 118, 474, 20, 309], [188, 97, 74, 311, 185, 454, 1270, 979, 993, 725], [507, 197, 185, 512, 772, 1254, 281, 282]]</t>
   </si>
   <si>
     <t>h256_ws2_idx2048_inbf16_outbf16_ID260</t>
   </si>
   <si>
-    <t>[[1372, 374, 116, 445, 169, 1801, 473, 140, 506, 28], [206, 142, 207, 433, 470, 304, 1834, 434, 239, 59, 480, 1346, 1880, 260, 68, 31, 156, 246, 2002, 121, 1258, 351, 966, 119, 89, 437, 402]]</t>
+    <t>[[1900, 647, 333, 265, 647], [97, 90, 399, 25, 34, 177, 113, 251]]</t>
   </si>
   <si>
     <t>h256_ws4_idx4096_inbf16_outbf16_ID261</t>
   </si>
   <si>
-    <t>[[47, 13, 449, 192, 92, 3473, 20, 1108, 335, 351, 447, 401, 1248, 173, 3527, 388], [1285], [152, 343, 103, 494, 327, 1412, 488, 0, 1101, 87, 204, 15, 103, 284, 36, 26, 338, 1240, 3704, 237, 251, 2518, 302, 188, 323, 374, 192, 4064, 489, 210], [507, 4008, 458, 107, 136, 477, 232, 1915, 342, 396, 505, 245, 3608, 334, 97]]</t>
+    <t>[[195, 444, 155, 131, 350], [243, 64, 385, 132, 31, 405, 96, 85], [107, 259, 439, 179], [209, 82, 288, 463, 187, 249, 431, 237, 1]]</t>
   </si>
   <si>
     <t>h256_ws8_idx8192_inbf16_outbf16_ID262</t>
   </si>
   <si>
-    <t>[[457, 422, 80, 141, 447, 96, 375, 64, 434, 2337, 6835, 537, 434, 466, 456, 56, 644], [188, 122, 55, 403, 327, 570, 102, 7314, 242, 441, 126, 268, 6404, 0, 203, 40, 420, 8086], [126, 67, 7486, 67, 461, 1325, 307, 358, 131], [81, 464, 358, 462, 1287, 161, 101, 275, 5722, 191, 206, 294, 25, 459, 8113, 248, 5843, 163, 217, 480], [15, 510, 1284, 243, 1647, 14, 373, 41, 6690, 252, 188, 209, 308, 205, 69], [14, 262, 440, 352, 263, 6263, 5392, 276, 236, 7624, 177, 138, 366], [229, 4912, 481, 141, 219, 4169, 234], [349, 335, 343, 80, 99, 467, 60, 265, 171, 501, 6031, 3012, 2501, 6700, 411, 395]]</t>
+    <t>[[260, 216, 1046, 1355], [20, 25, 261, 497, 383, 1518], [476, 788, 409], [463, 342, 763, 692, 172, 417], [360, 500], [100, 1605, 1426, 145, 259], [473, 1672, 346, 419, 281, 355], [218, 56, 459, 563, 375, 2, 37, 247, 253, 44]]</t>
   </si>
   <si>
     <t>h512_ws2_idx2048_inbf16_outbf16_ID263</t>
   </si>
   <si>
-    <t>[[236, 38, 915, 1934, 1279, 449, 366, 211, 385, 341, 393, 290, 243, 145, 429, 368, 277, 286, 233, 117, 336, 86, 372, 445, 1875, 42, 1962, 1424], [209, 1954, 2, 83, 154, 460, 189, 53, 787, 412, 159, 7, 507, 1568, 449, 213, 503, 432, 2027, 312, 369, 481, 51, 1676, 1634, 322]]</t>
+    <t>[[262], [17]]</t>
   </si>
   <si>
     <t>h512_ws4_idx4096_inbf16_outbf16_ID264</t>
   </si>
   <si>
-    <t>[[1210], [342, 71, 3102, 200, 3420, 329, 69, 285, 357, 170, 111, 2497, 17, 1685, 243, 216, 365, 446, 27, 2961, 278, 307, 138, 3967, 434, 3751, 488, 333, 359, 464, 493], [224, 3571], [319, 3099, 290, 454, 414, 80, 202, 2292, 3127, 68, 1155, 2785, 158, 440, 117, 490, 200, 331, 370, 484, 3447, 108, 368, 36, 488, 18, 335, 331, 218, 327]]</t>
+    <t>[[2, 332, 442, 1724, 31, 14, 367, 223, 464, 399], [457, 1452, 243, 144, 351, 1529, 153, 273], [1, 199, 239, 75, 285, 401], [112, 35]]</t>
   </si>
   <si>
     <t>h512_ws8_idx8192_inbf16_outbf16_ID265</t>
   </si>
   <si>
-    <t>[[508, 268, 20, 484, 439, 17, 220, 2480, 446, 7788, 121, 856, 170, 117, 238, 390, 354, 368, 26, 318, 6873, 54, 271, 2706, 5821, 110, 275, 50, 171, 308], [424, 238, 7459, 5775, 311, 495, 361, 206, 1118, 416, 2911, 773, 147, 166, 275, 3618, 286, 199, 237, 2767, 319, 399, 5, 225, 32, 440, 283, 412, 136, 350, 460], [5996, 270], [259, 2707, 289, 195, 6215, 85, 12], [60, 7863, 355, 284, 301, 5230, 504, 122, 289, 3, 442, 414, 6139, 215, 2135, 178, 426, 5190, 145, 351, 409], [150, 154, 125, 2257, 105], [281, 308, 447, 326, 167, 97, 69, 115, 137, 483, 861, 6266, 1095, 6, 239, 915, 21, 7982, 506, 2029, 268, 98, 329, 221, 193, 217, 186, 440, 4329, 273, 35, 50], [162, 294, 477, 53, 5484, 299, 26, 5381, 252, 402]]</t>
+    <t>[[263], [1099, 1283, 59, 489, 2041, 269, 95, 224, 471], [476, 291, 143, 365, 387, 145, 1118], [337, 141, 33, 419, 365, 105], [62, 296, 465, 153, 478, 417, 320], [408, 1064, 1056], [329], [322, 27, 313, 295, 64, 399, 339]]</t>
   </si>
   <si>
     <t>h64_ws2_idx2048_infp16_outfp16_ID266</t>
   </si>
   <si>
-    <t>[[209, 235, 366, 144, 1008, 603], [378, 460, 398, 144, 8, 490, 1994, 111, 508, 12, 335, 5, 1308, 276, 1616, 591]]</t>
+    <t>[[66], [409]]</t>
   </si>
   <si>
     <t>h64_ws4_idx4096_infp16_outfp16_ID267</t>
   </si>
   <si>
-    <t>[[10, 392, 397, 3983, 442, 164, 360, 24, 418, 547], [3882, 275, 4036, 85, 425, 252, 322, 3905, 216, 388, 345, 66, 286, 194, 1012, 482], [499, 1800, 480, 119, 297, 1554], [121, 2656, 484, 156, 193]]</t>
+    <t>[[315, 6, 128, 191, 179, 2026, 48, 329, 426], [105, 242, 345, 482, 278], [1975, 190, 776, 336], [277, 21, 109, 78, 172]]</t>
   </si>
   <si>
     <t>h64_ws8_idx8192_infp16_outfp16_ID268</t>
   </si>
   <si>
-    <t>[[6074, 274, 246, 1293, 284, 208, 361, 6057, 4609, 380, 2599, 170, 239, 18, 295, 367, 494, 247, 330, 411, 104, 327, 4819, 337, 305, 491], [76, 487, 192, 3643, 104, 346, 284, 2849, 385, 133, 466, 243, 79, 459, 4107, 276, 368, 76, 102, 79, 6329, 480, 3150, 223], [58, 508, 182, 134, 3053, 392, 146, 250, 7923], [277, 407, 6360, 423, 5731, 298], [466, 8, 16, 302, 93, 106, 5855, 262, 384, 3393, 428, 54, 201, 942, 501, 4951, 9, 203, 193, 2101, 196, 271, 381], [135, 183, 340, 2228, 938, 141, 75, 4445, 1, 299, 7061, 4, 123, 6224, 118, 4628, 283, 460, 293, 10, 296, 498, 5, 75, 58, 43, 84, 344, 346, 3797, 195], [7759, 62, 466, 21], [269, 785, 11, 285, 6524, 125, 5743, 201, 405, 329, 214, 457, 6207, 441, 97, 126, 150, 75, 75, 36]]</t>
+    <t>[[389, 267, 281], [342, 157, 486, 258, 32, 9, 475], [103, 163, 102, 65], [142, 1766, 432, 238], [238, 332, 150], [1874, 283, 265, 497, 286, 322, 340, 26, 258, 26], [1793, 1896, 1514], [465, 32, 31, 216, 1066, 409, 122, 1960, 47, 178]]</t>
   </si>
   <si>
     <t>h256_ws2_idx2048_infp16_outfp16_ID269</t>
   </si>
   <si>
-    <t>[[167, 527, 14, 266, 66, 17, 184, 300, 783, 193, 20, 111, 752, 2026, 108, 167, 1421, 323, 107, 495, 63], [71, 1825, 123, 110, 86, 220, 362, 439, 1795, 248, 1088, 75, 370, 210, 94, 207, 239, 38, 77, 86, 1663, 1636, 128, 472, 258, 423, 1924, 297]]</t>
+    <t>[[302, 479, 161, 356, 229, 72, 428, 793, 436, 148], [449]]</t>
   </si>
   <si>
     <t>h256_ws4_idx4096_infp16_outfp16_ID270</t>
   </si>
   <si>
-    <t>[[3656, 272, 450, 1458, 44, 328, 211, 473, 474, 75, 98, 154, 287, 46, 178, 2071, 52, 456, 136, 2617], [255, 507, 1987, 3237, 33, 238, 15, 52, 4085, 154, 208, 6, 182], [3896, 568, 61, 497, 25, 161, 486, 347, 147, 568, 269, 329, 398, 417, 474], [91, 584, 234, 444]]</t>
+    <t>[[369, 1652, 396, 1299, 437], [263, 95], [481, 384, 1008, 254, 476, 89, 471], [310, 90, 130, 115, 52, 174, 16, 436, 848]]</t>
   </si>
   <si>
     <t>h256_ws8_idx8192_infp16_outfp16_ID271</t>
   </si>
   <si>
-    <t>[[70, 394, 431, 53, 6610, 90, 343, 4864, 219, 71, 175, 4591, 167, 284, 72, 210, 446, 1321, 218, 7233, 105, 506, 484, 296], [482, 154, 6035, 306, 145, 408, 89, 3, 931, 416, 421, 473, 5801, 265], [18, 360, 410, 232, 3915, 22, 6003, 398, 422, 44, 83, 256, 419, 53, 8014], [185, 112, 240, 21, 7303, 284, 239, 449, 157, 362, 278, 490, 504, 160, 4122, 435, 4333, 6, 7475, 173, 38, 6770, 292, 430, 2444, 259, 54, 20, 171], [46, 5780, 142, 111, 15, 492, 457, 334, 370, 96, 120, 383, 246, 6763, 2591, 3059, 41], [2762, 140, 348, 392, 247, 7286, 202, 177, 68, 314, 224, 356, 291, 3910, 254, 324, 347, 354, 3561, 198], [410, 6117, 3210, 431, 317, 439, 128, 305, 340], [3582, 2653, 373, 188, 227, 235, 326, 493, 407, 23, 1842]]</t>
+    <t>[[369, 302, 471, 73, 289, 457, 106], [419, 1633], [194, 60, 377], [27], [360], [80, 969, 125, 248, 1242, 7], [148, 135], [138, 8]]</t>
   </si>
   <si>
     <t>h512_ws2_idx2048_infp16_outfp16_ID272</t>
   </si>
   <si>
-    <t>[[232, 60, 1348, 284, 457, 102, 487, 3, 213, 1653], [1467, 184, 81, 66, 96, 306, 164, 42, 1071, 1528, 322, 85, 337, 20, 215]]</t>
+    <t>[[1182, 68, 73, 84, 229], [4]]</t>
   </si>
   <si>
     <t>h512_ws4_idx4096_infp16_outfp16_ID273</t>
   </si>
   <si>
-    <t>[[2614, 36, 904, 69, 107, 189, 189, 30, 484, 323, 403, 122, 1157, 443, 10, 221, 4010, 204, 310, 154, 3790, 295, 216], [214, 267, 0, 3523, 84, 478, 1400, 14, 2672, 240, 419, 317, 575, 310, 159, 91, 251, 7, 129, 3029, 165], [308, 198, 99, 416, 3708, 3222, 406, 142, 475, 276, 217, 2584, 409, 444, 493, 130, 277, 4076], [1074, 236, 40, 294]]</t>
+    <t>[[475, 170], [30], [130, 197, 354, 1712, 332, 257, 108, 1130, 1250, 473], [364, 367, 281, 82]]</t>
   </si>
   <si>
     <t>h512_ws8_idx8192_infp16_outfp16_ID274</t>
   </si>
   <si>
-    <t>[[485, 451, 364, 290, 6, 249, 290, 474, 1314, 5721, 212, 508, 239, 295, 425, 119, 6708, 10, 4285, 371, 472, 323, 377, 320, 6386, 481, 2, 1089, 27, 1716, 355, 46], [476, 277, 4276, 6, 457, 1768, 492, 153, 316, 7136, 338, 356, 232, 168, 153, 220, 7765, 471], [5516, 126, 1, 105, 1441, 464], [5473], [229, 885], [376, 42, 221, 4342, 7875, 298, 232, 323, 428, 5835, 299, 157, 400], [119, 370, 104, 172, 443, 354, 265, 1279, 27, 33, 189, 191, 1012, 452, 117, 164, 299, 459, 350, 390, 7224, 3219, 6819], [415, 138, 7786, 389, 315, 419, 483, 2188, 482, 2531, 352, 476, 44, 1, 358, 277, 501, 3711, 390]]</t>
+    <t>[[16, 86, 237, 330, 85, 287, 413, 128, 479], [836, 34, 55, 236, 472, 76, 348], [287, 50, 1494, 246, 227, 453, 368, 112, 265], [78, 7, 8, 1907], [252, 639, 383, 107, 366, 421, 391], [386, 234, 394, 436, 1272, 207, 427], [393, 339, 9, 268, 392], [216, 168, 9, 510, 462]]</t>
   </si>
   <si>
     <t>h256_ws16_idx65536_random_inbf16_outbf16_ID275</t>
   </si>
   <si>
-    <t>[[308, 14, 11034, 88], [346, 218, 452, 384, 158, 250, 35, 226, 397, 266, 236, 4945, 228, 40368, 40716, 238, 54898, 183, 103], [488, 272, 81, 13650, 246, 286, 509, 16606, 326, 312, 48, 64118, 254, 442, 167, 166, 443, 59828, 37847, 417, 468], [17786], [149, 276, 420, 325, 118, 15, 506, 38281, 64518, 29], [324, 6, 42750, 6079, 12, 402, 151, 405, 220, 13, 25, 52, 479, 113, 7957, 46513, 434, 299, 442, 223, 375, 27127, 439], [435, 259, 507, 423, 43, 415, 11824, 112, 382, 30740, 16559, 454, 291], [47234, 63492, 48120, 166, 327, 328, 125, 326, 64020, 92, 60137, 359, 381, 42340, 399, 468, 41, 353, 199, 63, 7, 56, 185, 323, 160, 156, 52356, 387, 401, 308, 90, 488], [69, 139, 155, 108, 184, 58272, 61, 37119, 353, 68, 459, 64755, 240, 20774, 482, 317, 136], [91, 252, 59907, 322, 20036, 100, 237, 509, 25760, 456, 17, 365], [70, 360, 22281, 156, 404, 16785, 266, 170, 265, 240, 19, 20, 26604, 249, 365, 45, 10836, 25, 319, 374, 22443, 377, 45, 32], [24, 109, 42524, 33555, 318, 408, 413, 490, 505, 184, 40324, 184, 494, 71, 143, 327, 8662, 65, 19109, 310, 22, 176, 261, 82, 311, 138, 15273], [108, 3722, 141, 60077, 460, 313, 59082, 238, 203, 207, 309, 291, 502, 54262, 367, 145, 60, 138], [209, 5966, 327, 49, 444, 45956, 335, 89], [55, 12353, 279, 392, 162, 31, 61687, 492, 500, 202, 351, 347, 197, 48074, 54683, 226, 360, 183, 430, 229], [167, 142, 12681, 47, 333, 19300, 451, 390, 442, 23094, 334, 427, 366, 88]]</t>
+    <t>[[1524, 241, 143, 196, 330, 311, 242, 339, 181, 4], [230, 495, 341], [352, 1756, 293, 115, 88, 43, 261], [930, 493, 231, 502, 283, 105], [480, 15, 1035, 123, 29, 270, 22, 29, 22, 101], [398, 287, 112, 25, 803, 501, 342, 41, 48], [416, 2046, 289, 424, 481, 428, 422, 222, 107, 1629], [324, 231, 1456], [383, 1534, 1205, 1771, 315, 507, 510, 311, 488], [5, 1013], [359], [503, 267, 9, 405], [282, 23, 402, 1008, 1286, 84], [1420, 1168, 362, 436, 147, 266, 1514, 655, 282, 453], [1574, 314, 86, 863, 220, 308, 41, 28], [408]]</t>
   </si>
   <si>
     <t>h256_ws2_idx4096_random_infp32_outfp32_ID276</t>
   </si>
   <si>
-    <t>[[289, 1731, 508], [111, 3937, 485, 55, 306, 40, 1326, 148, 780, 432, 500, 874, 282, 477, 79, 112, 499]]</t>
+    <t>[[468, 265, 399, 482, 15, 197, 462], [819]]</t>
   </si>
   <si>
     <t>h256_ws16_idx16384_random_inbf16_outbf16_ID277</t>
   </si>
   <si>
-    <t>[[370, 263, 11802, 199, 4184, 182, 6156, 20, 431, 76, 482, 507, 15423, 357, 206, 337, 161, 324, 4472, 95, 105, 279, 73], [477, 6406, 499, 3, 95, 64, 302, 15036, 59, 432, 368, 376, 7514, 229], [13713, 121, 272, 116, 365, 5054, 405, 217, 408, 17, 227, 134, 265, 3498, 127, 12928], [54, 439, 472, 197, 261, 14337, 185, 178, 25, 357, 313, 3018, 366, 223, 4926, 11441, 365, 183, 135, 13716, 209, 435], [329, 6187, 331], [11534, 469, 180, 34, 11980, 297, 5, 306, 361, 313, 6380, 110, 342, 424, 339], [84, 484, 4573, 5599, 98, 339, 445], [29, 468, 4811, 124, 7418, 169, 5, 456, 15011, 508, 235, 203, 215, 1540, 229, 462, 452, 404, 188, 6813, 457, 257, 42, 2, 375, 115, 3094, 257, 501], [167, 443, 9807, 156, 12413, 454, 216, 3576, 300, 141, 5370, 115, 411, 442, 80, 13339, 210, 8218, 113, 509, 384, 260, 345, 510, 199, 248, 407, 490, 301, 41, 5545], [339, 512, 48, 99, 384, 24, 299, 6126, 196, 40, 27, 16217, 59, 37, 17, 344, 362, 479, 128, 15121, 255, 8335, 157, 393, 1115, 175, 286, 4473, 67, 211, 486, 8712], [261, 359, 212, 12590, 58, 333, 350, 431, 16206, 240, 357, 54, 355, 284, 71, 331, 376, 9965, 13748, 356, 2123], [2585], [14233, 223, 393, 144, 10753, 143, 18, 411, 13, 204, 268, 318, 260, 275, 15743, 240, 151, 72, 129, 429, 3601, 9600, 14191, 93, 42, 8, 453, 114, 63, 225], [459, 470, 14980, 358, 416, 14, 288, 11028, 5385, 325, 84, 329, 71], [8557, 17, 16350, 12004, 7603, 96, 416, 7629, 311, 315, 365, 185, 27, 14213, 178, 152, 412, 203, 430, 206, 496, 25, 82, 474, 306, 316], [203, 377, 275, 14495, 16010, 217, 510, 496, 22, 379]]</t>
+    <t>[[118, 95, 150, 31, 344, 152], [865, 82, 84, 179, 97, 428, 155, 450], [293, 1853], [1949, 103, 13], [159, 1020], [475, 224, 24, 160, 386], [471, 733], [1959, 506], [74, 1346], [466, 116, 47, 110], [292, 54], [21, 1829, 1867, 506, 1371, 412], [144, 344, 131, 88], [465], [171, 76, 199, 189, 16, 337, 432, 193, 142, 290], [1590, 506, 1412, 411, 71, 1546, 121, 389, 289, 389]]</t>
   </si>
   <si>
     <t>h128_ws16_idx8192_random_inbf16_outbf16_ID278</t>
   </si>
   <si>
-    <t>[[262, 201, 408, 2302, 341], [135, 448, 4479, 862, 426, 329, 52, 208, 223, 181, 74, 7472, 3625, 154, 4674, 275, 210, 179, 322, 135, 290, 265, 278, 404, 489], [54, 4273], [4168, 482, 3811, 7, 7292, 289, 397, 22, 416, 48, 414, 167, 209, 179, 330, 146, 2625], [5597, 319, 450, 68, 500, 269, 329, 43, 32, 342, 211, 7913, 1393, 480, 6, 376, 339, 5288, 232], [288, 164, 466, 121, 117, 6611, 95, 94, 244, 140, 435, 381, 254, 473, 127, 4161, 182, 5, 186, 6929, 405, 6063, 3617, 461], [341, 4622, 1276, 338, 4284, 419, 242, 492, 372, 342, 306, 169, 224, 3060, 402, 503, 323, 111, 7274, 265, 268, 86, 2544, 224, 495, 224, 466, 349, 1514, 369, 465, 418], [263, 6041, 286, 144, 266, 106, 430, 370, 307, 3311], [146, 154, 6597], [436, 6510, 741, 4410, 91, 69, 210, 203, 3911, 179, 38, 505, 219, 244, 189, 88, 478, 237, 422, 171, 4824, 157, 338], [369, 2238, 56, 1132, 466, 252], [257, 4590, 116, 6241, 182, 209, 46, 3709, 5260, 228, 347, 394, 335, 119, 204, 263, 165, 439], [0, 429, 28, 216, 47, 277, 93, 415, 168, 46, 5331, 385, 4340, 72, 145, 335, 197, 487, 2618, 2021, 258, 500, 5008, 4278, 414, 371, 39], [109, 103, 477, 357, 197, 496, 3792, 6825, 292, 4571, 260, 319, 282], [15, 184, 218, 220, 251, 540, 6450], [3066, 138, 497, 31, 387, 13, 255, 356, 335, 7879, 4159, 36, 500, 4581, 165, 5244, 108, 416, 135, 226, 362, 312, 89, 409, 1829, 174, 194, 165]]</t>
+    <t>[[770, 272, 504], [94, 112, 436, 172, 1798, 279, 342, 330, 1135, 362], [307, 98, 1485, 570], [178, 1631, 190, 417, 388, 1219, 13], [348, 73, 395, 132, 1252, 67, 227, 260, 250], [13, 446, 435, 476, 488, 469], [263, 446, 401, 279, 369, 119], [391], [340, 111, 360, 55, 419, 237], [311, 96, 151, 205], [141], [507, 130, 148, 51], [70], [109, 99, 176, 1798, 287], [397, 48, 439, 259, 94, 464, 109, 247, 1298], [482, 330, 357, 505, 492, 264, 338]]</t>
   </si>
   <si>
     <t>h128_ws2_idx8192_random_infp32_outfp32_ID279</t>
   </si>
   <si>
-    <t>[[346, 486, 58, 238, 6183, 174, 90, 67, 482, 47, 29, 144, 5471, 4557, 312, 373, 4910, 494, 3129, 68, 274, 362, 405, 329, 357], [195, 2362, 134, 287, 119, 141, 3110, 213, 224, 105, 359, 499, 6427, 107]]</t>
+    <t>[[390, 410, 419, 313, 158, 156, 369, 220], [183]]</t>
   </si>
   <si>
     <t>h128_ws16_idx32768_random_inbf16_outbf16_ID280</t>
   </si>
   <si>
-    <t>[[289, 504, 445, 32193, 16802, 4609, 365, 72, 396, 271, 165, 163, 70, 417, 409, 424, 12930, 52], [419, 442, 6, 272, 23416, 23703, 19666, 6538, 477, 208, 276, 244, 156, 341, 29, 179], [495, 33, 7853, 387, 24237, 391, 397, 182, 202, 107, 14883, 19369, 432, 21899, 26, 89, 277, 435, 410, 5990, 380, 144, 450, 506, 134, 317, 267, 200, 407], [483, 425, 451, 269, 36, 1346, 16544, 323, 238, 533, 30056, 262, 8062, 30268, 154, 509, 201, 235, 394, 3, 340, 123, 292, 50, 459, 472, 46], [439, 30613], [268, 28418, 21130, 368, 244, 384, 155, 206, 417, 18721, 145, 468, 275], [159, 16, 27541, 455, 23936, 94, 4, 308, 96], [48, 294, 60, 371, 188, 333, 379, 250, 185, 236, 310, 122, 313, 22, 205, 9503, 411, 22244, 8411, 17611, 12318, 466, 184, 379, 24646, 243, 11084, 405, 469, 248, 308], [197, 161, 3902], [16424, 53, 91, 107, 264, 27, 175, 254, 27509, 280, 148, 5, 4851, 154, 149, 213, 432, 12359, 266, 253, 10324, 110, 100], [352, 63, 581, 258, 6398, 17895, 219, 350, 402, 35, 389, 158], [367, 71, 406, 432, 309, 323, 356, 129, 365, 148, 422, 613, 131, 383, 1448, 38, 88, 503, 16044, 348, 245, 16890, 176, 25844, 160, 16671, 507, 156, 300, 450], [23023], [300, 394, 17059, 22], [28, 100, 26607, 422, 416, 2011], [16585, 21, 332, 29, 128, 2301, 84, 167, 296, 232]]</t>
+    <t>[[123, 497, 337, 496, 1165, 378], [129, 466, 279, 494, 196, 100, 214, 329, 407], [252, 191], [243], [299, 118, 1194, 145, 179, 190, 188], [227, 1419, 474, 1471, 442, 77, 491, 294], [451], [302, 116, 277, 432, 288, 450, 492, 204, 318, 462], [9, 387, 1052, 243], [303, 183, 224, 59, 437, 298], [359, 117], [206, 1096, 340, 403, 842, 261, 136, 299, 329], [368, 391], [102, 1383, 1265, 397, 259, 129, 495, 1324, 242], [409, 1193, 1562, 409, 254, 35, 1008, 126, 365, 40], [60, 163, 505, 113, 361, 1027, 130]]</t>
   </si>
   <si>
     <t>h64_ws8_idx16384_random_infp32_outfp32_ID281</t>
@@ -911,25 +911,25 @@
     <t>[[2048, 64]]</t>
   </si>
   <si>
-    <t>[[8957, 58, 177, 138, 461, 266, 5439, 244, 461, 246, 356, 159, 5665, 237, 25, 212, 404, 305, 4413, 10695, 86], [475, 384, 348, 34, 280, 2507, 11807, 7328, 447, 43, 352, 44, 17, 15257, 305, 84, 236, 3145, 95, 438, 7322, 12441, 136, 324, 154, 282, 34, 11, 302, 268, 10], [468, 3112, 504, 183, 202, 150, 245, 288, 370, 7731, 2991, 499, 78, 256, 412, 163, 13683, 403, 15097, 442, 177, 394], [11533, 171], [144, 447, 454, 657, 407, 6789, 225, 225, 248, 451, 7844, 7, 480, 51, 11607, 68, 497], [7758, 292, 331, 3580, 10291, 362, 190, 13737, 506, 102, 20, 7632, 324, 123, 46, 218, 118, 14068, 356, 442, 184, 362, 283, 317, 268, 141, 193, 357], [339, 244, 234, 184, 160, 31, 299, 79, 1732, 259, 11971, 416, 8066, 5895, 331, 312, 1483, 80, 8477, 487, 209, 245, 175, 261, 59, 281], [500, 37, 137, 214, 449, 155, 128, 445, 6377, 11560]]</t>
+    <t>[[116, 499, 1867, 50, 191, 209], [239, 155, 509], [147], [4, 461, 421], [259, 134, 428, 347], [211, 415, 240, 208, 271, 236, 180, 303, 331], [185, 445, 62, 1467, 248, 388, 1111, 244, 297], [107, 387, 76, 61, 2, 389, 1788, 443]]</t>
   </si>
   <si>
     <t>h64_ws16_idx32768_random_inbf16_outbf16_ID282</t>
   </si>
   <si>
-    <t>[[119, 446, 0, 150, 503, 466, 233, 82, 386, 113, 32619, 423, 440, 23605, 24905, 29875, 17, 116, 178, 158, 159, 37, 435, 103, 10597, 13526, 432, 143, 240], [137, 325, 14018, 410, 39, 22, 116, 93, 231, 19328, 20370, 14505, 327, 496, 183, 13850, 202, 6, 209, 368, 2492, 31502, 304, 285, 354, 60, 400, 69, 498, 3, 503], [32679, 289, 13701, 161, 279, 22968, 241, 10266, 507, 416, 485, 13039, 203, 476, 439, 320, 30, 412, 73, 278, 429, 311, 9, 46, 72, 65, 14152, 119], [259, 358, 412, 367, 25106, 3003, 405, 54, 447, 393, 31542, 102, 350, 378, 204, 72, 254, 88, 187, 302, 6573, 252, 27488, 45, 369], [500, 210, 388, 271, 456, 4, 395, 144, 509, 29, 476, 8976, 446, 455, 98, 30217, 14012, 356, 131, 15, 181, 487, 34, 306, 259, 265, 243, 12348, 455, 11242, 15656, 27335], [31923, 442, 15, 56, 195, 17558, 371, 112, 135, 84, 378, 496, 357, 2194], [285, 96, 18571, 29, 32, 310, 388, 122, 3, 89, 95, 137, 7629, 20093, 125, 147, 22185, 290, 257, 303, 9156], [400, 19562, 401, 298, 86, 476, 11269], [8693], [407, 452, 2742, 137, 481, 437, 18, 157, 28945, 448, 270, 244, 313, 256, 396, 14412, 117, 22718, 356, 371, 18435, 291, 198, 98, 133, 38, 9700, 214, 421, 228], [294, 29304, 378], [29469, 407, 453, 265, 258], [20758, 129], [118, 25, 28324, 483, 7162, 502, 361, 352, 210, 20, 372, 450, 11284, 331, 122, 42, 17799, 1051, 161, 62, 115, 17, 16471, 251, 339, 52], [278, 390, 255, 461, 488, 248, 29611, 20002, 12851, 209, 98, 256, 152, 255, 193, 441, 322, 16039], [88, 458, 0, 106, 31973, 162, 443, 11668, 322, 512, 500, 71, 18903, 40, 332, 233, 8545]]</t>
+    <t>[[417, 115, 78], [25], [1966, 372, 257, 257, 441], [453, 82, 557, 160, 313, 442], [1166, 687], [5, 1495, 116, 353, 76, 132, 64, 32], [533, 502, 302, 265, 201, 183, 129, 347, 1944], [870, 152, 121, 169, 623, 254, 221, 301, 285, 460], [20, 226], [332, 248, 403, 986, 376, 147], [478, 202, 254, 158, 474, 72, 786, 535, 253], [84, 1378], [22, 330, 327, 1729, 270, 1054, 1824, 280, 209, 295], [264, 32, 333, 1890, 1937], [484, 1137, 366, 418, 588, 2, 214, 337], [106, 493]]</t>
   </si>
   <si>
     <t>h512_ws4_idx4096_random_infp16_outfp16_ID283</t>
   </si>
   <si>
-    <t>[[332, 346, 524, 465, 243, 249, 65, 122, 3276, 2218, 126, 373, 371, 486, 267], [4058, 424, 967, 8, 220, 49, 109], [57, 470, 367, 2773, 2608, 139, 281, 422, 2882, 147, 343, 257, 156, 214, 205, 281, 419, 142, 215, 3846, 383, 305, 268, 41, 323, 466, 130, 1599, 2793, 1603, 11, 214], [4, 171, 503, 384, 3080, 254, 177, 2861, 375]]</t>
+    <t>[[381, 228], [1764, 14, 195, 413, 331, 203, 189, 472, 265, 137], [1301, 69, 488, 85, 1002, 226, 1819, 189, 1943, 846], [959]]</t>
   </si>
   <si>
     <t>h64_ws4_idx4096_random_infp32_outfp32_ID284</t>
   </si>
   <si>
-    <t>[[3495, 273, 2345, 240, 71, 157, 31, 113, 61, 41], [23, 3746], [216, 224, 261, 456, 470, 105, 1031, 3696], [337, 150, 474, 3545, 3512, 3388, 3769, 29, 76, 88, 209, 3815, 232, 465, 417, 15, 140, 502, 77, 181, 459, 508]]</t>
+    <t>[[433, 7, 720, 215, 223, 511], [114, 205, 1541, 102, 98, 108, 89, 99, 83], [469, 198, 491, 472, 247, 500, 371, 1530], [42, 491, 131, 771, 4, 172]]</t>
   </si>
   <si>
     <t>h512_ws4_idx8192_random_infp16_outfp16_ID285</t>
@@ -938,7 +938,7 @@
     <t>[[2048, 512]]</t>
   </si>
   <si>
-    <t>[[418, 124, 297, 2166, 495], [122, 1889, 69, 17, 420, 686, 457, 296, 6022, 420, 180, 5573, 315, 334, 186, 449, 248, 402, 132], [177, 1344, 341, 121, 189, 436, 34, 230, 463, 608, 373, 251, 448, 81, 5384, 470, 117, 271, 428, 473, 218, 346, 7712, 60, 2300, 80, 505, 251, 4169, 72], [235, 345, 327, 90, 7769, 172, 411, 111, 151, 310, 400, 6656, 1973]]</t>
+    <t>[[311, 1590, 328, 214, 1206], [493, 374, 10, 342, 504], [135, 437, 467, 1178, 439, 66, 1795, 185, 233, 497], [77, 291, 1419, 299, 149, 123]]</t>
   </si>
   <si>
     <t>h512_ws4_idx16384_random_infp16_outfp16_ID286</t>
@@ -947,25 +947,25 @@
     <t>[[4096, 512]]</t>
   </si>
   <si>
-    <t>[[1517, 11835, 236, 160, 485, 439], [245, 101, 103, 14, 328, 1848, 428, 433, 243, 5099, 157, 81, 821], [492, 270, 345, 240, 2303, 14517, 103, 232, 388, 215, 385, 216, 289, 14857, 437, 126, 106, 1869, 373, 7475, 246, 447, 470, 400, 9445, 30], [12745]]</t>
+    <t>[[1247, 1187, 32, 80, 13, 59, 251], [380, 138], [504, 437, 92, 291, 314, 511], [1280, 215, 457, 160, 327, 906, 232, 449]]</t>
   </si>
   <si>
     <t>h128_ws2_idx2048_random_inbf16_outbf16_ID287</t>
   </si>
   <si>
-    <t>[[279, 1620, 250, 472, 94, 56, 360, 211, 897, 978, 660, 179, 107, 126, 245, 474, 25, 212, 97, 1151, 195, 500, 384, 1553, 398, 126], [33, 462, 189, 547, 245, 491, 150, 293, 245, 1666, 1456, 225, 1772, 175, 85, 214, 339, 447, 163, 391, 81, 379, 369, 1616, 476]]</t>
+    <t>[[356, 444, 451], [420, 93, 258, 8, 52, 1366, 226]]</t>
   </si>
   <si>
     <t>h256_ws8_idx8192_random_infp32_outfp32_ID288</t>
   </si>
   <si>
-    <t>[[180, 415, 313, 8178, 4038, 82, 247, 3206, 439, 480, 14, 261, 258], [4828, 474, 16, 82, 6512, 507, 883, 429, 31, 503, 81, 340, 211, 397, 289], [36, 65, 149, 277, 112, 19, 12, 5133, 256, 57, 130, 1346, 393, 4421, 312, 6367, 99, 1468, 202, 90, 266, 7, 337, 428, 362, 229, 401, 6209, 195, 22], [187, 4851, 502, 228, 127, 6184, 154, 355], [128, 127, 263, 5421, 4205, 377, 5552, 309, 404, 180, 353, 7920, 2678, 19, 372, 287, 155, 364, 754, 49, 427, 290, 457, 345, 22, 97, 30, 485, 162], [5515], [7802, 5659, 279, 412, 477, 44, 512, 21, 2371, 376, 212], [7947, 57, 2320, 140, 207, 75, 268, 152, 157, 363, 133, 8154, 62, 0, 354, 7714, 150, 3309, 24, 273, 336, 270]]</t>
+    <t>[[67, 771, 451, 313, 1914, 89, 7, 397, 405, 173], [1284, 503], [2028, 511, 562, 47, 382, 70, 1663, 5], [960, 46], [337, 288, 364, 359, 338], [449, 97, 303, 247, 357], [220, 392], [83, 117, 93, 30, 1260, 1998]]</t>
   </si>
   <si>
     <t>h128_ws16_idx16384_random_infp16_outfp16_ID289</t>
   </si>
   <si>
-    <t>[[283, 171, 28, 218, 3690, 78, 282, 447, 212, 209, 14286, 3702, 21, 234, 63, 373, 333, 50, 324, 9063, 434, 14, 456, 4394, 507, 7356], [329, 485, 25, 1033, 205], [14328, 285], [9191, 159, 497, 6461, 359, 238, 413, 174, 188, 492, 14453, 472], [327, 86, 428, 9477, 5108, 152], [242, 345, 411, 8122, 146, 233, 200, 8515, 9437, 450, 495], [915, 9443, 110, 109, 163, 388, 382, 66, 103, 14556, 490, 187, 97, 175, 337, 356, 454, 436, 7347], [133, 480, 4666, 3856, 101, 305, 446, 210, 200, 232, 219, 1956, 500, 255, 36, 25, 497, 451, 10214, 9265, 132, 15458, 164, 43, 101, 499, 135, 58, 205, 491], [112, 488, 2228, 499, 604, 485, 132, 359, 343, 220, 84, 7, 5743, 259, 251, 54, 420, 12223, 43, 92, 88, 430, 9116, 340, 128, 272, 3727, 13], [923, 300, 12598, 374, 449, 11389, 441, 176, 3, 433, 480, 404, 390], [92, 464, 208, 2025, 464, 494, 381, 7164, 53, 248, 223, 421, 245, 209, 8260, 6510], [138, 214, 8818, 33, 339, 490, 354, 427, 219, 468, 247, 15676, 104, 5540, 127, 11946, 14969, 356, 195, 223, 357], [6637], [7522, 5048, 5992, 420, 178, 74, 5, 362, 148, 415, 26, 137, 345, 313, 3068, 91, 15, 6, 123, 429, 7501, 400], [494, 26, 15626, 122, 72, 12964, 50, 5573, 11324, 270, 3612, 9, 149, 81, 452, 289, 19, 247, 297, 317, 348, 6357, 267, 171, 76, 429, 396], [2954, 455, 433, 164, 70, 160, 22, 175, 249, 492, 110, 410, 306, 227, 107, 414, 8447, 6334, 333, 507, 3919, 30, 105, 479, 5058, 2789, 55, 42, 258, 11306, 350]]</t>
+    <t>[[453, 93, 374, 189, 142, 122, 345, 1643, 53], [486, 373, 1509, 386, 467, 99], [132, 1737, 351, 234, 310], [1821], [1290, 277, 31, 376, 164, 44, 101], [450, 221, 10, 25, 102, 371, 210], [301, 444, 504, 1139, 84, 284], [183, 367, 85, 191, 382, 67], [440, 1813, 198, 1032], [253, 200, 325], [128, 14, 85, 204, 74, 403, 413, 178], [437, 421, 123, 418, 313, 116, 418, 509, 322], [464, 50, 213], [306, 349, 331, 494, 1909, 499, 230, 175], [57, 190], [195]]</t>
   </si>
   <si>
     <t>h512_ws16_idx8192_random_inbf16_outbf16_ID290</t>
@@ -974,43 +974,43 @@
     <t>[[512, 512]]</t>
   </si>
   <si>
-    <t>[[326, 1223, 114], [454, 5128, 101, 461, 709, 10, 209, 304, 261, 432, 177, 348, 106, 2129, 305, 1374, 480, 372, 228, 3374, 372, 391, 1201, 429, 305, 318, 350, 303, 144], [294, 3609, 486, 413, 121, 5638, 5563, 255, 330, 55, 359, 454, 485], [65, 318, 419, 547, 225, 442, 7914, 63, 461, 41], [115, 293, 495, 6384, 219, 147, 4435, 332, 2411, 70, 167, 274, 282, 475, 417], [104, 728, 5205, 264, 99, 254, 452, 249, 332, 1284, 442], [23, 5059, 1048, 6, 454, 115], [262, 136, 4378, 2677, 253, 176, 147, 5373, 203, 492, 37, 3562, 378, 302, 328, 478, 335, 12, 134, 7734, 890, 211, 278, 79, 264, 456, 142, 241, 2698, 14, 48, 459], [441, 510, 2784, 4981, 62, 207, 6508, 271, 97, 595, 144, 149, 40, 505, 299, 355, 302, 219, 199, 431, 377, 215, 8086, 301, 260], [485, 5, 449, 6730, 72, 32, 5024, 240, 2, 1816, 92, 234, 308, 96, 363, 3449, 483, 19, 361], [2315, 267, 5786, 271, 5692, 298, 495, 30, 411, 505, 220, 441, 116, 159, 246, 259, 476, 314, 158, 3824, 252, 358, 7785, 336, 949, 488, 410, 202], [419, 329, 125, 57, 270, 481, 236, 444, 7822, 4929, 296, 0, 418, 112, 3354, 3338], [3702, 232, 288, 111, 76, 201, 4288, 51, 422, 338, 7873, 97, 484, 480, 3122, 394, 132, 341, 281, 32], [466, 8016, 424, 337, 622, 34, 299, 17, 3, 336, 6722, 341, 452, 125, 208, 241, 2416, 338, 12, 100, 172, 212, 1128], [5374, 462, 96, 452], [6889, 153, 4796, 173, 452, 14, 171, 98, 443, 391, 236, 133, 275, 371, 3280, 242, 279, 363, 73, 201, 7828, 129, 2393, 481]]</t>
+    <t>[[1827, 239, 45, 29, 359, 239, 437, 249, 1807], [500, 1659, 1356], [47, 396, 274, 116, 168, 465, 408, 1709, 40, 93], [91, 253, 206, 399, 207, 363, 1950, 29, 335, 109], [413, 863, 244, 442, 367, 105], [382, 113, 35, 189], [79, 156, 114, 746, 303], [478, 1460], [1563, 176, 371, 481], [511, 427, 1797, 195, 231, 41, 237, 324, 248, 1250], [254, 29, 274, 110, 74, 326, 317, 458, 944], [103, 245, 1929, 164, 102, 222, 443, 184, 715, 1966], [391, 304, 506, 374, 204, 483], [1180], [45, 290, 312], [491, 294, 179, 33, 400, 450]]</t>
   </si>
   <si>
     <t>h512_ws8_idx4096_random_inbf16_outbf16_ID291</t>
   </si>
   <si>
-    <t>[[172, 8, 228, 114, 258, 335, 253, 683, 76, 69, 4045, 423, 272, 486, 106, 388, 267, 25, 444, 170, 2042, 184, 2484, 240, 2053, 2221], [18, 144, 2115, 7, 216, 1405, 374], [268, 884, 39, 349, 1000, 252, 374, 208, 86, 485, 346, 882, 115, 3403, 110, 299, 403, 2153, 382, 330, 37], [355, 304, 365, 48, 3701, 210, 125, 327, 433, 465, 3130, 178, 405, 60, 327, 459, 2199, 494, 493, 3956, 243, 9, 1613], [430, 429, 4034, 1625, 449, 203, 173, 463, 80, 353, 2736, 179], [237, 37, 890, 421], [1396], [292, 1083, 845, 356, 1558, 344, 463, 312, 451, 302, 302, 108, 11, 155, 8]]</t>
+    <t>[[54, 1808], [19, 228, 251, 386, 54, 180, 319, 5, 172, 28], [290, 169, 145, 345, 1893, 6], [1899, 1305, 189, 281, 446], [466, 65, 23, 41, 670, 242, 386, 397], [639, 91, 194, 139, 1, 306], [490], [11, 384, 3, 13]]</t>
   </si>
   <si>
     <t>h64_ws2_idx4096_random_inbf16_outbf16_ID292</t>
   </si>
   <si>
-    <t>[[273, 2074, 1619, 434, 507, 315, 48, 3419, 2224, 467, 157, 213, 407, 182, 320, 16, 18], [227, 1779, 17, 195, 351, 326, 214, 2078, 1397, 274, 192]]</t>
+    <t>[[213, 272, 226, 469, 490], [183, 59, 161, 65]]</t>
   </si>
   <si>
     <t>h256_ws4_idx16384_random_inbf16_outbf16_ID293</t>
   </si>
   <si>
-    <t>[[12692, 336, 477, 424], [170, 9, 254, 46, 463, 25, 5895, 9567, 1060, 74, 166, 143], [8235], [1724, 99]]</t>
+    <t>[[391, 410, 439, 337, 75, 255, 446, 23, 405, 121], [159], [206, 733, 482, 366, 495, 471, 434], [79, 17, 903, 357, 69, 176, 285, 387, 188]]</t>
   </si>
   <si>
     <t>h64_ws8_idx16384_random_infp16_outfp16_ID294</t>
   </si>
   <si>
-    <t>[[262, 416, 293, 138, 10851, 14114, 115, 191, 93, 120, 295, 9426, 215, 346, 10, 426, 477, 59, 191, 212, 397, 13265, 229, 217, 7692, 45, 5162], [72, 154, 285, 493, 15, 137, 241, 14569, 422, 178, 15848, 14, 77, 65, 95, 399, 379, 4214, 14270, 3882, 257, 54, 90, 230, 11129, 180, 257, 302, 317, 504], [176, 5408, 489, 270, 176, 1, 467, 455, 60, 131, 1249, 19, 257, 479, 420, 414, 103, 403, 78, 15815, 233, 7411, 80, 2151, 352], [99, 8776, 93, 169, 347, 68, 11760, 411, 216], [11628, 416, 473, 50, 251, 9270, 442, 391, 391, 398, 41, 69, 36, 18, 167, 427, 13101, 471, 10784, 253, 363, 257, 14754, 36], [665, 319, 340, 367, 151, 9768, 9512, 438, 244, 398, 478, 270, 477, 405, 174, 2592, 5826, 15146, 412, 99, 143, 405, 108, 239, 314, 181], [99, 3689, 349, 7131, 438, 487, 44, 267], [13609, 283, 228, 135, 357, 126, 404, 284, 24, 32, 16333, 409, 784]]</t>
+    <t>[[1321, 310, 474, 494], [424, 376], [84, 26, 1681], [79, 39, 276], [43, 383, 243, 411, 315, 376], [485, 364, 386, 1184, 270, 101, 471], [317, 430, 359, 372, 937], [601, 293, 476, 4, 179, 222, 384, 123]]</t>
   </si>
   <si>
     <t>h512_ws16_idx65536_random_infp16_outfp16_ID295</t>
   </si>
   <si>
-    <t>[[501, 310, 222, 28053, 46388, 272, 385], [341, 18903, 56, 3, 418], [313, 485, 280, 62419], [200, 2016], [5, 290, 166, 92, 115, 54, 40969, 46, 416, 62805, 60712, 148, 158], [404, 402, 42880, 65, 390, 129, 387, 170, 38775, 406, 80, 23808, 238, 286, 35, 487, 409, 9561, 88, 181, 9661, 138, 72, 306, 31, 324, 74, 341, 370, 35289], [3867], [243, 85, 34770, 148, 43261, 10, 103, 148, 482, 39, 5, 14, 497, 3332, 30, 171, 501, 37, 3944, 205, 132, 85, 254, 173, 8285, 23241, 202, 457, 284], [468, 40011, 271, 137, 320, 194, 7525, 477, 472, 414], [155, 147, 55825, 512, 311, 457, 469, 145, 28196, 768, 399, 365, 34278, 98, 291, 188, 351, 393, 134, 354, 374, 27656, 172, 288], [331, 108, 161, 94, 61488, 116, 401, 346, 8927, 184, 307, 212, 295, 71, 97, 272, 13098, 213, 182, 13, 10882, 41, 120, 36445, 281, 81, 86, 51550], [59168, 486, 366, 338, 139, 43642, 11, 478], [440, 444, 85, 335, 52055, 298, 18429, 50, 33, 15556, 213, 244], [442, 16162, 172, 460, 49, 409, 508, 63, 21, 64008, 5259, 237, 417, 470], [264, 492, 6181, 359, 202, 426, 172, 27892, 335], [6, 11, 115, 198, 462, 376, 31914, 163, 181, 286, 141, 199, 97, 427, 350, 364, 7146, 9742, 51627, 51982, 478, 99, 464]]</t>
+    <t>[[1312, 72, 150, 1951, 1891], [454, 485, 370], [348, 331, 155], [1781, 44, 499, 77, 1046, 394], [1093, 90, 49, 506, 275, 369, 1602, 66, 1214], [57, 2026, 465, 351, 69], [276, 152, 286, 280], [103, 375, 434], [44, 325, 1531, 74, 419, 293, 273, 440, 95], [497, 1870, 130], [4, 7, 506, 121, 267, 475, 68, 456, 30], [227, 397, 190, 1233], [309, 339, 157, 1964, 1305], [463, 372, 79, 133, 436, 388, 314, 327], [80, 492, 455, 510, 38, 480, 219, 152], [111, 733, 150, 51, 711, 439, 320]]</t>
   </si>
   <si>
     <t>h64_ws4_idx4096_random_infp32_outfp32_ID296</t>
   </si>
   <si>
-    <t>[[182, 10, 3740, 167, 369, 459, 167, 440, 69, 35, 1871, 3179, 2549, 271, 251, 213, 359, 295, 306, 359, 3705, 3287, 359, 56, 408, 56], [116, 3826, 320, 3452, 495, 373, 60, 186, 245, 42, 233, 462, 238, 416, 145, 3686, 2882], [315, 3760, 360, 302, 103, 64, 461, 310, 42, 108, 4014, 26, 381, 377, 376, 249, 384, 1206, 783, 3756, 171, 336, 434, 3811, 107, 292, 450], [401, 143, 59, 98, 348, 428, 1560, 303, 442, 373, 371, 182, 321, 14, 2, 65, 161, 2126, 502, 486, 114, 3945, 3395, 176, 121, 2724, 307, 569, 330, 1471, 345]]</t>
+    <t>[[136, 236, 475, 1526, 34, 252, 1125, 2043], [21, 454, 358, 218, 252, 291, 1385, 1148, 377, 991], [120, 1464], [217, 398, 167, 1263, 227]]</t>
   </si>
   <si>
     <t>h64_ws2_idx1024_random_inbf16_outbf16_ID297</t>
@@ -1019,31 +1019,31 @@
     <t>[[512, 64]]</t>
   </si>
   <si>
-    <t>[[492, 216, 438, 413, 307, 17, 27, 470, 985, 334, 328, 996, 348, 244, 183, 468, 6, 331, 905, 48, 821, 136, 457, 380, 543, 38, 684, 332, 398], [886]]</t>
+    <t>[[1000, 261, 1199, 618, 359, 457, 9, 39], [490, 86, 491]]</t>
   </si>
   <si>
     <t>h512_ws2_idx8192_random_infp32_outfp32_ID298</t>
   </si>
   <si>
-    <t>[[469, 7789, 358, 40, 434, 402, 93, 500, 162, 6281, 269, 419, 224, 6919, 491, 356, 498, 2811, 40, 981, 28, 304], [407, 7016, 251, 424, 80, 3751, 371, 233, 88, 3076, 189, 264, 463, 7068, 238, 202, 398, 7, 2279, 53, 309]]</t>
+    <t>[[431, 224, 268, 115, 394, 298, 511, 413, 430, 138], [95, 347]]</t>
   </si>
   <si>
     <t>h128_ws16_idx16384_random_infp32_outfp32_ID299</t>
   </si>
   <si>
-    <t>[[424, 875, 144, 342, 60, 480, 203, 11736, 13055, 421, 369, 491, 273, 152], [133, 2295, 335, 8048, 79, 219, 223, 386, 423, 15, 9303, 275, 448, 255, 144, 1081, 360], [221, 13179, 15481, 40, 95, 297, 467, 344], [160, 2530, 162, 10070, 468, 390, 444, 324, 367], [400, 348, 387, 427, 500, 188, 15965, 106, 364, 9061, 180, 373, 231, 3863, 196, 190, 470, 413, 4542, 120, 478, 12181], [114, 12938, 258, 288, 290, 300, 375, 11639, 294, 289, 274, 168, 431, 295, 292, 107, 50, 179, 1297, 14, 7407, 10878, 408, 113], [211, 237, 10794, 416, 5055, 510, 284, 390, 319, 176, 88, 56, 9354], [311, 215, 0, 164, 103, 9890, 4116, 326, 435, 226, 139, 230, 414, 208, 4809, 139, 286, 371, 144, 238, 106, 2801, 50, 102, 349, 303, 14901, 317, 131, 6592, 337, 3341], [149, 8509, 5870, 277, 134, 6018, 173, 511, 463, 136, 286, 61], [1458, 276, 496, 332, 15886, 419, 8058, 5237, 432, 161, 102, 403, 171, 97, 380, 77, 202, 201], [383, 428, 458, 317, 308, 249, 256, 111, 14306, 290, 404, 198, 488, 11539, 474, 404, 432, 387, 81, 5055, 15899, 1270, 398, 134, 74, 1441, 413, 137, 20], [8641], [23, 91, 512, 84, 356, 15248, 486, 147, 14847, 203, 42, 441, 7951, 161, 921, 13618, 3905, 298, 107, 265, 512, 125, 297, 495, 315, 337, 433], [419, 422, 106, 440, 1343], [8582, 15505, 151, 60, 357, 101, 9038, 502, 436, 8931, 3298, 432, 475, 25, 380, 10313, 395, 281, 299, 255, 302, 107, 350, 346, 44, 230, 343, 262], [6255, 58]]</t>
+    <t>[[253, 258, 318], [331, 1207, 181, 20, 1993, 1932, 1577, 1800, 74, 490], [146, 1370, 405, 318, 165, 494, 209, 96, 426, 389], [114, 57, 1235, 139], [423, 1034, 483, 187, 287, 197, 1708], [127, 401, 257, 405, 1992, 426, 150, 1420, 349, 371], [203, 438, 51, 286, 97, 113, 163], [744, 292, 283], [461, 143, 400, 439], [169, 418, 329, 725, 204, 1], [449, 174, 508, 445, 18, 1251, 221, 8], [156, 470, 287, 210, 113, 170, 334, 257, 58], [373, 153, 500, 541, 721, 94, 320, 217], [1518, 780, 227, 137, 216, 142, 469, 478], [31, 1192, 117, 213, 426, 92, 11, 105, 796, 1990], [369, 86, 54, 115, 42, 312, 1794]]</t>
   </si>
   <si>
     <t>h256_ws2_idx8192_random_inbf16_outbf16_ID300</t>
   </si>
   <si>
-    <t>[[102, 7, 6923, 6439, 195, 293, 466, 6670, 505, 3871, 71, 1, 250, 177, 88, 16], [3752, 436, 3693, 305, 238, 342, 359, 334, 506, 2078, 25, 269, 453, 166]]</t>
+    <t>[[322, 196, 109, 302, 243, 389, 96, 297], [414, 1, 504]]</t>
   </si>
   <si>
     <t>h256_ws4_idx4096_random_infp32_outfp32_ID301</t>
   </si>
   <si>
-    <t>[[266, 101, 1543, 170, 394, 709, 201, 52, 133, 202], [1483, 220], [4090, 314, 224, 805, 1997, 470, 414, 493, 310, 450, 411], [404, 282, 507, 23, 411, 281, 3937, 4, 2033, 2399, 469, 425, 483, 3622, 195, 3550, 221, 19, 271, 373, 3155, 507, 374, 295, 219, 60, 78]]</t>
+    <t>[[212, 2012, 116, 301, 487], [1182, 129, 305, 197, 274, 241], [288, 774, 141, 201, 258, 224, 1857], [182, 2, 486, 141, 351, 274, 468]]</t>
   </si>
   <si>
     <t>h64_ws8_idx32768_random_infp16_outfp16_ID302</t>
@@ -1052,91 +1052,91 @@
     <t>[[4096, 64]]</t>
   </si>
   <si>
-    <t>[[285, 206, 23362, 66, 244, 133, 205, 199, 13129, 20, 454, 32, 6651, 395, 429, 307, 381, 494, 80, 392, 21686, 13841, 191, 123], [193, 9436, 28445, 28472, 109, 149, 235, 201, 459, 463, 224, 41, 490, 506, 178, 98, 361, 28714, 352, 313], [113, 23010, 249], [445, 13237, 16329, 391, 186, 17, 254, 16670, 144, 142, 484, 390, 17, 13523, 506, 345, 309, 287, 457, 188, 363, 342, 404, 29111, 190, 4835], [25418, 390, 262, 235, 174, 110, 8064], [198, 481, 256, 422, 20240, 18720, 68, 5, 180], [221, 348, 444, 483, 442, 13759, 309, 319, 388, 276, 25766, 203, 32622], [175, 30213, 480, 496, 13641, 7, 230, 21796, 199, 304, 259, 216, 218, 411, 21543, 78]]</t>
+    <t>[[331, 388], [350, 122, 1266, 160], [460, 238, 452, 344, 97, 355, 259, 208], [138, 257], [241, 156, 25, 873, 273, 488, 1302, 52], [445, 488, 116, 468, 56, 376, 425], [53, 276, 110, 217, 341, 416, 253, 505, 154, 82], [399, 7, 48]]</t>
   </si>
   <si>
     <t>h64_ws4_idx8192_random_infp16_outfp16_ID303</t>
   </si>
   <si>
-    <t>[[6280], [188, 5081, 146, 36, 212, 208, 1139, 380, 214, 51], [458, 130, 7144, 118], [32, 201, 392, 11, 472, 979, 145, 67, 217, 6525, 512, 143, 32, 6921, 360, 239, 293, 164, 234, 31, 2870, 165, 1572]]</t>
+    <t>[[92, 139], [210, 503, 36, 454, 345, 325, 276, 310, 461, 444], [672, 276, 7, 72, 35, 422, 327, 103, 26], [483, 74]]</t>
   </si>
   <si>
     <t>h512_ws16_idx32768_random_inbf16_outbf16_ID304</t>
   </si>
   <si>
-    <t>[[24256, 100, 196, 295, 329], [433, 241, 24781, 49], [51, 15162, 445, 8418, 164, 498, 101], [29267, 21492, 366, 410, 498, 202], [18964, 9321, 406, 475, 478, 197, 22473, 157, 489, 483, 429, 13926, 210, 32, 1588, 207, 29029, 323, 487, 218, 493, 200, 97, 210, 92, 323], [11, 370, 446, 287, 9500, 113, 17676, 153, 18255, 87, 454, 897, 220, 272, 89, 463, 395, 250, 36, 249, 58, 507, 17088], [122, 5456], [384, 336, 160, 28742, 127, 7669, 327, 399, 100, 488, 504, 505, 311, 120, 23, 24386, 363, 480, 223, 62, 9273, 12452, 448, 103, 335, 285, 85, 222, 8026, 472, 30804, 59], [13927, 302, 475, 485, 27590, 332, 16944, 506, 236, 397, 205, 139, 31108, 369, 169, 12459, 11, 315, 176, 307, 74, 373, 428, 421], [254, 41, 214, 422, 10045, 210, 12128, 24729, 123, 24756, 426, 99, 112, 160, 20616, 448, 331, 63, 122, 475, 199, 172, 345, 511, 347, 268, 323, 19482, 419], [191, 244, 293, 324, 83, 306, 2436, 113, 1502, 434, 27810, 370, 394, 256, 504, 30091, 477, 78, 27498, 452, 446, 171, 346, 9325, 370, 329, 51], [10360, 297, 298, 73, 22, 18094, 3693, 21, 182, 289, 410, 104, 335, 71, 19130, 324, 59, 298, 106, 88], [433, 494, 187, 11957, 186, 277, 134, 224, 25046, 402], [460, 487, 104, 10258, 330, 402, 29633, 72, 480, 147, 13974, 110, 429, 395, 3], [3313, 169, 45, 290, 194, 372, 235, 440, 364, 378, 424, 344, 382, 267, 831, 32018, 428, 23948, 470, 405, 73, 284, 19691, 454, 147, 338, 488, 7691], [266, 441, 332, 25593, 196, 94, 4733, 268, 296, 11136, 110, 95]]</t>
+    <t>[[498, 70, 238, 302, 221, 124, 140, 1066, 338], [403, 202, 151], [1893, 191], [459], [1135, 295, 191, 329, 255, 145], [263, 365, 483, 434, 467, 369, 459, 181], [127, 375, 401, 245], [328, 282, 14, 207, 277], [387, 346, 38, 333], [482, 646, 151, 591, 219, 153, 294, 427, 268, 1276], [108, 228, 345, 1950, 495], [529, 505, 452, 196, 137, 198, 128, 228, 297], [429, 222, 418, 204, 771], [119, 2038, 208, 496, 369, 466], [36, 385, 379, 797, 26, 111, 376, 1443, 357, 322], [348, 79, 73, 38]]</t>
   </si>
   <si>
     <t>h64_ws16_idx32768_random_infp32_outfp32_ID305</t>
   </si>
   <si>
-    <t>[[108, 302, 461, 375, 124, 332, 28272, 67, 36, 117, 15072, 479, 141, 20348, 105, 158, 2950, 243, 38], [438, 206, 166, 9647, 69, 348, 0, 11029, 232, 15], [23323, 31266, 313, 174, 25681, 72, 414, 184, 33, 490, 66, 108, 85], [311, 18, 247, 20698, 222, 60, 504, 477, 75, 232, 28926, 327, 492, 26427, 421, 5, 8736, 224, 156, 417, 184, 318, 270, 23053, 200], [416, 8227, 121], [361, 292, 30638, 27371, 111, 232, 500, 15870, 354, 225, 465, 139, 132, 449], [112, 8249], [194, 17006, 473, 56], [128, 470, 257, 286, 318, 491, 281, 30226, 23, 461, 110, 203, 24666, 37, 313, 1628, 27282, 170, 204, 219], [8569, 325, 386, 116, 155], [83, 101, 451, 25, 436, 108, 24838, 28, 317, 21903, 18029, 2, 125, 24, 254, 443, 135, 81, 18373, 493, 22546, 423], [24216], [143, 17910, 17504, 148, 23383, 23246, 307, 50, 165, 21, 456, 443, 235, 447, 21593, 371, 393, 147, 335, 501, 327, 238, 8858, 491, 221, 134, 288, 481, 73, 138, 7465, 163], [375, 6622, 503, 4715, 96, 437], [24487, 214, 433, 416, 223, 150, 380, 20866, 372, 336, 274, 371, 230, 243, 18486], [30776, 148, 472, 292, 299, 433, 454, 215, 359, 242, 445, 152, 19, 418, 9304, 342, 357, 1269, 32094, 420, 16906, 102, 399, 218]]</t>
+    <t>[[286, 49, 110], [289, 1411, 6, 1529, 268, 238, 146, 61, 138, 164], [1444, 379, 278, 695, 508, 153, 498, 363, 511], [503], [284, 401, 52, 348, 94, 125], [1537, 93, 430, 36, 132, 282, 589], [236, 370], [377, 381, 1758, 97, 485, 449, 33, 398], [482, 419, 339, 231, 320, 21, 429, 355, 1665], [1568, 173, 215, 804, 496, 502, 285], [979, 504, 287, 312, 3, 73, 56], [482, 145, 242, 803, 497, 2045, 386, 457, 390], [247, 99, 426, 1377, 456, 389, 127, 583, 1925], [477, 52, 445, 339, 1160, 19, 34, 60], [123, 173, 110], [329, 450, 166, 511, 416]]</t>
   </si>
   <si>
     <t>h64_ws16_idx65536_random_infp16_outfp16_ID306</t>
   </si>
   <si>
-    <t>[[21303, 373, 465, 411, 17641, 339, 509, 146, 180, 293, 450, 51553, 97], [463, 66, 489, 510, 336, 46, 466, 21029, 336, 439, 45010, 178, 55310, 333, 81, 57874, 341, 216, 125, 119, 356, 314, 341, 312, 44110, 121, 39332, 413, 346], [32738, 228, 216], [369, 359, 394, 35436, 2866, 36273, 362, 172, 367, 136, 272, 147, 127, 301, 432, 394, 408, 7450, 57134, 439, 335, 62, 461, 127, 309, 11060, 340, 224, 391, 15542, 98], [129, 352, 433, 40251, 342, 355, 19031, 439, 153, 228, 9, 383, 381, 221, 388, 476, 63079, 40371], [271, 286, 346, 34758, 19, 61116, 172, 301, 37915, 439, 331], [22520, 64366, 30547, 18852, 148, 496, 368, 179, 309, 240, 340, 141, 279, 26, 189, 130], [65491, 380, 389, 388, 502, 21, 349, 239, 488, 28, 39772, 27077, 8558, 243, 170, 426, 59192, 101, 53, 315, 28, 124, 491, 315, 300, 399, 22686], [61005, 5, 100, 466], [2, 417, 65512, 380, 404, 44837, 362, 396, 355, 356, 27374, 30], [289, 392, 416, 359, 28275, 46647, 392, 24402, 18423, 48894, 360, 229, 86, 46370, 232, 324, 233, 425, 250, 91, 451, 339, 41, 418, 51, 65127, 219, 510, 150, 466, 455, 498], [487, 293, 12330, 126, 480, 178, 45, 279, 114, 10772, 122, 154, 494, 35808, 114, 3168, 52, 170, 41418, 19101, 82, 50, 367, 165, 493, 473], [163, 338, 181, 40668, 31568, 80, 9, 428, 290, 101, 48636, 342, 43, 500, 353], [315, 64504, 403, 67, 38, 76, 355, 258, 192, 51, 387, 186, 10538, 39703, 92, 141, 44, 31, 5923, 231, 45416, 49243, 228, 8, 323, 278, 170, 456], [318, 42523, 315, 44727, 360, 369], [29875]]</t>
+    <t>[[649, 265, 1394, 71, 471, 298, 398, 74], [408], [389, 126, 476, 158], [1759, 1460, 433, 240], [148, 215, 159, 58, 338], [722, 424, 290, 241, 270, 30], [66, 418, 443, 84, 206, 133, 235, 340], [5], [761, 456, 423], [439, 1296, 455, 400, 345, 204, 909], [215, 54], [1296, 77, 164], [334, 55, 987, 231, 1974, 252], [158, 437, 343, 128, 355, 504], [231, 1715, 119, 20, 57, 78, 1329, 168, 109], [345, 83, 50, 1668, 490, 301, 289, 149, 812]]</t>
   </si>
   <si>
     <t>h512_ws2_idx1024_random_infp16_outfp16_ID307</t>
   </si>
   <si>
-    <t>[[287, 70, 371, 700, 23, 562, 597, 293, 184, 952, 27, 159, 444, 197, 428, 229, 393, 370, 485], [5, 512, 500, 286, 126, 906, 994, 339, 409, 391, 61, 410, 706, 228, 185, 150, 295, 36, 644, 421]]</t>
+    <t>[[349, 416, 362, 299, 259], [650, 31, 277, 138, 157, 454, 294, 19, 1118]]</t>
   </si>
   <si>
     <t>h64_ws8_idx4096_random_infp16_outfp16_ID308</t>
   </si>
   <si>
-    <t>[[299, 427, 967, 1879, 2451, 486, 2976, 97, 29, 712, 120, 63, 207, 118, 1214, 260, 248, 315, 69, 93, 193, 487, 293, 204, 94, 472], [173, 88, 190, 427, 3125, 4087, 488, 226, 296, 35, 588, 83, 334, 117], [237, 148, 363, 3263, 444, 3925, 57], [7, 403, 2339, 263, 57, 283, 354, 157, 65, 438, 892, 358, 354, 288, 489, 1057, 1480, 68, 181, 400, 3335, 2537, 207, 5, 112, 45, 604, 23, 191, 266, 191, 500], [298, 851, 22, 74, 2789, 122, 431, 472, 467, 219], [1734, 187, 311, 81, 489, 367, 931, 477, 76, 398, 710, 148, 3122, 388, 300, 229, 119, 285, 3231, 221, 37, 205], [78, 542, 316], [177, 3476]]</t>
+    <t>[[83, 180, 246, 157, 1940, 403, 912, 389], [2, 293], [1684, 92, 303, 331, 161, 500, 148], [45], [377, 423, 460, 397], [613, 393, 455, 448, 406, 200, 207, 7, 88, 993], [237, 216, 228, 383], [288, 1263, 305, 417, 316, 48, 737, 78]]</t>
   </si>
   <si>
     <t>h512_ws8_idx32768_random_inbf16_outbf16_ID309</t>
   </si>
   <si>
-    <t>[[26114, 83, 404, 28993, 316, 12, 415, 284, 11138, 457, 291, 15943, 455, 298, 267, 364, 53, 134, 6218, 474, 454], [16525, 365, 61, 1, 17723, 440, 0, 345, 153, 500, 4180, 471, 232, 355, 25832, 41, 47, 288, 21013, 269, 227, 50], [31593, 156, 479, 7, 487, 8222], [248, 9085, 146, 13, 118, 114, 12215, 203, 407, 53, 133, 105, 477, 25814, 1006, 61], [69, 97, 112, 4813, 288, 15625, 68, 85, 60, 31763, 108, 423, 223, 413, 3, 25732, 60, 193, 296, 23395, 437, 316, 28576, 482, 438, 229], [177, 510, 278, 20792, 24, 361, 106, 310, 475, 498, 377, 26736, 8296, 397, 6914, 239, 110, 417], [32, 32102, 196, 354, 20887, 271, 152, 153, 21, 54, 147, 11310, 113, 138, 25273, 7, 239, 10837, 24663, 183, 283, 314, 360, 441, 481, 512, 331, 427, 183, 14563, 459], [136, 16028, 127, 500, 186, 439, 274, 3988, 235]]</t>
+    <t>[[1264, 185, 389, 279, 1595, 323, 142, 215, 185, 181], [196, 222, 74, 134, 297, 185, 247, 471], [170, 14, 100, 433], [267, 193, 276, 214, 66], [460, 3, 508, 431, 1202, 1354, 139], [1126, 180, 111, 45, 15, 405, 245, 446], [354, 118, 135, 231, 236, 38], [1765, 411, 437, 354, 404, 46, 482, 228]]</t>
   </si>
   <si>
     <t>h128_ws2_idx1024_random_inbf16_outbf16_ID310</t>
   </si>
   <si>
-    <t>[[593, 492], [167, 819, 17, 796, 89, 97, 107, 310, 720, 459, 434, 193, 412, 50, 260, 596, 429, 169, 119, 459, 497, 929, 356, 237, 377, 1016]]</t>
+    <t>[[429, 131, 20, 351, 347], [37, 311, 61, 431, 51, 386, 854]]</t>
   </si>
   <si>
     <t>h256_ws4_idx4096_random_infp16_outfp16_ID311</t>
   </si>
   <si>
-    <t>[[491, 208, 289, 492, 3545, 430, 2421, 191, 234, 222, 358, 311, 155, 4054, 175, 908, 311], [3970, 126, 373, 311, 201, 146, 24, 311, 470, 3782, 176, 219, 448, 379, 183, 217, 487, 3897, 1724], [1290, 412, 1467, 468, 281, 230, 170, 208], [3340, 1, 90, 293, 58, 103, 664, 400, 1738, 1778, 235, 235, 458, 231, 276, 114, 331, 436, 101, 368, 477, 178, 103, 26, 487, 3556, 478, 917, 135, 187]]</t>
+    <t>[[1337, 325, 169], [92, 252, 613, 372, 1256, 922], [156, 1648, 332, 505, 199, 457, 390], [130, 287]]</t>
   </si>
   <si>
     <t>h64_ws16_idx8192_random_infp16_outfp16_ID312</t>
   </si>
   <si>
-    <t>[[470, 313, 391, 177, 465, 7690, 147, 492, 8149, 333, 829, 31, 155, 376], [447, 8163, 1849, 2, 157, 194, 363], [57, 2663, 4343, 1703, 274, 438, 417, 320, 181, 183, 3239, 304, 153, 5, 236, 122, 415, 158, 207, 6829, 357, 245, 501], [189, 7681, 490, 172, 2382, 118, 61, 467, 504], [463, 309, 505, 4916, 325, 3461, 201, 341], [7229], [465, 368, 30, 344, 5629, 855, 2316, 183, 264, 106, 11, 361, 489, 257, 129, 55, 231, 124, 242, 126, 101, 398, 40, 1720, 1800, 1754, 484, 254], [120, 107, 171, 343, 18, 503, 279, 246, 3250, 160, 5521, 8001, 278], [95, 101, 184, 27, 561, 317, 4316, 220, 247, 308, 6697, 124, 7, 29, 66, 5620, 61, 303, 138, 238, 386, 213, 2078, 453, 4], [33, 7020, 345, 214, 303], [216, 430, 180, 164, 490, 134, 5219, 1431, 497, 94, 498, 60, 7568, 369, 227], [7367, 412, 463, 491, 114, 190, 346, 556, 333, 5463, 202, 224, 107, 378, 6580, 333, 441, 19, 361, 306, 243, 159, 30, 8066], [510, 289, 2366], [179, 140, 16, 148, 283, 4749, 0, 24, 2924, 412], [317, 12, 8004, 140, 449, 63, 446, 407, 420, 357, 356, 244, 41, 42, 141, 53, 2526, 238, 225, 291, 456, 5355, 2402, 308, 281, 295, 366, 2327, 360, 1848], [288, 436, 6685, 456, 486, 146, 197, 472, 233, 195, 253, 291, 1179, 328, 5584, 184, 367, 4710, 42, 230, 5469, 3934, 169, 321, 173, 313]]</t>
+    <t>[[286, 408, 377, 479, 38, 140, 1635, 401], [118, 292, 206], [806, 68, 210, 51, 107, 543, 158, 270], [429, 1542, 1447, 886, 54, 266], [288, 7, 1120, 171], [407, 823, 308, 388, 430, 52, 25, 47, 155], [821, 274, 232, 279, 460, 296, 188, 359, 461, 1389], [483, 148, 169, 334], [286, 405, 300, 281], [205, 135, 447, 450, 329], [603, 433, 347, 375, 456, 88, 424, 310, 60], [466], [240, 398, 218, 401, 251, 420, 146, 430, 223, 1542], [235], [88, 188, 301, 367], [458, 137, 74, 17, 53]]</t>
   </si>
   <si>
     <t>h128_ws8_idx4096_random_infp16_outfp16_ID313</t>
   </si>
   <si>
-    <t>[[1752, 268, 61, 697, 65, 180, 195, 280, 211, 3565, 2681, 189, 121, 18, 335, 447, 8, 3291, 201, 21, 420, 61, 231, 428, 3189, 106], [232, 769, 47, 497, 18, 2907], [75, 44, 506, 205, 427, 477, 3725, 288, 239, 333, 2518, 177, 3145, 236, 318, 24, 2887, 171, 187, 760, 166, 237, 271, 3, 62, 3186, 278], [274, 70, 501, 1180, 465, 321, 4, 3585, 331, 2485, 370, 496, 327, 298, 318, 1196], [156, 994, 386, 57, 2927, 364, 1587, 170, 2720, 102, 232, 136, 292, 100, 83, 28, 321], [323, 484, 140, 3633, 228, 262, 2897], [504, 259, 247, 213, 62, 2477, 3836, 383, 476, 438, 436, 2829, 128, 418, 215], [1948, 178, 468, 24, 234, 478, 472, 62, 3288, 91, 41, 400, 497, 505, 48, 1309, 264, 2074, 391, 47, 3025, 271, 63]]</t>
+    <t>[[437, 252, 1840, 499, 112, 475, 431, 177], [80, 401], [190, 1515, 454, 270, 440], [195, 57, 1252, 254], [256, 1123, 436], [98, 1403, 219, 167, 904, 322, 200, 1443, 225], [273, 628, 211, 495, 284, 100, 503], [333]]</t>
   </si>
   <si>
     <t>h256_ws4_idx16384_random_infp32_outfp32_ID314</t>
   </si>
   <si>
-    <t>[[376, 354, 313, 12958, 453, 224, 401, 639, 35, 6389, 234], [47, 259, 294, 59, 3635, 445, 7282, 5319, 9002, 168, 341, 299, 463, 349, 28, 413, 124, 434, 458, 389, 466, 48, 35, 2575, 373], [269, 135, 337, 263, 14735, 11266, 501, 298, 71, 437, 357, 477, 268, 470, 15837, 161, 293, 2386, 220, 7434, 162], [59, 450, 6964, 115, 184, 365, 466, 495, 256, 250, 405, 439, 85, 3242, 42, 169, 3621, 404, 305, 107, 6076, 5, 33, 132, 4048, 12631]]</t>
+    <t>[[506, 208, 118, 494], [412, 44, 478], [63, 161, 53, 438], [96, 124, 481, 506, 424, 281, 227, 86, 364]]</t>
   </si>
   <si>
     <t>h128_ws8_idx32768_random_inbf16_outbf16_ID315</t>
   </si>
   <si>
-    <t>[[25932], [512, 417, 12858, 212, 31, 423, 388, 3293, 140, 193, 312, 237, 280, 15674, 122, 55, 22615, 299, 190, 421, 460, 311, 71, 28074, 232, 193, 1412, 211, 17, 266], [391, 422, 3399, 376, 498, 18, 464, 443, 3, 368, 24808, 32, 273, 9289, 28261, 234], [313, 191, 24971, 3393, 347, 94, 452, 415, 298, 458, 170, 25526], [241, 28368, 334, 427, 180, 360, 146, 24788, 442, 7981, 245, 474, 398, 119, 464, 375, 18097], [354, 349, 26812, 43, 310, 345, 398, 85, 508, 189, 227, 343, 247, 265, 457, 148, 351, 7694, 296, 99, 197, 17185, 2738, 164, 309, 6793, 412, 2282, 437], [49, 2620, 155, 238, 166, 490, 32729, 308], [269, 483, 28880, 32374, 471, 202, 91]]</t>
+    <t>[[59, 443, 462, 28, 174], [188, 389, 489, 113], [317, 71, 9, 394, 158, 468, 613, 476, 608], [209, 500, 355, 1476, 221, 1028, 483, 338, 183, 99], [318, 213, 1150], [1449, 159, 260, 118, 414, 558, 395], [315, 88, 347, 1733, 282, 18, 878, 577, 76, 279], [111, 1501, 417]]</t>
   </si>
   <si>
     <t>h256_ws2_idx4096_random_infp16_outfp16_ID316</t>
   </si>
   <si>
-    <t>[[2365, 62, 193, 316, 409, 1, 318, 91, 293, 371, 3936, 358, 3, 229, 1397], [2789, 328, 373]]</t>
+    <t>[[479, 1120, 129, 101, 411, 1079, 264, 512], [83, 200, 41, 8, 267, 437, 219, 182]]</t>
   </si>
   <si>
     <t>h256_ws8_idx4096_random_infp16_outfp16_ID317</t>
@@ -1145,1249 +1145,1249 @@
     <t>[[512, 256]]</t>
   </si>
   <si>
-    <t>[[319, 105, 12, 462, 306, 122, 218, 468, 2734, 140, 84, 142, 455, 1971, 496, 317, 264, 96, 443, 2749, 1682, 2336, 448], [319, 490, 60, 427, 473, 794, 3082, 388, 43], [265, 121, 2187, 354, 994, 713, 503, 101, 449, 405, 439, 1053, 108, 398, 208, 349, 351, 37, 377, 137, 21, 229, 2713, 317, 294, 4070, 476, 141, 2292, 242, 434], [141, 227, 4079, 124, 332, 42, 3673, 118, 160, 347, 51, 9, 583], [435, 490, 385, 63, 2857, 404, 3315, 454, 165, 502, 328, 274, 114, 86, 211, 3515, 134, 1847, 501, 135, 243, 3912, 3033, 83, 53, 217, 406, 171, 351, 326], [3261, 349, 492, 123, 48, 2583, 494, 307, 441, 57, 18, 443, 372, 221, 372, 2632, 3039, 212], [224, 1950, 1430, 186, 168, 512, 64, 459, 802, 211, 10, 427, 442, 352, 361], [138, 1241, 491, 450, 177, 294, 744, 79, 127, 504]]</t>
+    <t>[[352, 1159, 506, 471, 88, 43, 168], [458], [126, 329, 1580, 271, 160], [48, 20, 1383, 333, 65, 287, 36, 884, 1791], [213, 413, 245, 3, 1175], [32, 308, 79, 90, 223], [446], [408, 22]]</t>
   </si>
   <si>
     <t>h256_ws8_idx32768_random_infp32_outfp32_ID318</t>
   </si>
   <si>
-    <t>[[13718, 314, 10447, 32480, 122, 461, 479, 266, 13840, 125, 137, 144, 412, 422, 11037, 134, 123, 40, 433, 42, 58, 120], [313, 266, 356, 139, 455, 279, 109, 6655, 1, 28151, 393, 315, 155, 347, 382, 8116, 218, 298, 165, 18669], [435, 30038, 5540, 466, 208, 126, 68, 250, 179, 127, 32492, 494, 512, 79, 345, 477, 39, 17510, 421, 3270, 161, 129, 17427, 232, 1, 454, 273, 17366, 273, 10, 153, 319], [16546, 11, 105, 128], [159, 164, 16541, 314, 346, 431, 175, 13352, 271, 152, 18946, 396, 434, 365, 20582, 64, 393, 4623, 478, 80, 37, 204, 25, 30451, 324, 42, 368], [7, 82, 313, 21458, 125, 322, 69, 447, 276, 346, 395, 460, 29638, 122, 329, 28, 224, 470, 20777, 32433, 30491], [186, 374, 116, 17473, 386, 2347, 250], [20, 21184, 510, 88, 284, 17, 391, 14665, 903, 442, 298, 136, 334, 449, 397]]</t>
+    <t>[[1150, 99], [588, 835, 172, 432, 418, 34], [369, 246, 381, 627, 92, 154, 262, 69, 1781, 155], [406, 146, 405, 21, 292, 29, 505], [246, 391, 173, 370, 276, 1260, 316], [254, 163, 93, 489, 462, 395, 206, 1621], [1868, 452, 199, 414], [1054, 108, 407, 153, 187, 462, 1117, 161]]</t>
   </si>
   <si>
     <t>h512_ws8_idx8192_random_infp16_outfp16_ID319</t>
   </si>
   <si>
-    <t>[[125, 49, 277, 476, 422, 288, 448, 267, 250, 6696, 2200, 7, 36, 496, 389, 87, 184, 2444, 6, 346, 1682, 4858, 257], [2547, 459, 123, 470, 395, 349, 335, 475, 236, 4520, 316, 275, 6893, 3379, 186, 116], [81, 144, 302, 249, 226, 478, 5063, 247, 4565, 511, 86, 113, 421, 6266, 485, 135, 1823, 135, 29, 56, 359, 426, 327, 242, 351, 329, 3869, 92, 4036], [2759, 472, 218, 6028, 20, 407, 388, 379], [1795, 377, 312, 140, 4823, 302, 133], [321, 207, 361, 2477, 204, 1439, 8, 6830, 500, 363, 390, 494, 7176, 247, 428, 324, 129, 7, 277, 2811, 173, 119], [449, 424, 419, 7727, 2903, 418, 222, 407, 459, 466, 7122], [400, 51, 488, 245, 4965, 363, 198, 339, 1438, 237, 279, 269, 5985, 55, 4788, 4120, 127, 322, 379, 401, 253, 392, 41, 344, 400, 212, 227, 129, 7394, 5960, 434, 431]]</t>
+    <t>[[37, 420], [222], [380, 1026, 1393, 126, 443, 422, 341, 11, 279, 18], [306, 537, 212, 1957], [28, 391, 24, 354, 267], [1073, 67, 469, 164, 367, 340, 1595], [1029, 155, 70, 133, 11, 204, 353], [125, 472, 431, 171, 131, 364, 800, 253]]</t>
   </si>
   <si>
     <t>h512_ws8_idx32768_random_inbf16_outbf16_ID320</t>
   </si>
   <si>
-    <t>[[87, 115, 425, 3258], [34, 16, 31031, 285, 200, 220, 368, 17251], [309, 115, 32360, 328, 149, 255, 162, 26564, 501, 52, 479, 158, 142, 110, 433, 5970, 116, 214, 69, 363, 478, 441, 110, 24677, 3927], [124, 7, 406, 469, 28680, 309, 375, 259, 482, 28593, 17279, 297, 0, 325, 186, 181, 18376, 4], [208, 241, 444, 159, 7538, 17190, 281, 357, 129, 390], [19145], [374, 439, 205, 345, 7851, 156, 317, 136, 133, 268, 129, 407, 442, 398, 8666, 113, 29285, 410, 237, 28855, 14192, 3656, 112, 370, 114, 179, 11477, 103, 411, 503, 451], [349, 17456, 214, 160, 313, 162, 52, 323, 11994, 355, 27762, 346, 22763, 396, 231, 16356, 177, 222, 460, 198, 396, 333, 380, 489, 65, 31293, 11, 233]]</t>
+    <t>[[432, 65, 187, 219, 446, 93, 303, 233], [308], [340, 290, 422, 215, 440, 381, 196, 574], [259, 180, 115, 55], [94, 456, 1804, 1639, 396, 750, 253], [258, 273], [490, 287], [364, 95, 862, 223, 412, 1401, 425, 287, 110]]</t>
   </si>
   <si>
     <t>h128_ws16_idx65536_random_inbf16_outbf16_ID321</t>
   </si>
   <si>
-    <t>[[222, 120, 167, 65014, 305, 90, 353, 51525, 288, 243, 189, 280, 72, 255, 59524], [187, 206, 48169, 21720, 467, 331, 17402, 154, 49051, 509, 489, 243, 484, 370, 237, 161, 371, 121, 127, 365, 58563, 193, 80, 420, 24016, 390], [293, 46094, 494, 48213, 68, 442, 241], [482, 23179, 507, 40330, 86, 346, 495, 316, 65407, 16, 96, 164, 91, 253, 373, 10277, 2, 166, 429, 468, 68, 213, 13768, 354, 364, 511, 286, 32935, 267], [201, 14944, 388, 238, 51, 60699, 316, 192, 97, 25, 415, 37103, 493, 253, 132, 56780, 426, 291], [477, 262, 52883, 292, 202, 240, 124, 40, 442, 432, 34506, 50248, 224, 67], [214, 361, 222, 228, 298, 271, 64, 405, 1918, 300, 16624, 331, 26041, 422, 43573, 98, 348, 262, 173, 165, 58560, 181], [183, 279, 42405, 447], [15044, 385, 354, 289, 384, 360, 2167, 175, 369, 254, 383, 23, 40900, 93, 365, 55263], [41192, 89, 192, 203, 371, 414, 388, 348, 7515, 434], [327, 26833, 256, 293, 46827, 201, 41455, 320, 94, 128, 203, 153, 173, 191, 448, 415, 12145, 34, 101, 17, 128, 91, 386, 228, 113, 309, 338, 254, 29682, 11415, 20175, 158], [259, 336, 22, 21154, 457, 35994, 501, 184, 164, 501, 47565, 265, 320], [241, 60, 59271, 457, 45447, 358, 445, 385, 35027, 394, 419], [370, 460, 41836, 369, 300, 305, 222, 136, 14122, 39508, 182, 54843, 232, 56, 348, 24601, 316, 32, 159, 485, 96, 20, 4], [332, 147, 198, 143, 51, 261, 326, 277, 73, 47343, 35308, 315, 43557, 300, 314, 26475, 114, 340, 85, 347, 131, 419, 117, 56198], [317, 73, 50, 40, 37, 208, 335, 26865, 39, 488, 52476, 310, 85, 424, 46266, 219, 154, 14452, 58828, 227, 507, 142, 268, 94, 509]]</t>
+    <t>[[100, 396, 487, 107, 535, 363], [345, 188, 154, 247, 46, 494, 1007, 117, 200], [443, 445, 8], [1443, 293, 371, 332, 1279, 265, 215, 140, 426, 367], [1973, 242, 481, 197, 66, 296, 388], [353, 265, 287, 213, 86, 80, 36], [326, 197], [491, 1836, 66, 5, 224, 385], [1], [390, 502, 7, 115, 47, 403, 378, 105], [730], [409, 201, 140], [950, 394, 711], [332, 40, 359, 115], [67, 397, 53, 501, 32, 585, 1771, 136], [240, 16, 317, 225, 106, 854, 133, 42, 385]]</t>
   </si>
   <si>
     <t>h128_ws4_idx4096_random_infp16_outfp16_ID322</t>
   </si>
   <si>
-    <t>[[171, 814, 357, 1041, 396, 389, 102], [446, 75, 1303], [361, 322, 470, 380, 127, 3832, 408, 32, 45, 6, 4039, 3459, 876, 469, 227, 194, 1064, 367, 209, 176, 93, 339, 396, 226, 136], [3966, 180, 1602, 530, 3014, 453, 506, 449, 302, 431, 209, 168, 78, 235, 473, 289, 511, 341, 2368, 160, 418, 282, 387]]</t>
+    <t>[[1409, 88], [402], [345, 319, 147, 358, 478, 1947, 107], [1568, 368, 271, 139, 325, 81, 106, 214, 161]]</t>
   </si>
   <si>
     <t>h512_ws8_idx16384_random_inbf16_outbf16_ID323</t>
   </si>
   <si>
-    <t>[[352, 141, 16022, 258, 221, 102, 47, 151, 314, 416, 209, 5025, 464, 122, 6798, 195, 2226, 481, 458, 91, 6357, 462, 502, 367, 11155, 422, 313, 398, 489], [23, 15327, 198, 436, 375, 266, 344, 13, 374, 308, 111, 396, 12423, 14917, 465, 253, 148, 9, 466, 125, 4182, 2169, 90, 10647, 273, 134, 335, 68], [133, 7544, 9790, 94, 315, 3516, 137, 134, 157, 142, 190, 10927, 278, 220, 342, 408], [286, 324, 189, 266, 365, 334, 10747, 4572, 51, 86, 25, 148, 2975, 327, 251, 249, 64, 147, 110, 9136, 73, 326, 299, 468, 3769], [8882, 221, 32, 505, 3120, 280, 464], [101, 6604, 102, 321, 274, 218, 218, 684, 8], [251, 355, 55, 13421, 302, 266, 5, 11017, 497, 6, 504, 464, 216, 4, 13480, 3754, 64, 86, 176], [128, 11119, 39, 7811, 299, 16, 413, 261, 209, 436, 330, 9031, 480, 186]]</t>
+    <t>[[319, 23, 209, 42, 462, 245, 939], [232, 278, 129, 77, 445, 254, 499, 388, 102, 204], [333, 1737, 183, 476, 84, 138, 119, 101, 167, 249], [670], [150, 152, 277, 198, 481, 53, 90, 82, 113], [10, 60, 145, 464, 502, 179, 455, 385, 151, 305], [485, 1928, 1752], [114, 430, 163, 1903, 471, 125, 459, 116, 350]]</t>
   </si>
   <si>
     <t>h128_ws8_idx16384_random_inbf16_outbf16_ID324</t>
   </si>
   <si>
-    <t>[[14339, 469, 157], [842, 216, 236, 62, 448, 169, 6370, 258, 98], [4594, 461, 510, 184, 189, 195, 11, 285, 246, 184, 5003, 243, 440, 74, 9718], [842, 458], [391, 353, 487, 241, 1, 502, 4678, 114, 201, 5017, 52, 372, 456, 361, 329, 21, 14355, 356, 8721, 19, 297, 439, 14237, 364, 8254, 500, 272, 80, 460, 39, 6799, 20], [137, 448, 68, 6179], [15902, 131, 301, 217, 6997, 18, 404, 495, 114, 478, 9777, 341, 242], [9462, 7171, 236, 431, 16, 396, 295, 487, 288, 257, 203, 180, 327, 500, 295, 389, 121, 15693, 8202, 105, 2551, 369, 441]]</t>
+    <t>[[109, 314, 1678, 253, 128, 454, 362, 273, 463], [244, 136, 418], [1623, 1703, 19, 47], [1928, 1059, 303, 2047, 15, 198, 511, 104, 216, 1780], [216, 67, 215, 494, 60, 89], [223], [432, 341, 341, 480, 433], [1120, 286, 287, 1525, 138, 422, 315]]</t>
   </si>
   <si>
     <t>h64_ws2_idx8192_random_infp32_outfp32_ID325</t>
   </si>
   <si>
-    <t>[[122, 143, 498, 7732, 228, 7463, 3663, 248, 162, 430, 89, 363, 431, 10, 412, 417, 210, 5313, 459, 191, 286, 6957, 119, 172, 4963, 456, 52], [104, 5379, 24, 47, 289, 4851, 58, 171, 186, 86, 3795, 303, 200]]</t>
+    <t>[[218, 267, 448, 480, 466, 438, 374, 346, 1358], [85, 31, 186, 2030, 91]]</t>
   </si>
   <si>
     <t>h64_ws16_idx16384_random_inbf16_outbf16_ID326</t>
   </si>
   <si>
-    <t>[[1599, 336, 487, 1, 464, 288, 2027, 267, 220, 321], [13, 128, 50, 94, 4757, 10253], [488, 410, 44, 153, 89, 363, 6150, 395, 104, 926, 350, 462, 1204, 407, 324, 86, 3399, 482, 8079, 483, 3335, 97, 154, 356, 114, 443, 133, 432, 431, 229], [7266], [194, 110, 15059, 231, 6483, 312, 5069, 41, 319, 317, 417, 7029, 62, 240, 505, 8, 315, 4], [478, 280, 53, 8803], [371, 32, 9112, 367, 4585, 274, 38, 6993, 313, 127, 92, 89, 194], [288, 423, 337, 489, 15, 347, 14225, 74, 15426, 184, 453, 1891], [447, 23, 91, 68, 6, 135, 13207, 6344], [5952, 132, 504, 444, 298, 647, 172, 482, 416, 326, 449, 5616, 2372, 200, 363, 16, 371, 11849, 424, 8682, 8, 291, 458, 177, 509, 106, 326, 12574, 195, 274, 235], [283, 85, 298, 3960, 114, 346, 424, 152, 1350, 28, 184, 374, 416, 98, 458, 34, 13929, 152, 490, 416, 3015, 9890, 2, 16215, 67, 67, 428], [265, 324, 168, 3596, 368], [299, 463, 422, 906, 165, 324, 269, 2930, 13214, 114, 173, 93, 282, 6946, 177, 316, 219, 454, 13227, 29, 286, 183], [329, 13313, 125, 287, 242, 165, 366, 72, 272, 15512, 346, 441, 126, 9317, 4766, 5314, 88, 249, 96, 385, 60], [33, 124, 132, 315, 143, 580, 399, 433, 4708, 165, 454, 5676, 89, 285, 450, 359, 61, 10552, 464, 5264, 15, 210, 379, 111, 407], [12568, 351, 366, 12015, 6180, 487, 447, 478, 211, 413, 351, 33, 238, 386, 242, 485, 84, 172, 149, 331, 429, 57, 12144, 226, 151, 136, 8971, 471, 12164, 432, 394, 11071]]</t>
+    <t>[[440, 385, 73, 306, 329, 392, 220], [170, 456, 631, 36, 487, 431, 192, 264, 211], [76, 327, 30], [267, 394, 287], [4, 117, 1802], [102, 1845, 1256, 447, 164, 259, 708, 1512], [370, 259, 713, 548], [332, 51, 1339], [312, 332, 159], [372, 411, 302, 298, 1190, 194, 440, 72], [1055], [158, 414, 1471, 125, 227, 318, 238, 432, 419], [384, 458, 444, 157, 162, 1651, 446, 69, 398], [321, 161, 375], [466, 1516, 418, 165, 278, 430], [493, 58, 1747]]</t>
   </si>
   <si>
     <t>h256_ws8_idx8192_random_infp32_outfp32_ID327</t>
   </si>
   <si>
-    <t>[[493, 1384, 107, 296, 474, 290, 1972, 6340, 884, 171, 235, 490, 33, 10, 447, 329, 369], [144, 192, 3139, 185, 352, 94, 5886, 287, 303, 186], [2901, 294, 351, 385, 7123, 359, 6, 129], [354, 132, 62, 191, 3444, 161, 4799, 4268, 511, 13, 342, 25, 8175, 411, 334, 27, 502, 416, 197, 3, 430, 508, 4275], [5402, 54, 408, 166, 6783, 239, 377, 27, 443, 3819, 121, 6275, 310, 228, 298, 403, 4258, 136, 463, 73, 122, 7958, 301, 194, 352, 142], [155, 2068, 195], [403, 203, 24, 342, 178, 224, 257, 380, 346, 48, 37, 31, 272, 208, 643, 6021, 340, 137, 2477, 4129, 327, 452, 475, 301, 6936], [443, 19, 339, 7279]]</t>
+    <t>[[149, 177, 110, 301], [482, 213], [175, 221, 534, 475, 401, 224], [479, 216, 27, 5, 1669], [382, 239, 434, 77, 44], [510, 1751, 476, 36, 219, 353, 676, 978, 402], [1084, 94], [474, 357, 100, 409, 238, 336, 497, 421, 86, 427]]</t>
   </si>
   <si>
     <t>h256_ws8_idx32768_random_infp32_outfp32_ID328</t>
   </si>
   <si>
-    <t>[[20757, 402, 9680, 414, 30, 373, 60, 68, 134, 176, 22403, 481, 1039, 148, 173, 15936, 465, 146, 337, 46, 388], [468, 364, 32213, 290, 285, 220, 254, 179, 449, 230, 8788, 503, 17900, 389, 19415, 363, 390, 410, 447], [449, 483, 69, 242, 108, 509, 375, 171, 107, 257, 128, 295, 487, 127, 21189, 22522, 462, 467, 107, 4712, 161, 27868, 117, 203, 481, 30261, 179, 507, 20093, 188, 16577, 171], [270, 75, 67, 128, 37, 239, 18271, 443, 28052, 141, 196, 470, 20533, 25528, 269, 436], [4401, 78, 221, 145, 234, 278, 17183, 444, 379], [208, 30031, 52, 316, 482, 311, 18507, 21984, 199, 93, 194, 1601, 468, 54, 434, 288, 228, 113, 26132, 4603, 176, 478, 65, 403, 52, 198], [30432, 51, 362, 17, 49, 275, 346, 327, 359, 3855], [14164, 14904, 107, 401, 28690, 265, 379, 36, 206, 181, 498, 240, 138, 290, 283, 209, 373, 23, 288, 354, 266, 80, 5044, 5042]]</t>
+    <t>[[272, 500, 71, 691], [471, 462, 132, 97, 372, 279], [244], [143, 449, 105], [54, 436, 491, 399], [488, 82, 89], [157], [89, 1891, 6]]</t>
   </si>
   <si>
     <t>h64_ws4_idx4096_random_infp16_outfp16_ID329</t>
   </si>
   <si>
-    <t>[[460, 3190, 236, 312, 473, 3864, 140, 2843, 170, 492, 367, 441, 87, 3217, 390, 48, 459], [262, 220, 2012, 3587, 251, 438, 372], [2019, 1314, 154, 2026, 283, 405, 369, 1022, 332, 427, 284, 507, 289, 23, 286, 373, 298, 375, 271, 174, 8, 3325, 258, 72, 60, 201, 64, 272, 4008, 209], [450, 206, 504, 15, 19, 2547, 881, 256, 443]]</t>
+    <t>[[68, 413, 83, 90, 15, 1694, 404, 106, 414, 338], [1763, 63, 284, 66, 98, 12, 105, 74, 137], [1674, 103, 414, 189, 508, 440, 337], [101, 18, 500, 1600, 14, 404, 232, 382]]</t>
   </si>
   <si>
     <t>h64_ws4_idx8192_random_inbf16_outbf16_ID330</t>
   </si>
   <si>
-    <t>[[160, 5559, 3339, 147, 285, 2874, 430, 156, 145, 454, 45, 456, 480, 89, 87, 476, 512, 472, 4457, 455], [340, 315, 461, 6587, 432, 475, 4490, 1952, 117, 388, 8134, 205, 191, 160, 167, 85, 70, 152, 253, 391, 367, 1115, 7130, 126, 57, 138], [7868, 39, 217, 11, 91, 37, 15, 70, 187, 5008, 375, 1573, 96], [163, 374, 6371, 31, 135, 223, 7275, 217, 75, 327, 325, 88, 500, 440, 2605, 341, 54, 135, 490, 143, 265, 2799, 25, 936, 448, 75, 359, 130, 115, 7634, 666]]</t>
+    <t>[[457, 54, 2006, 477, 258], [80, 226, 1996], [421, 307, 157, 1900, 120, 211, 90, 405], [136, 1066, 485, 795, 489, 1595, 984, 1962, 433]]</t>
   </si>
   <si>
     <t>h256_ws16_idx32768_random_infp32_outfp32_ID331</t>
   </si>
   <si>
-    <t>[[325, 197, 19327], [130, 889, 221, 289, 10682, 297, 464, 253, 12526, 304, 386, 43, 426, 43, 4628, 20, 394, 419, 166, 14419, 41, 385], [164, 407, 190, 263, 6432, 73, 3, 69, 39, 224, 473, 211, 10, 40, 3335, 23849, 509, 482, 365, 9, 14178, 45, 512, 5433, 299], [10718, 22465, 69, 510, 445, 308, 458, 182, 362, 169, 444, 249, 83, 2298, 30394, 87, 57, 203], [35, 14644], [63, 90, 162, 116, 417, 504, 511, 20299, 295, 356, 173, 442, 80, 275, 3747, 31285, 388, 166, 19, 471, 489, 4340, 271, 399, 10703, 614, 128], [5171, 132, 12, 1, 363, 458, 466, 475, 361, 195, 426, 280, 219, 355, 248, 29800, 493, 29564, 16, 37, 11, 247, 233, 7366, 202, 282, 14600, 3844], [15564, 46, 329, 452, 406, 8793, 142], [264, 195, 298, 490, 3389, 459, 43, 461, 454, 5125, 64, 143, 86, 336, 11804, 13509, 459, 476, 316, 129, 3, 84, 103, 413, 383, 24946, 16244, 490, 269, 387, 25891, 241], [464, 15739, 21017, 387, 1, 454, 484, 152, 23789, 262, 469, 364], [9, 244, 408, 20567, 503, 470, 247, 323, 2188, 137, 23998, 483, 179, 287], [27902], [490, 102, 448, 30265], [28247, 488, 263, 26175, 406, 133, 132, 409, 195, 464, 410, 20508, 456, 455, 26752, 101, 220], [259, 3007, 186, 150, 87, 26906], [130, 404, 17395, 62, 200, 11, 32, 272, 342, 11515, 314, 499, 108, 57, 110, 403, 126, 352, 379, 303, 369, 20456, 23397, 294, 381, 339, 12, 23612, 32038, 160, 9602]]</t>
+    <t>[[14, 185, 1156, 195, 322], [241], [709, 961, 20, 740, 404], [306, 306, 501, 362, 492, 1991], [97, 506, 202, 1866], [337, 141, 350, 159, 327, 412, 305, 96, 436], [147], [304, 327, 387], [132, 213, 1654, 386], [233, 86, 471, 76, 79, 202, 55], [326, 346, 92, 107, 1267], [130, 306, 1816, 622, 467, 422, 379, 153], [240, 394, 103, 60, 107, 40, 333], [491, 199, 398, 327, 283, 184, 75], [212, 406, 368, 340], [390, 401, 95, 327, 430]]</t>
   </si>
   <si>
     <t>h512_ws4_idx8192_random_infp16_outfp16_ID332</t>
   </si>
   <si>
-    <t>[[225, 7844, 188, 5948, 435, 68, 332, 7919, 38, 259, 1110, 504, 7054, 129, 453, 333, 56, 5339, 37, 883, 164, 508, 180, 27, 255, 185, 510, 321, 449, 486, 127, 239], [196, 294, 215, 154, 461, 207, 150, 4587, 7808, 227, 415, 4680, 392, 328, 289, 35, 5565, 414, 426, 181, 179, 298, 4965, 154, 485, 487, 162, 983], [506, 48, 5236, 291, 352, 323, 309, 340, 217, 45, 218, 317, 138, 649, 121, 4058, 222, 4900, 230, 84, 320, 86, 99, 106, 445, 4629, 5931, 125, 106, 185], [3947, 505, 243, 2564, 801, 360, 282, 480, 217, 252, 181]]</t>
+    <t>[[1422, 216, 247], [383, 223, 205, 74, 13, 73, 197, 148, 184], [310, 392, 497, 456, 427], [171, 361, 18, 9, 231, 848, 195, 456, 171]]</t>
   </si>
   <si>
     <t>h64_ws2_idx4096_random_inbf16_outbf16_ID333</t>
   </si>
   <si>
-    <t>[[440, 15, 379, 301, 100, 240, 3335, 212, 26, 590, 90, 472, 146, 404, 1743, 1573], [168, 20, 205, 420, 252, 212, 3373, 233, 3921, 182, 93, 473, 182, 324, 182, 190, 2121, 160, 1164]]</t>
+    <t>[[129], [302, 1075, 360, 485, 281, 471, 801, 445, 226]]</t>
   </si>
   <si>
     <t>h256_ws8_idx4096_random_inbf16_outbf16_ID334</t>
   </si>
   <si>
-    <t>[[409, 219, 191, 376, 1430, 83, 74, 3728, 432, 126, 369, 369, 607, 459, 481, 64, 2250, 154, 265, 226, 54, 2441, 1748, 85, 410, 2779, 143, 362, 48, 73, 509, 334], [108, 63, 3128, 20, 471, 219, 2649, 364, 61, 21, 190, 70, 437, 224, 86, 36, 1540, 457, 447, 402, 314, 186, 3387, 331, 301, 346, 68, 4062, 951], [458, 3057, 296, 691, 226, 69, 461, 240, 399, 1164, 202, 145, 420], [430, 3308, 2449, 1861, 19, 83, 48, 260, 288, 375, 176, 157, 267, 351, 290], [483, 229, 216, 3953, 458, 1044, 326, 365, 2018, 401, 476, 190, 11, 161, 3539, 167, 179, 7, 424], [93, 40, 147, 2297, 358, 166, 163, 1216, 187, 80, 21, 479, 191, 950, 2342, 117], [474, 469, 455, 2015, 94, 34, 3193, 171], [1036]]</t>
+    <t>[[399, 121, 488, 18, 142, 58, 37, 100, 127, 160], [257, 335, 1990, 1011, 457, 390, 672, 426, 323], [1848, 1738, 182, 444], [386, 1446, 123, 3, 42, 245, 251, 213, 246, 12], [477, 486, 188, 145, 328], [244, 57, 311, 79, 15, 1253, 1976, 930, 446], [26, 249, 117, 260, 1135, 241, 94, 163], [333, 1381, 448, 1384, 374, 4, 1539, 92]]</t>
   </si>
   <si>
     <t>h256_ws8_idx4096_random_inbf16_outbf16_ID335</t>
   </si>
   <si>
-    <t>[[433, 436, 1172, 2061, 20, 302, 451, 496, 428, 225, 424, 321, 2082, 208, 2096, 162, 23, 450, 357, 4, 257, 3906, 226, 277, 899, 74, 260], [1060, 52, 507, 183, 2106, 349, 183, 345, 167, 409, 464, 415, 1625, 84, 1603, 459, 323, 437], [159, 444, 3597, 369, 3599, 447, 166, 101, 432, 288, 425, 54, 343, 247, 201, 36, 3620, 293, 458, 199, 124, 862, 1, 2729, 392, 111, 240, 241, 5, 2680], [335, 394, 368, 2549, 1082, 315, 203, 129, 3889, 251, 213, 308], [3898, 232, 108, 339, 87, 2407, 125], [160, 2570, 202, 253, 144, 315, 288, 457, 447, 226, 546, 314, 99, 319, 2804, 301, 228, 3111, 2126, 47, 197], [260, 401, 3561, 2640, 2815, 374, 246, 459, 1963, 299, 264, 31, 292, 80, 72, 378, 367, 135, 139], [319, 1775, 18, 480, 444, 63, 454, 325, 503, 305, 1811, 474, 1506, 13]]</t>
+    <t>[[297, 98, 484, 156, 158, 466, 472, 128, 50, 177], [189, 34, 407], [63, 444, 465, 183, 123, 177, 89, 151], [444, 344, 23, 1047], [237, 298], [43, 143, 78, 211, 496, 248, 168], [372, 610, 428, 173, 54, 453, 365, 248, 743], [497, 332, 1371, 127, 75, 320, 389, 126, 497, 480]]</t>
   </si>
   <si>
     <t>h64_ws16_idx16384_random_inbf16_outbf16_ID336</t>
   </si>
   <si>
-    <t>[[59, 351, 476, 145, 97, 6572, 419, 196, 3031, 409, 60, 4908, 378, 481, 324, 76, 289, 9485, 351], [383, 10323, 466, 32, 252, 14295, 4532, 346, 314, 481, 26, 3384, 350, 127, 317, 9016, 425, 26, 328, 145, 389], [2568, 18, 14786, 401, 475, 482, 465, 12540, 384, 14, 268], [378, 418, 448, 7956, 150, 3312, 12126, 139, 408, 12304, 240, 37, 209, 393, 138, 2, 440, 397, 11619, 385, 98, 66, 246], [368, 172, 211, 14759], [505, 426, 251, 1079, 69, 6703, 486], [3218, 479, 5671, 417, 183, 228, 369, 34, 142, 118, 128, 319, 84, 106, 117, 5146, 4138, 421], [9194, 111, 382, 145, 313, 1539, 53, 84, 14773, 16095, 179, 33, 454, 511, 99, 186, 123, 374, 34, 451, 406, 148, 263, 288, 248, 142, 172, 484, 415, 2337, 14044, 9563], [16, 14705, 5, 179, 305, 131, 217, 1331, 416, 467, 174, 463, 309, 142, 396, 450, 16283, 382, 155, 3845, 462, 290, 8087, 104], [12, 8192, 5420, 460, 316, 9677, 267, 11, 490, 321, 382, 343], [451, 232, 8728, 230, 190, 500, 276, 347, 5051, 360, 378, 217, 139, 2648, 15463, 14796, 428, 48, 270, 8163, 466, 277, 94, 290, 340, 327], [240, 31, 12128, 346, 24, 211, 65, 58, 231, 295, 6875, 404, 6279, 130, 263], [254, 5157, 146, 165, 15861, 34, 4408, 460, 1656, 415, 246, 472, 336, 11, 261, 508, 58, 368, 511, 4171, 102, 205], [407, 356, 491, 12862, 119, 12141, 432, 12798, 82, 490, 432, 397, 133, 201, 114, 56, 13209, 96, 482, 423], [471, 14, 482, 342, 5897, 334, 201, 275, 6348], [99, 15825, 322, 192, 172, 2874, 212, 215, 202, 361, 99, 350, 11864, 247]]</t>
+    <t>[[390, 368, 1068, 185, 263, 318, 27, 292], [506, 255, 215, 85], [709, 499], [370, 353, 117, 1417, 12, 411, 151, 202, 178, 178], [265, 458, 479, 311, 243, 141, 346, 345, 122, 444], [215, 156, 371], [362, 22, 430, 429], [173, 509, 219, 131, 225, 401, 164, 490, 372], [288, 292, 365, 269, 376], [169, 123, 391, 15, 76, 182, 1, 55, 416, 162], [453, 103, 49, 100, 13, 9, 275, 146], [488], [388, 6, 26, 822, 54, 245, 434, 1044], [328, 459, 1797, 355, 187, 324], [1660, 455, 41, 234], [39, 409, 16, 405, 8]]</t>
   </si>
   <si>
     <t>h512_ws2_idx2048_random_infp32_outfp32_ID337</t>
   </si>
   <si>
-    <t>[[508, 360, 1703, 318, 343, 1090, 1913, 481, 348, 11, 225, 294], [24, 272, 312, 497, 1812, 187, 769, 382, 379, 53, 1256, 462, 831, 233, 178, 196, 308, 133, 195, 443, 692, 772, 470, 182, 410, 341, 46]]</t>
+    <t>[[428, 187, 505, 1194, 730, 277, 21, 352, 262, 315], [1268, 167, 503]]</t>
   </si>
   <si>
     <t>h128_ws8_idx16384_random_inbf16_outbf16_ID338</t>
   </si>
   <si>
-    <t>[[438, 289, 301, 236, 14112, 433, 425, 2466, 465, 320, 110, 1128], [390, 466, 208, 15265, 467, 306, 34, 379, 14268, 214], [171, 30, 219, 15867, 98, 393, 82, 833, 2375, 333, 134, 119, 319, 98, 315, 426, 15435, 465], [148, 64, 9058, 269, 384, 130, 275, 94, 75, 494, 441, 13, 10251, 12564], [367, 11, 13413, 228, 380, 16240, 151, 4, 224, 1089, 308, 239, 9352, 339, 82, 339, 460, 37, 264, 256, 13164, 103, 439, 19, 195, 37, 260, 13079, 495, 351], [133, 98, 47, 72, 472, 12416, 46, 2126, 1397, 493, 12030, 377, 102, 371, 416, 112, 263], [456, 46, 460, 148, 13452, 151, 18, 345, 254, 371, 88, 312, 8764, 496, 505, 397, 522, 307, 425, 489, 5039, 177, 269, 318, 5012, 64, 14620], [367, 73, 1615, 6411, 242, 113, 212]]</t>
+    <t>[[1330, 325, 67, 1050, 196, 209, 53, 440, 13], [141, 201, 130, 44, 200, 1438, 134, 271, 404], [319, 348, 374], [1850, 312, 67], [270, 37, 972], [1554, 14], [457, 136, 15, 362, 489], [332, 587, 510, 51, 220, 442]]</t>
   </si>
   <si>
     <t>h128_ws8_idx8192_random_infp16_outfp16_ID339</t>
   </si>
   <si>
-    <t>[[41, 163, 6231, 428, 364, 523, 102, 175, 17, 351, 439, 372, 5312, 163, 71, 270, 311, 5108, 56, 253, 186, 4879, 469, 4504, 349, 210, 347, 17, 224, 2646, 220], [236, 3653, 504, 1550, 403, 2630, 181, 244, 369, 7332, 86, 451, 469, 423, 168, 257, 5128, 435, 439, 153, 339, 54, 163, 449, 202, 1705, 12, 244, 81, 27], [3613, 430, 454, 98], [7335, 212, 479, 367, 42, 481, 119, 2040], [471, 392, 339, 4914, 20, 173, 290, 57, 1050, 271, 484, 100, 4553, 107, 9, 109, 456, 4960, 439, 68, 267, 334, 8083, 461], [411, 8188, 6594, 289, 316, 259, 452, 251, 401, 387], [20, 425, 1654, 126, 421, 4465, 240, 238, 303, 466, 378, 453, 473, 3557, 3800, 28, 40, 12], [8, 424, 1919, 2, 248, 3473]]</t>
+    <t>[[112, 359], [423, 197, 1006, 110, 256, 354], [462], [504, 348, 117, 16, 5, 82], [856, 573], [847, 51], [330, 174, 40, 11, 398, 60, 15, 1341, 12], [328, 28, 423, 440, 159]]</t>
   </si>
   <si>
     <t>h512_ws4_idx8192_random_infp32_outfp32_ID340</t>
   </si>
   <si>
-    <t>[[2010, 417, 454], [2553, 451, 418, 364, 291, 441, 386, 3164, 5940, 253, 57, 303, 99, 111, 503, 59, 5973, 378, 295, 455], [191, 244, 365, 6988], [7246, 362, 3752, 1, 441, 193, 224, 1141, 37, 280, 302, 5267, 202, 406, 285, 341]]</t>
+    <t>[[116, 352, 808], [263, 112, 341, 12, 483], [343, 222, 355, 163, 405, 341, 243, 277], [114, 300, 345, 302, 171, 26]]</t>
   </si>
   <si>
     <t>h128_ws4_idx16384_random_infp16_outfp16_ID341</t>
   </si>
   <si>
-    <t>[[12055, 174, 12351, 91, 457, 238, 21, 291], [1675, 7972, 67, 337, 413, 12519, 334, 152, 244, 31, 366, 274], [6497, 28, 245, 397, 70, 500, 51, 202, 427, 174, 393, 44, 468, 414, 10245, 344, 509, 992, 47, 33, 290, 330, 404, 56, 12436, 2014, 11832], [7616, 392]]</t>
+    <t>[[334, 182, 65, 239, 147, 95, 495, 141, 398], [397, 481, 580, 11, 119, 29], [1845, 903, 36, 142, 260, 1844, 128, 32, 67], [405, 137, 1081, 25, 1813, 22, 1605]]</t>
   </si>
   <si>
     <t>h256_ws8_idx16384_random_infp32_outfp32_ID342</t>
   </si>
   <si>
-    <t>[[508, 121, 202, 165, 190, 437, 6517, 144, 209, 73, 79, 85, 7001, 12600], [497, 165, 127, 64, 2201, 4169, 300, 385, 347, 5057, 401, 271, 101, 235, 270, 491, 443, 380, 266, 16075, 478, 302, 438, 8509, 460, 2386], [462, 131, 325, 390, 470, 245, 170, 358, 11478, 82, 218, 407, 9603, 87, 372, 241, 3128, 5234, 386, 230, 97, 14659, 418, 429, 446], [386, 508, 129, 166, 8625], [119, 508, 408, 25, 350, 423, 102, 11434, 1724, 11928, 459, 275], [306, 189, 10265, 114, 494, 229, 82, 12018, 99, 222, 14906, 469, 26, 1024, 52, 54, 312, 71, 458], [158, 274, 429, 424, 241, 494, 219, 504, 15487, 338, 9455, 161, 403, 47, 375, 19, 112, 391, 14225, 11799, 479, 9333, 14, 163, 87, 385, 12394, 129], [284, 6386]]</t>
+    <t>[[155, 464, 365, 259, 427, 75, 43, 1743, 155], [65, 378, 234, 81, 8, 306, 438, 1349], [300, 1880], [432, 164, 442, 160, 483, 450, 949, 388], [30, 339], [373, 542, 180, 602, 96, 243, 305, 388], [194], [230, 308, 458, 270, 887, 60, 232, 395, 260, 579]]</t>
   </si>
   <si>
     <t>h64_ws16_idx16384_random_infp16_outfp16_ID343</t>
   </si>
   <si>
-    <t>[[7, 10743, 337, 389, 48, 151, 504, 327, 2874, 97, 10092, 440, 214, 317, 174, 11, 13690], [438, 451, 395, 210, 359, 439, 354, 232, 170, 220, 439, 29, 175, 422, 471, 284, 295, 14976, 62, 101, 109, 949, 11492, 178, 4761, 65, 7448, 11398], [96, 230, 185, 93, 4207, 10539, 365, 504, 450, 505, 265, 364, 66, 5173, 158], [153, 864, 8080, 252, 476, 248, 49, 439, 83, 10241, 399, 10693, 304, 370, 299, 317, 197, 510, 2299, 253, 7577, 18, 13362, 471, 430, 159, 221, 195, 128, 377, 488], [245, 87, 2568, 74, 262, 168, 205, 360, 3740], [453, 470, 214, 14310, 399, 650, 253, 301, 6471, 102, 5808, 381, 296, 197, 126, 1185, 263, 451, 307, 116, 145, 354, 454, 83, 109, 12753, 362], [130, 4728, 15843, 9798, 502, 319, 134, 178, 322, 492, 497, 377, 320, 313, 232, 15612, 321, 152, 486, 327], [112, 191, 15479, 198, 422, 482, 9300, 17, 164, 20, 15118, 9979, 509, 376, 209, 459, 4372, 102, 357, 276, 33, 110, 81, 262, 72, 154, 2255, 156, 421], [5038], [110, 457, 202, 481, 335, 386, 399, 11659, 122, 5370, 140, 217, 512, 416, 177, 204, 541, 285, 6937, 186, 390, 422, 9, 192, 11087], [509, 293, 8985, 444, 27, 310, 3, 14403, 145, 13615, 352], [244, 15400], [331, 294, 479, 9598, 95, 16, 60, 3810, 138, 342, 183, 170, 1764, 914, 373, 409, 142, 6608, 357, 390, 490, 256, 172, 340], [15715, 11026, 20, 371, 409, 115, 390, 51, 128, 362, 31, 163, 476, 16219], [118, 220, 99, 175, 479, 21, 6880, 4069, 3, 433], [5392, 95, 401, 258, 432, 166, 10560]]</t>
+    <t>[[225, 414, 276, 334, 471, 334, 65, 44, 1970], [1799, 162, 192, 1445, 379, 443], [546, 163, 137], [253, 376], [405, 414, 984, 294, 1266, 247, 33], [19, 30, 349, 265, 421, 142], [1508, 317, 500, 195, 321], [187, 206, 477, 463, 322, 108, 1729, 77, 339, 275], [1135, 1433], [188, 359, 275], [64, 249, 505, 1274, 215, 439, 56, 163, 200, 1430], [26, 428, 476, 1151], [300, 226, 172, 1330, 490, 333], [1488, 232], [87, 446, 477, 469, 144, 510, 128, 367, 480, 391], [310, 261, 455, 75, 497, 257, 936, 266, 354, 323]]</t>
   </si>
   <si>
     <t>h512_ws4_idx2048_random_infp16_outfp16_ID344</t>
   </si>
   <si>
-    <t>[[421, 502, 1771, 128, 400, 436, 1751, 1091, 386, 291, 165], [366, 81, 53, 1810, 1768, 366], [406, 258, 411, 337, 750, 1394, 1113, 242, 364, 60, 678, 81, 80, 50, 444, 7, 174, 18, 364, 84], [344, 23, 343, 69, 315, 72, 99, 1841, 1548, 481, 449, 484, 1054, 105, 114, 169, 0, 352, 396, 151, 1841, 1373, 7]]</t>
+    <t>[[135, 355, 340, 186, 41, 2, 378], [23], [140, 10, 311, 390, 209], [231, 484, 123, 358, 17, 1847, 110, 42, 95, 381]]</t>
   </si>
   <si>
     <t>h512_ws4_idx16384_random_infp16_outfp16_ID345</t>
   </si>
   <si>
-    <t>[[377, 4591, 207, 77, 15118, 313, 139], [377, 13, 12315, 443, 4309, 510, 477, 245], [11008, 447, 424, 209, 12035, 117], [97, 238, 276, 10084, 14396, 354, 276, 475, 378, 286, 74, 12652, 425, 221, 362, 203, 45, 445, 2122, 58, 304, 52, 14025, 81]]</t>
+    <t>[[1769, 307, 379, 391, 213, 335, 90, 269, 155], [172, 372, 440, 385], [116], [449, 86]]</t>
   </si>
   <si>
     <t>h128_ws2_idx2048_random_inbf16_outbf16_ID346</t>
   </si>
   <si>
-    <t>[[112, 463, 410, 646, 29, 133, 374, 466, 309, 473, 288, 291, 665, 379, 397, 144, 1305, 1565, 71, 185, 488, 1505, 369, 73, 69, 1215, 381, 240, 1014, 489, 186, 255], [387, 3, 253, 590]]</t>
+    <t>[[1255, 389, 175, 70, 299, 109, 452], [436, 67]]</t>
   </si>
   <si>
     <t>h128_ws8_idx4096_random_inbf16_outbf16_ID347</t>
   </si>
   <si>
-    <t>[[20, 1036, 305, 360, 291, 78, 124, 462, 1218, 379, 1399], [1625, 184, 2, 91, 335, 3520], [489, 351, 1218, 320, 372, 2870, 423, 373, 204, 486], [133, 250, 3899], [254, 108, 2352, 62, 257, 430, 394, 425, 290, 1581, 345, 3711, 223, 519, 57, 180], [2585, 1329, 71, 114, 268, 399, 314, 1343, 195, 301, 240, 188, 98, 436, 107, 1292, 355, 237, 183, 455, 990], [3439, 325], [3402, 405, 814, 223, 148, 875, 129, 381, 37, 145, 1135, 47, 395, 328, 106, 294, 86, 357, 155, 318]]</t>
+    <t>[[1129, 331, 509, 360], [224, 437, 1326, 68, 264, 424, 113, 357], [823], [51, 133, 795, 97, 285, 1550, 195, 491, 1198, 146], [32, 297, 278, 458, 378, 315, 88, 881], [454, 98], [153, 367, 479, 227, 450, 387, 7], [38, 238, 252, 31, 196, 64, 143, 280, 395]]</t>
   </si>
   <si>
     <t>h64_ws4_idx16384_random_inbf16_outbf16_ID348</t>
   </si>
   <si>
-    <t>[[506, 32, 436, 3565, 127, 284, 101, 95, 3864, 97, 479, 198, 13550, 455, 160, 97, 39, 11978, 324, 190, 483, 98, 333, 216, 351, 3833, 3283, 38, 325, 13078, 204], [7625, 328, 14142, 29, 470, 396, 323, 48, 110, 94], [12794], [1656, 108]]</t>
+    <t>[[1000, 108, 193], [294, 316, 518, 161, 743, 307, 240, 104, 438], [287, 345, 109, 248, 324, 22, 223, 1581], [314, 473, 329, 185, 75, 81, 232, 306, 9]]</t>
   </si>
   <si>
     <t>h64_ws4_idx8192_random_infp16_outfp16_ID349</t>
   </si>
   <si>
-    <t>[[3287, 1021, 192, 208, 468, 93, 374, 6581, 98, 2920, 476, 4416, 345, 79, 206, 28, 440, 88, 148, 59, 69, 331, 506], [255, 2763], [186, 364, 111, 2, 1230, 5000, 115, 432, 6896, 209, 3, 171], [153, 945, 91, 144, 60, 455, 27, 246, 6782, 1030, 346]]</t>
+    <t>[[193, 62, 1539, 250, 330, 217], [1435, 1333, 502, 219], [1101, 802], [391, 61, 54, 342, 227, 453]]</t>
   </si>
   <si>
     <t>h128_ws4_idx8192_random_inbf16_outbf16_ID350</t>
   </si>
   <si>
-    <t>[[2696, 100, 16, 285, 70, 429, 180, 5697, 411, 2183, 72, 165, 386, 90, 80, 491, 3641, 500, 373], [304, 5760, 78, 7, 157, 142, 231, 231, 1368, 302, 347, 227, 0, 140, 390, 1729, 11, 184, 4365, 5560, 222, 53], [5060], [155, 327, 419, 39, 1445, 347, 1491, 3541, 1327, 457, 511, 441, 401, 149, 318, 187, 15, 50, 2214, 492, 486]]</t>
+    <t>[[251, 158, 49, 463, 8, 29, 1543, 1279, 209, 377], [178, 335, 339, 21, 258, 308, 510], [986, 87, 166, 795, 394, 254, 240, 1651, 143], [87, 270, 88, 67, 122, 23, 464, 432, 331]]</t>
   </si>
   <si>
     <t>h512_ws16_idx8192_random_inbf16_outbf16_ID351</t>
   </si>
   <si>
-    <t>[[490, 485, 21, 3461, 403, 2873, 375, 499, 148], [504, 8020, 2266, 7464, 512, 471, 465, 6, 135, 179, 284, 359, 338], [245, 228, 103, 5384, 430, 19, 4927], [5457, 273, 284, 204, 4, 253, 309, 5655, 362, 234, 411, 113, 1396, 236, 172, 20, 685], [59, 4753, 5637, 43, 1806, 438, 433, 300, 107, 466, 99], [4149, 303, 70, 300, 3275, 140, 368, 215], [240, 258, 721, 247, 359, 187, 506, 214, 91, 7518, 13, 443, 44, 164, 2073, 3572, 41, 1970, 65, 27, 182, 292, 20, 57, 91], [6608, 394], [141, 16, 38, 3, 531, 1199, 29, 319, 213, 123, 20, 1070, 7335, 380, 251, 9, 452, 51, 401, 219, 355, 304, 6485, 4826, 159, 281], [9, 3711, 403, 29, 274, 401, 344, 345, 325, 417, 8187, 1039, 248, 350, 165, 121, 225, 2622, 1781, 498, 466], [150, 367, 332, 65, 39, 50, 7101, 123, 13, 6100, 440, 1132, 470, 256], [314, 287, 340, 2744, 49, 24, 88, 5617, 7134, 232, 216, 182], [50, 1139, 1841, 386, 279, 139, 297, 341, 4753, 3933, 144, 498, 15, 302, 120, 17], [262, 3953, 305, 174, 511, 81, 133, 3914, 342, 442, 73, 111, 5481, 20, 401, 475, 452, 301, 483, 206, 4267, 175, 7393], [4830], [222, 397, 368, 3678, 343, 4, 1880, 453, 315, 6772, 387, 88, 63, 471, 118, 202, 403, 5244, 101]]</t>
+    <t>[[202, 143, 57, 119, 193, 427, 163, 3], [133, 125, 113], [1294], [266, 94, 188, 38, 1231, 384, 1134, 539, 78], [124, 34, 497, 118, 272, 705, 97], [494, 115, 309, 302, 512, 44, 363, 179, 299], [47, 264, 95, 1830, 366, 1787, 231, 263, 299], [139, 110, 171, 392, 335], [396, 923, 138, 1021, 189, 129, 1225, 92, 329, 332], [472, 497, 459, 84, 1888], [460, 297, 418, 333, 553, 35, 379, 104, 235, 26], [861, 306, 1993, 420, 31, 431], [381, 1759, 396, 85, 4, 459, 348, 30, 266], [1496, 450, 465], [136, 55, 494, 1272], [78, 393, 311, 153, 1662, 334, 347]]</t>
   </si>
   <si>
     <t>h512_ws4_idx16384_random_inbf16_outbf16_ID352</t>
   </si>
   <si>
-    <t>[[387, 9542, 6337, 109, 160, 243, 94, 479, 359, 113, 14520, 5671, 264, 21, 31, 397, 88], [284, 340, 75, 1986, 298, 6867, 296, 167, 382, 8312, 150, 164, 32, 4067, 410, 216, 233, 235, 299, 201, 193, 329, 24, 199, 6291, 76, 413, 1898, 496, 233, 8197], [15677, 3234, 1836, 425, 32, 938, 207, 302, 69, 36, 28, 256, 196, 240, 418, 26, 250, 388, 420, 6542, 407, 476], [355, 15420, 38, 359, 80, 5839, 497, 448, 387, 2844, 327, 362]]</t>
+    <t>[[300, 39, 112, 133, 506, 229, 56], [438, 398, 286], [264, 19, 332, 315, 257], [318, 313, 329, 319, 1221, 36, 30, 13, 174]]</t>
   </si>
   <si>
     <t>h128_ws8_idx32768_random_inbf16_outbf16_ID353</t>
   </si>
   <si>
-    <t>[[505, 18298, 56, 9934, 181, 92, 300, 2474, 89, 288, 459, 165, 80, 357, 12698, 9], [426, 55, 266, 166, 18217, 352, 372, 233, 332, 488, 185, 29180, 137, 29, 81, 220, 400, 5109, 22953, 207, 28279], [15, 497, 108, 27, 335, 281, 5832, 30767, 280, 129, 18561], [249, 456, 361, 370, 123, 29858, 482, 428, 361, 511, 17799, 469, 150, 138, 53, 31806, 5745, 244, 194, 22665, 481, 129], [330, 22631], [501, 5126, 198, 182, 159, 76, 482, 28663, 337, 254, 58, 9, 365, 14774, 6, 275, 15966, 117, 284, 187, 357, 292, 73, 20476], [497, 176, 12342], [354, 23232, 73, 185, 413, 18415, 253, 97, 196, 426, 21455, 189, 239, 327]]</t>
+    <t>[[71, 471, 276, 428, 378, 87, 262, 246, 1154, 27], [114, 362, 459, 482, 120, 269, 336, 291], [146, 298, 242, 267, 478], [284, 144, 1253, 649, 1175, 330, 71], [32, 130], [101, 269, 1148, 331], [734, 206], [475, 360, 331, 976, 79, 231, 22, 448, 495]]</t>
   </si>
   <si>
     <t>h256_ws16_idx16384_random_inbf16_outbf16_ID354</t>
   </si>
   <si>
-    <t>[[171, 12168, 201, 151, 338, 7617, 295, 246, 104, 321, 210, 429, 233, 8107, 303, 461, 324, 2491, 188, 291, 137, 350, 161, 8227, 1484, 504, 84, 310, 460, 306], [110, 203, 8527, 325, 96, 182, 372, 285, 15687, 310, 361, 158, 4416], [160, 381, 5551, 145, 11052, 169, 293, 221, 258, 94, 457, 413, 286, 73, 373, 475, 180, 282, 2707, 9079, 40, 5497, 377], [375, 510, 11966, 360, 255, 1566, 255, 428], [365, 270, 393, 489, 213, 463, 70, 236, 4627, 7040], [3731, 6046, 189, 3762, 217, 65, 35, 300, 4800, 427, 185, 378, 62, 11, 217, 179, 354, 114, 18], [12388, 204, 16242, 430, 270, 14996, 70, 184, 104, 75, 9968, 53, 284, 276, 314, 91, 4075, 46, 437, 357, 174], [325, 170, 33, 236, 236, 185, 298, 12750, 11700, 195, 231, 16343, 5584, 161, 282, 137, 11458, 182, 492, 453, 157, 304, 4769, 86, 288, 124, 199], [98, 344, 249, 1, 138, 482, 224, 511, 249, 5617, 80, 9972, 460, 33, 118, 341, 252, 12767, 209, 78, 275, 4813, 359, 213, 151, 469, 12631, 164, 4992], [16315, 194, 432, 10577, 118, 412, 1556, 305, 36, 450, 414], [6581, 14959, 350, 54, 474, 224], [56, 296, 7, 6790, 15335, 8, 12713, 222, 264, 63, 374, 148, 185, 141, 9546, 382, 358, 126, 18, 5112, 489, 197], [4, 8816, 414, 14210, 435, 282, 439, 279, 75, 285, 366, 233, 5919, 40, 247, 9255, 58], [133, 446, 464, 13614, 281, 423, 328, 241, 469, 439, 163, 151, 302, 2755, 5171, 473, 504, 11158, 165, 358], [461, 12107, 10229, 221, 12363, 302, 437, 218, 206, 14519, 338, 31, 73, 502, 120, 18], [74, 10714, 187, 8158, 62, 441, 444, 30, 6600, 405, 15009, 370, 77, 337, 325, 9459, 12974, 177, 263, 277, 24, 116, 1, 442, 361, 281]]</t>
+    <t>[[347, 1675, 477, 864, 412, 307, 19], [291, 407, 250, 1989, 440, 78, 983, 647, 478, 1530], [71], [266, 1108, 85, 325, 86, 35, 384], [326, 392, 499, 193, 396, 312, 262, 139, 122, 503], [415, 189, 482, 24, 327, 267], [730, 394, 345, 56, 263, 467, 1629], [6, 743, 278, 61, 184, 76, 617, 96], [195], [280, 347, 1637], [189, 80, 457, 286, 444, 222, 451], [26, 256, 88, 89], [10], [2047, 237, 126, 216, 311], [406, 223, 68], [423, 201, 58]]</t>
   </si>
   <si>
     <t>h64_ws4_idx8192_random_inbf16_outbf16_ID355</t>
   </si>
   <si>
-    <t>[[4, 4764, 244, 7144, 7481, 424, 478, 489, 188, 160, 203, 236, 232, 190, 68, 504, 312, 1273, 421, 39, 109, 151, 265, 1494], [415, 8153, 300, 43, 486, 4059, 491, 363, 349, 482, 332, 419, 206, 163, 1388, 475, 1644, 13, 510], [1162, 473, 447, 414, 2118, 175, 442, 162, 165, 2990, 25, 483], [1355, 294, 66, 147, 88, 172, 303, 353, 433, 150, 268, 205, 181, 52, 6606, 279, 4209, 4463, 1707, 43, 5390, 391, 313, 441, 410, 162, 471]]</t>
+    <t>[[1051, 1969, 38, 70, 417], [255, 118, 421, 345, 441, 276, 288, 439, 191, 1336], [38, 1805, 243, 325, 95, 208, 72, 132], [79, 141, 254, 174, 483]]</t>
   </si>
   <si>
     <t>h64_ws2_idx8192_random_inbf16_outbf16_ID356</t>
   </si>
   <si>
-    <t>[[27, 2448, 449], [176, 184, 322, 119, 421, 269, 51, 1445, 71, 3069, 101, 81, 2530, 348, 459, 4390, 466, 165, 4627, 272, 371, 413, 368, 35, 270, 1967]]</t>
+    <t>[[220, 246, 789, 478, 193, 739, 493], [301]]</t>
   </si>
   <si>
     <t>h64_ws2_idx4096_random_inbf16_outbf16_ID357</t>
   </si>
   <si>
-    <t>[[187, 1555, 316, 175, 3995, 100], [132, 286, 3956, 460, 415, 437, 161, 1453, 18, 374, 189, 3782, 356]]</t>
+    <t>[[222, 166, 282, 378, 452, 1057], [341, 79, 1436, 212, 125, 1934, 244, 195, 359, 9]]</t>
   </si>
   <si>
     <t>h128_ws2_idx4096_random_inbf16_outbf16_ID358</t>
   </si>
   <si>
-    <t>[[703, 207, 205, 366, 209, 148, 557, 167, 111, 237, 98, 372, 487, 475, 507, 98, 163, 1620, 673], [444, 252, 3048, 1508, 145, 444, 7, 76, 140, 51]]</t>
+    <t>[[273, 100, 325, 510, 399, 124, 411, 422, 492, 279], [489, 234, 466]]</t>
   </si>
   <si>
     <t>h128_ws4_idx2048_random_infp32_outfp32_ID359</t>
   </si>
   <si>
-    <t>[[118, 235, 118, 161, 93, 20, 310, 91, 158, 132, 343, 216, 189, 400, 332, 284, 560, 66, 449, 563, 259, 524, 82, 385, 213, 29, 1579, 697, 334, 838, 105, 529], [1833, 379, 285, 119, 511, 304, 386, 437, 186, 81, 239, 342, 141, 495, 335, 52, 919, 26, 283, 127, 28, 1295, 259, 1027, 1582, 877, 442], [195, 88, 454, 1632, 243, 463, 79, 386, 300, 506, 261, 41, 45, 409, 1158, 47, 174, 337, 98, 1569, 136, 495, 1917, 296, 1177, 1787, 204, 260, 48, 42, 1900], [259, 107, 397, 349, 1570]]</t>
+    <t>[[629, 263, 60, 55, 206, 500, 431, 417, 121], [205, 257, 356, 177, 184, 140, 105], [1215, 896, 140], [461, 190, 214, 481, 905]]</t>
   </si>
   <si>
     <t>h64_ws16_idx16384_random_infp16_outfp16_ID360</t>
   </si>
   <si>
-    <t>[[500, 482, 436, 118, 475, 56, 97, 336, 268, 4938, 10, 286, 6384, 117, 337, 491, 10414, 138, 348, 1249, 355, 5609, 505, 445], [12640, 402, 236, 506, 195, 366, 8, 362, 297, 7224], [383, 42, 502, 4246, 12732, 73, 7314, 188, 176, 509, 469, 437, 128, 410, 282, 364, 14218, 169, 344, 6710, 223], [195, 503, 401, 394, 6, 380, 142, 284, 471, 1625, 181, 360, 11130, 3976, 483, 449, 507, 243, 115, 12397, 437, 11896, 498, 2517, 392, 225, 494, 210], [22, 64, 3618, 399, 1539, 464, 328, 872, 83, 402, 419], [75, 15068], [294, 32, 467, 10911, 8660, 396], [2189, 112, 326, 63, 62, 195, 108, 54, 95, 11570, 457, 3793, 57, 486, 483, 144, 304, 4954, 234, 362, 412, 11455, 203, 68, 157, 293, 9347], [8925], [219, 266, 727, 353, 175, 14838, 433, 8, 502, 227, 242, 223, 10, 340, 5631, 13972, 499, 373, 29, 323, 109, 70, 143, 184, 15171, 383, 330, 218, 4354], [278, 254, 372, 361, 8731], [426, 217, 262, 286, 346, 11346, 273, 9190, 91, 81, 476, 12317, 342, 12083, 177, 9905, 383, 420, 75, 139, 140, 91], [14510, 5679, 233, 207, 317, 12206, 127, 3540, 284, 337, 299, 76, 158, 438, 85, 26, 507, 250, 196, 163], [101, 15221, 195], [2551, 15541, 60, 348, 223, 12417, 489, 396, 116, 163, 387, 490, 385], [157, 364, 210, 456, 157, 440, 16139, 39, 10036, 189, 150, 178, 124, 1296, 93, 6367, 115, 6367, 246, 188, 354, 300, 132]]</t>
+    <t>[[498, 60, 23, 321, 408, 208, 1691, 254], [2036, 478, 40, 1403, 1983, 498, 282, 433, 86, 217], [295, 95, 153, 136, 43, 274, 463, 212, 441], [169, 477], [502, 511, 32, 360, 448, 233, 409, 280], [909, 1877, 404], [269, 383, 727, 397, 46, 79, 240, 1516], [470], [312, 398, 303, 56, 88], [151, 328, 448, 1104], [1867, 56, 412, 93, 1848, 336], [307, 132, 319], [1752, 141, 1806, 484, 218, 66, 314, 338, 424, 39], [241, 93, 1611, 507], [23, 1105, 20, 4, 126, 510], [1944, 319]]</t>
   </si>
   <si>
     <t>h512_ws8_idx32768_random_infp32_outfp32_ID361</t>
   </si>
   <si>
-    <t>[[9455, 209, 58, 490, 138, 124, 285, 17294, 8, 77, 3375, 53, 8, 97, 11108, 3], [780, 377, 168], [442, 405, 13904, 295, 71, 206, 17629, 397, 86, 278], [168, 277, 189, 61, 470, 409, 285, 19148, 18723, 264, 363, 170, 170, 3120, 26660, 304, 500, 440, 379, 26, 302, 214, 22297, 169], [387, 4890, 57, 439, 32561, 347, 322, 75, 51, 296, 495, 17236, 340], [421, 405, 416, 5, 8383, 28, 55, 411, 12205, 126, 19535, 340, 422, 472, 168, 161, 2877, 363], [167, 173, 7691, 371, 275, 312, 155, 27613, 134, 460, 215, 100, 52, 289, 415, 4657, 254, 343, 5868, 15578, 222, 453, 126, 6360, 229, 455, 62, 243, 4, 475], [190, 32286, 282, 63, 115, 2179, 64, 112, 200, 287, 25890, 459, 388, 16209, 510, 439, 497, 84, 503, 17700, 257, 412]]</t>
+    <t>[[46, 488, 370, 835, 2009], [348, 379, 228, 733, 454, 7, 478, 369, 457], [106, 13, 34, 232], [1288, 213, 429, 1959, 108, 66, 370, 471, 202, 469], [162, 52, 388, 452], [628, 245, 191, 45, 389, 319, 453, 400], [245, 122, 42, 1967, 205, 439, 164, 96, 146], [67, 71, 390, 500, 173, 76, 371, 269]]</t>
   </si>
   <si>
     <t>h512_ws2_idx2048_random_infp16_outfp16_ID362</t>
   </si>
   <si>
-    <t>[[202, 1899, 809, 358, 116, 22], [195, 341, 891, 497, 557, 57, 400, 163, 411, 408, 291, 1741, 65, 12, 1569, 142, 497, 81, 892, 281, 448, 274, 363, 327]]</t>
+    <t>[[33, 31, 270, 121, 325, 79, 171, 96, 136], [355, 1119, 490, 366, 407, 264, 155, 206, 43, 271]]</t>
   </si>
   <si>
     <t>h128_ws16_idx32768_random_infp32_outfp32_ID363</t>
   </si>
   <si>
-    <t>[[138, 244, 36, 488, 97, 471, 25322, 256, 420, 486, 120, 335, 463, 13, 0, 191, 27703, 78, 32, 812, 24074, 103, 336, 16696, 137, 467, 16723, 337], [16188, 503, 20096, 35, 476, 421, 204, 356, 441, 278, 292, 12072], [241, 254, 318, 37, 32282, 203, 15, 151, 20990, 267, 6502, 101, 181, 5019, 404, 93], [29721, 308, 325, 268], [19597], [328, 251, 10147, 170, 22246, 497, 5683, 4, 282, 244, 253], [11940, 401, 110, 414, 243, 92, 331, 486, 30852, 254, 247, 370, 270, 103, 3937, 159, 23816], [31, 32481, 188, 171, 18689, 251], [247, 264, 81, 17582, 325], [82, 2996, 4536, 358, 20496, 18871, 415, 21968, 265, 98, 250, 425, 286, 481, 370, 507, 308, 242, 202, 183, 352], [26238, 502, 472, 431, 195, 312, 4540, 215, 488, 31, 274, 368, 27702, 414, 7095, 175, 409, 154, 214], [77, 237, 161, 478, 481, 398, 266, 26, 316, 10648, 98, 182, 464, 325, 80, 51, 32, 29085, 11480, 7309], [192, 17, 5048, 444, 116, 437, 25, 226, 23023, 248, 86, 168, 270, 25, 96, 341, 490, 330, 15800, 5102, 69, 26691, 3760, 213, 138, 23664, 132, 159, 300, 61, 317], [214, 27287, 7556, 87, 487, 485, 5517, 25, 386, 9, 493, 463, 242, 477], [423, 127, 200, 469, 86, 29908, 23784, 332], [148, 6898, 441, 338, 186, 455, 20421, 265, 264, 495, 51, 17002, 381, 477, 247, 110, 402, 455, 365, 272, 25110, 9661, 262, 84, 267]]</t>
+    <t>[[369, 449, 1770, 14, 24, 121, 96, 34, 1573], [1162, 875, 80, 280, 355, 307, 460, 233, 323, 220], [434, 245, 2, 378], [63, 266, 24, 102, 478], [46, 39, 296, 32, 165, 263, 238, 215], [102, 46, 92], [102, 413, 365, 449], [953, 209, 283, 100, 73, 212, 130, 29, 212, 493], [15, 14, 445, 153, 120], [235, 166, 494], [79], [228, 1044, 142], [1788, 280, 272, 132, 207], [70, 4, 6, 335, 552, 389, 2023, 66, 482], [454, 955, 205, 303, 638, 1284, 263, 306, 192], [100, 460, 505, 40, 281, 1135, 9, 370, 587]]</t>
   </si>
   <si>
     <t>h128_ws2_idx4096_random_infp16_outfp16_ID364</t>
   </si>
   <si>
-    <t>[[132, 1442, 465, 239, 15, 315, 347, 99, 3939, 287, 3941, 393, 11, 220, 910, 247, 161, 150, 59, 316], [248, 2965, 480, 302, 99, 2122, 296, 12, 3934, 1280, 172, 100, 125, 441, 465, 298, 395, 81, 281, 198, 362, 91, 3937, 211, 39]]</t>
+    <t>[[442, 227, 382, 93, 200], [1108, 1854, 1225, 493, 334]]</t>
   </si>
   <si>
     <t>h64_ws4_idx2048_random_inbf16_outbf16_ID365</t>
   </si>
   <si>
-    <t>[[93, 360, 21, 364, 389, 1637, 207, 136, 199, 406, 623, 50, 928, 443, 402, 514, 681, 148, 382, 65, 151, 174, 174, 189, 478], [23, 93, 121, 682, 495, 174, 121, 1315], [109, 682, 1396, 1085, 194, 100, 293, 446, 188, 240, 111, 19, 374, 208, 36, 352, 241, 277, 188, 59, 385, 1844, 1167, 360, 495, 89, 115, 626], [327, 2, 806, 1846, 401, 908, 37, 251, 487, 101, 527, 52, 462, 430, 250, 101, 334, 359, 340]]</t>
+    <t>[[92, 328, 1273, 507, 166, 157, 248, 1917, 449, 141], [328, 361, 162, 1, 1870, 278, 346, 434, 596], [468, 182, 500, 92, 561, 8], [1710, 372, 252, 389, 435, 116, 470]]</t>
   </si>
   <si>
     <t>h512_ws4_idx4096_random_inbf16_outbf16_ID366</t>
   </si>
   <si>
-    <t>[[1403, 73], [239, 131, 354, 262, 58, 131, 1715, 3364, 75, 187, 172, 3687], [507, 125, 147, 443, 391, 52, 1729, 201, 358, 18, 241, 205, 380, 461, 2114, 2708, 1615, 205], [365, 507, 1327]]</t>
+    <t>[[105, 17, 491, 68, 318, 355], [1103, 290, 1937, 493, 236, 6], [85, 113, 277, 619, 66, 89, 280, 222, 216], [438, 470, 166]]</t>
   </si>
   <si>
     <t>h64_ws2_idx2048_random_infp32_outfp32_ID367</t>
   </si>
   <si>
-    <t>[[218, 35, 257, 307, 169, 458, 288, 369, 395, 392, 2012, 361, 1405, 358, 202, 851, 304, 64, 56, 1481], [1321, 34, 55, 98, 1714, 505, 1647, 491, 222, 149, 114, 401, 50, 125, 249, 178, 319, 495, 972, 947, 403, 214, 502, 236, 87]]</t>
+    <t>[[287, 428, 1382, 293, 132, 409, 214], [455, 238, 53, 258, 258, 30, 507]]</t>
   </si>
   <si>
     <t>h64_ws2_idx8192_random_inbf16_outbf16_ID368</t>
   </si>
   <si>
-    <t>[[113, 7407, 448, 4943, 36, 161, 7382, 123, 446, 93, 410, 86, 405, 388, 512, 382, 747, 2210, 384, 442, 415, 58, 148, 160, 33, 5971, 90], [57, 294, 281, 258, 508, 171, 6645, 252, 2850]]</t>
+    <t>[[286, 1254, 176, 499, 94, 2038], [226]]</t>
   </si>
   <si>
     <t>h256_ws8_idx16384_random_inbf16_outbf16_ID369</t>
   </si>
   <si>
-    <t>[[2967, 448, 16, 83, 64, 15431, 464], [426, 276, 6893, 38, 156, 166, 448, 35, 164, 210, 359, 310, 470, 1959, 409, 179, 7333, 360, 11352, 23, 318, 45, 119, 8618, 331, 5823], [478, 17, 64, 2555, 15608, 82, 89, 221, 3065, 218, 271, 157, 493], [3764, 45, 364, 13007, 94, 152, 192, 255, 512, 409, 227, 230, 334, 8474, 404, 12786, 249, 119, 465, 120], [255, 8419, 44, 175, 305, 501, 132, 83, 7482, 338, 403, 198, 464, 510, 280, 12642, 13617, 2021, 147, 342, 294, 415, 189, 395], [5241, 189, 145, 402, 419, 12906, 78, 213, 183, 13512, 7379, 176, 13, 461, 270, 430, 51, 434, 312, 276, 230, 267, 320, 3997, 229], [4, 342, 8583], [9472, 13937, 424, 269, 250, 397]]</t>
+    <t>[[124, 350, 1379, 213, 527, 219, 423], [20, 393, 52, 64, 380], [1777, 1702, 101, 33], [278, 511, 413, 508, 81, 1430, 240, 1480, 284, 152], [224, 240, 301, 1432], [428, 140, 219], [53, 510, 6, 44, 1670, 285, 380, 1882, 345], [345, 26, 500, 435, 400]]</t>
   </si>
   <si>
     <t>h256_ws2_idx1024_random_inbf16_outbf16_ID370</t>
   </si>
   <si>
-    <t>[[235, 361, 172, 794, 711, 120, 63, 74, 473, 20, 396, 920, 269, 181, 840, 333, 2, 96, 2, 122, 272, 597, 464, 282, 356, 173, 151, 642, 936, 288, 421], [864, 473, 321, 549, 326, 803, 134, 428, 29, 154, 264, 343, 22, 40, 379, 350, 705, 263, 21, 284, 748, 216, 191, 407, 169]]</t>
+    <t>[[7, 234, 311, 172, 378, 14, 234], [316, 324, 219, 220, 518, 186]]</t>
   </si>
   <si>
     <t>h256_ws2_idx8192_random_infp16_outfp16_ID371</t>
   </si>
   <si>
-    <t>[[7681, 185, 8121, 305, 63, 2111, 36, 158, 60, 436, 28, 7661, 48, 6, 452, 149, 496], [7534, 475]]</t>
+    <t>[[173, 1899, 251, 432, 371, 190, 8, 662, 462, 233], [396, 207, 285, 242, 1264, 308, 22, 493]]</t>
   </si>
   <si>
     <t>h64_ws2_idx8192_random_inbf16_outbf16_ID372</t>
   </si>
   <si>
-    <t>[[362, 466, 477, 311, 18, 335, 7766, 508, 320, 2758, 504, 2353, 265, 208, 151, 1248, 390, 7092, 508, 292, 96, 192, 210, 52, 496, 5382, 335, 381], [4264, 489, 34, 399, 6492, 491]]</t>
+    <t>[[400, 1934, 216, 493, 245, 263, 512, 1, 1332], [512, 486]]</t>
   </si>
   <si>
     <t>h512_ws16_idx8192_random_infp32_outfp32_ID373</t>
   </si>
   <si>
-    <t>[[3791, 7, 444, 15, 428, 197, 2888, 244], [269, 408, 54, 118, 103, 128, 216, 14, 291, 3244, 337, 73, 103, 91, 14, 279, 6740, 5903, 372, 1943, 337, 225, 324, 376, 2907, 1528], [415, 474, 7824, 447, 248, 173, 345, 17, 382, 6666, 5160, 344], [5319, 93, 46, 130, 80, 136, 6984], [4254, 322, 36, 317, 298, 7421, 352, 53, 457, 109], [7, 164, 1748, 5657, 278, 470, 72, 189, 120, 480, 4085, 391, 154, 393, 151], [347, 6400, 464, 261, 293, 451, 5522, 296, 344], [2202, 393, 224, 1044, 304, 45, 193, 289, 12, 2847, 427, 374, 408, 278, 170, 183, 95, 14, 1818], [101, 5128, 467, 177, 261, 379, 389, 7802, 220, 63, 308, 5903, 496, 213, 5391, 144, 480, 117, 385, 328], [251, 291, 7738, 7725, 4774, 275, 55, 1071, 461, 238, 418, 184, 164, 160, 376, 84, 295, 99, 309, 125, 5644, 81, 441, 501], [6733, 109, 53, 354, 55, 340, 508, 218, 4920, 4461, 339, 18, 179, 3947, 428, 322, 1847, 243, 99, 265, 92, 285, 45], [170, 98, 5143, 3526, 459, 374, 451, 4080, 202, 86, 35, 300, 4, 75, 2606, 81, 101], [427, 490, 26, 440, 5751, 430, 193, 453, 148, 497, 3536, 51, 403, 2157, 4844, 381, 279, 178], [378, 496, 356, 222, 441, 442, 5348, 100, 472, 225, 195, 466, 6352, 2046], [84, 4350, 1797, 249, 45, 47, 31, 19, 2469, 281, 3024, 272, 3041, 109, 176, 267, 240, 84, 340, 3551, 192, 59, 361, 271, 185, 273, 455, 170, 5764, 127, 229, 61], [90, 5860, 178, 299, 444, 4417, 152, 353, 194, 179, 389, 838, 61, 26, 468, 380, 7826, 171, 506, 216, 297, 2867, 3908, 293, 230, 6452, 372, 499, 188, 454, 73]]</t>
+    <t>[[385, 213, 1848, 439, 376, 281, 231], [50, 144, 296, 355, 9, 150, 512], [287, 111, 96, 15, 655, 287, 469], [105, 74, 386, 347, 261, 262, 230, 336], [7, 63, 86, 423, 98, 2, 235], [1591, 264, 461, 844], [280, 998, 487, 92], [297], [493, 212], [88, 250, 226, 303, 289, 358, 1942], [545, 1545, 361, 309, 298, 447, 29, 54, 213], [200, 156, 173, 117, 362], [305, 1, 144], [28, 293, 2039, 327, 31, 57], [459, 345, 463, 360], [374, 465, 197, 454, 65, 206]]</t>
   </si>
   <si>
     <t>h128_ws2_idx2048_random_infp32_outfp32_ID374</t>
   </si>
   <si>
-    <t>[[336, 112, 405, 68, 131, 252, 273, 474, 386, 946, 504, 508, 146, 190, 1513, 420, 1382, 414, 105, 1673, 1515, 398, 169, 747, 44, 4, 92, 304], [400, 687]]</t>
+    <t>[[478, 53, 1627, 233, 170, 200], [408, 352, 270, 61, 35, 55, 291, 205, 261]]</t>
   </si>
   <si>
     <t>h256_ws4_idx2048_random_infp32_outfp32_ID375</t>
   </si>
   <si>
-    <t>[[13, 415, 422, 1778, 393], [1360, 468, 192, 257, 141, 250, 93, 252, 1196, 97, 302, 225, 469, 215, 479, 1106, 1246, 10, 829, 116, 177, 269, 415, 504, 118, 238, 1651], [241, 421, 297, 240, 1373, 1, 1079, 411, 1931, 18, 325, 1879, 1549, 1756, 174, 489, 41, 368, 160, 444, 473, 161, 293, 21, 353, 41], [431, 43, 447, 107, 387, 1844, 62, 84, 1857, 372, 459, 620, 1692, 149, 499, 164, 236, 68, 164, 434, 1225, 377]]</t>
+    <t>[[425, 194, 379, 233, 19], [49, 24, 389, 381, 488, 124], [1238, 215, 208, 466, 1174], [346, 376, 450]]</t>
   </si>
   <si>
     <t>h128_ws8_idx4096_random_infp16_outfp16_ID376</t>
   </si>
   <si>
-    <t>[[3851, 410, 107], [576, 3716, 101, 41, 75, 210, 242, 29, 165, 2227, 368, 187, 2608, 146, 48, 1197, 130, 313, 353, 474, 399, 427, 101, 2745, 235, 195, 89, 498, 232, 854, 409, 29], [277, 120, 369, 381, 43, 2576, 63, 98, 28, 3623, 116, 186, 165, 464, 94, 19, 118, 439, 302, 945, 144, 57, 445, 3450, 204, 1013, 155, 128, 3311, 372], [860, 241, 658, 339, 385, 3454, 285, 169, 221, 2435, 459, 129, 370, 468, 308, 511, 287, 3903, 92, 444, 492, 2833, 264, 395, 147, 186], [252, 99, 461, 359, 3906, 126, 318, 490, 262, 300, 233, 3440, 104, 714, 3218, 93], [508, 208, 50, 2854, 16, 437, 390, 1137, 309, 187, 495, 7, 307, 113, 492, 405, 1325, 355, 16, 2000, 111, 2531, 478, 380, 362, 231, 314, 512, 4063], [2674, 290, 391, 144, 468, 33, 364, 391, 660, 467, 48, 35, 55, 339, 22, 3136, 284, 455, 379, 45, 346, 2124, 33, 3597, 1866, 308, 474, 489, 53, 1190, 197], [2292, 275, 220, 95, 246, 176, 137, 297, 409, 237, 434, 318, 346, 467, 292, 4089, 460, 744, 3182, 145, 3946, 12, 277, 309]]</t>
+    <t>[[302, 459, 300, 468, 390, 425, 381, 101, 318], [123, 377], [370, 318], [1550, 116, 491, 351, 280, 170], [254, 67, 243, 505, 216, 352, 448, 170, 366], [220, 472, 459], [271, 63, 1619], [406, 494, 384, 430, 351]]</t>
   </si>
   <si>
     <t>h512_ws16_idx8192_random_infp16_outfp16_ID377</t>
   </si>
   <si>
-    <t>[[188, 109, 157, 7748, 140, 254, 444, 77, 1949, 201, 326, 3269, 85, 160, 470, 16, 193, 4515, 6711, 299, 7, 54, 372, 118, 487, 7381, 113, 393], [288, 498, 486, 7521, 3235, 205, 4108, 4678, 332, 370, 312, 134, 258, 117, 201, 374, 373], [408, 43, 1560, 396, 166, 369, 5445, 3, 306], [6680, 344, 166, 8022, 423, 84, 87], [5491, 177, 128, 25, 231, 14, 317, 273, 3769, 172, 2709], [131, 218, 368, 376, 177, 13, 446, 4535, 296, 439, 79, 221, 5265, 438, 224, 13, 261, 4, 419, 2891, 129, 382, 112, 48, 630, 485, 254, 3739, 371, 1334], [215, 49, 145, 6256, 169, 349, 3697, 2108, 123, 459, 472, 6061, 310, 9, 59, 807, 159, 81, 504, 209, 170, 211, 476], [5921, 34, 356, 395], [6586, 472, 375, 444, 2727, 60, 6287, 246, 347, 241, 411, 442, 140], [492, 471, 457, 1732, 56, 250, 284, 171, 423, 4933, 246, 151, 256, 7921, 34, 109, 91, 8047, 140, 99, 2872], [216, 1638, 512, 334, 526, 89, 232, 304, 50, 483], [4946, 91, 76, 198, 1965, 5557, 6031, 464, 459, 5730, 251, 277, 63, 452, 147, 230, 265, 39, 6, 337, 268, 254, 439, 232, 2605, 1093, 370, 278, 148, 33, 217, 132], [1550, 406, 134, 90, 273, 1434, 166, 118, 307, 440, 154, 212, 287, 199, 8032, 248, 504, 314, 1632, 232, 4828, 47, 9, 443, 217], [868, 427, 399, 113, 488, 1827, 228, 94, 7773, 49, 71, 293, 464, 275, 256, 285, 72, 7531], [6855, 136, 93, 2655, 43, 6360, 491, 385, 241, 473, 353, 304, 224, 80, 366, 83, 409, 287, 5307, 394], [311, 51, 357, 383, 311, 279, 5982, 230, 243, 325, 444, 122, 6425, 233, 217, 228, 481, 4140, 3074, 359, 281, 5774, 72, 478]]</t>
+    <t>[[1172, 139, 341, 214, 34, 457, 28, 57], [266, 472, 1830, 1861, 339, 261, 363, 150, 152], [498], [402, 512], [43, 1268, 33, 381, 304, 406, 465, 448, 186, 108], [143, 495, 242, 432, 100, 235, 130], [87, 219, 1571], [336, 2021], [479, 195, 43, 435, 487, 342, 198, 450, 453, 481], [204, 408], [137], [416, 312, 328, 629, 202, 462], [543, 148, 442], [75, 987, 465, 201, 491, 179, 71], [436, 530, 510], [259, 1066, 58, 140, 68, 382, 278, 20]]</t>
   </si>
   <si>
     <t>h512_ws4_idx8192_random_inbf16_outbf16_ID378</t>
   </si>
   <si>
-    <t>[[78, 22, 5431, 261, 238, 1939, 61, 171, 26, 401, 14, 144, 9, 2235, 241, 191, 27, 2720, 446, 156, 34, 90, 247, 423, 5942, 149, 492, 375, 3847, 354], [39, 6129, 7959, 216, 48, 492, 347, 2370, 73, 63, 95], [141, 80, 390, 384, 3016, 351, 6759, 308, 315, 428, 310, 343, 438, 2575], [498, 279, 58, 92, 99, 404, 115, 450, 302, 320, 7672, 146, 4385, 417, 4361, 35, 5528, 347, 278, 187, 403, 186, 461, 4100, 3496, 71, 24]]</t>
+    <t>[[1300, 1503], [467, 149, 168, 140, 229, 109, 430, 222], [412, 196, 315, 318, 153, 155, 300, 84], [479, 82, 109, 148, 386, 14, 369, 1261, 356]]</t>
   </si>
   <si>
     <t>h256_ws16_idx32768_random_infp16_outfp16_ID379</t>
   </si>
   <si>
-    <t>[[18, 8385, 299, 496, 11980, 485, 232, 29379, 62, 19, 20839, 464, 37, 22, 290, 362, 10531, 506, 131, 239, 443], [23848, 78, 457, 485, 195, 2, 134, 52, 79, 48, 321, 463, 13503, 122, 387, 117, 299, 153, 318, 274, 28295, 13175, 7392], [32051, 20919, 65, 325, 468, 478, 223, 73, 423, 191, 254, 204, 4010, 340, 4894, 232, 84, 499], [81, 464, 125, 68, 268, 229, 16954, 367, 169, 3266, 150, 76, 15884], [327, 72, 380, 1887, 14098, 406, 48, 180, 322, 26], [398, 32467, 423, 20140, 497, 382, 269, 470, 435, 479, 82, 54, 23, 158, 499, 510, 55, 19, 492, 448, 461, 28164, 393, 316, 338, 31269, 391, 21362, 3033], [40, 100, 31387, 12856, 344, 169, 129, 302, 487, 223, 22867, 5592, 39, 499, 19260, 14920, 443, 475, 216, 136, 385, 159, 177, 168, 67, 338], [441, 490, 510, 315, 189, 353, 227, 431, 147, 28910, 9730, 249, 54, 99, 30553, 16, 217, 336, 310, 262, 340, 391, 10810, 467, 11445, 15522, 173], [30060, 137], [498, 337, 85, 197, 262, 205, 27026, 479, 141, 225, 87, 119, 62, 81, 285, 208, 26427, 448, 302, 374, 25373, 465, 144, 73, 32, 254, 3768, 10701, 15288, 94], [227, 67, 18097, 383, 215, 395, 63, 28565, 2697, 367, 38, 444, 337, 422, 37, 130, 221, 26553, 141, 216, 419, 27021, 44, 114, 29255, 331, 380, 257, 310, 346, 101, 5185], [190, 253, 408, 332, 504, 119, 426, 373, 364, 19359, 20879, 110, 21, 243, 471, 3465, 8080], [5088, 121, 40, 32, 116, 192, 133, 242, 2484, 490, 234, 254, 260, 296, 8965, 17918], [74, 248, 279, 410, 392, 10803, 22, 164, 21166, 12924, 8, 434, 266, 315, 1192, 80, 7979, 335, 96, 13, 152, 215, 493, 381, 133, 66, 84, 11683], [204, 11, 144, 439, 277, 138, 64, 475, 26492, 31067, 394, 286, 46, 223, 135, 100, 18997, 361, 30, 20942], [26, 406, 209, 31, 210, 5705, 352, 272, 18249, 208, 31977]]</t>
+    <t>[[338, 21, 206, 874], [484, 42, 121], [134, 450], [76, 275, 197, 485], [164, 157, 414, 52, 334, 415, 235, 65, 199, 440], [353, 270, 363, 389, 494], [14, 110, 394, 396, 119, 324, 390], [401, 388, 241, 861, 1997], [52, 22, 110, 286, 182, 165, 102, 487], [269, 403, 452], [491, 394, 425, 331, 125], [246], [230, 279, 581, 237, 2034, 53, 315], [219, 3, 180, 448, 1837, 339], [178, 407, 303], [500, 392, 113, 108, 1668, 481]]</t>
   </si>
   <si>
     <t>h256_ws2_idx8192_random_inbf16_outbf16_ID380</t>
   </si>
   <si>
-    <t>[[203, 2062, 399, 119, 480, 477, 157, 1623, 256, 409, 160, 59, 389, 5861, 2189, 406, 1962, 324, 149, 59, 279, 346, 420, 458, 316, 3794, 382], [472, 268, 308, 320, 4496]]</t>
+    <t>[[234, 400, 162, 144, 452, 122, 484], [365, 378, 489, 424, 1511, 613]]</t>
   </si>
   <si>
     <t>h128_ws2_idx1024_random_infp16_outfp16_ID381</t>
   </si>
   <si>
-    <t>[[519, 200, 467, 463, 184, 349, 113, 185, 104, 389, 192, 31, 443, 840, 586, 270, 529, 158, 438, 135, 354, 717, 76, 401, 897, 242, 500], [738, 324, 205, 49, 25, 388, 360, 293, 355, 196, 443, 110, 365, 979, 150, 690, 740, 194, 362, 230, 347, 215, 744, 432, 838, 361, 480, 263, 512, 686, 188]]</t>
+    <t>[[374, 82, 6, 238], [20, 255, 10]]</t>
   </si>
   <si>
     <t>h64_ws4_idx2048_random_inbf16_outbf16_ID382</t>
   </si>
   <si>
-    <t>[[447, 359, 494, 190, 433, 508, 355, 1253, 355, 337, 302, 1886, 1365, 411, 1835, 292, 250, 183, 1388, 337, 160, 997, 27, 156, 190, 140, 211, 92, 401, 217, 1727], [385, 34, 233, 273, 773], [1546, 313, 225, 60, 495, 486, 320, 276, 1118, 439, 434, 1791, 177, 11, 279, 2, 335, 1879, 266, 411, 348, 330, 1810, 280, 29, 152, 771, 120], [458, 125, 489, 584]]</t>
+    <t>[[262, 365, 278, 69, 82, 19, 387, 486], [329, 455], [342, 152, 411, 1249, 382, 137, 311, 1123, 1586, 468], [419, 316, 144, 320, 319, 194, 33, 382, 1288]]</t>
   </si>
   <si>
     <t>h128_ws4_idx2048_random_inbf16_outbf16_ID383</t>
   </si>
   <si>
-    <t>[[1328, 474], [303, 584, 237, 192, 470, 471, 433, 494, 1512, 204, 280, 333, 1479, 187, 20, 79, 498, 205, 89, 1372], [440, 475, 1199, 337, 1517, 1833, 504, 374, 963, 388, 297, 335, 760, 384, 343, 468, 480, 391, 153, 85, 366, 634, 387, 307, 94, 65, 394], [53, 277, 181, 156, 127, 480, 99, 333, 15, 1541, 244, 83, 505, 1904, 0, 177, 31, 110, 1481, 285, 1625, 1948, 1315, 79, 31, 399]]</t>
+    <t>[[518, 255, 334, 274, 182, 394, 57], [105, 176, 346, 331, 105, 432, 1799], [133], [66]]</t>
   </si>
   <si>
     <t>h64_ws16_idx16384_random_infp32_outfp32_ID384</t>
   </si>
   <si>
-    <t>[[10124, 472, 11889, 12034, 296, 285, 76, 432, 72, 85, 164, 15987, 321, 1024, 370, 289, 97, 16338, 456, 36, 493, 139, 242, 296, 1, 85], [62, 285, 289, 1302, 438, 329, 141, 4189], [191, 294, 289, 316, 485, 194, 1187, 21, 241, 484, 219, 261, 10145, 509, 181, 14053, 140, 7212], [5892, 197, 243, 392, 369, 227, 268, 232, 311, 4273, 298, 170, 487, 151, 15175, 75, 15049, 129, 422], [345, 37, 125, 454, 253, 276, 312, 1388, 329, 5792], [385, 927, 345, 61, 12209, 363, 481], [100, 269, 496, 12765, 506, 80, 143, 185, 227, 177, 1476, 27, 6730, 284, 300, 152, 496, 311, 10166, 237, 445, 487, 472, 257, 4832, 165, 404, 470, 10528, 322], [195, 495, 2405], [2146, 202, 351, 178, 478, 65, 251, 15716, 209], [394, 307, 6195, 187, 499, 309, 430, 30, 9339, 57, 334, 15022, 203], [293, 354, 487, 13350, 253, 253, 349, 138, 180, 296, 465, 14456, 62, 161, 3154], [259, 372, 121, 411, 179, 114, 208, 14989, 308, 390, 492, 1033, 172, 347, 205, 254, 2193, 462, 180, 14615], [63, 348, 358, 13480, 480], [499, 171, 7617, 13103, 12, 505, 255, 4209, 413, 329, 23, 276], [8113], [345, 399, 103, 118, 15168, 13879, 349, 59, 150, 16026, 258]]</t>
+    <t>[[803, 284, 166, 240, 197, 90, 82], [245, 328, 215, 433, 79, 287, 278, 689, 833], [960, 270, 109, 244, 171, 48, 33, 170], [781, 1587, 178, 258], [74, 512, 218, 279], [85, 445, 951, 418, 165, 399], [430, 54, 53, 1106, 1723, 179, 3], [1660, 343, 246, 374], [431, 145, 158, 220], [73], [259, 45, 1635, 376, 155, 76, 472], [354], [251], [433, 457], [87, 78, 88, 307, 165, 675, 95, 504], [332, 403, 1061, 50, 304, 1098, 115, 466]]</t>
   </si>
   <si>
     <t>h64_ws8_idx4096_random_infp32_outfp32_ID385</t>
   </si>
   <si>
-    <t>[[162, 133, 1020], [82, 435, 1663, 393, 94, 11, 296, 14, 270, 380, 2323, 455, 371, 343, 367, 146, 396, 1231, 1714, 1312, 284, 309, 2, 154, 59, 163, 1428, 396, 66], [469, 370, 280, 362, 220, 34, 4093, 1375, 187, 452, 285, 236, 3430, 399], [272, 3866, 300, 66, 214, 111, 443, 3695, 2602, 93, 65, 263, 166, 447, 427, 2573, 492, 233, 300, 2366, 200], [29, 113, 388, 356, 407, 300, 3047, 238, 1174, 304, 3599, 426, 120, 492, 2262, 43, 362, 321], [425, 3904, 296, 211, 136, 1927, 1963, 154, 507, 453, 326, 257, 143], [265, 370, 290, 3517, 173, 31, 3155, 291, 273], [170, 64, 3754, 2007, 363, 459, 211, 256, 3419, 311, 506, 359, 488, 2864, 40, 2943, 342, 1147, 112, 154, 2, 275, 186, 236, 392, 161]]</t>
+    <t>[[464, 233, 318, 94, 179, 510, 422, 137], [29], [485, 25, 164], [161, 349, 471, 1261, 171, 164, 463, 330], [1920, 248, 36, 1338, 457, 143, 190, 62, 115], [259, 1592, 139, 36, 462, 226, 203, 323, 208, 1200], [387, 237, 145, 512, 9, 188, 463, 419, 897], [100, 508, 395, 18, 268, 350, 146, 246, 283]]</t>
   </si>
   <si>
     <t>h128_ws16_idx16384_random_infp16_outfp16_ID386</t>
   </si>
   <si>
-    <t>[[275, 316, 265, 8891, 391, 318, 367, 233, 410, 3679, 450, 443, 118, 91, 433, 417, 286, 8952, 55, 57, 248, 372, 3603, 4408, 503, 14446, 451, 369], [9457, 289, 10164, 255, 14831, 343, 11, 98, 378, 185, 95, 53, 270], [443, 261, 469, 51, 15298, 417, 7611, 394, 317, 13954, 464, 9515, 436, 270, 356, 29, 499], [107, 484, 81, 245, 132, 12919, 273, 1778, 5968, 20, 44], [4018, 458, 306, 5825, 119, 456, 8, 50, 462, 27, 479, 14072, 3964, 489, 82, 259], [463, 8117, 504, 176, 356, 348, 244, 186, 242, 318, 968, 346, 329, 15153, 139, 16, 418, 277, 381, 7152], [438, 291, 135, 416, 85, 69, 260, 9379, 518, 487, 324, 5168, 304, 159, 474, 241, 12683, 450], [512, 7, 364, 265, 3655, 119, 457, 319, 343, 9687, 262, 330, 63, 11189], [509, 267, 458, 119, 353, 427, 79, 2684, 8090, 132, 152, 373, 338, 8614, 411], [14, 86, 361, 372, 481, 415, 166, 425, 14960, 13326], [379, 120, 29, 176, 7957], [361, 14682], [218, 250, 464, 109, 15023, 238, 4992, 3212, 280, 4107, 127, 315, 373, 317, 443, 338, 15437, 307, 3, 401, 430, 431, 247], [353, 99, 14520, 48, 472, 13102, 25, 104, 424, 337, 31, 12397, 6, 172, 302, 424, 9591, 267, 15845, 440, 498, 485, 294, 34, 61], [256, 269, 101, 341, 204, 362, 16121, 449, 321, 33, 358, 78, 346, 277, 6309, 16, 285, 5862, 13529, 347, 12367, 33], [383, 16022, 154, 375, 263, 287, 420, 407, 498, 11819, 157, 261, 21, 15675, 260, 509, 3743, 15719, 140, 341, 276, 108, 4, 42, 201, 14736, 368]]</t>
+    <t>[[182, 59, 230, 369, 1748, 102, 123, 356, 244, 1281], [475, 280, 1284, 373], [28, 721, 116, 281, 338, 546, 195, 77, 254], [201], [112, 1652, 29, 240], [45, 406, 1203, 229, 12], [702, 221], [69, 317, 114, 1252, 326, 1176, 283, 341], [338, 312, 380, 387, 1782, 154, 476, 1384, 284], [252, 310, 67], [285, 265, 1903, 60, 347, 52, 1194], [427, 504, 33, 435, 232, 492, 459, 385], [401, 508, 111, 282, 528, 392, 181, 784, 166, 1938], [386, 483, 2002, 133, 396, 1382, 330, 412, 121, 88], [1259, 2015, 326, 300, 134, 138, 136], [311, 1023, 404, 78, 416, 204, 192, 321, 491, 375]]</t>
   </si>
   <si>
     <t>h64_ws4_idx16384_random_inbf16_outbf16_ID387</t>
   </si>
   <si>
-    <t>[[512, 456, 5581, 41, 299, 506, 56, 254, 447, 432, 76, 338, 15444, 2231, 72, 8090], [261, 3718, 387, 431, 138, 284, 319, 262, 239, 7685], [3, 386, 199, 90, 6246, 54, 22, 493, 163, 56, 130, 2836, 285, 427, 2633, 185, 141, 351, 162, 10321, 9107, 197, 94], [369, 182, 116, 342, 481, 229, 201, 7664, 7173, 190, 1648]]</t>
+    <t>[[230], [100, 66, 1546], [333, 301, 848, 1889, 435, 81, 30, 366], [444]]</t>
   </si>
   <si>
     <t>h64_ws4_idx8192_random_infp16_outfp16_ID388</t>
   </si>
   <si>
-    <t>[[133, 227, 402, 480, 6297, 6277, 256, 142], [219, 188, 80, 22, 76, 8169, 478, 339, 185, 6932, 272, 7827, 163, 7773, 82, 339, 4663, 34, 482, 28, 251], [277, 3327, 3692, 440, 499, 110, 272, 18, 209, 404, 3746, 239, 4170, 481, 3305, 160, 40, 149, 418, 281, 101, 510, 56, 3, 226, 150, 458, 3490, 113, 111], [444, 492, 7905]]</t>
+    <t>[[392, 270, 412], [1611, 619, 130, 468, 776, 1759, 292, 499], [433, 1263, 271, 149, 48, 367, 152], [274]]</t>
   </si>
   <si>
     <t>h128_ws4_idx2048_random_inbf16_outbf16_ID389</t>
   </si>
   <si>
-    <t>[[210, 492, 1034, 313, 299, 152, 1363, 94, 379, 86], [332, 545, 1040, 152, 290, 51, 397, 70, 51, 70, 557], [427, 420, 430, 395, 359, 217, 121, 331, 2, 242, 11, 1900, 1311, 326, 504, 315, 30, 1256, 1951, 407, 486, 1041, 408, 571, 332, 302, 64], [1157, 401, 361, 503, 510, 158, 442, 19, 193, 982, 668, 32, 502, 253, 198]]</t>
+    <t>[[239, 483, 196, 334], [489, 104, 134, 1922, 219, 135, 782, 1489, 60], [76, 740, 438, 155, 451, 331, 277, 1], [649]]</t>
   </si>
   <si>
     <t>h64_ws16_idx65536_random_infp16_outfp16_ID390</t>
   </si>
   <si>
-    <t>[[159, 243, 512, 275, 457, 393, 435, 283, 97, 453, 129, 51273, 318, 36944, 19281, 303, 406, 204, 449, 454, 61, 43, 495, 56, 356, 415, 418, 166, 15756, 34210, 54300, 58605], [310, 231, 168, 80, 35243], [28739, 410, 264, 35759, 454, 50399, 233, 399, 196, 165, 428, 498, 482, 193], [100, 307, 502, 191, 124, 505, 63985, 472, 31736, 5623, 489, 349, 432, 366, 170], [360, 11, 36, 178, 133, 12900, 110, 397, 413, 18996, 463, 511, 381, 30, 279, 343, 337, 399, 14277, 3023], [405, 293, 169, 58526, 476, 362, 39947], [165, 34, 388, 485, 478, 53261, 184, 35565, 20333, 385, 483, 453, 367, 131, 195, 117, 25441], [21359, 462, 380, 8, 12, 125, 208, 423, 255, 417, 49207, 418, 63, 185, 51, 25923, 11112, 289, 335, 184, 59983, 391, 506, 242, 134, 478, 155, 474, 37611], [6581, 10705, 98, 242, 374, 12, 100, 48857, 175, 187, 217, 299, 60367, 173, 340, 365, 159, 204, 338, 31582, 152, 85], [437, 56, 488, 15993, 349, 65125, 161, 185, 63169, 329, 18], [249, 76, 4218, 26160, 165, 330, 35, 195, 62174, 92, 210, 362, 443], [63891, 410], [65233, 21173, 274, 469, 17213, 486, 214, 308, 5, 85, 64201, 463, 250, 173, 249, 119, 193, 139, 298, 72, 493, 467, 60848, 235, 123], [354, 278, 87, 147, 33327, 376, 25759, 31, 50, 398, 494, 443, 502, 493, 504, 40929, 33447, 2794, 297, 475, 202, 236, 444, 67, 371, 67, 476, 7, 40862, 212], [100, 417, 20321, 474, 252, 115, 41206, 393, 255, 267, 278, 80, 128, 2, 27310, 504, 369, 400, 62282, 315, 46192, 325, 366, 378, 60535, 385, 95], [429, 16239, 162, 26624, 275, 96, 62510, 403, 69, 52944, 20, 295, 284, 239, 112, 249, 207, 353]]</t>
+    <t>[[234, 321, 204, 399, 118, 504, 447, 218], [180, 135, 507, 505, 464, 25, 186], [310, 1296], [232, 102, 483, 26, 787, 203, 223], [1833, 1252, 347, 77], [1753, 420, 359, 256, 126], [225, 166, 341, 272, 500, 267], [1845, 228, 171, 155, 251, 429, 344], [65], [183, 15, 92, 402], [45, 83, 487, 466, 385, 290, 493, 400, 847, 455], [243, 204, 467, 407, 188], [1270, 542, 155, 363, 217, 372], [505, 311, 71, 333, 116, 214, 233], [151], [18, 1, 408, 795, 66, 488, 480]]</t>
   </si>
   <si>
     <t>h64_ws4_idx16384_random_infp32_outfp32_ID391</t>
   </si>
   <si>
-    <t>[[253, 127, 277, 6257, 13658, 137, 413, 331, 451, 71, 55, 351, 374, 258, 8431, 370, 36, 456, 459, 262, 463, 7723, 8408, 49, 3393, 39, 186], [421, 6843, 165, 511, 231, 182, 271, 500, 318, 169, 10, 10756, 345, 220, 164, 472, 447, 6737, 408, 13279], [6015, 208, 240, 117, 11380, 217, 435, 118, 290, 506, 25, 90, 506, 464, 5680, 305, 6111, 86, 142], [6139, 115, 310, 332, 509, 130, 4516, 433, 16049, 24, 6410, 1886, 413, 503, 475, 501, 273, 173, 261, 321, 127, 42, 134, 458, 512]]</t>
+    <t>[[388, 451, 509, 334], [99, 272, 447, 143], [776], [341, 91, 341]]</t>
   </si>
   <si>
     <t>h512_ws4_idx8192_random_inbf16_outbf16_ID392</t>
   </si>
   <si>
-    <t>[[2375, 136, 504, 315, 337, 1627, 139, 244, 278, 497, 174, 7452, 496, 484, 395, 12, 6214, 398, 139, 153, 197, 7561], [2441, 333, 192, 12, 4101, 435, 164, 473, 99], [132, 151, 4939, 55, 47, 2607, 62, 24, 493, 5639, 97, 101], [369, 3101, 130, 111, 63, 4270, 221, 2184, 116, 407, 248, 146, 83, 6149, 462, 1371, 142, 97, 199, 110, 137, 7, 82]]</t>
+    <t>[[456, 408, 329, 423, 7], [225, 352], [1074, 424, 336, 14, 487, 226, 202], [77, 324, 37, 276, 336, 110]]</t>
   </si>
   <si>
     <t>h128_ws8_idx32768_random_infp16_outfp16_ID393</t>
   </si>
   <si>
-    <t>[[141, 27245, 316, 20045, 470, 398, 512, 409, 187, 15937, 21653, 105, 300, 375, 191, 21399, 47, 162, 286, 257, 312, 101, 5205, 288, 420, 272, 211, 308, 74, 18632, 42], [468, 73, 64, 457, 10635, 20688, 434, 412, 291, 1607, 496], [483, 445, 2754, 329, 9955, 472, 254, 408, 335, 392, 33, 13714, 29151, 511, 146, 307], [384, 131, 312, 16391, 27, 916, 417, 329, 64, 232, 280, 8406, 9, 31430, 270, 361, 260, 218], [54, 26329, 488, 417, 182], [472, 8538, 13236, 211, 34, 364, 484], [185, 20799, 241, 423, 457, 30630, 318, 60, 6743, 465, 205, 232, 118, 84, 19463, 207, 281], [4254]]</t>
+    <t>[[345], [415, 572, 267, 25, 117], [343, 251, 376, 405, 1485, 342, 113], [454, 162, 222, 1592, 127, 462, 195, 185], [271, 325, 361, 417, 420], [809, 144], [421, 255, 333, 61, 478, 257, 91, 91, 143, 282], [333, 115]]</t>
   </si>
   <si>
     <t>h256_ws2_idx8192_random_infp16_outfp16_ID394</t>
   </si>
   <si>
-    <t>[[4888, 245], [5, 885, 471, 7611, 275, 5927, 134, 137, 197, 55, 496]]</t>
+    <t>[[215, 477, 396, 472, 402, 815, 348, 295], [1650, 137, 870, 399]]</t>
   </si>
   <si>
     <t>h64_ws4_idx2048_random_infp16_outfp16_ID395</t>
   </si>
   <si>
-    <t>[[475, 88, 1626, 337, 458, 1833, 276, 246, 59, 416, 1763], [360, 334, 213, 463, 344, 1621, 948, 412, 366, 343, 0, 730, 406, 26, 432], [1213, 1171, 281, 421, 243, 269, 492, 222, 409, 365, 450, 185, 493, 43, 480, 161, 474, 1578, 506, 455, 494, 754, 2, 319, 23, 831, 1403, 298, 233, 1935, 302], [180, 426, 1756, 503, 183, 284, 407, 38, 261, 137, 1398, 1495]]</t>
+    <t>[[285, 350, 256, 492, 294, 415, 272, 22, 180], [375, 248], [131, 176], [38, 349, 280, 257, 243, 489, 403, 201, 296, 1549]]</t>
   </si>
   <si>
     <t>h256_ws4_idx2048_random_infp16_outfp16_ID396</t>
   </si>
   <si>
-    <t>[[241, 320, 488, 10, 1698, 491, 1428, 692, 423, 57, 76, 259], [224, 1858, 1732, 390, 218, 146, 364, 220, 1811, 672, 480, 98, 282, 272, 214, 498, 1447, 102, 236, 496, 846, 240, 366, 23, 281, 203, 205, 343, 198, 1466, 392], [281, 1359, 148, 267, 1054, 76, 418, 248, 164, 1301, 1490, 139, 166, 402, 165, 1002, 140, 148, 308, 493, 277, 283, 209], [22, 199, 607, 58, 755, 443, 113, 325, 371, 631, 138, 77, 954, 218, 152, 498, 462, 981, 63, 176, 305, 322, 409, 350, 395, 233, 1504, 508, 173]]</t>
+    <t>[[505, 138, 1586, 331, 59, 506, 225, 482, 1513], [40, 504, 16, 749], [365, 1790, 323, 368, 230], [107, 394, 456, 499, 495]]</t>
   </si>
   <si>
     <t>h64_ws16_idx32768_random_infp16_outfp16_ID397</t>
   </si>
   <si>
-    <t>[[370, 214, 12823, 450, 17920, 31859, 94, 217, 413, 320, 482, 496, 275], [507, 389, 403, 12351, 241, 31, 16544, 165, 103, 429, 99, 287, 1157, 27, 428, 6446, 437], [110, 18, 99, 445, 26331, 342, 7868, 238, 418, 269, 17059, 368, 494, 187, 50, 31, 389, 13048, 108, 465, 221, 176, 46, 3253, 60], [25109, 294, 16080, 284, 361, 71, 48], [420, 344, 425, 19, 71, 24493, 412, 490, 28061, 245, 476, 15361, 129, 211, 98, 17887, 489, 226, 661, 157, 112, 31568, 365, 347, 233, 375, 339, 397, 815, 324, 193], [347, 10, 26016, 386], [5380, 258, 467, 16011, 3, 248, 20, 239, 25544, 33, 257, 17815, 18, 23, 276, 94, 257, 8854, 16720, 389, 158, 2, 17, 56, 99, 179, 361, 484], [343, 494, 13450], [168, 86, 1566, 57, 13589, 497], [111, 456, 130, 39, 467, 31594, 184, 15144], [71, 302, 29408, 425, 25009, 297, 374, 391, 5788, 167, 4859, 197, 306, 304, 349, 285, 395, 390, 304, 476, 51, 31, 1744], [160, 37, 432, 30462, 412, 6882, 344, 374, 225, 468, 29743, 362, 365, 332, 76, 49, 830, 506], [121, 1259], [294, 254, 31414, 281, 0], [259, 313, 67, 506, 9963, 270, 312, 411, 340, 92, 355, 3939, 308, 30185, 77, 494, 228, 1815, 136, 108], [39, 7945, 305, 15912, 211, 129, 326, 23521, 113, 1680, 453, 178, 100, 160, 22, 215, 30, 14054, 216, 14843, 245, 99, 136, 427, 256, 83]]</t>
+    <t>[[481, 67], [64, 186, 1667, 324, 232, 382, 205, 454], [274, 809, 458], [260, 338, 588, 306, 341, 87, 1775, 382, 57, 149], [72, 213, 337, 83], [398, 46, 236, 460, 1124, 405, 278, 497, 165, 345], [511, 197, 6], [1673, 386, 389, 87, 353, 95, 431], [249, 37, 75, 512], [1446, 384, 225, 14, 1521, 476, 439], [176, 43, 114], [418, 198], [172, 419], [423, 538], [468, 316, 414, 363, 605, 244, 196], [119, 15, 408]]</t>
   </si>
   <si>
     <t>h128_ws8_idx16384_random_infp32_outfp32_ID398</t>
   </si>
   <si>
-    <t>[[5903], [504, 14825, 7695, 14320, 456, 182, 442, 218, 223, 298, 437, 302, 483, 10415, 291, 412, 482, 425, 299, 234, 6161, 144, 270, 344, 292, 52, 189, 204, 178, 14878], [451, 14086], [125, 429, 59, 9529, 154], [425, 418, 77, 13733, 55, 14105, 154, 108, 490, 357, 284, 10614, 166, 121, 352, 12245, 454, 12271, 52, 490, 6594, 379, 468, 402, 173, 293, 9531, 80, 88, 75, 360, 470], [231, 33, 458, 6458], [274, 489, 422, 31, 447, 509, 11775, 341, 4155, 281, 12320], [452, 25, 51, 490, 491, 8615, 223, 409, 214, 435, 368, 6703, 1037, 57, 287, 323, 5365, 297, 499, 421, 2583, 267, 287]]</t>
+    <t>[[136, 204, 1964, 272, 151, 448, 58, 40, 290, 465], [288, 387, 119, 241, 352], [226, 261, 1527, 216, 105, 245, 422], [379, 10, 32], [91, 293, 36, 144], [301, 337, 485, 495, 381], [110], [1364, 1920, 82, 945, 231, 410, 390, 336, 233]]</t>
   </si>
   <si>
     <t>h256_ws2_idx4096_random_inbf16_outbf16_ID399</t>
   </si>
   <si>
-    <t>[[1456, 490, 132, 39, 296, 3515, 16, 3990, 441, 190, 286, 16, 32, 175, 85, 237, 2895, 231, 509, 475], [3370, 192, 304, 123, 376, 478, 3852, 336, 125, 354, 760, 349, 21, 3489, 398, 441, 388, 913, 293, 474, 109, 432, 133, 320]]</t>
+    <t>[[511, 446, 341, 307, 19, 322], [947, 333, 231, 184]]</t>
   </si>
   <si>
     <t>h512_ws2_idx2048_random_infp16_outfp16_ID400</t>
   </si>
   <si>
-    <t>[[210, 444, 233, 461, 318, 1301, 56, 1328, 506, 358, 1317, 172, 322], [1825, 2, 1335, 164, 392, 478, 17, 1919, 345, 1194, 90, 389, 253, 151, 795, 252, 397, 122, 258, 503, 417, 1704, 54, 249, 423, 221, 475, 353]]</t>
+    <t>[[17, 150], [473, 681]]</t>
   </si>
   <si>
     <t>h64_ws16_idx16384_random_infp32_outfp32_ID401</t>
   </si>
   <si>
-    <t>[[484, 109, 39, 179, 254, 2070, 352, 8156, 186, 245], [66, 192, 334, 3663, 72, 192, 12364, 326, 424, 2214, 397, 338, 1849, 485, 421, 178, 393, 118, 2056, 147, 26, 265], [323, 237, 69, 4161, 167, 23, 313, 11123, 394, 201, 12711, 192, 33, 70], [238, 451, 116, 8164, 364, 241, 237, 30, 3472, 296, 426, 393, 27, 77, 69, 183, 362, 286, 260, 303, 8195, 178, 8625, 290, 354, 10574, 276, 6, 8283, 453], [13947, 508, 10, 290, 14612, 173, 76, 8761, 59, 242, 260, 348], [448, 78, 381, 2429, 185], [187, 13968, 117, 121, 495, 220, 9779, 452, 270, 187, 297, 10685, 61, 424, 14197, 29, 394, 413, 14, 219, 4330, 325, 18], [174, 16, 415, 1843, 120, 423, 311, 108, 185, 470, 11480, 78, 335, 318, 15574, 10117, 132, 394, 322, 6047, 439, 11635, 505, 11452, 460, 185, 36, 199, 178, 484, 267], [487, 82, 41, 382, 462, 353, 253, 242, 476, 245, 7, 9989, 111, 7571, 8410, 773, 187, 71], [439, 147, 11898, 443, 8, 4, 88, 452, 484, 97, 15469, 60, 5844, 498, 133, 161, 119, 5120, 391, 330, 161, 439, 227, 1261], [371, 3, 268, 20, 14160, 86, 14804, 241, 8117, 187, 285, 387, 335, 340, 225, 3830, 510, 366, 93], [67, 7063, 439, 422, 474, 5065, 370], [14231, 1847, 305, 425, 1731, 172, 247, 297, 161, 170, 459, 192, 112], [6782, 356, 115, 2437, 30, 143, 391, 336, 176], [441, 243, 12454, 205, 503, 295, 4, 63, 9634, 7747, 425, 132, 167, 407, 95, 455, 194, 316, 432, 9805, 15671, 254, 91, 8876, 119, 127], [8622, 219, 192, 3050, 162, 3245, 140, 273, 451, 57, 179, 307, 512, 134, 465, 122, 4501, 121, 478, 6029, 329]]</t>
+    <t>[[2033], [427, 435, 298, 1102], [122, 234, 303], [508, 39, 415, 503, 488, 1972, 241, 821], [426, 251, 377, 506, 69, 468], [497, 91, 463, 349, 430, 145, 157, 98], [452, 1400, 1194, 84, 337, 253], [239, 313, 476, 482, 353, 281, 446, 115], [1964, 315], [831, 471, 44, 98, 384, 101], [400, 362, 454, 254, 214, 1508, 218], [260, 405, 71, 277, 1218, 178, 641, 280, 300], [394], [476, 433, 427, 277, 75, 872, 35], [243], [101, 468]]</t>
   </si>
   <si>
     <t>h256_ws16_idx32768_random_infp32_outfp32_ID402</t>
   </si>
   <si>
-    <t>[[26253, 77, 251, 485, 88, 304, 492, 437, 276, 27448, 220, 22386, 372, 207, 125], [308, 574], [436, 52, 7838, 118, 74, 28930, 85, 22, 292, 479, 27082, 405, 422, 440], [491, 71, 387, 851, 122, 4506], [452, 502, 13, 4958, 239, 365, 357, 77, 105, 19272], [456, 267, 349, 4486, 396, 19905, 224, 267], [23269, 72, 13933, 137, 334, 375, 336, 199, 505, 22044, 15914, 254, 306, 305, 3, 400, 27656, 20, 1740, 171, 175, 14, 285, 476, 231, 5, 412, 164], [306, 331, 377, 386, 287, 383, 180, 11088, 489, 351, 357, 27895, 23608, 356, 16865, 386, 257, 12206, 170, 16, 405, 51, 505, 381, 429], [17, 26950, 227, 11984, 25744, 69, 262, 125, 65, 22, 98, 17588, 497, 396, 75, 439, 143, 8, 97, 13780, 506, 3, 203], [22852, 25467, 469, 24998, 471, 429, 408, 496, 187, 432, 168, 45, 47, 175, 260, 21528, 26455, 50, 160, 316, 282, 204, 30668, 210, 191, 302, 154], [38, 130, 314, 428, 19643, 197, 457, 228, 281, 58, 458, 231, 279, 32623, 119, 366, 429, 29316, 11700], [312, 28328, 435, 245, 430, 188, 479, 72, 32419, 429, 474, 378, 172, 3838, 22580, 512, 332, 256, 158, 509, 388, 4591, 33, 171], [478, 368, 324, 12252, 123, 10738, 30, 17, 395, 20592, 281, 219, 130, 496, 119, 146, 24182], [240, 124, 27332, 5], [127, 396, 510, 439, 378, 7168, 253, 379, 28699, 456, 116, 129, 15852, 299, 254, 373, 64, 378, 25374, 406, 126, 43, 10990, 458, 158, 238, 180, 123, 104, 6282, 27126, 298], [31028, 501, 304, 392, 13, 182, 377, 9659, 9291, 205, 357, 19447, 439, 423, 245, 259, 58, 219, 23842, 281, 243]]</t>
+    <t>[[347, 320], [343, 110, 8, 111, 512, 405, 332, 33], [1224, 338, 141, 625, 260, 489], [161, 368, 215, 227, 379, 165, 337, 488, 379, 187], [380, 254, 1434, 268], [237, 1173, 478, 156, 33, 503, 343, 89, 313], [76, 48, 224, 351, 1909, 225, 278, 397, 148, 49], [474, 901], [356, 110, 1295, 253, 1453, 128], [321, 346, 36, 1635, 185, 175, 800], [475, 24, 442, 411, 346, 100, 449, 410, 47, 215], [121, 313, 106, 704, 448], [486], [55, 263, 198, 100, 512, 101, 393], [866, 811], [2014, 205]]</t>
   </si>
   <si>
     <t>h256_ws8_idx4096_random_inbf16_outbf16_ID403</t>
   </si>
   <si>
-    <t>[[292, 214, 3618, 312, 185, 500, 2636, 2142, 441, 13, 479, 2499, 506, 339, 56, 1447, 362, 90, 3710, 6, 96, 3, 501, 247, 181, 413, 144, 270, 836, 58, 7, 281], [368, 105, 3120, 511], [1422, 90, 393, 47, 91, 373, 170, 236, 3213, 353, 1695, 24, 3364, 206, 484, 160], [3270], [187, 503, 244, 1, 312, 434, 442, 348, 314, 1240, 343, 413, 282, 338, 3073, 1270, 1516], [279, 383, 29, 70, 508, 355, 3508, 212, 512, 1986, 509, 3540, 198, 508, 458], [181, 309, 690], [399, 76, 382, 314, 3593, 481, 504, 37, 189, 298, 200, 509, 17, 414, 471, 154, 157, 3942, 132, 371, 491, 55, 1155, 379, 2217, 2652, 263, 158, 157, 3798, 3141]]</t>
+    <t>[[103, 812], [187, 194], [1346, 79, 128, 417, 489, 505, 419, 425], [464, 54, 80, 203, 88, 402, 304], [135, 945, 1635, 1125, 322, 151, 357], [502], [364], [789]]</t>
   </si>
   <si>
     <t>h512_ws2_idx4096_random_infp32_outfp32_ID404</t>
   </si>
   <si>
-    <t>[[404, 416, 339, 169, 305, 401, 2646, 185, 441, 471, 59, 355, 293, 1812, 3533, 476, 565], [1703, 119, 1363, 482, 244, 16, 321, 429, 393, 50, 321, 1950, 81, 1095, 100, 295, 113, 276]]</t>
+    <t>[[85, 12, 50, 461, 138, 80, 91], [375]]</t>
   </si>
   <si>
     <t>h64_ws4_idx16384_random_infp16_outfp16_ID405</t>
   </si>
   <si>
-    <t>[[447, 3064, 95, 394, 372, 11552], [240, 12442, 395, 286, 10193, 486, 347, 3715, 360, 127, 487, 50, 385, 5578, 45, 55, 262, 486, 15547, 252, 158, 69, 436, 87, 8167, 349, 249], [281, 424, 274, 259, 203, 227, 498, 321, 225, 3908, 941, 148, 11908, 10880, 417, 178, 191, 131, 128, 73, 105, 863, 443, 12664, 512, 157], [11896, 320, 505, 85, 343, 471, 12809, 148, 0, 161, 441, 403, 5301, 43, 146]]</t>
+    <t>[[460, 184, 425, 95], [1467], [361, 469, 1304, 31, 513, 364, 411, 333, 354], [608, 547, 435, 224, 160, 279, 426, 494]]</t>
   </si>
   <si>
     <t>h512_ws2_idx1024_random_inbf16_outbf16_ID406</t>
   </si>
   <si>
-    <t>[[108, 365, 191, 1014, 308, 464, 837], [192, 32, 945, 8, 204, 403, 770, 286, 102, 196, 250, 338, 33, 118, 714, 476, 79, 401, 691, 28]]</t>
+    <t>[[303, 439, 445, 209, 429, 14, 185], [841, 310, 1033, 212, 1837, 59, 108, 465]]</t>
   </si>
   <si>
     <t>h512_ws8_idx4096_random_infp32_outfp32_ID407</t>
   </si>
   <si>
-    <t>[[372, 339, 436, 438, 1039], [2557, 13, 173, 450, 364, 139, 53, 126, 296, 223, 69, 289, 204, 511, 111, 148, 80, 2285, 2170, 2024, 14, 504, 260, 1324], [312, 1364, 1946, 68, 292, 32, 37, 410], [127, 467, 61, 162, 41, 102, 3682, 130, 144, 15, 215, 25, 296, 3688, 512, 446, 224, 3984, 283, 903, 2916, 96], [237, 242, 160, 176, 2800, 175, 203, 198, 1947, 1877, 142, 363], [316, 2821, 351, 1751, 4, 503, 124, 199, 301, 153, 290, 478, 202, 102, 2047, 488, 900, 85, 159, 133, 2151, 101, 438, 511, 511, 292, 376, 322, 538], [368, 185, 66, 144, 32, 338, 3535, 41, 2641, 425, 1269, 397, 3962, 48, 308, 421, 455, 322], [812]]</t>
+    <t>[[313, 370, 174, 412, 424, 192, 230], [401, 442, 742, 33, 1188, 210, 163, 495, 166], [173, 413, 352, 129, 492, 140], [133, 533], [53, 13, 1624], [1838], [157, 176, 455, 147, 199, 1060, 1658], [141]]</t>
   </si>
   <si>
     <t>h256_ws2_idx4096_random_infp32_outfp32_ID408</t>
   </si>
   <si>
-    <t>[[159, 29, 3769, 2691, 246, 243], [306, 318, 270, 490, 285, 398, 2038, 4080, 236, 429, 428, 350, 171, 369, 343, 63, 3371, 496, 829, 107, 1671, 505, 187, 431, 283]]</t>
+    <t>[[457, 35, 5, 290, 502, 1255, 269], [129, 140, 1847]]</t>
   </si>
   <si>
     <t>h256_ws8_idx8192_random_infp16_outfp16_ID409</t>
   </si>
   <si>
-    <t>[[421, 273, 6783, 338, 397, 6025, 391, 5892, 319, 56, 1157, 496, 278, 20, 103, 375, 240, 3229, 9, 375, 408, 452], [70, 419, 306, 97, 505, 4526, 9, 6909, 95, 352], [174, 1182, 59], [7024, 301, 123, 4058, 279, 148, 400, 510, 38, 248, 155, 207, 3728, 370, 7314, 333, 73], [101, 5, 5204, 14, 8025, 316, 465, 201, 324, 118, 351, 361, 3627, 327, 243, 286, 477, 133, 82, 82, 17, 1817, 6267, 168, 318, 109, 421, 2731], [1134, 268, 20, 402, 219, 325, 2668, 445, 159, 423, 387, 460, 431, 54, 39, 2804, 1700, 2783, 497, 58, 337, 298, 389], [80, 335, 1295, 153, 297, 288, 260, 82, 261, 454, 254, 7173, 108, 228, 203, 4710, 203, 21, 414, 395, 740, 500, 7, 7, 6890, 430, 507, 507, 6014, 367], [8, 121, 385, 134, 129, 1733, 7487, 449]]</t>
+    <t>[[275, 135, 481, 151, 384, 37, 777], [159, 150], [237, 141, 318, 413, 235, 319], [290, 245, 264], [205, 231], [474, 713, 508, 76, 107, 305, 346, 482, 705, 192], [418, 111, 108, 447, 12, 131, 102, 259, 26], [243, 505]]</t>
   </si>
   <si>
     <t>h128_ws2_idx1024_random_infp32_outfp32_ID410</t>
   </si>
   <si>
-    <t>[[453, 651, 707, 380, 294, 289, 479], [452, 158, 9, 290, 332, 100, 93, 315, 487, 113, 774, 687, 248, 196, 469, 267, 106, 39, 1023, 87, 56, 539, 165, 1023, 77]]</t>
+    <t>[[152, 1764], [364, 79, 65, 117, 507]]</t>
   </si>
   <si>
     <t>h128_ws16_idx32768_random_infp32_outfp32_ID411</t>
   </si>
   <si>
-    <t>[[88, 30, 128, 300, 3058, 24161, 178, 9613, 449, 110, 179, 266, 6928, 42, 505, 495, 511, 310, 131, 462, 274, 352, 30170, 36, 26, 21245, 211], [3400, 312, 235, 319, 31941, 22158, 124, 78, 118, 379, 289, 139, 2, 149, 19, 1779, 497, 266, 113, 364], [32019, 9, 54, 295, 19880, 5020, 4686, 20192, 371, 106, 60, 402, 310, 6, 310, 243, 234, 299, 239, 157, 403, 113], [145, 84, 12, 79, 385, 64, 9023, 30585, 170], [2179, 57, 440, 176, 16026, 29, 177], [18, 93, 437, 433, 119, 106, 292, 115, 387, 403, 294, 160, 169, 15800, 74, 448, 22845, 40, 31248, 17, 394, 5628, 399, 310, 302, 351, 31871, 22947, 474, 505], [87, 8314, 13714, 367, 76, 127, 439, 364], [217, 100, 421, 28673, 180, 0, 371, 425, 29606, 473], [15160, 462, 15944, 352, 239, 91, 321, 11737, 345, 342, 452, 387, 328, 9, 14, 33, 509, 435, 43, 56, 81, 162, 359, 8517, 19450, 361, 96, 23869], [427, 410, 27, 88, 26557, 310, 361, 79, 438, 28, 9628, 42, 230, 22836, 15425, 303], [22051, 6086, 10060, 341, 56, 183, 70, 197, 318, 106, 99, 162], [94, 8686, 105, 153, 361], [480, 9653], [440, 29716, 99, 453], [224, 220, 400, 12302, 51, 492, 34, 415, 18933, 267, 28869, 159, 93], [229, 146, 28, 2771, 383, 466, 8839, 141, 27557, 314, 313, 97, 17, 1, 433, 15080, 170, 332, 337, 91, 2112, 323, 110]]</t>
+    <t>[[14, 149], [100, 302, 294, 349, 495, 129, 450, 442, 493, 474], [27], [217, 73, 213, 198, 207, 251, 406, 362], [44, 499, 993], [135, 194, 330, 241, 8, 72, 54, 110], [305, 231, 353, 355, 420], [359, 16, 155, 111, 507, 86, 375, 132], [364, 46, 382, 309], [9, 692, 424, 508, 87, 196, 128, 188, 23], [233, 414, 229, 1058], [130, 512, 1418], [277, 1869], [450, 375, 172, 39, 292, 300, 367, 212, 221], [256, 283, 464, 270, 122, 1530, 254, 1482], [121, 437, 155, 146, 76, 19, 768, 1920, 474]]</t>
   </si>
   <si>
     <t>h256_ws4_idx4096_random_infp32_outfp32_ID412</t>
   </si>
   <si>
-    <t>[[324, 5, 103, 220, 130, 207, 2750, 489, 3, 241, 1108, 3244, 306, 391], [366, 439, 149, 470, 3007, 263, 2198, 368, 13, 302], [224, 3158, 1708, 62, 496, 1874, 277, 13, 313, 329, 53], [1974, 61, 480, 354, 321, 3578, 8, 377, 240, 4078, 345, 484, 114, 29, 166, 634, 375, 237, 173, 285, 498, 4029, 113, 105, 485, 26, 2992, 358, 465, 1984, 326, 244]]</t>
+    <t>[[231, 477, 191, 563, 349, 1622], [296, 575, 2034, 1591, 258, 496, 269, 373, 305], [781, 24, 64, 307, 163, 249, 165], [203, 436, 287, 991, 336, 121, 121, 193, 334, 436]]</t>
   </si>
   <si>
     <t>h256_ws16_idx65536_random_inbf16_outbf16_ID413</t>
   </si>
   <si>
-    <t>[[224, 175, 363, 97, 59, 12414, 78, 384, 61243, 149, 61795, 161, 20793, 297, 507, 126, 240, 406, 258, 194, 143, 45764, 355, 37, 257], [29440, 277, 21, 118, 22266, 48, 358, 36877, 297, 248, 293, 5381, 285, 94, 25933, 398, 497, 410, 263, 65002, 390, 87, 429, 133, 324, 445], [33430, 213, 60809, 54158, 318, 310, 214, 335, 129, 87, 338, 372, 212, 98, 5987, 73, 56], [18774, 4, 20254, 88, 26089, 264, 3971, 471, 58116, 120, 266, 507, 0, 190, 163, 13604, 149, 256, 14, 109, 156, 214, 247, 12, 77, 133, 6], [248, 159, 255, 51621, 52216, 275, 40685, 63, 450, 197, 180, 381, 342, 485, 241, 17, 437, 56640, 472, 249, 49679, 77, 401, 255], [17163, 220, 168, 422, 40, 51069, 127], [415, 58, 53, 496, 253, 28, 193, 239, 247, 320, 232, 18830, 328, 321, 34594, 6112, 31, 10, 44723, 335, 430, 295, 27896], [317, 407, 63674, 6626, 488, 499, 426, 382, 72], [50748, 133, 70, 170, 482, 36576], [417, 419, 2, 388, 352, 48239, 346, 213, 271, 5047, 228, 53718, 144, 320, 379, 62250, 172, 132, 102, 338, 20, 21675], [234, 54185, 92], [4551], [120, 492, 51, 57, 8204, 198, 37975, 486, 38984, 133, 139], [30573, 50], [424, 406, 135, 435, 299, 28561, 168, 68, 2983, 83, 57196, 228, 4, 452, 195, 96, 1116, 183, 165, 69, 20, 33350, 143, 449, 137, 38, 76, 36120, 251], [288, 391, 152, 6, 469, 60840, 14, 109, 56, 140, 403, 443, 100, 107, 47874, 32792, 60, 88, 21192, 375, 29, 380, 461, 44073, 493, 379, 279, 5807, 195, 420]]</t>
+    <t>[[176, 220, 264, 420, 247, 201, 1227], [82, 119, 1902], [504, 1602, 238, 1115, 31, 36, 83, 27], [82, 477, 361, 1633, 1418, 335], [457, 65, 164, 72, 414, 321, 177], [386, 117, 1093, 108, 338, 2, 246, 289], [169, 404, 164, 57, 428, 333, 108, 813, 278], [384, 221, 306, 207, 139, 1748, 302, 503, 48, 1932], [310, 103, 1831, 233, 20, 414, 377, 224], [488, 1014, 460, 281, 58, 459, 457, 424, 409], [79, 362], [15], [406, 124, 1106, 1918], [8, 423, 65, 819, 30, 477, 509, 338, 316], [208, 44, 438, 308, 284], [11, 459, 1244, 54, 246, 209, 104, 504, 282]]</t>
   </si>
   <si>
     <t>h256_ws8_idx32768_random_inbf16_outbf16_ID414</t>
   </si>
   <si>
-    <t>[[321, 54, 290, 453, 17927, 83, 11877, 57, 86, 320, 439, 30512, 7290, 229, 255, 470], [397, 172, 451, 229, 46, 467, 192, 7324, 227, 8652, 6958, 369, 239, 6632, 247, 125, 20648, 478, 334, 138, 90], [152, 122, 192, 4553, 430, 492, 28434, 136, 22216, 310, 494], [10916, 448, 18, 459, 25128, 174, 485, 382], [149, 215, 166, 219, 71, 372, 283, 307, 10300, 4948], [30006, 151, 137, 287], [465, 215, 251, 179, 396, 2187, 53, 427, 11221, 446, 19489, 101, 376, 7419, 112, 20, 99, 78, 361, 158, 14475, 393, 300, 58, 301, 68, 57, 14778, 274], [265, 100, 365, 65, 416, 168, 144, 331, 311, 350, 361, 2674, 207, 18898, 114, 3052, 308, 17, 13317]]</t>
+    <t>[[1521, 54, 232], [205, 122, 336, 338, 1971, 484, 45, 299, 171], [483, 195, 94, 289, 93, 511, 188], [449], [2008], [130, 273, 887, 199, 7, 1922, 268, 1956, 6, 227], [463, 300], [335, 1787, 436, 168, 194]]</t>
   </si>
   <si>
     <t>h256_ws2_idx8192_random_infp16_outfp16_ID415</t>
   </si>
   <si>
-    <t>[[248, 220, 296, 370, 493, 445, 132, 4944, 6, 308, 318, 3265, 454, 6056, 463], [457, 4410, 1673, 166, 97, 485, 177, 235, 34, 685, 227, 503, 198, 414, 227, 3171]]</t>
+    <t>[[177, 65, 501, 438, 150, 714, 369, 23, 14], [281, 197, 2044, 256, 37, 438, 439]]</t>
   </si>
   <si>
     <t>h64_ws4_idx16384_random_inbf16_outbf16_ID416</t>
   </si>
   <si>
-    <t>[[399, 14774, 272, 36, 216], [274, 7730], [80, 70, 10, 6076, 5708, 42, 34, 132], [291, 14499, 219, 456, 98, 104, 2649]]</t>
+    <t>[[291, 669, 137, 327, 304, 1465], [436, 280, 305, 453, 509], [133, 376, 974, 1123, 39, 287, 202, 157, 261, 409], [288, 330, 406, 234, 188, 399, 216, 374, 309]]</t>
   </si>
   <si>
     <t>h256_ws16_idx32768_random_infp32_outfp32_ID417</t>
   </si>
   <si>
-    <t>[[385, 104, 20, 112, 170, 78, 488, 131, 274, 248, 38, 8894, 17178, 447, 183, 13967, 27933, 204], [21189, 295, 92, 17, 315, 3214, 246, 184, 26026, 470, 310, 506, 55, 59, 110, 208, 33, 2805, 30, 479, 339, 5788, 329, 492, 54, 469, 505, 320, 479, 22299, 41, 4824], [9506, 482, 429, 384, 369, 172, 1894, 28156, 27920, 76, 175, 304, 486, 302, 46, 135, 170, 451, 53, 433, 130, 144, 392, 8571, 483, 76, 434, 15599, 154, 166], [209, 185, 436, 22663, 249, 133, 101, 61, 58, 428, 376, 28488, 67, 17723, 178, 444, 368, 8881, 103], [418, 15957, 71, 24899, 435, 431, 274, 0, 386, 23861, 127, 477, 330, 124, 286, 128, 496, 46, 435, 16222, 33, 319, 32094, 259, 202], [4560, 222, 400], [228, 425, 449, 16840, 217, 18290, 28130, 86, 125, 7155, 11, 284, 314, 31, 400, 437, 3], [192, 157, 26441, 46, 211, 9328], [92, 13015, 353, 475, 346], [144, 264, 244, 94, 177, 243, 47, 412, 199, 395, 13445, 7715, 23411, 361, 490, 193, 313, 14589, 20328, 399, 117, 150, 158, 15], [107, 465, 16197, 292, 2068, 139, 71, 109, 393, 183, 136, 11037, 386, 284, 263, 16427], [195, 21847, 353, 169, 196, 120, 491, 85, 283, 220, 182, 1105, 3867, 493, 460, 14043, 497, 15293, 12, 185, 405, 399], [260, 5, 2772, 354, 413, 20675, 24014, 289, 118, 465, 7], [245, 452, 449, 11393, 107, 379, 57, 412, 360, 2492, 50, 463, 24459, 324, 255, 11056, 315, 117, 358, 394], [18, 14576, 335, 12885, 265, 283, 52, 491, 412, 70, 216, 222, 815, 11108, 402, 6357, 352, 325, 406, 173, 27], [360, 225, 19461, 297, 16316, 9340, 455, 375, 267, 244, 436, 183, 313]]</t>
+    <t>[[506, 447, 1854, 457, 476, 1593, 157, 309, 228], [196, 102, 94], [350], [425, 410, 171, 230, 327], [1985, 425, 1614, 200, 1566, 87, 283], [971, 331, 59, 229, 237, 184, 144, 136, 410, 325], [227, 445, 16, 357, 2048, 55, 415], [212, 252, 110], [1785, 372, 229, 283, 1576, 307], [1381], [498, 356, 265, 415], [147, 1452, 120], [1, 90, 76, 451, 2, 250], [322, 512, 1714, 41, 251, 1827, 411], [300, 266], [337, 281, 144, 193, 13, 1227, 298, 205, 267, 109]]</t>
   </si>
   <si>
     <t>h128_ws8_idx16384_random_infp16_outfp16_ID418</t>
   </si>
   <si>
-    <t>[[500, 74, 258, 493, 5, 2760, 446, 7819], [161, 113, 16153, 11147, 265, 249, 9, 124, 308, 213, 167, 410, 2991, 368, 420, 257, 9270, 152, 13118, 420, 196, 47], [471, 9539, 76, 203, 71, 6257], [80, 156, 2712, 13899, 1043, 5174, 118, 416, 26, 176, 477, 173, 69, 389, 297, 479], [356, 325, 15622, 498, 6246, 337, 30, 230, 171], [8721, 56, 473, 412, 289, 207, 494, 348, 160, 14595, 422, 395, 11465, 334], [427, 333, 113, 263, 9782, 226, 146, 178, 484, 121, 108, 188, 346, 199, 2762, 9140, 145, 9999], [55, 498, 3211, 380, 214, 89, 156, 31, 342, 15, 146, 446, 566, 139, 1099]]</t>
+    <t>[[237, 489, 401, 187, 1766, 173, 509, 1339, 505, 511], [78, 1572, 500, 979, 231, 315, 417, 133, 487, 275], [221, 21, 1009, 64, 6, 390, 497, 207, 135, 161], [428, 188, 8, 490, 123, 416], [31, 456, 353, 71, 27, 252, 464, 266, 258, 277], [91, 331, 1827, 269, 494, 507, 300], [449, 508, 318, 18], [408, 475]]</t>
   </si>
   <si>
     <t>h128_ws2_idx1024_random_inbf16_outbf16_ID419</t>
   </si>
   <si>
-    <t>[[657, 913, 349, 8, 183, 39, 170, 33, 323], [192, 38, 448, 501, 619, 25, 136, 372, 700, 479, 1001, 1, 126, 927, 505, 266, 238, 296, 137]]</t>
+    <t>[[2], [280, 26, 1281, 398, 325, 363]]</t>
   </si>
   <si>
     <t>h512_ws2_idx4096_random_infp32_outfp32_ID420</t>
   </si>
   <si>
-    <t>[[20, 238, 5, 215, 285, 136, 61, 702, 588, 369, 166, 249, 164, 91, 424, 961, 32, 239, 2243], [1092, 564, 269, 3957, 90, 1394, 3776, 2274, 271, 498, 293, 129, 55, 201, 58, 334, 2986, 80, 54, 430, 376, 295, 406, 449, 125, 414, 459, 298, 41, 352, 273]]</t>
+    <t>[[231, 457, 77, 330, 478, 1527], [256, 468, 95, 279, 457, 322, 452]]</t>
   </si>
   <si>
     <t>h128_ws8_idx16384_random_infp16_outfp16_ID421</t>
   </si>
   <si>
-    <t>[[395, 14434, 312, 91, 332, 10588, 404, 7075, 8, 381, 433, 105, 14399, 45, 506, 68, 418], [9599], [12495, 304, 409, 504], [352, 382, 237, 16, 5558, 438, 437, 5850, 301, 433, 56, 429, 332, 483, 22, 11968, 394, 34, 14, 149, 421, 4648, 38, 7225, 370, 16117], [21, 2445, 7561, 96, 344, 501, 218, 65, 141, 138, 12773, 149, 13750, 283, 111, 308, 13, 373, 13407, 83, 53, 300, 39, 8777, 200, 256, 485, 313], [111, 38, 114, 432, 243, 394, 116, 5698, 358, 1624], [3214, 350, 11], [304, 155, 202, 475, 307, 168, 200, 477, 87, 287, 436, 12000, 472, 3743, 144, 212, 6268, 118, 335, 340, 216, 143, 7912, 511, 13, 127, 11299, 317, 5644]]</t>
+    <t>[[828], [796, 60], [296], [124, 346, 709, 342, 144, 328, 210], [289, 8, 425, 385, 37, 221], [168, 125, 451], [446, 654, 327], [29, 187, 389, 405, 283, 296, 277, 231, 200]]</t>
   </si>
   <si>
     <t>h64_ws4_idx8192_random_infp16_outfp16_ID422</t>
   </si>
   <si>
-    <t>[[6587, 3609, 124, 249, 286, 31, 82, 504, 7240, 414, 298, 276, 61, 510, 421, 236, 318, 5, 124, 340, 2512, 265, 276, 5845, 424, 5259, 428], [356, 193, 347, 6569, 194, 414, 431, 6336, 412, 278, 341, 5, 362, 419, 6500, 4119, 72, 9, 8, 113, 86, 508, 6482, 485, 3235, 350, 147, 1418, 322, 60, 10], [5390, 35, 40, 477, 5915, 214, 444, 373, 358, 89, 7, 175, 479, 407, 4528, 99, 104, 132, 1112, 280, 285, 449, 424, 4153, 318, 965], [3667, 158, 137, 28, 19, 259, 5663, 19]]</t>
+    <t>[[306, 405, 1778, 252, 270, 45, 147, 112], [269, 164, 343, 114, 224, 279, 1385, 275], [179, 294, 267], [246, 430, 393, 265, 448, 439, 323, 433]]</t>
   </si>
   <si>
     <t>h256_ws2_idx4096_random_infp32_outfp32_ID423</t>
   </si>
   <si>
-    <t>[[4075, 301, 491, 799, 489, 330, 457, 172], [485, 445, 320, 72, 299, 135, 2269, 22, 3279, 90]]</t>
+    <t>[[1998, 178, 483, 214], [84, 42]]</t>
   </si>
   <si>
     <t>h64_ws4_idx2048_random_infp16_outfp16_ID424</t>
   </si>
   <si>
-    <t>[[1695, 110, 193, 483, 392, 468, 699, 268, 369, 677, 429, 299, 163, 64], [324, 24, 247, 450, 84, 268, 504, 806, 333, 380, 507, 57, 244, 467, 139, 1504, 352, 25, 613, 2006, 227, 282, 2003], [507, 499, 475, 185, 1019, 363, 520, 413, 13, 415, 446, 189, 501, 359, 464, 396, 272, 248, 1730, 195, 425, 1739, 67, 780, 171, 875, 366, 124, 298], [753, 166, 384, 27, 418, 293, 64, 499, 119, 410, 3, 1333, 300, 587, 26, 103, 358, 470, 532, 358]]</t>
+    <t>[[412, 83, 490, 462, 1483], [53, 122, 469, 435, 285, 384, 501, 1243, 104], [297], [394, 465, 1346, 319, 12, 216]]</t>
   </si>
   <si>
     <t>h128_ws8_idx8192_random_inbf16_outbf16_ID425</t>
   </si>
   <si>
-    <t>[[474, 239, 347, 479, 187, 154, 166, 411, 6639, 20, 401, 280, 6751, 3424, 6336, 317, 2765, 218, 12, 418, 29, 36, 347, 95, 39, 465, 358, 229, 129, 495, 7330, 1945], [177, 8, 6343, 380, 1, 119, 237, 272, 8006, 270, 360, 334, 351, 6022, 353, 146, 136, 7899, 352, 2847, 78, 335, 367, 178, 144, 8190, 15, 83, 347, 326], [5944, 360, 381, 7883, 433, 310, 43, 72, 130, 359, 208, 121, 107, 495, 189, 4047, 4948, 496, 6081, 233, 244], [3647, 310, 182, 490, 287, 5018], [1235, 75, 287, 53, 181, 163, 5937, 0, 482, 289, 6843, 441, 544, 293, 238, 182, 302, 86, 111, 447], [146, 3867, 213, 2661, 504, 390, 495, 210, 7618, 332, 118, 1539, 244, 31, 322, 414], [287, 71, 194, 3290, 320, 304, 178, 187, 304, 392, 184, 41, 458, 409, 378, 126, 142, 6551, 123, 4302, 3053, 440, 6753, 143, 308, 7096, 171, 378, 316], [294, 73, 275, 359, 37, 782, 278, 147, 4454, 6108, 83, 161, 3019, 163, 353, 450, 191, 102]]</t>
+    <t>[[20, 345, 409, 1498, 1687], [498, 2029, 146, 126, 319, 274, 229], [243, 1396, 1083], [346, 30, 12], [166, 201, 238, 127, 163, 148], [144], [194, 115, 322, 334, 415, 263, 19], [494, 349, 356]]</t>
   </si>
   <si>
     <t>h64_ws8_idx4096_random_inbf16_outbf16_ID426</t>
   </si>
   <si>
-    <t>[[30, 96, 304, 383, 1384, 253, 254, 996, 60, 347, 406, 411, 251, 196, 381, 3168, 345, 399, 180, 39, 1432, 3714, 67, 279], [414, 490, 386, 47, 3715, 1727, 72, 84, 171, 4064, 269, 97, 51, 503, 1843, 241, 87, 28, 432, 421, 9, 1471], [388, 168, 512, 1343, 89, 226, 410, 850, 156, 90, 281, 402, 2135], [202, 128, 223, 3610, 270, 1314, 3325, 176, 38, 473, 43, 316, 25, 3394, 339, 488, 417, 363, 273, 213, 120, 1900, 2794, 268, 488, 35], [795, 506, 501], [185, 466, 256, 496, 410, 236, 290, 444, 122, 2967, 119, 1447, 212, 380, 3423], [44, 3123], [1371, 334, 424, 490, 2, 2627, 92, 362]]</t>
+    <t>[[512, 193, 73, 10, 381, 470, 210, 151, 361], [382, 96, 277, 133, 411, 87], [159, 427, 1623, 135, 240, 194], [1798, 402, 65], [16, 782, 376, 1422, 423, 130, 336], [159, 367, 244, 82, 294], [119], [393, 346]]</t>
   </si>
   <si>
     <t>h64_ws2_idx1024_random_infp16_outfp16_ID427</t>
   </si>
   <si>
-    <t>[[719, 214, 422, 239, 143, 540, 155, 396, 231, 359, 397, 10, 421, 639, 434, 128, 12, 284, 367, 144, 148, 478, 203, 545, 418, 911, 383, 84, 860, 89], [695, 467, 149, 72, 199]]</t>
+    <t>[[417, 230, 66, 316, 138, 80, 184, 506, 46, 471], [512, 42, 131, 186, 349, 59, 1302, 466, 243, 86]]</t>
   </si>
   <si>
     <t>h256_ws16_idx8192_random_inbf16_outbf16_ID428</t>
   </si>
   <si>
-    <t>[[37, 5, 72, 7313, 120, 263, 78, 390, 480, 2806, 475, 278, 477, 85, 312, 2415, 357, 3801, 258, 163], [579, 485, 219, 65, 8], [22, 2938, 242, 425, 27, 20, 1926, 235, 495, 313, 206, 186, 157, 6953, 7561, 164, 1039, 99, 174, 10, 406, 56, 216, 268], [5681], [5809, 165, 379, 385, 292, 305, 462, 213, 4007, 121, 1836, 400, 7838, 1484, 3, 485, 439, 403, 262, 176, 6929, 94, 462, 209, 290, 511, 339, 283, 131, 179], [5397, 76, 249, 411, 382, 164, 509, 269, 40, 390, 268, 179, 4456, 5873, 337, 288, 1131, 211], [1167, 441, 3108, 476, 150, 467, 377, 219, 6315, 3493, 141, 433, 292, 334, 269, 57, 267], [7949, 179, 355, 440, 7683, 374, 281, 51, 260, 487, 6841, 2957, 445, 134, 462, 448, 185, 64, 5810, 248, 430, 432, 399, 115, 87, 2450], [512, 7636, 417, 0], [1197, 5168, 148, 493, 88, 422, 637, 367, 6508, 229, 262, 353, 155, 221, 99, 187, 476, 2141, 38, 4832, 503, 388, 158, 326, 76, 248, 454, 130], [331, 2595, 287, 331, 6623, 15, 154, 7053, 127, 237, 4, 442, 222, 3268, 347, 236, 301, 256, 186, 7417, 244, 167, 380, 85, 4875, 234, 7135, 408, 231, 209, 155], [12, 455, 1492, 6570, 212, 492, 396, 6370, 450, 196, 206, 52, 401, 59, 367, 408, 4134, 426, 417, 397, 6601, 18], [8174, 2, 350, 1926, 261, 343, 266, 3488, 432, 287, 497, 297, 140, 361, 3827, 119, 281, 221, 5321, 323, 251, 252, 410, 481, 258, 498, 4514], [261, 124, 200, 1540, 424, 345, 47, 4756], [3627, 339, 325, 325, 2779, 130], [502, 1882, 316, 10, 503, 147, 288, 38, 325, 8083]]</t>
+    <t>[[119, 318, 515, 471, 133, 1187], [490, 234, 128, 137, 1068, 153], [704, 344], [164, 31, 445, 227, 146, 1118, 398, 321, 357], [191, 232], [223, 72, 460, 131, 508, 211, 265], [305, 462, 59, 333, 412], [320, 818, 1235, 331], [1953, 662, 310, 51, 7, 143, 355], [1885, 839, 141, 65, 288, 229, 369, 444], [120, 192, 288, 763, 880, 178, 1244, 199, 489, 311], [796, 375, 12, 343, 331, 258], [477, 117, 1689], [254, 437, 392, 224, 368], [184, 162, 324, 233, 997, 465, 31, 65, 354, 96], [2, 448, 1812, 435, 217, 2038, 1892, 559, 307, 392]]</t>
   </si>
   <si>
     <t>h256_ws4_idx16384_random_infp32_outfp32_ID429</t>
   </si>
   <si>
-    <t>[[269, 13066, 295, 508, 314, 197, 442, 167, 356, 261, 147, 486, 122, 327, 289, 2399, 11020, 1, 3126, 257, 1613, 410, 74, 498, 445, 19, 10045, 405, 322, 206], [352, 264, 203, 147, 233, 181, 417, 302, 4777, 300, 14387, 165, 8028, 316, 18, 312, 197, 13490], [4960, 406, 416, 283], [2649, 6279, 489, 379, 253, 486]]</t>
+    <t>[[421, 237, 506, 410, 17, 1992], [786, 285], [327, 409, 1653, 280, 207, 340, 449, 170, 1], [382, 970, 1564, 481, 2]]</t>
   </si>
   <si>
     <t>h128_ws8_idx8192_random_infp32_outfp32_ID430</t>
   </si>
   <si>
-    <t>[[3603, 5352, 233, 338, 249, 170, 125, 4, 237, 382, 358, 2486, 53, 344, 921, 355, 478, 331], [4252, 494, 24, 173, 488, 91, 7333, 229, 204], [127, 2420, 423, 2263, 15, 385, 507, 254, 96, 506, 71, 7136, 272, 369, 4354, 3506, 201, 75, 385, 506, 1, 65, 199, 449, 410, 68, 4681, 47], [825, 166, 367, 485, 4510, 192, 286, 47, 144, 337, 357, 111, 201, 200, 6006, 298, 448, 3222, 2093, 413, 82], [231, 3475, 154, 314, 508, 10, 315, 402, 4942, 457, 5182, 330, 63, 76], [14, 486, 4599, 850, 15, 50, 7483, 240, 254, 1522, 120, 51, 480, 365, 372, 374, 371, 182, 91, 259, 142, 283, 3445, 141, 5, 489, 62, 2885, 344, 153], [60, 5565, 491, 273], [23, 355, 8001, 263, 2157, 53, 350, 222, 10, 819, 176, 105, 232, 336, 4661, 352, 5577, 243, 41, 166, 324, 157, 430, 165, 196, 456, 49, 125, 344, 334, 8099, 7957]]</t>
+    <t>[[241, 229], [82], [223, 484, 426, 391, 500, 140, 1503, 84], [321, 271, 460, 732, 474], [465, 32], [250, 341, 875, 123, 285, 1637, 477, 1509], [620, 980, 72, 5, 391, 242, 1041, 385], [53, 147, 389, 320, 388, 443]]</t>
   </si>
   <si>
     <t>h64_ws4_idx2048_random_infp32_outfp32_ID431</t>
   </si>
   <si>
-    <t>[[359, 98, 761, 66, 459, 1495, 179], [253, 411, 36, 123, 78, 233, 225, 338, 766, 37, 853, 244, 342, 1911, 392], [112, 870, 177, 0, 33, 303, 219, 51, 1612, 14, 297, 83, 1536, 233, 319, 1548, 500, 3, 935, 419, 447, 396], [192, 359, 272, 191, 525, 460, 64, 227, 824, 1253, 35, 641, 435, 136, 367, 179, 46, 1750, 236, 176, 375]]</t>
+    <t>[[370, 325, 676, 179, 298, 455, 286], [449, 459], [317, 1935, 55, 190], [416, 456, 300]]</t>
   </si>
   <si>
     <t>h256_ws16_idx8192_random_inbf16_outbf16_ID432</t>
   </si>
   <si>
-    <t>[[447, 267, 301, 52, 105, 431, 89, 5535, 420, 1995, 281, 102, 7554], [1120, 2744, 436, 261, 128, 497, 335, 203, 200], [1423], [40, 369, 222, 246, 282, 484, 271, 427, 2406, 301, 274, 416, 1585, 91, 5042, 201, 972, 287, 495, 544, 239, 435, 213, 108, 1712, 506], [3858, 294, 477, 267, 352, 293, 2275, 5657, 402, 395, 404, 69, 123, 496, 150, 1936, 44, 30, 39, 3320, 356, 86], [336, 265, 22, 5960, 24, 6297, 415, 1912, 330, 59, 318], [703, 124, 399], [431, 1288, 294, 8, 385, 483, 300, 301, 188, 212, 7682, 240, 250, 29, 156, 6469, 460, 6781, 269, 99, 63, 208, 472, 26, 141, 6399, 341, 356, 39, 812], [293, 232, 166, 55, 507, 85, 49, 6638, 233, 7872, 443, 8019, 208, 4826, 425, 79, 285, 5559, 429, 318, 22], [380, 343, 400, 43, 245, 6061, 6924, 2306, 272, 247, 5147, 43, 64, 412, 430, 281, 481, 275, 424], [478, 327, 437, 6547, 387, 1276, 50, 15, 272, 289, 198, 150, 509, 143, 233, 317, 196, 252, 52, 309, 4466, 206, 2387, 212, 136, 6079, 2142, 203, 357], [1947, 257], [379, 2715, 393, 235, 492], [57, 3953, 374, 180, 128, 1814, 167, 381], [439, 382, 228, 6732, 4, 5368, 120, 194, 78, 7877, 346, 102, 5528, 3384, 479, 217, 151, 37, 145, 277, 40, 330, 458], [129, 280, 365, 406, 59, 623, 452, 223, 5772, 330]]</t>
+    <t>[[1533, 370, 734, 362, 274, 266], [329, 346, 327, 35], [254, 183], [105, 1686, 96, 204], [314, 144], [149, 72, 359, 494, 397], [465, 180, 393], [1574, 437, 47, 300, 454, 458, 317, 238], [1017, 1209, 426, 428, 289, 404, 159], [458, 175, 8, 116, 514, 168, 116, 171, 318], [367], [58, 344, 351], [103, 308], [193, 53, 78, 479, 1781, 188, 298, 117, 1232, 12], [42, 419, 200, 8, 407, 1235, 61, 110, 113, 431], [215, 388, 20]]</t>
   </si>
   <si>
     <t>h64_ws2_idx1024_random_infp32_outfp32_ID433</t>
   </si>
   <si>
-    <t>[[289, 583, 263, 150, 402, 202, 142, 12, 174, 821, 440, 589, 304, 754, 448, 162, 227, 223, 342, 923, 50, 487, 503, 145, 268, 763], [451, 20, 75, 466, 277, 244, 605, 459, 800]]</t>
+    <t>[[155, 284, 413, 314, 1540], [1567, 85]]</t>
   </si>
   <si>
     <t>h64_ws8_idx4096_random_infp16_outfp16_ID434</t>
   </si>
   <si>
-    <t>[[351, 602, 80, 74, 330, 395, 757, 260, 459, 3375, 331, 506], [14, 756, 391, 3], [83, 122, 402, 2737, 398, 329, 242, 430, 311, 394, 342, 1575, 377, 348, 3445, 89, 403, 299, 3494, 3910, 36, 474, 187, 468, 324, 326, 1431, 317, 456], [310, 125, 2849, 96, 3354, 30, 82, 297, 448, 291], [78, 3878, 454], [1065, 1578, 402, 394, 397, 353, 67, 1731, 354, 65, 363, 446, 138, 442, 756, 436, 182, 337], [99, 62, 3965, 70, 225, 150, 482, 425, 101, 998, 423, 468, 349, 268, 401, 508, 87, 74, 920, 51, 1943, 299, 222, 244, 2452, 3254], [979, 57, 301, 505, 302, 313, 3543, 17, 480, 371, 73, 345, 448, 609, 211]]</t>
+    <t>[[482, 423, 201, 320, 1037, 1481, 290], [278, 53, 374, 356], [383, 116], [370, 449, 396, 58, 397, 34, 15, 385, 206, 117], [372, 128, 445, 375, 369], [11, 224, 1724, 451, 174, 386], [387], [260, 92, 400, 81, 293, 1706, 274, 1306]]</t>
   </si>
   <si>
     <t>h128_ws2_idx2048_random_infp16_outfp16_ID435</t>
   </si>
   <si>
-    <t>[[1407, 74, 12], [1915, 456]]</t>
+    <t>[[377, 462, 81, 94], [397, 254, 134, 124, 1117, 274, 249, 451, 405]]</t>
   </si>
   <si>
     <t>h64_ws16_idx8192_random_infp16_outfp16_ID436</t>
   </si>
   <si>
-    <t>[[7601, 57, 303, 272, 488, 4043, 5206, 288, 19, 415, 465, 192, 396, 105, 333, 19, 436, 338, 1014, 275, 6446, 3, 332, 339], [50, 3252, 7152, 506, 371, 354, 117, 226, 441, 372, 288, 38, 354, 4283, 86, 274, 321, 455, 418, 512, 7343, 1862, 170, 5154, 39, 455], [36, 270, 448, 51, 210, 1634, 67, 6105, 458, 315], [126, 400, 167, 294, 320, 380, 320, 447, 6940, 215, 467, 419, 3476, 4495, 379, 5491, 431, 452, 311, 408, 141, 24, 270, 21, 319, 374, 2628, 108, 7661], [3054, 347, 377, 439, 317, 5740, 429, 3752, 56, 131, 478, 178, 4803, 494, 42, 487, 364, 118, 478, 349, 2358, 1], [110, 1011], [24, 57, 110, 191, 237, 7742, 504, 1194, 234, 284, 419, 5536, 153], [101, 6030, 388, 3552, 361, 96], [438, 203, 434, 4907, 5174, 192, 226], [403, 451, 7497, 90, 171, 210, 123, 3121, 119, 2431, 291], [372, 451, 1845, 243, 7783, 236, 333, 55, 132, 486, 165, 2712, 4975, 507, 9, 215, 509, 4099, 148, 426, 224], [2103], [69, 199, 7569, 56, 128, 189, 174, 307, 4746, 139, 421, 26, 252, 147, 2597], [414, 4167, 255, 175, 512, 511, 6461, 246, 413], [440, 388, 4994, 20, 6, 342, 232, 58, 1139, 313, 123, 102, 221, 4186, 469, 115, 116, 260, 1962, 2433, 57, 419, 35, 4964, 323, 494, 188, 413], [282, 6671, 205, 26, 476, 186, 488, 1046, 2164, 3014, 287, 383, 155, 422, 335, 270, 153]]</t>
+    <t>[[261, 73], [321], [1523, 43, 1012, 279, 190, 393, 355], [460, 415, 244, 45, 274, 1035, 249, 185, 302, 249], [440], [469, 156, 512, 485, 42], [805, 86, 232, 106, 245, 282], [433, 183, 471, 462, 437], [258, 65, 189, 395, 350, 317, 148], [387, 47, 17, 277, 401, 1782, 458, 1753, 46], [1945, 454], [343, 1931, 331, 60, 1300, 1970, 62, 6], [471, 162, 125, 494, 434, 443], [149, 88, 1796, 176, 779], [87, 1450, 302, 53, 384, 196, 242, 256, 112], [1145, 246]]</t>
   </si>
   <si>
     <t>h64_ws4_idx4096_random_inbf16_outbf16_ID437</t>
   </si>
   <si>
-    <t>[[3246, 286], [1778], [394, 341, 452, 410, 3909, 682], [3928, 199, 463, 135, 28]]</t>
+    <t>[[339, 375, 1142, 109, 344, 293, 119, 1378, 178], [437, 350, 399, 477, 337, 416, 176, 275, 912], [175, 256], [123, 36, 285, 33, 225]]</t>
   </si>
   <si>
     <t>h512_ws4_idx16384_random_infp16_outfp16_ID438</t>
   </si>
   <si>
-    <t>[[298, 134, 83, 232, 11208, 14302, 342, 53, 443, 343, 102, 194, 8586, 12362, 51, 411, 35, 468], [12865, 396, 4099, 190, 391, 291, 504, 220, 59, 5378, 285, 449, 215, 459, 300, 8, 169, 147, 538, 4214, 6, 467, 3, 161, 58, 26, 3932, 161], [117, 310, 361, 3859, 304, 15924, 32, 5511, 430, 264, 111, 374, 146, 267, 22, 9356, 45, 89, 272, 141, 287, 2395, 440, 270, 198, 108, 5423, 404, 328], [139, 155, 52, 7248, 170, 92, 8609, 32, 29]]</t>
+    <t>[[231, 63, 1341, 371, 469, 323, 1729, 92], [27, 1, 286, 86, 476], [30, 488, 650, 1417, 507, 242], [36, 209, 161, 202, 237, 650, 20, 961, 291]]</t>
   </si>
   <si>
     <t>h512_ws2_idx8192_random_inbf16_outbf16_ID439</t>
   </si>
   <si>
-    <t>[[230, 5435, 289, 98, 456, 212, 470, 3030, 204, 7], [320, 109, 76, 37, 3440, 374, 7713, 79, 447, 162, 4477, 308, 318, 4738, 102, 442, 51, 49, 470, 231, 5099, 179, 29, 361, 405]]</t>
+    <t>[[36], [1958, 368, 217, 438]]</t>
   </si>
   <si>
     <t>h512_ws16_idx65536_random_inbf16_outbf16_ID440</t>
   </si>
   <si>
-    <t>[[197, 291, 76, 470, 154, 453, 8668, 185, 479, 55828, 38515, 11, 9316, 92, 366, 133, 463, 109, 323, 368, 294, 398, 39278, 321, 6, 53338, 466, 303, 432], [22935, 26987, 10, 183, 232, 10, 401, 200, 5327, 57, 236, 329, 95, 245, 415, 28, 55525, 225, 302, 455], [108, 327, 379, 293, 25704, 46171, 97, 452, 62045, 59, 56, 439, 461, 19, 22, 9137, 340, 274, 294], [58623, 493, 83, 1], [50001, 459, 2922, 57, 299, 388, 52443, 29, 11002, 245, 24697, 79, 125, 167, 385, 170, 86, 366, 30, 429, 148], [41, 130, 31865, 461, 26627, 477], [192, 456, 52885, 45, 118, 83, 385, 201, 16547, 14148, 26889, 413, 98, 5, 329, 500], [354, 375, 136, 438, 32287, 344, 15742, 466, 10344, 59779, 17346, 127, 152, 403, 21, 101, 62142, 288, 299, 255, 353, 314, 294, 183, 175, 25, 398], [178, 476, 26820, 58959, 235, 30516, 44154, 4, 210, 248, 31, 334, 388, 303, 185, 160, 507], [27173], [467, 194, 18159, 448, 505, 459, 134, 245, 377, 98, 91, 39, 132, 20340, 485, 260, 243, 16575, 106, 16110, 298, 492, 507, 24, 272, 63299, 310, 48034, 315, 20784, 433], [49440, 45, 433, 42130, 282, 41813, 299, 50, 480, 358, 289, 499], [43549, 115, 21, 41312, 261, 311, 354, 13, 57987, 35, 342, 12316, 320, 419, 108, 16, 429, 145, 9959, 49149, 110, 6, 225, 332, 431, 216, 54, 144], [29573, 337, 510, 14332, 457, 313, 303, 246, 263, 256, 352, 321, 117, 56, 457, 28832, 479, 184, 441, 508, 334, 346, 59236, 200, 55847], [400, 480, 192, 39, 154, 63136, 337, 46178, 326, 501, 29978], [63, 127, 308, 475, 307, 40717, 373, 244, 320, 4277, 49, 19592, 175, 22845, 400, 357, 39279, 261, 510, 485, 139, 6, 418]]</t>
+    <t>[[460, 155, 1497, 315, 78, 130, 65, 506], [175], [503, 506, 77, 134, 375, 574, 287, 1187], [312, 325], [346, 4, 169, 172, 46], [397, 482, 300, 272, 383, 458, 441, 11, 240, 299], [274], [245, 12, 264, 411], [499, 1266, 259, 157, 459, 48, 1051, 489, 1447, 194], [38, 52, 477, 452], [840, 76], [359, 451, 17, 501, 116, 1542, 355], [960, 215, 81, 220, 410], [477, 1219, 1076, 136, 392, 395, 63], [457, 67, 189], [332, 243, 95, 503, 282]]</t>
   </si>
   <si>
     <t>h256_ws2_idx4096_random_infp16_outfp16_ID441</t>
   </si>
   <si>
-    <t>[[236, 433, 94, 384, 3121, 505, 1386, 176, 99, 385, 184, 400, 23, 3682, 416, 2212, 329, 168, 134, 124, 51, 3743, 320, 197, 340, 3664, 328, 379], [1292, 50, 484, 9, 16, 792, 2468, 115, 905, 506, 336, 323, 343, 315, 371, 271, 349]]</t>
+    <t>[[373, 503, 54, 507, 144, 349, 186], [1013, 107, 206, 316, 111]]</t>
   </si>
   <si>
     <t>h256_ws2_idx8192_random_infp16_outfp16_ID442</t>
   </si>
   <si>
-    <t>[[448, 181, 939, 337, 2206, 294, 44, 502, 287, 39], [405, 5751, 488, 115, 6303, 185]]</t>
+    <t>[[396, 144, 1684, 290, 33, 187], [343, 467, 226]]</t>
   </si>
   <si>
     <t>h256_ws16_idx8192_random_infp32_outfp32_ID443</t>
   </si>
   <si>
-    <t>[[5663, 6587, 265, 13, 127, 4616, 195, 170, 7036, 226, 6378, 377, 192, 317, 183, 85, 290, 423, 450, 33, 152, 6116, 254, 399, 168, 113, 240, 429, 437], [126, 482, 179, 102, 274, 8155, 426, 451, 1735], [266, 6702, 86], [7570, 353, 7551, 211, 66, 7966, 500, 995, 120, 450, 94, 434, 58, 374, 217, 404, 310, 425], [3961, 37], [316, 336, 2013, 355, 5501, 7186, 848, 234, 399, 351, 155, 170, 247, 5119, 251, 472, 408, 194, 162, 150, 36], [452, 447, 369, 29, 25, 57, 4588, 1240, 7602, 392, 317, 444, 15, 6625, 68, 384, 2, 481, 3453, 360, 124, 489], [265, 149, 386, 4363, 94, 3804, 358, 110, 2023, 399, 502, 3521, 484, 276, 424, 413, 425, 463, 2574, 107, 280, 151, 310, 438, 321, 1310, 3, 126, 205, 496], [5163, 3780, 87, 58, 102, 75, 293, 7891, 467, 277, 126, 434, 61], [214, 386, 4479, 315], [206, 2796, 5768, 112, 67, 154, 224, 252, 68, 196], [54, 197, 408, 29, 394, 38, 313, 8093, 387, 3419, 52, 3085, 106, 283, 484, 358, 6633, 253, 235, 6453, 398, 201, 459, 52, 4340, 2993, 322, 261, 355, 438, 126], [18, 296, 429, 361, 429, 218, 7907, 3567, 425, 19, 62, 110, 450, 240, 32, 374, 291, 2656, 486, 243, 139, 6925, 216, 185, 6190, 1923], [2240, 49, 251, 486, 272], [52, 50, 607, 328, 89, 135, 7165, 390, 121, 7326, 123, 173], [283, 382, 3731, 5764, 306, 350, 247]]</t>
+    <t>[[97, 178, 16, 1470, 403, 202, 407], [43, 332, 185, 492, 208, 488, 508, 27], [185, 96], [410, 1728, 93, 1919, 213, 499, 214, 471, 457, 221], [15], [1637, 311, 882, 427, 136, 5, 1322], [446], [98, 415, 629, 31, 272, 404, 451, 1795, 480, 66], [1007, 205], [1483, 472, 170, 1033, 394, 343, 370, 28], [362], [83, 193], [328], [487, 273], [269, 90, 156], [453, 493]]</t>
   </si>
   <si>
     <t>h128_ws8_idx32768_random_infp16_outfp16_ID444</t>
   </si>
   <si>
-    <t>[[14826], [20524, 466, 444], [262, 83, 340, 355, 409, 144, 29390, 260, 23264, 2247, 161, 11, 108, 463, 251, 354, 72, 73, 433, 10, 495, 145, 353, 319, 26932, 13920, 438, 409, 217, 48, 6843, 16657], [5704, 343], [424, 178, 71, 205, 248, 434, 457, 282, 13497, 16279, 50, 170, 259, 32489, 49, 485, 385, 32, 24529], [297, 266, 19, 157, 499, 299, 8594, 407, 308, 236, 4156, 28707, 6740, 397, 95, 41, 364, 52, 9763, 487, 249, 430, 299, 141, 25242, 398, 454, 467, 288, 100], [98, 109, 410, 237, 310, 6302, 24402, 39, 22, 24159, 320], [87, 5288, 135, 130, 475, 307, 333, 7320, 447, 65, 137, 15137, 283, 421, 9, 230, 25730, 240]]</t>
+    <t>[[1637, 424, 75, 482, 21, 264, 40, 148], [226, 172, 261, 182, 468, 257, 176], [351, 608, 4, 226], [417], [190, 331, 346, 1489, 401], [10, 1087, 116, 602, 428], [8, 376, 362], [1, 67, 34, 399, 212]]</t>
   </si>
   <si>
     <t>h256_ws16_idx65536_random_infp16_outfp16_ID445</t>
   </si>
   <si>
-    <t>[[191, 180, 16249, 14623, 12, 291, 2823, 108, 6654, 456, 363, 473, 28, 50396, 381, 120, 43, 493, 329, 495, 315, 455], [418, 20238, 300, 746, 298, 432, 56], [13754, 422, 423, 496, 400, 20, 390, 338, 26, 26570, 33835, 385, 121, 119, 481, 53564, 433, 229, 37246, 75, 134, 452, 233, 204, 309, 12186, 117, 251], [52927], [445, 14946, 489, 7, 103, 72, 36133, 10, 63830, 133, 322, 464, 51734, 43, 423, 227], [497, 211, 297, 385, 217, 167, 120, 120, 484, 228, 12, 270, 18209, 318, 183, 57, 228, 37, 12391, 401, 3, 26700, 505, 15079, 45259, 54936], [349, 458, 376, 508, 405, 334, 309, 35271, 33542, 32, 396, 7508, 415, 245, 153], [333, 64264, 32824, 316, 251, 427, 20, 253, 70, 319, 60415, 476, 292, 375, 31924, 452, 215, 466, 452, 124], [508, 30, 4775, 66], [397, 260, 274, 246, 36535], [440, 332, 310, 218, 37047, 11399, 88, 253, 26677, 416, 316], [368, 61653, 503, 202, 145, 107, 49903, 370, 140, 284, 122, 12684, 342, 175], [310, 413, 52, 308, 324, 464, 37, 63552, 374, 60, 57308, 284, 182, 32350, 45159, 496, 138, 330, 309, 24, 168, 7137, 34, 123], [189, 510, 50, 57014, 25588, 111, 49201, 270, 117, 305, 395, 346, 20173, 444, 453, 409, 495, 97, 193, 489, 394, 51, 66, 336, 339, 2789, 7209], [253, 63821, 22953, 390, 509, 171], [8027, 137, 46599, 334, 167, 51057, 316, 447, 26, 226, 95, 78]]</t>
+    <t>[[421, 10, 340, 364, 65, 45, 222, 1225], [268, 307, 300, 429, 437, 751, 348, 371, 351, 434], [278, 30, 489, 392, 129, 391], [105, 242, 394, 332, 1792, 1211, 59, 1637], [494, 362, 130], [508, 279, 25, 436, 326, 316], [784], [482, 306, 809, 7, 239], [1876, 216, 337, 434, 104, 391, 430, 180, 409], [153], [344, 1572, 39], [411, 231, 391, 491, 308, 985, 392, 29, 489, 344], [362, 456, 329, 1076], [73, 489, 332, 66, 213, 1069, 136, 296, 374], [31, 333, 1235, 17], [496]]</t>
   </si>
   <si>
     <t>h64_ws2_idx4096_random_infp16_outfp16_ID446</t>
   </si>
   <si>
-    <t>[[177, 228, 274, 143, 155, 93, 236, 465, 87, 2252, 439, 35, 3878, 147, 2744, 196, 142, 143, 449, 335, 1993, 1032, 47, 99, 159, 2868, 315, 425, 206, 498, 2372], [107, 1369, 396, 437, 196, 433, 1596, 279, 366, 402, 285, 97, 2337, 101, 163, 2060, 337, 490, 425, 3647, 3296, 271, 499, 465, 421, 275, 444]]</t>
+    <t>[[1032, 624, 1298, 350, 328, 838], [478, 308, 1698, 127]]</t>
   </si>
   <si>
     <t>h512_ws4_idx2048_random_inbf16_outbf16_ID447</t>
   </si>
   <si>
-    <t>[[1641, 332, 508, 1625, 58, 397, 157, 220, 468, 2032, 126, 146, 57, 446, 18, 161, 51, 1120], [1711, 108, 502, 387, 139], [316, 367, 323, 36, 394, 451, 498, 1955, 1238], [319, 237, 147, 424, 1598, 132, 169, 446, 320, 379, 249, 266, 494, 296, 156, 180, 1452, 1018, 997, 405, 310, 128, 1194, 42]]</t>
+    <t>[[1265, 274, 315, 693, 372, 221, 721], [435, 1787], [134, 1570, 171, 187, 147, 315, 254, 284], [245, 26, 56]]</t>
   </si>
   <si>
     <t>h256_ws8_idx4096_random_infp32_outfp32_ID448</t>
   </si>
   <si>
-    <t>[[291, 237, 488, 380, 154, 1484, 2602, 43, 212, 465, 3858, 152, 3078, 303, 0, 338, 327, 1533, 260, 298, 230, 397], [3519, 2384, 247, 674, 462, 291, 405, 492, 106, 409, 373, 133, 59, 406, 281, 452, 3767], [507, 2111, 50, 290, 147, 432, 56, 1678, 4, 213, 475, 1, 88, 380, 362, 219, 54, 396, 180, 2595, 176, 1553, 575, 3505, 0, 203, 100], [474, 238, 244, 156, 2944, 255, 201, 298, 747, 165, 291, 1089, 378, 937, 455, 28, 309, 350, 468, 109, 330, 2469, 333, 264, 70, 10, 413, 415, 3503, 235, 2868], [392, 480, 192, 3571, 379, 64, 1081, 256, 414, 94, 455, 178, 2983, 1226, 148, 446, 360, 179, 453, 482, 422, 123, 148, 226, 1428, 106, 1631, 111, 395, 56], [408, 166, 3225], [2408, 400, 2581, 182, 470, 28, 490, 451], [91, 139, 493, 339, 339, 76, 449, 1470, 363, 1230, 62, 121, 155, 82, 474, 500, 496, 2829, 184, 329, 2983, 16, 3419, 287, 132, 258, 4081, 489]]</t>
+    <t>[[132, 124, 485, 70, 366, 296, 308, 347], [506, 265, 11], [512, 397, 528, 1820, 379, 493, 453], [1505, 55, 421, 1240, 324, 426, 116], [89, 209, 491, 543, 303, 191, 301, 454, 30, 365], [432, 172, 492, 298], [338, 455, 280, 384], [448, 207, 1095, 506, 504, 267, 1140]]</t>
   </si>
   <si>
     <t>h512_ws2_idx8192_random_inbf16_outbf16_ID449</t>
   </si>
   <si>
-    <t>[[6943, 125, 376], [6870, 156, 228, 6429, 247, 457]]</t>
+    <t>[[222, 120], [265, 376, 235]]</t>
   </si>
   <si>
     <t>h512_ws8_idx16384_random_inbf16_outbf16_ID450</t>
   </si>
   <si>
-    <t>[[7178, 4], [306, 494, 7978, 477, 155, 104, 380, 336, 257, 173, 5561, 2586, 398, 461, 226, 401, 135, 267, 14, 473, 3450, 4109, 3931, 151, 158, 55], [326, 387, 1260, 8086, 328, 74, 6], [71, 260, 223, 3213, 3716, 38, 352, 40, 437, 2205, 459, 382, 505, 3898, 292, 102, 344, 436, 447, 370, 234, 467, 236, 291, 15604, 14, 11017, 471], [8713, 468, 152, 318, 111, 53, 258, 77, 8931, 1077, 489, 86, 206, 326, 205, 358, 5158, 483, 229, 484, 425, 12, 14888], [163, 105, 282, 500, 6898, 1087], [507, 10, 154, 192, 13941, 1870, 178, 414, 222, 450, 326, 9153, 414], [478, 379, 415, 387, 5434, 2578, 246, 127, 338, 362, 503, 79, 67, 212, 483, 14551, 467, 238, 243, 15461, 246, 353, 245, 3762, 199, 474, 424, 11893, 60, 476]]</t>
+    <t>[[1613, 98, 305, 51, 55, 271, 1875, 70], [402, 239, 1799, 145, 16, 425, 141, 427, 1542, 386], [337, 14, 111, 1414, 342, 413, 487, 365, 363, 106], [303], [436, 165, 307, 490, 764, 511, 42, 395], [268], [437, 500, 281], [1278, 269, 352, 1896, 463]]</t>
   </si>
   <si>
     <t>h128_ws2_idx2048_random_infp16_outfp16_ID451</t>
   </si>
   <si>
-    <t>[[469, 20, 1511, 173, 173, 457, 281, 69, 491, 242, 997, 341, 277, 506, 502, 382, 256, 109, 268, 1516, 117, 1579, 56, 1423, 383], [516, 1825, 425, 1340, 261, 355, 1631, 198, 449, 429, 133, 70, 182, 467, 453, 282, 103, 313, 343, 1675, 469, 427]]</t>
+    <t>[[487, 103, 999, 55], [24, 417]]</t>
   </si>
   <si>
     <t>h512_ws2_idx8192_random_inbf16_outbf16_ID452</t>
   </si>
   <si>
-    <t>[[271, 6012, 251, 387, 438, 4169, 4653, 46, 416, 237, 386, 274, 218, 244, 25, 4774, 350, 52, 211], [483, 451, 7513, 389, 430, 3597, 102, 373, 324, 140, 318, 114, 146, 350, 154, 398, 6022, 497, 177, 144, 3486, 223, 5493, 442, 290, 1789]]</t>
+    <t>[[369, 381, 360, 1511], [61, 255, 1780, 1210, 355]]</t>
   </si>
   <si>
     <t>h128_ws16_idx16384_random_inbf16_outbf16_ID453</t>
   </si>
   <si>
-    <t>[[12300, 198, 486, 177, 254, 340, 3081, 97, 507, 1219, 1204, 268, 481, 40, 14260, 253, 84, 210, 358, 507, 393, 312, 348, 456, 62, 59, 255, 48, 213, 2928], [280, 3300, 169, 421, 337, 3070, 121, 80, 299, 220, 628, 15, 261, 2686, 245, 184, 277, 7502, 80, 324, 472], [328, 8289, 12020, 60, 26, 252, 492], [278, 185, 448, 267, 438, 188, 4929, 174, 4832, 18, 3757, 492, 180, 269, 12, 46, 618, 314, 322], [111, 4, 476, 114, 239, 4351, 386, 82, 492, 268, 380, 50, 418, 300, 214, 9889, 247, 15844, 2721, 329, 6546, 179, 341], [10279], [325, 223, 388, 270, 13977, 349, 14695, 265, 11787, 16026, 203, 21, 267, 103, 46, 441, 67], [377, 474, 104, 414, 298, 15488, 205, 475, 429, 352, 311, 7, 407, 291, 10964, 445, 415, 15151, 413, 271, 6034, 462, 10772, 224], [113, 12139, 212, 336, 476, 244, 13601, 40, 126, 15911, 452, 164, 5582, 505, 380, 408, 263, 229, 162, 493, 286, 336, 132, 401, 14349], [300, 102, 10412, 10, 287, 236, 395, 11575, 260, 406, 99, 31, 8738, 12373, 165, 275], [384, 5028, 1932, 460, 261, 452, 220, 12980, 26, 185, 308, 355, 467, 290, 89], [189, 463, 60, 4485, 7350, 478, 187, 133, 291, 14323, 118, 455, 195, 237, 11129, 176, 237, 203, 114, 74, 148, 8979], [322, 174, 68, 24, 398, 6004, 292, 204, 5137, 395, 4494, 331, 44, 13445, 9163, 15, 142, 163, 434, 466, 74, 3857, 86, 97, 9856, 268, 502, 265, 352, 451, 469], [321, 294, 1665, 239, 202], [214, 119, 135, 12288, 11318, 11, 507, 498, 245], [7935, 23, 73, 296, 429, 8922, 320, 55, 407, 271, 206, 407, 377, 4424, 281, 301, 246, 13314, 286, 334]]</t>
+    <t>[[425, 460, 368, 376, 509, 224, 369, 299], [916, 1025], [1530], [352, 463, 256, 38, 319, 390], [224, 1175, 57, 169], [174, 874, 186, 197, 149, 184], [1942, 363, 1921, 42, 145, 135, 45], [722, 419], [521, 145, 87, 472, 149, 449, 266, 132], [501, 1582, 30, 377, 311], [438, 169, 433, 27, 338, 433], [384, 158, 735, 587, 108, 130, 1218], [25, 179, 241, 64, 436, 497, 978, 289, 535], [437, 1743, 401], [1509, 1022, 179, 396, 218, 415, 1686], [466, 1172]]</t>
   </si>
   <si>
     <t>h128_ws4_idx4096_random_infp32_outfp32_ID454</t>
   </si>
   <si>
-    <t>[[30, 3092, 106, 228], [247, 257, 3975, 505, 33, 131, 506, 3734, 272, 41, 179, 512, 332, 2794, 482, 261, 40, 323, 336, 2819, 105, 1193, 59, 64, 271, 1269, 105, 353, 60, 233], [81, 451, 453, 284, 1444, 3343, 462, 210, 492, 242, 88, 14, 1468, 423, 68, 1071, 231, 274, 74, 456, 892, 2182, 154, 143, 32, 66, 398, 231], [443, 225, 131, 232, 232, 372, 481, 596, 267, 2149, 89, 2890, 457, 2124, 4082, 107, 1976, 204, 441, 217, 156, 40, 78, 179, 458, 309]]</t>
+    <t>[[128, 79, 383, 188], [1113, 165, 369], [1350, 459, 321, 369], [1495, 131, 74]]</t>
   </si>
   <si>
     <t>h128_ws4_idx16384_random_inbf16_outbf16_ID455</t>
   </si>
   <si>
-    <t>[[103, 461, 33, 183, 374, 11094, 77, 494, 109, 15226, 220, 455, 2655, 11834, 325, 306, 46, 346, 294, 461, 313, 452, 376, 10296], [7300, 7707, 226, 14725, 511, 231, 155, 24, 54, 360, 12440, 128, 309, 86, 325, 218], [11169, 353, 1954, 226, 354, 432, 21, 234], [225, 342, 11678, 197, 368, 410, 7276]]</t>
+    <t>[[240, 116, 80, 154, 295, 264, 496, 260], [8, 246, 436, 420, 305, 99, 174, 444, 403], [445, 458, 172, 263, 987, 282, 294, 497, 141], [304, 287, 132, 328, 1684, 588, 35]]</t>
   </si>
   <si>
     <t>h128_ws4_idx16384_random_infp32_outfp32_ID456</t>
   </si>
   <si>
-    <t>[[169, 327, 14110, 246, 277, 360, 304, 133, 11641, 43, 354, 327, 2358, 33, 344, 14, 2587, 11291, 159, 380, 324, 433, 378, 208, 41, 258, 14457], [2837, 7910, 174, 65, 185, 12, 286], [96, 310, 93, 361, 9367, 167, 4687, 186, 195, 234], [223, 271, 122, 379, 316, 81, 319, 246, 60, 10028, 258, 10153, 9297, 512, 252, 3762, 419, 477, 8447, 341, 140, 164, 366, 490]]</t>
+    <t>[[318, 297, 501, 465, 196, 219, 1062, 493, 453, 176], [512, 113, 360, 285, 168, 357, 346, 489], [323], [67, 383, 260]]</t>
   </si>
   <si>
     <t>h256_ws8_idx8192_random_infp32_outfp32_ID457</t>
   </si>
   <si>
-    <t>[[399, 8, 30, 6249, 33, 306, 7574, 137, 122, 266, 4999, 3524, 137, 364, 124, 416, 357, 510, 110, 280, 4518, 101, 3, 78], [5477, 1843, 385, 140, 403, 79, 72, 3244, 10, 317, 196, 378, 375, 472, 1134, 337, 114, 2849, 1579, 323, 135, 449, 235, 363, 321, 412, 252, 382, 292, 286], [336, 468, 259, 7125, 166, 1, 7202, 63, 56, 357, 176, 152, 96, 6765, 21, 91, 3096, 132], [508, 154, 5153, 123, 427, 82, 361, 476, 89, 3298, 14, 458, 2926, 58, 118, 2270, 481, 62, 333, 66, 4966], [83, 128, 89, 105, 95, 487, 247, 268, 485, 1782, 491, 51, 469, 435, 283, 2870, 3650, 3925, 397, 6480, 373, 206, 274, 145, 81, 3460], [3625, 269, 7, 404, 413, 132, 277, 2369, 189, 3320, 80], [396, 87, 19, 502, 289, 466, 96, 2329, 349, 1961, 6178, 229], [201, 435, 19, 317, 5823, 6314, 375, 145, 52, 283, 193, 7532, 192, 78, 261]]</t>
+    <t>[[275], [188, 283, 100, 403, 625, 277], [149, 368, 2027, 1199, 153], [495, 1975, 108, 135, 464, 25, 162, 366, 421, 355], [395, 1553, 1918, 139, 96, 424, 388, 284, 412, 80], [164, 400, 1460], [178, 32, 369], [1681, 216, 64, 120, 436, 396, 284, 461]]</t>
   </si>
   <si>
     <t>h64_ws2_idx2048_random_infp16_outfp16_ID458</t>
   </si>
   <si>
-    <t>[[159, 280, 324, 606, 175, 404, 10, 170, 489, 489, 468, 1688, 22, 328, 462, 996, 71, 353, 414, 1779, 2006, 238, 421, 98, 1008, 26, 20, 472, 278, 423], [354, 1157]]</t>
+    <t>[[430, 9, 433], [419, 63, 291]]</t>
   </si>
   <si>
     <t>h64_ws4_idx2048_random_infp32_outfp32_ID459</t>
   </si>
   <si>
-    <t>[[219, 488, 1402, 173, 219], [225, 388, 385, 7, 260, 798, 414, 1101, 273, 335], [1391, 488, 231, 370, 221, 274, 1533, 225, 509, 360, 19, 435, 39, 595, 470, 329, 79, 63, 444, 408, 117, 457, 1002, 981, 445], [494, 320, 218, 926, 308, 194, 431, 374, 374, 1326, 1183, 406]]</t>
+    <t>[[135, 371, 105, 130, 498, 34], [183, 133, 1665, 859, 122, 48, 315, 165, 191, 406], [506, 1870, 419, 208, 46], [312]]</t>
   </si>
   <si>
     <t>h64_ws8_idx4096_random_infp16_outfp16_ID460</t>
   </si>
   <si>
-    <t>[[152, 319, 122, 81, 65, 421, 271, 111, 2052, 1633, 237, 1359, 64, 63, 41, 466, 3550, 1469, 396, 431, 305, 48, 110, 658, 24, 427], [181, 3398, 241, 103, 94, 349, 299, 1429, 247, 87, 0, 225, 3473, 1452, 246, 137], [511, 3784], [149, 273, 216, 363, 46, 444, 63, 187, 216, 348, 105, 2747, 457, 740, 2881, 384, 239, 1939], [2573, 34, 2543, 111, 480, 498, 186, 3173, 206, 52, 199], [361, 167, 301, 9, 2291, 200, 2450, 446, 126, 180, 22, 237, 311, 3188, 57, 184, 486, 215, 2935, 335, 1925], [21, 275, 201, 54, 2459, 32, 138, 2628, 316, 66], [2272, 479, 435, 315]]</t>
+    <t>[[192, 535], [2020, 139, 285, 446, 1563, 291, 187, 410, 232, 446], [147, 18, 352, 345, 138, 1919, 395, 367], [255, 409, 493, 257], [274, 948, 453, 1768, 466, 356, 450, 238, 153], [250], [348, 356, 1312, 48, 217, 266, 259, 276, 53], [160, 1689, 804]]</t>
   </si>
   <si>
     <t>h512_ws2_idx4096_random_infp16_outfp16_ID461</t>
   </si>
   <si>
-    <t>[[315, 190, 469, 292, 504, 474, 375, 361, 271, 3493, 3553, 584, 74, 68, 375, 374, 327, 2347], [40, 229, 125, 360, 206, 423, 299, 168, 474, 229, 3896, 420, 1736, 195, 327, 447, 2570, 2264, 327, 424, 3581]]</t>
+    <t>[[163], [172, 892]]</t>
   </si>
   <si>
     <t>h128_ws8_idx8192_random_infp32_outfp32_ID462</t>
   </si>
   <si>
-    <t>[[27, 7875, 204, 182, 112, 5239, 295, 36], [7150, 244, 381, 107, 137, 432, 3098, 167, 467, 214, 330, 459, 80, 46, 212, 318, 668, 5324, 186, 374, 460, 3452, 509, 476, 181, 2326, 438, 448, 454], [4264, 34, 44, 151, 6280, 111, 7312, 12, 205, 2, 499, 762, 145, 499, 71, 71, 450, 192, 4, 235, 213, 462, 386, 839, 22, 1690], [389, 384, 355, 413, 2255, 774, 206, 11, 343, 138, 119, 5684, 94, 178, 151], [4496], [349, 5451, 470, 295, 465, 170, 488, 3266, 304, 432, 7335, 56, 439, 234, 31, 143, 293, 208, 6733, 122], [94, 213, 456, 3211, 188], [1625, 152, 474, 2494, 420, 400, 231]]</t>
+    <t>[[430, 458, 226], [318, 377, 107, 159, 274, 1017, 86, 371, 319, 464], [369, 143, 260], [28, 246, 118, 188, 220], [160, 431], [239, 55, 1578, 1911, 286, 256], [495, 291, 493, 355, 297, 278], [354, 381, 178, 29, 470, 717, 396, 262, 146, 507]]</t>
   </si>
   <si>
     <t>h256_ws2_idx4096_random_infp16_outfp16_ID463</t>
   </si>
   <si>
-    <t>[[2026, 104, 227, 333, 3064, 63, 500, 315, 1063, 323, 35, 90, 227], [338, 287, 452, 267, 494, 297, 32, 166, 2340, 2111, 456, 282, 3261, 1142, 691, 464, 416, 61, 57, 255, 475, 29, 31, 363]]</t>
+    <t>[[117, 465], [53, 389, 309, 134]]</t>
   </si>
   <si>
     <t>h512_ws4_idx16384_random_infp32_outfp32_ID464</t>
   </si>
   <si>
-    <t>[[33, 12440, 89, 1, 429, 505, 508, 315, 312, 325, 12146, 388, 195, 1033, 13434, 170, 200, 506, 481, 216, 11762, 90, 360, 284, 11, 5828, 6150, 199, 218, 297, 6], [166, 342, 96, 195, 12, 263, 303, 76, 839, 389, 89, 4206, 15752, 114, 154, 7, 234, 31, 428, 4151, 290, 503, 1, 163, 98, 9394, 270, 303, 1423], [299, 355, 82, 166, 7759, 152, 414, 374, 372, 12518, 13833, 466, 475, 24, 428, 176, 13525], [15551, 505, 235, 13135, 421, 11]]</t>
+    <t>[[394, 210, 420, 497, 1069, 456, 404, 362, 127, 115], [181, 45, 118], [287, 370, 459, 61, 374, 505, 370, 109, 102, 254], [475, 998, 258, 261, 433, 1074, 249]]</t>
   </si>
   <si>
     <t>h512_ws16_idx32768_random_inbf16_outbf16_ID465</t>
   </si>
   <si>
-    <t>[[10731, 21428, 496, 364, 429, 372, 234, 26828, 250, 23, 252, 199, 90, 76, 16941, 413, 499, 425, 383, 129, 289, 397, 289, 339, 402, 489, 25061, 116, 21998, 416], [21940, 296, 13304, 22400, 13609, 202, 90, 107, 465, 134, 357, 32590, 14, 31071, 389, 86, 2, 84, 345, 312, 204, 183, 423, 299, 199, 80], [302, 453, 21571, 152, 8020, 342, 374, 171, 496, 393, 479, 329, 498, 234, 223, 412, 155, 157, 212, 284, 454, 458, 44, 30924, 5954, 16061, 402, 22323, 145], [358, 30763, 123, 358, 460, 385, 360, 30350, 111, 4506, 463, 366, 7917, 25, 80, 153, 315, 126, 473], [172, 320, 411, 194, 418, 319, 73, 60, 233, 172, 430, 161, 31743, 16097, 333, 14408, 218, 315, 476, 343, 381, 149, 7205, 4183], [92, 213, 290, 115, 189, 27964, 16873, 51, 232, 15474, 400, 196, 17], [504, 31254], [315, 355, 364, 383, 27167, 390, 321, 217, 21837, 130, 461, 398, 29, 262, 470, 17705, 28168], [26355, 146, 341, 484, 69, 32486, 14606, 330, 92, 216, 30973, 72, 5627, 474, 302, 94, 137, 64, 322, 510, 323, 203, 36], [454, 417, 492, 91, 173, 20764, 33, 207, 19269, 18774, 139, 371], [28088, 495, 454, 220, 510, 193, 468, 5135, 5203, 459, 25, 31627, 82, 237, 481, 190, 142, 263, 17966, 267, 352, 477, 421, 1952, 364, 8708, 419, 444, 203, 165, 296, 369], [339, 1799, 19690, 262, 192, 321, 37, 22226, 15, 14042, 352, 85, 2, 404, 100, 405], [270, 383, 246, 29145, 240, 758, 251, 243, 29493, 497, 428], [22, 2, 29680, 54], [264, 195, 355, 0, 265, 245, 22355, 350, 260, 174, 199, 491, 21378, 172, 348, 452, 6689, 61, 186, 208, 116, 26728, 297, 252, 90, 32065, 9991, 452], [55, 146, 205, 370, 495, 426, 150, 4720, 283, 14499, 1096, 201, 250, 176, 400, 87, 199, 6599]]</t>
+    <t>[[154, 487, 156, 1785, 508, 177, 77, 407, 70], [168, 51, 7, 383, 347, 377], [288, 294, 393, 429, 319, 179, 302], [370, 862, 450, 1981, 240, 448, 135, 204, 59], [445, 406, 306, 420, 302, 315, 167, 906, 19], [123, 114, 306, 6, 478, 398, 578, 378], [240, 14, 459, 762], [473, 161, 314, 191, 179, 44, 249, 16, 27], [430, 68], [1638, 673, 198, 143, 250, 267], [36, 29], [290, 995, 23, 50, 79, 29, 234, 209, 266], [361, 110, 50, 387], [475, 169, 616], [54], [435, 175, 436]]</t>
   </si>
   <si>
     <t>h512_ws4_idx8192_random_inbf16_outbf16_ID466</t>
   </si>
   <si>
-    <t>[[206, 190, 112, 268, 318, 2235, 314, 180, 4700, 55, 222, 1543, 67, 1602, 225, 345, 367, 63, 1192, 3956, 277, 343, 362, 138, 28, 388, 391, 9, 298], [82, 424, 452, 463, 506, 157, 433, 159, 333, 194, 258, 39, 2003, 453, 4915, 8154, 173, 188, 108, 3522, 1818, 351, 89, 209, 463, 482, 6670, 269, 355, 301], [5836, 505, 118, 474], [103, 136, 2232, 5503, 48, 120, 193, 416, 38, 154, 155, 46, 35, 73, 486, 378, 36, 153, 496, 930, 6521, 204, 655, 336]]</t>
+    <t>[[77, 203, 1278, 394, 294, 416], [1269, 342, 271], [298, 448, 95, 991, 23, 1500, 499], [362, 805, 487, 472, 243, 337]]</t>
   </si>
   <si>
     <t>h64_ws2_idx2048_random_inbf16_outbf16_ID467</t>
   </si>
   <si>
-    <t>[[509, 644, 417, 68, 351, 451, 182, 364, 1158, 24, 467, 146, 1521, 434], [165, 29, 1485, 237, 466]]</t>
+    <t>[[409, 1323, 438, 30], [214, 503, 155, 222, 271, 356, 434, 151, 232]]</t>
   </si>
   <si>
     <t>h256_ws4_idx8192_random_inbf16_outbf16_ID468</t>
   </si>
   <si>
-    <t>[[464, 2936, 451, 157, 229, 401, 144, 483, 317, 622, 5701, 448, 254, 309, 243, 54, 2545, 373, 47, 59, 503, 5790, 410], [21, 809, 68, 35, 110], [3854, 45, 371, 261, 378, 188, 163, 294, 450, 339, 7677, 170, 6319], [263, 319, 424, 0, 6928, 251, 224, 311, 352, 8148, 2602, 496, 3058, 4258, 170, 441, 154, 5865, 350, 432, 100, 503, 7, 446, 399, 146, 386, 4345, 440, 284, 364]]</t>
+    <t>[[301, 166, 180, 299, 793], [258, 490, 400, 404, 717], [390, 955, 62, 163, 339, 244, 19], [386, 1480, 187]]</t>
   </si>
   <si>
     <t>h256_ws8_idx8192_random_infp16_outfp16_ID469</t>
   </si>
   <si>
-    <t>[[751], [67, 6345, 7590, 113, 463, 123, 436, 453, 107, 303, 285, 192, 316, 4849, 327, 401, 25, 4436], [8033, 5586, 26, 196, 10, 308, 282, 334, 342, 4402, 160, 366, 194, 375, 149, 246, 317, 380, 16, 260, 3973, 43, 101, 276, 3150, 2070, 463, 143, 474, 346, 5982, 411], [351, 7961, 508, 304, 424], [446, 913, 88, 374], [164, 8058, 1530, 123, 497, 193, 191, 38, 350, 230], [160, 405, 4888, 6466, 61, 7219, 77, 5248, 307, 454, 349, 2136, 490, 477, 361, 169, 274, 27, 252, 130, 7008, 229, 461, 449, 470, 52], [317, 96, 165, 4974, 164, 449, 474, 334, 2157, 388, 248, 337, 341, 369, 1695, 504, 483, 282, 458, 7045, 132, 462, 3646, 415]]</t>
+    <t>[[353, 222, 280, 495, 219], [415, 1105], [35, 400], [391, 187, 1530, 393, 64, 99, 511, 315, 168], [237, 331, 125, 473, 10, 186, 45, 297, 294, 285], [326], [115, 83], [411, 485, 1392, 351, 1650, 109, 379, 352]]</t>
   </si>
   <si>
     <t>h64_ws16_idx65536_random_infp32_outfp32_ID470</t>
   </si>
   <si>
-    <t>[[48980, 407], [152, 322, 21631, 468, 499, 19140, 19583, 133, 152, 283, 212, 119, 56937, 453, 218, 38, 232, 256, 138], [433, 468, 405, 403, 26, 14802, 253, 297, 312, 434, 290, 363, 292, 35950, 171, 32, 264, 42369, 33116, 22529, 139, 456, 293, 165], [17508], [164, 60424, 223, 150, 7316, 59, 418, 58, 356, 392, 66, 55495, 305, 29, 240, 43862, 56318, 72, 96, 332, 162], [165, 5520, 210, 218, 206, 367, 58021, 278, 411, 67, 103, 13414, 213, 416], [135, 15746, 107], [104, 34715, 24, 351, 56, 60383], [5056, 153, 480, 512, 121, 135, 334, 62963, 506, 176, 230, 33884, 502, 278, 38, 421, 354, 3282, 352, 321, 130, 302, 59070, 149, 364, 198, 398, 772, 28462, 503, 149], [139, 465, 235, 36, 30259, 321, 234, 16200], [456, 94, 23779, 344, 15122, 33, 215, 127, 246, 14146, 135, 455, 367, 382, 1, 48, 64401], [4083, 100, 53510, 43, 157, 62, 180, 304, 284], [388, 37, 65305, 188, 245, 44773, 36585, 42, 319, 60103, 490, 5267, 215, 200, 482, 133, 118, 8, 295, 43, 67, 438], [417, 354, 4, 113, 62164, 495, 105, 260, 22955, 20873, 270], [109, 96, 10549, 38131, 381, 478, 369, 57177, 396, 14828, 454, 488, 115, 404, 33, 53, 416, 6, 84, 508, 133, 229, 471, 31538, 147, 257, 164, 135, 343, 47746], [480, 338, 470, 41830, 210, 41397, 483]]</t>
+    <t>[[893, 435, 541, 1869, 1014], [482], [92, 13, 299, 194, 382, 1005], [27, 387], [223, 175, 1285, 302, 1629, 28, 1797, 158, 393, 28], [112, 34], [249, 224, 114, 444, 268, 17, 342], [473, 484], [252, 286, 1218], [366, 408, 349, 465, 19, 37], [61, 1222, 294, 96, 598, 235], [504, 406], [1406, 1105], [385, 35, 415], [45, 419, 205], [122, 644, 286, 1741, 352]]</t>
   </si>
   <si>
     <t>h512_ws8_idx4096_random_inbf16_outbf16_ID471</t>
   </si>
   <si>
-    <t>[[3093, 386, 142, 412, 76, 4048, 158, 209, 203, 31, 246, 154, 198, 2843, 465, 821, 408, 114, 0, 407, 2171, 185, 316, 358, 174], [411, 348, 1606], [214, 321, 2760, 473, 367, 363, 72, 414, 381, 141, 246, 411, 177, 3695, 463, 263, 342, 3262, 732, 195], [236, 107, 118, 8, 104, 1107, 1625], [511, 181, 359, 293, 2694, 211, 2316, 9, 164, 16, 3925, 5, 352, 301], [334, 3414], [1297, 202, 437, 295, 167, 26, 505, 144, 129, 439, 17, 450, 186, 350, 432, 355, 146, 128, 3770, 2005, 319, 48, 3376, 16, 267, 1902, 740, 128], [461, 1533, 2318, 179, 381, 431, 61, 43, 1746, 132, 282, 206, 3321, 206, 483, 327, 130, 54, 469, 331, 1516, 124, 421, 274, 171, 369, 1878, 220, 152]]</t>
+    <t>[[135, 224, 447, 130, 84, 289, 1173], [382, 464, 1341, 14, 479, 377, 230, 275, 337], [192, 1836, 263, 322, 1608, 92, 1695, 108, 198], [215, 209, 1536, 119], [79, 19, 422, 397, 78, 992, 271, 439], [471], [256, 477, 271], [31, 126, 141, 238, 164, 362, 397, 269, 181, 65]]</t>
   </si>
   <si>
     <t>h512_ws8_idx8192_random_infp32_outfp32_ID472</t>
   </si>
   <si>
-    <t>[[1687, 399, 71, 260, 369, 177, 366, 481, 168, 478, 512, 6582, 449, 6540, 328, 6329, 355, 229, 7049, 491, 55, 160], [467, 376, 234, 226, 288, 140, 509, 2225, 355, 407, 390, 368, 3306, 260, 4987], [401, 81, 172, 390, 259, 484, 338, 75, 344, 3808, 2380, 43, 375, 476, 4466, 5223, 278, 267, 154, 71, 371, 2999, 457, 33, 391], [3781, 38], [307, 111, 371, 120, 390, 7034, 7939], [152, 7886, 91, 352, 2968, 327, 95, 70, 496, 406, 6730, 216], [133, 4068, 575, 345, 1312, 301, 311, 16, 501, 223, 374, 115, 509, 321, 3922, 41, 314, 2293, 273, 7932, 191, 162, 1640, 172, 129, 186, 120, 35, 443, 332, 229, 103], [287, 151, 9, 405, 448, 7147, 262, 7629, 395, 273, 127, 80, 484, 120, 354, 494, 363, 6082, 229, 5294, 6053]]</t>
+    <t>[[37, 509, 70, 9, 238, 1560, 369], [714, 356], [371, 438], [387, 354, 502, 341], [79, 267, 228, 159, 195, 217], [259, 12, 447, 275, 192, 25, 1752], [366, 485, 354], [134, 443, 147, 464, 194]]</t>
   </si>
   <si>
     <t>h512_ws16_idx8192_random_inbf16_outbf16_ID473</t>
   </si>
   <si>
-    <t>[[1898, 294, 75, 443, 80, 476, 6042, 97, 53, 496, 330, 59, 184, 441, 5095, 123, 57, 126, 202, 217, 5905, 5291, 3916, 321, 75, 134, 303, 331, 422, 405], [195, 46, 5234, 482, 173, 959, 275, 268, 245, 150, 437, 322, 3077, 32, 284, 498, 7268, 62, 372], [27, 268, 177, 442, 6372, 216, 445, 6394, 276, 443], [465, 349, 1050, 425, 127, 157, 296, 6243, 17, 56, 72, 3837, 156, 145, 2558, 25, 389, 153, 3597, 492, 430, 273, 2, 396, 4159, 428], [5005, 215, 177, 501, 224, 4610, 476], [112, 2152, 25, 5087, 371, 143, 147, 149, 47, 456, 433, 176, 365, 374, 2617, 177, 82, 4640, 452, 106, 3039, 17, 157], [166, 2969, 3954, 5, 190, 494], [102, 212, 167, 439, 6128, 102, 250, 942, 328, 3, 5814, 218, 109, 7956, 466, 297, 99, 320], [114, 3672, 462, 6252, 283, 4374, 18, 226, 254, 2257, 74, 218, 165, 184, 392, 264, 5461, 764, 143, 79, 272, 347, 404, 400, 479, 48, 250], [24, 371, 6384, 37, 138, 386, 501, 2091, 6602, 78, 420, 3268, 365, 300, 269, 305, 74, 96, 457, 300, 390, 386, 321, 5145, 77, 437, 189, 8036, 196, 1174, 249], [245, 136, 223, 307, 1667, 2248, 330, 238, 4009, 201, 277, 306, 342, 481, 136, 67, 34, 55, 86, 3383], [4515, 269, 427, 3511, 112, 4775, 2712, 306, 305, 368, 73, 14, 318, 131, 6350, 244, 257, 333, 170, 115, 256, 186], [234, 54, 197, 4358, 43, 346, 1566, 2488, 84, 339, 164, 104, 510, 36, 26, 2809, 26, 178, 487, 220, 486, 153, 358, 3826], [504, 4073, 431, 432], [1717, 2651, 314, 436, 33, 296, 505, 369, 255, 2021, 273, 386, 25, 415, 28, 7622, 231, 234, 395, 1109, 249], [111, 334, 296, 1523, 25, 5328, 217, 507]]</t>
+    <t>[[89, 1594, 285, 171, 62, 673], [104, 1732, 17, 363, 305, 350, 359, 285, 415], [246, 344, 452, 176, 1972, 347, 104, 198, 985, 298], [65, 214, 238, 353, 319, 554, 369, 659, 512], [118, 353, 384, 2036, 345, 365, 243, 242, 70, 745], [117, 1308, 476, 275, 354, 11], [40, 1088, 350, 235, 56, 249, 396, 1049, 26, 431], [283, 477, 1262, 76, 393, 421, 246, 217], [1605, 396, 206, 168, 241], [240, 308, 1616, 287, 129], [561, 313, 267, 1937, 74, 402, 487], [624, 495], [125, 342, 428, 82, 168, 223, 248, 386, 359], [263, 80, 48], [22, 429, 358, 485], [311, 388, 349]]</t>
   </si>
   <si>
     <t>h128_ws16_idx65536_random_infp32_outfp32_ID474</t>
   </si>
   <si>
-    <t>[[73, 52, 432, 49363, 37, 59126, 91, 419, 113, 451], [329, 9, 358, 409, 42135, 191, 23718, 54206, 509, 406, 18], [53360, 49102, 487, 320, 50, 361, 183, 221, 485, 0, 40413, 167, 54, 187, 464, 183, 276, 76, 276, 497, 428, 7, 320, 157, 30215, 47317, 4982, 238, 499, 394], [214, 279, 143, 267, 358, 305, 193, 294, 296, 498, 216, 40955, 491, 372, 45942, 17806, 468, 70, 294, 24, 184, 240, 60675, 28749], [35398, 283, 92, 14202, 254, 28215, 71, 171, 301, 371, 457, 148, 337, 155, 161], [354, 26289, 132, 295, 341, 23265], [57639, 355, 452, 8501, 34889, 122, 446, 214, 172, 173, 335, 94, 102, 51], [428, 139, 176, 296, 277, 63, 17552, 64, 358, 13, 483, 145, 11210, 20, 273, 51, 473, 14298, 255, 60147], [54088, 323, 202, 390, 90, 59008, 474], [17749, 20, 64350, 424, 114, 125, 339, 111, 26461, 38549, 322, 19, 222, 62247, 83, 497, 405, 419, 49, 47992, 167, 71, 212, 16, 468, 401], [334, 53, 483, 135, 330, 87, 12560, 1551, 45, 207, 37, 192, 15836], [241, 176, 221, 259, 203, 19, 434, 342, 101, 177, 7617, 6, 59464, 6076, 334, 235, 229, 69, 454, 231, 485, 28921, 49463, 487, 147, 46, 37812], [0, 132, 61550, 315, 114, 87, 24722, 35, 306, 24034, 42, 74, 18892, 121, 287, 171, 486, 2, 252, 44, 11, 64, 32639, 398, 480], [42476, 283, 41, 33, 49979, 99, 81, 427, 348, 132, 225, 106, 42100, 205, 42278, 377, 123], [7399], [220, 392, 65471, 466, 105, 197, 297, 42592, 55391, 480, 40, 344]]</t>
+    <t>[[1330, 193, 306, 242, 341, 221, 411], [325, 69], [24, 329], [201, 28, 369], [229, 507, 326, 433, 1190], [502, 123, 28, 218, 333], [108, 211, 1183, 1775], [299, 579], [339, 1264, 287, 344], [1046, 172, 90, 456], [858, 20, 150, 8, 493, 451, 143, 504, 338], [1609, 140], [444, 377, 38], [1372, 323, 7, 168, 132, 160, 427, 499, 169, 421], [1107, 493, 78, 499, 449, 4, 187], [400, 38, 402, 61, 144, 229, 337]]</t>
   </si>
   <si>
     <t>h64_ws16_idx65536_random_infp16_outfp16_ID475</t>
   </si>
   <si>
-    <t>[[59875, 293, 348, 12961, 21, 128, 251, 276, 63110, 256, 216, 188, 188, 388, 401, 246, 19389, 251, 424, 161, 410, 498, 22132, 315, 62789, 495, 494, 281, 502, 228, 16396], [131, 308, 50504], [4860, 198, 120, 387, 408, 119, 93, 49, 397, 50596, 304, 197, 65, 18408, 282, 241, 40336, 129, 70], [10, 302, 331, 61495, 33, 29173, 81, 233, 169, 378, 325, 17264, 122, 309, 475, 231, 334, 383, 166, 192, 502, 6958, 472, 75, 53912], [9, 299, 55, 27472, 234, 59428, 376, 153, 136, 454, 57241, 276, 355, 127], [11, 27030, 175, 223, 511], [318, 25768, 49, 309, 281, 167, 55, 46725, 405, 53419, 255, 471, 508, 17711, 348, 218], [430, 90, 12525, 97, 145, 368, 100, 336, 102, 507, 33289, 94, 330, 39, 342, 22296, 105, 60155, 393, 122, 143, 220, 313, 44, 40, 423, 16597, 7, 42835, 364, 65326, 78], [62054, 5251, 128, 253, 508, 391, 103, 54100, 279, 56, 271, 415, 28], [367, 91, 262, 9833, 25626, 239, 274, 45744, 455, 80, 430, 128, 22, 269, 331, 22216, 420, 315], [137, 46120, 416, 470, 393, 475, 504, 208, 224, 128, 43830, 37543], [297, 43084, 154, 9186, 254, 501, 161, 477, 81, 259, 61883, 217, 226, 2730, 29986, 258, 463, 130, 387, 100, 177, 113, 59], [360, 146, 2, 59, 9159, 276, 2966, 306, 170, 501, 291, 50001, 358, 411, 23], [257, 458, 222, 253, 32153, 38511, 321, 285, 390, 353, 165, 166, 40287, 8796, 446, 108, 490, 439, 99, 141, 505, 30105, 228, 491, 270, 158, 62249], [335, 111, 433, 11911, 439, 221, 24361, 206, 62886, 417, 373, 101, 177, 452, 59, 43948, 157], [58933, 463, 33368, 502, 485, 405]]</t>
+    <t>[[344], [498], [141, 2035, 503, 491, 677], [424, 455, 371], [418, 491, 380, 336, 118, 1204, 1184, 958], [160, 176, 258, 263, 1213, 156], [175, 1796, 439], [879, 247, 304, 410, 506, 345, 491, 92], [463, 111, 373, 153, 292, 9, 1951, 210, 398, 342], [29, 505, 270, 403, 455], [53, 888, 1, 881, 16, 165, 236, 46, 97], [400, 87, 29], [1875, 95, 270, 127, 146, 373, 512, 191, 385], [190, 262, 494, 744, 312, 320], [89], [129, 506, 497, 226]]</t>
   </si>
   <si>
     <t>h256_ws2_idx8192_random_infp32_outfp32_ID476</t>
   </si>
   <si>
-    <t>[[393, 153, 50, 7808, 470, 492, 499, 14, 6661, 503, 39, 5924, 447], [237, 4782, 2, 334, 466, 435, 7126, 19, 490, 6944, 448, 166, 380, 367, 376, 420, 1, 3288, 34, 207, 115, 393, 7431, 130, 445]]</t>
+    <t>[[371, 302, 213, 156], [1575, 125, 413]]</t>
   </si>
   <si>
     <t>h512_ws16_idx8192_random_inbf16_outbf16_ID477</t>
   </si>
   <si>
-    <t>[[2841, 990, 398, 63, 212, 451, 170, 1386, 145, 198, 10, 476], [497, 501, 3702, 226, 345, 1453, 340, 4655, 335, 439, 4416, 457, 199, 16, 190, 5951, 23, 306, 92, 7661, 279, 2, 295, 267, 116, 394, 434], [441, 1988, 231, 310, 258, 693], [6808, 89, 455, 161, 424, 208, 120, 3849], [218, 121, 335, 336, 3088, 2511, 37], [94, 65, 1608, 78, 60], [325, 89, 19, 126, 6447, 412, 7748, 6374, 416, 49, 259, 328, 136, 356, 6902, 111, 510, 89, 318, 218, 438, 333, 3987, 172, 102], [164, 369, 242, 3993, 95, 49, 98, 7, 477, 348, 3352, 4895, 74, 2, 3494, 265, 17, 398, 453, 466, 226, 342, 3472], [6, 323, 176, 6980, 470, 128, 1187, 77, 125], [44, 480, 893, 228, 455, 94, 378, 7, 108, 462, 19, 76, 61, 316, 7496, 327, 1670, 1, 746], [7977, 5534, 142, 366, 413, 224, 344, 250, 247, 7030, 492], [66, 318, 2311, 4091, 3809, 380, 425, 263, 27, 276, 86, 382, 298, 8172, 126, 128, 448, 1086, 7958, 81, 350, 390, 221, 195, 260, 223, 72, 36, 396], [5403, 6851, 141, 4442, 306, 481, 45, 287, 139, 85, 364, 217, 210], [26, 8023, 465, 283, 60, 309, 187, 215, 3454, 368, 176, 1461, 292, 38, 7, 490, 4029, 342], [393, 4235, 431, 142, 7428, 56, 450, 192, 2283, 221, 89, 125, 3727, 100, 391, 542, 78, 197, 53, 179, 24], [2523, 4606, 261, 244, 372, 68, 512, 294, 510, 2795, 448, 456, 10, 168, 449]]</t>
+    <t>[[452, 2027, 1957, 43], [157, 443, 83], [79, 318], [93, 29], [232, 2], [395, 272, 500, 392, 218, 221, 271], [465, 406, 165, 330, 417, 1987, 314, 38, 354], [1271, 360, 211, 833, 61], [351, 149, 47, 127, 420, 134, 277], [484], [674, 283, 102, 489], [1790, 1318, 446, 202, 164, 447], [38], [459, 91, 150, 248, 430, 247, 5], [464, 47, 242, 1337, 157, 516, 867], [456, 125, 242, 140, 485, 153, 142]]</t>
   </si>
   <si>
     <t>h64_ws4_idx16384_random_infp16_outfp16_ID478</t>
   </si>
   <si>
-    <t>[[148, 358, 3801, 1778, 364, 160, 312, 11504, 366, 16110, 462, 88, 467, 13489, 395, 505, 256, 162, 18, 133, 415, 249, 196, 304], [402, 145, 18, 45, 11656, 14, 431, 443, 208, 10391, 10119, 389, 349, 242, 368, 13404], [7791, 438, 1847, 13556, 423, 279, 8236, 322, 414, 12348, 275, 220, 391, 173, 13551, 206, 159, 83, 45, 86, 45, 415, 351, 303, 396, 7, 38, 253], [327, 2199, 343, 410]]</t>
+    <t>[[365, 392, 799, 1730], [478, 331, 73, 1811, 272, 386, 321, 466, 274], [456, 201, 484, 247, 71, 496], [190, 508, 64, 32, 172, 424, 262]]</t>
   </si>
   <si>
     <t>h128_ws8_idx32768_random_infp16_outfp16_ID479</t>
   </si>
   <si>
-    <t>[[148, 155, 135, 11623, 13681, 2, 2862, 482, 148, 245, 123, 174], [399, 456, 301, 98, 237, 5, 134, 143, 436, 16441, 233, 354, 357, 501, 1997, 458, 57, 282, 25160, 417, 24982, 381, 16841, 464, 94, 114, 335, 325, 1021, 388], [345, 493, 5184, 200, 228, 281, 15142, 312], [58, 412, 283, 23241, 490, 22486], [373, 391, 4592, 19442, 182, 235, 308, 255, 455, 4914, 337, 509, 325, 8881, 430, 286, 121, 118, 97, 411, 32, 28860, 214, 415], [21179], [453, 370, 28920, 151, 392, 199, 10460, 311, 142, 262], [19847, 28980, 17, 423, 144, 299, 456, 368, 394, 489, 284, 279, 9507]]</t>
+    <t>[[135, 22, 440, 118, 392, 486, 312], [73, 296, 506, 66, 336, 2, 385, 126], [293, 374, 120, 395, 40, 446, 317, 20, 53, 378], [1733, 117], [298, 157, 443, 285, 322, 409, 303, 290, 99, 163], [474, 342], [492], [29, 126, 265, 1561, 306, 144, 272]]</t>
   </si>
   <si>
     <t>h64_ws2_idx4096_random_infp16_outfp16_ID480</t>
   </si>
   <si>
-    <t>[[415, 3759, 128], [91, 490, 288, 52, 992, 361, 1716, 3415, 9, 748, 338, 89, 506, 83, 483, 427, 192, 109, 156, 136]]</t>
+    <t>[[327, 918], [1345]]</t>
   </si>
   <si>
     <t>h256_ws4_idx8192_random_infp16_outfp16_ID481</t>
   </si>
   <si>
-    <t>[[391, 5612], [497, 386, 110, 363, 300, 266, 4941, 49, 3595, 6003, 456, 148, 180, 3261, 266, 275, 379, 247, 141, 1554, 373, 7108, 5, 229, 942, 462, 440, 5, 258, 321, 225, 236], [510, 7686, 504, 74, 80, 74, 125, 314, 2559, 42, 6719, 15], [370, 489, 2870, 110, 112, 164, 5686, 158, 79, 77, 466, 504, 200, 337, 6448]]</t>
+    <t>[[42, 62], [169, 139, 98, 295, 432], [506, 297, 413, 464, 377, 447, 17, 318, 214, 349], [488, 475, 422, 334, 201, 592, 416, 96]]</t>
   </si>
   <si>
     <t>h256_ws4_idx2048_random_infp32_outfp32_ID482</t>
   </si>
   <si>
-    <t>[[152, 1144, 382, 289, 436, 501, 232, 457, 235, 93, 318, 173, 1305, 1598, 360, 248, 182, 13, 1689, 259, 10, 253, 120, 387, 236, 1242, 151, 1109], [80, 25, 241, 612, 373, 1746, 182, 1435, 342, 221, 362, 439, 502], [181, 421, 81, 1982, 8, 296, 479, 321, 1787, 452], [113, 427, 487, 66, 145, 495, 120, 269, 587, 1251, 366, 105, 348, 29, 304, 422, 963, 462, 743, 89, 224, 1381, 1176, 104, 256, 314, 1523, 358, 246, 335, 114, 480]]</t>
+    <t>[[71, 1225, 163, 368], [110, 850, 956, 341, 406, 1454, 378, 492], [567, 274, 46, 117, 1616, 279, 430, 434], [151, 55]]</t>
   </si>
   <si>
     <t>h64_ws2_idx4096_random_infp32_outfp32_ID483</t>
   </si>
   <si>
-    <t>[[283, 1193, 157, 451], [2175, 456, 411, 1322, 335, 467, 502, 278, 72, 853, 103, 244, 2673, 251, 508, 71, 502, 172, 1518, 2245, 157, 426, 12, 454, 431, 251, 303, 118, 880, 199, 302, 299]]</t>
+    <t>[[473, 468, 135, 322, 1025, 407, 397, 208, 387], [180, 209, 1275]]</t>
   </si>
   <si>
     <t>h64_ws16_idx16384_random_inbf16_outbf16_ID484</t>
   </si>
   <si>
-    <t>[[267, 248, 387, 41, 379, 488, 7789, 488, 262, 150, 227, 134, 395, 52, 395, 12531, 4262, 91, 15526, 13485, 329, 480, 466, 8022, 419, 302, 380, 68, 191, 478], [99, 13027, 277, 10, 9865, 502, 383, 99, 1459, 312, 358, 28, 238, 10183, 311, 424, 190, 4, 113], [232, 206, 8660, 408, 17, 150, 486, 339, 15996, 165, 315, 219, 5427, 438, 36], [512, 33, 202, 415, 7624, 91, 457, 2, 1794, 111, 10726, 494, 323, 441], [407, 4672, 481, 241, 500, 405, 67, 267, 91, 5312, 36, 8039, 441, 108, 119, 5402, 273, 15961, 270, 16, 35, 301, 217, 469, 234, 6842], [242, 414, 6, 3975, 232, 6458, 269, 327, 481, 13762, 181, 254, 156, 12, 3610, 282, 411, 27, 329, 10625, 503], [4234, 397, 33, 379, 15012, 356, 338, 111, 15345, 11, 16, 55, 345, 450, 1546, 138, 326, 380], [490, 4020, 348, 90, 367, 15655, 308, 440, 379, 429, 479, 557, 385, 413, 423, 489, 70, 420, 2910, 48, 12699, 408, 460], [256, 126, 354, 187, 367, 470, 304, 16251, 148, 195, 8749, 16011], [53, 254, 402, 7809, 2579, 152, 128, 142, 6232, 108, 60, 2799, 13721, 345, 96, 2888, 483, 30, 196, 476, 489, 292, 179, 172, 204, 39, 43], [217, 1017, 156, 122, 183, 57, 209, 8512, 171], [224, 163, 9212, 94, 424, 48, 269, 3523, 355, 9251, 29, 1316, 258, 19, 435, 442, 15389, 102, 198, 443, 145, 459, 50, 498, 141], [4468, 5847, 503, 63, 498, 14370, 250, 358, 359, 345, 8, 318, 5320, 141, 48, 134, 12483, 369, 3717, 442, 72, 88, 369, 320, 67, 456, 312, 84, 105], [162, 4756, 40, 265, 251, 119, 362, 448, 447, 7, 10464, 442, 9589], [212, 389, 114, 637, 297, 3044, 11407, 49, 55, 82, 484], [395, 175, 64, 286, 5824, 10545, 173, 295, 285, 434]]</t>
+    <t>[[212, 1855, 498, 291], [1630, 9, 80, 343, 492], [461, 256, 400, 430, 1951, 234, 39, 150, 271], [270, 87, 54, 166, 491, 42, 1231], [434, 218, 170, 107, 263, 34, 862, 557], [374, 447, 1414, 125, 168, 189, 356, 101, 219], [74, 4, 191], [487, 92, 419, 377, 1385, 194], [259, 514, 218, 296, 25, 263, 87], [184, 157, 405, 934, 497, 335, 1593], [1650, 115, 317, 248, 215, 412, 402, 1350, 204], [374, 196, 6, 172, 124, 596, 39, 252], [363, 74, 358, 202, 463, 333, 444, 103, 410, 180], [1955, 195, 141, 324], [362, 232, 242, 465, 86, 426], [387, 430, 134, 507, 64, 413, 155, 211]]</t>
   </si>
   <si>
     <t>h64_ws4_idx4096_random_inbf16_outbf16_ID485</t>
   </si>
   <si>
-    <t>[[510, 1493, 424, 27], [451, 326, 3876, 1599, 221, 156, 963, 158, 194, 485, 179, 463, 468, 280, 457, 393, 376, 88, 1684, 258, 2232], [310, 293, 230, 1529, 278, 72, 422, 152, 1, 184, 217, 491, 3965, 399, 696, 305, 160, 1142, 28, 238, 2482, 53, 423], [2459, 402, 386, 472, 744, 224, 163, 8, 46, 3798, 505]]</t>
+    <t>[[144], [204, 93, 471, 407, 233, 496, 396], [453, 395, 175, 92, 369, 26, 492, 104, 72, 287], [20, 153, 115]]</t>
   </si>
   <si>
     <t>h512_ws2_idx8192_random_inbf16_outbf16_ID486</t>
   </si>
   <si>
-    <t>[[3, 395, 4185, 334, 195, 10, 3075, 1891, 205, 34, 7357, 81, 498, 293, 210, 61, 445, 464], [192, 483, 6490, 180, 432, 47, 56, 321, 338, 111, 303, 0, 395, 410, 6748, 14, 207, 2151, 1491, 421, 506, 336, 4086, 143, 2724, 398, 7838, 346, 142, 144, 461, 388]]</t>
+    <t>[[885, 141, 166, 41, 179, 446, 25, 294, 61, 1455], [474, 21]]</t>
   </si>
   <si>
     <t>h64_ws4_idx4096_random_infp32_outfp32_ID487</t>
   </si>
   <si>
-    <t>[[3335, 293, 1597, 699, 508, 2352, 2391, 408, 112, 269, 341, 85, 342, 470, 163, 474, 228, 274, 188, 55, 10, 223, 1872, 63, 287, 128, 72, 128, 444, 97, 1519], [7, 259, 3612, 290, 141, 160, 2422, 255, 426, 2848, 175, 27, 102, 121, 173, 171, 485, 451, 3767, 291], [360, 207, 480, 452, 361, 2770, 672, 460, 2239, 485, 328, 110], [233, 372, 156, 3090, 390, 139, 350, 376, 17, 272, 2960, 231, 414, 108, 151, 1018, 1173, 385, 314, 1052, 371, 226, 64, 341, 418, 399, 961, 306, 33]]</t>
+    <t>[[177, 457, 172, 325, 103], [370, 38, 1362, 224, 701, 237, 352], [200, 222, 501, 166, 450], [345, 461, 1636, 158, 37]]</t>
   </si>
   <si>
     <t>h256_ws4_idx4096_random_inbf16_outbf16_ID488</t>
   </si>
   <si>
-    <t>[[400, 381, 3715, 505, 152, 482, 510, 2364, 98, 38, 581, 399, 456, 322, 2429, 2202, 155, 118, 178, 28, 34, 41, 220, 184, 3114, 474, 6, 25], [120, 3672, 335, 3836, 291, 162, 2264, 285, 847, 460, 392, 471, 292, 345, 479, 69, 334, 386, 109, 503, 450, 80, 108, 146, 149, 183, 207, 1681, 310, 1191], [92, 3585, 148, 49, 497], [970, 1866, 437, 393, 137, 147, 71, 88, 488, 350, 296, 75, 384, 2218, 509, 2506, 630, 295, 38, 471, 476, 98, 145, 166, 3216, 509]]</t>
+    <t>[[1276, 235, 353, 270, 271, 303], [2, 288, 43], [297, 348, 493, 245, 375], [140, 350, 130, 223, 274, 93, 95, 447, 464]]</t>
   </si>
   <si>
     <t>h128_ws2_idx2048_random_inbf16_outbf16_ID489</t>
   </si>
   <si>
-    <t>[[45, 60, 894, 1326, 78, 193, 505, 135, 371, 44, 467, 959, 1210, 1210, 471, 407, 387, 607, 342, 54, 55, 341, 54, 300, 71, 76, 105, 286, 409], [286, 154, 504, 687, 408, 363, 254, 25, 1158, 155, 340, 400, 1054, 554, 593, 231, 496, 425, 36, 474, 352, 89, 197, 1958, 262, 293, 262, 433]]</t>
+    <t>[[2006, 207, 362], [377, 366, 177, 206, 503, 512]]</t>
   </si>
   <si>
     <t>h128_ws16_idx8192_random_infp32_outfp32_ID490</t>
   </si>
   <si>
-    <t>[[235, 254, 3457, 10, 136, 167, 406, 4708, 346, 150, 7654, 28, 242], [39, 24, 276, 9, 5, 121, 7512, 210, 4743, 401, 231, 234, 3053, 418, 5014, 363, 462, 402], [61, 3796, 95, 312, 164, 250, 208, 284, 105, 174, 1283, 2831, 181, 453], [121, 7999, 6930, 1473, 450, 420, 402, 7612, 42, 257, 28, 44, 109, 453, 372, 233, 7980, 6260, 501, 493, 62, 203, 232, 398, 345, 454, 338, 55, 444, 120, 119, 3689], [345, 349, 119, 311, 416, 138, 387, 1714, 4707, 420, 493, 345, 118, 35, 323, 395, 1539, 6918, 225, 313, 5592, 255, 181], [1527, 456, 446, 449, 2, 100, 7224, 171], [7144, 154, 28, 4373, 481, 111, 314, 168, 196], [464, 83, 2494, 337, 71, 129, 8061, 2062, 396, 351, 2259, 187, 144, 410, 189, 71, 6577, 165, 469, 5250, 378, 32, 6, 282, 483, 359], [57, 171, 18, 566, 261, 204, 6102, 47, 247, 504], [838, 472, 169], [1988], [1673, 324, 7182, 192, 301, 512, 378, 484, 5955, 74, 505], [5, 431, 1103, 311], [2845, 334, 7320, 6522, 337, 256, 307, 211, 26, 455, 30, 40, 419, 330, 196, 5845, 413, 49, 305, 334], [410, 64, 369, 168, 417, 361, 462, 425, 3876, 3460, 223, 113, 7598, 125, 457, 436, 69, 2369, 280, 5866, 274], [7216, 194, 297, 351, 180]]</t>
+    <t>[[42, 432, 63, 301, 251], [128, 303, 51], [357, 257, 1397, 227, 326, 254, 308, 267, 436, 694], [17, 314, 155, 128, 320, 15, 140, 164, 247], [109, 228, 111, 347, 467, 143, 126, 159, 1227, 832], [380, 318, 254, 460], [408, 26], [2038, 156, 939, 498], [290, 382, 186, 338, 50, 1728, 250, 736, 403], [389, 1815, 423, 98, 480, 1823, 334], [416, 281, 240, 498, 365, 204, 363], [221, 84, 430, 192, 439, 4], [10, 231, 365], [87, 414, 243, 285, 89], [333, 1226], [358, 55, 385, 331, 484, 285]]</t>
   </si>
   <si>
     <t>h256_ws2_idx8192_random_inbf16_outbf16_ID491</t>
   </si>
   <si>
-    <t>[[479, 1415, 235, 413, 352, 236, 242, 321, 4493, 7236, 27, 328, 259, 36, 168, 305, 6640, 66], [398, 44, 210, 493, 0, 41, 48, 417, 291, 1551, 358, 342, 375, 87, 153, 304, 6555, 115, 220, 384, 1160, 4952, 8167, 5340, 80, 52, 67, 44, 91, 5095, 192, 178]]</t>
+    <t>[[146, 47, 1321], [415, 39, 131, 70, 1609, 718, 417, 79, 384]]</t>
   </si>
   <si>
     <t>h128_ws4_idx4096_random_infp32_outfp32_ID492</t>
   </si>
   <si>
-    <t>[[131, 2357, 142, 39, 362, 308, 303, 114, 3026, 63, 2992, 382], [2, 93, 3319, 403, 294, 381, 58, 470, 2922, 281, 1173, 1754, 82, 244, 7, 5, 47, 60, 46, 353, 3626, 108, 2362, 252, 104, 71, 330, 103, 1690, 253, 230, 286], [508, 375, 430, 480, 490, 301, 3689, 3371, 372, 166, 476, 2449, 219, 172, 271, 2976, 317, 15], [206, 1625, 392, 4006, 362, 342, 89, 76]]</t>
+    <t>[[46, 1003, 1318, 455, 465, 193, 224, 292], [1103, 362, 94, 474, 76], [215, 1440, 321, 127, 350, 306, 98, 467, 320], [228, 176, 354, 5, 362]]</t>
   </si>
   <si>
     <t>h64_ws2_idx4096_random_infp32_outfp32_ID493</t>
   </si>
   <si>
-    <t>[[443, 331, 1391, 4039, 38, 61, 280, 29, 266, 1443, 392, 403, 2705, 452, 26, 237, 239, 242, 1], [439, 331, 437, 2668, 441, 486, 502, 409, 2070, 80, 4055, 171, 77, 1936, 70, 89, 87, 187, 472, 68, 185, 197, 3503, 198, 425]]</t>
+    <t>[[345, 507, 447], [447, 199, 29, 190, 441]]</t>
   </si>
   <si>
     <t>h512_ws8_idx8192_random_inbf16_outbf16_ID494</t>
   </si>
   <si>
-    <t>[[2868], [167, 347, 447, 7572, 92, 487, 6876, 72, 146, 168, 3673, 179, 123], [296, 68, 503, 437, 2695, 160, 199, 493, 3123, 443, 8189, 132, 498, 1213, 5033, 407, 410, 168, 4919, 180, 312, 118, 504, 9, 115, 1726, 254, 245, 187, 198, 453, 478], [490, 40, 270, 22, 154, 4866, 119, 3149, 7974, 94, 276, 510, 323, 193, 300, 6796, 60, 208, 226, 406, 21, 3018], [244, 1185, 5645, 242, 3, 215, 379, 314, 7666, 222, 390, 2573, 308, 6269, 393, 393, 5591, 98, 234, 490, 6879, 237, 256, 482, 286, 169, 0, 461, 346, 484, 227], [1380, 333, 81, 478, 155, 298, 4139, 346, 443, 207, 374, 430, 284, 145, 482, 174, 358, 1793, 8094, 83, 137, 1478, 53, 431, 7608, 54, 440, 462], [42, 2454, 284, 270, 296, 203, 201, 202, 3822, 162, 213, 437, 474, 7401, 431], [247, 468, 4639, 383, 3593, 439, 102, 272, 508]]</t>
+    <t>[[92, 203, 64], [1221, 91, 299, 133, 412, 456], [304], [165, 482, 438, 358, 489, 300, 124, 401, 449], [260, 357, 454], [1286, 153, 122, 1, 463, 395, 66], [646, 509, 140], [495, 198, 440]]</t>
   </si>
   <si>
     <t>h64_ws2_idx2048_random_infp32_outfp32_ID495</t>
   </si>
   <si>
-    <t>[[156, 690, 872, 51, 350, 269, 1074, 168, 336, 141, 496, 142, 302, 1067, 334, 1314, 385, 367, 352, 330, 192, 236, 283, 1088, 282, 491, 263, 264, 39], [1227, 51]]</t>
+    <t>[[108, 157], [1739, 907, 2, 470, 238, 210, 137, 120, 105, 120]]</t>
   </si>
   <si>
     <t>h256_ws8_idx32768_random_infp32_outfp32_ID496</t>
   </si>
   <si>
-    <t>[[55, 328, 134, 1068, 258, 13361, 494, 484, 214], [296, 1077, 234, 281, 160, 19921], [468, 182, 137, 31596, 273, 436, 4750, 368], [204, 27997, 501, 399, 493], [400, 94, 270, 46, 269, 64, 359, 141, 10056, 384, 19868, 129, 3256], [373, 261, 287, 248, 8, 30499, 227, 430, 302, 200, 19072, 41, 4141, 414, 78, 9056, 128], [85, 461, 0, 149, 4731, 363, 19333, 27868, 83, 30, 24, 343, 31021, 298, 128, 312, 19467, 420, 367, 282, 286, 105, 321], [164, 68, 184, 51, 309, 26580, 16312]]</t>
+    <t>[[316, 50], [19, 6, 637, 410, 503, 289, 63, 495, 227, 106], [154, 371], [489, 151, 1816, 243, 508], [401, 34, 357], [229, 82, 258, 364], [474, 298, 608, 363, 1949], [199, 127, 237]]</t>
   </si>
   <si>
     <t>h512_ws4_idx4096_random_inbf16_outbf16_ID497</t>
   </si>
   <si>
-    <t>[[356, 2085, 483, 74, 482, 222, 107, 266, 3239, 459], [713, 476, 29, 342, 120, 1492, 2613, 87, 1304, 436, 181, 282, 237, 49, 89, 135, 968, 82, 430, 3291, 393, 1551, 98, 454, 214, 276, 229, 125, 293, 244, 179, 292], [771, 460, 961, 203, 226, 509, 482, 362, 199, 12, 432, 20, 3024, 117, 150, 166, 825, 332, 864, 132, 440, 2402, 297, 239, 218, 274, 164], [465, 510, 2337, 3066, 59, 485, 290, 465, 439, 40, 203, 1171, 33, 241, 990, 487, 171, 227, 350, 1811, 13]]</t>
+    <t>[[485, 2032, 53, 18, 1984, 371, 497, 412], [162, 120, 299, 31], [287, 220, 250, 68, 595, 403, 298, 624, 497], [295, 1047, 275, 178, 297, 403, 381]]</t>
   </si>
   <si>
     <t>h512_ws8_idx4096_random_infp32_outfp32_ID498</t>
   </si>
   <si>
-    <t>[[266, 3930, 231, 510, 312, 838, 432, 289], [133, 3617, 3239, 194, 265, 126, 95, 4087, 252, 168, 315, 304, 6, 474, 57, 1555, 449, 4070, 496, 471, 343, 127, 418, 28, 3442, 453, 344, 229, 471, 2712, 162], [235, 200, 511, 1760, 242, 367, 375, 2751, 360, 3456, 130, 123], [2849, 212, 411, 3411, 3054, 223, 144, 478, 73, 113, 3909, 493, 126, 2369, 332, 346, 69, 469, 410, 442, 201], [160, 132, 1615, 97, 96, 489, 304, 69, 1576, 105, 165, 436, 114, 314, 202, 166, 3295, 3279, 243, 56, 52, 4000, 24], [1513, 308, 511, 428, 695, 8, 112, 98, 406, 452, 167, 377, 126, 2473, 2322, 385, 268, 497, 89, 1], [2446, 389, 108, 360], [402, 39, 481, 76, 97, 1404, 63, 126, 260, 439, 340, 483, 47, 327, 3193, 159, 3906, 3399, 316, 341, 437, 412, 290, 365, 234, 1566, 430, 29, 2337, 498]]</t>
+    <t>[[378, 700, 86], [171, 71, 383], [363, 275, 47, 286, 321, 205, 819], [490, 2032, 29, 157, 236, 451], [494, 116, 365, 56, 85, 10, 48], [201, 399, 621, 451, 97, 263, 6, 479], [43, 503, 457, 199, 183, 83, 147, 191, 354, 161], [409, 211]]</t>
   </si>
   <si>
     <t>h64_ws2_idx1024_random_infp16_outfp16_ID499</t>
   </si>
   <si>
-    <t>[[103, 855, 128, 814, 360, 411, 712, 456, 328, 377, 5, 576, 183, 510, 564, 157, 469, 979, 61, 229, 411, 201, 359, 434, 89, 36], [655, 10, 471, 603, 334, 207]]</t>
+    <t>[[2010, 680, 501, 111, 454], [1298, 392, 769, 303, 409, 54]]</t>
   </si>
   <si>
     <t>h64_ws2_idx8192_random_infp32_outfp32_ID500</t>
   </si>
   <si>
-    <t>[[284, 393, 103, 430, 5094, 4411, 460, 312, 7562, 4205, 354, 14, 261, 401, 271, 436, 303, 507, 450, 284, 502, 47, 143, 1761, 477, 482, 409, 4161, 352, 284], [1998]]</t>
+    <t>[[509], [63, 210, 323, 24, 91, 361]]</t>
   </si>
   <si>
     <t>h128_ws4_idx4096_random_inbf16_outbf16_ID501</t>
   </si>
   <si>
-    <t>[[183, 152, 144, 53, 331, 15, 22, 2441, 362, 1582, 3313, 85, 143, 266, 199, 187, 642, 174, 153, 459], [2594], [3264, 295, 288, 154, 174, 209, 372, 49, 131, 2214, 121, 455, 319, 1675, 36, 85, 2652, 344, 161, 7, 488, 483, 110, 465, 1531, 418, 309, 271, 3790, 258, 778], [80, 333, 431, 158, 657, 3350, 503, 132, 2343, 485, 413, 185, 336]]</t>
+    <t>[[24, 120, 197], [353, 411, 499, 376], [377, 294, 1785, 504, 512, 29, 27], [355, 97, 48, 1954, 963, 356]]</t>
   </si>
   <si>
     <t>h128_ws2_idx1024_random_inbf16_outbf16_ID502</t>
   </si>
   <si>
-    <t>[[295, 1005, 621, 145, 480, 218, 97, 127, 500, 1010, 448, 51, 59, 201], [427, 218, 717, 414, 177, 464, 227, 198, 270, 113, 77, 834, 664, 316, 398, 137, 93, 344, 239, 738]]</t>
+    <t>[[93, 264, 72], [263, 1093, 654, 151, 180, 369, 56, 311]]</t>
   </si>
   <si>
     <t>h128_ws4_idx4096_random_infp32_outfp32_ID503</t>
   </si>
   <si>
-    <t>[[75, 281, 2588, 304, 438, 1820, 132, 482, 2856, 118, 21, 209, 305, 284, 184, 212, 272, 259, 3635, 106, 2570, 488, 178, 253, 172], [257, 737, 512, 244], [317, 489, 423, 154, 2248, 361, 2929, 388, 503, 292, 121, 20, 2462, 2818, 1434, 13, 301, 146, 403, 31, 36], [17, 216, 244, 298, 432, 754, 1686, 1043, 342, 146, 104, 64, 1429, 65, 355, 314, 163]]</t>
+    <t>[[401, 209, 2, 347, 586, 91], [1504, 294], [502], [40, 661, 108, 298]]</t>
   </si>
   <si>
     <t>h512_ws2_idx8192_random_inbf16_outbf16_ID504</t>
   </si>
   <si>
-    <t>[[2092, 277, 400, 396, 116, 103, 193, 239, 879], [25, 258, 169, 7836, 382, 254, 261, 453, 336, 7892]]</t>
+    <t>[[736, 189], [689, 113, 19, 3, 357, 447, 2, 70, 1416]]</t>
   </si>
   <si>
     <t>h256_ws2_idx1024_random_inbf16_outbf16_ID505</t>
   </si>
   <si>
-    <t>[[949, 101, 204, 69, 494], [29, 806, 105, 683, 240, 141, 221]]</t>
+    <t>[[35, 571, 178, 240, 1535], [1731, 376]]</t>
   </si>
   <si>
     <t>h64_ws4_idx2048_random_inbf16_outbf16_ID506</t>
   </si>
   <si>
-    <t>[[241, 1205, 158, 371, 99, 227, 335, 1725, 349, 290, 339, 942, 297, 14, 73, 112, 1776, 189, 111], [275, 16, 350, 58, 1383, 600, 161, 187, 1748, 100, 12], [326, 357, 20, 11, 1737, 473, 265, 138, 251, 823, 437, 61, 195, 66, 243, 247, 944, 256, 382, 206, 193, 467, 1505, 885], [18, 1083, 60]]</t>
+    <t>[[441, 179, 499, 3, 960, 240, 345, 482], [83], [330], [358, 42, 405, 156, 272, 155, 239, 341, 177, 110]]</t>
   </si>
   <si>
     <t>h128_ws8_idx32768_random_infp16_outfp16_ID507</t>
   </si>
   <si>
-    <t>[[58, 316, 456, 190, 303, 2, 358, 485, 12, 228, 177, 84, 11653, 12, 502, 247, 13617, 311, 248, 1100, 187, 57, 23402, 7603, 452, 228, 159, 121, 23555], [12626, 394, 125, 95], [24881, 109, 502, 264, 180, 33, 53, 30328, 171, 355, 347, 8163, 506, 349, 402, 30, 232, 167, 387, 10933, 135, 7225, 296, 212, 449, 122, 422, 322, 8895, 414, 264, 7644], [45, 476, 109, 200, 109, 359, 74, 79, 6423, 181, 102, 296, 308, 17347, 9837], [124, 227, 150, 10277, 297, 9186, 443, 99, 60, 106, 282, 8672], [31436, 18, 24, 414, 353, 308, 172, 159, 22342], [13209, 23968, 344, 1885, 182, 53, 47, 437, 350, 155, 113], [13940, 433, 111, 70, 490, 166, 272, 11084, 310, 58, 259, 25950, 471, 29753, 11, 379, 27, 335, 338, 458, 400, 14171]]</t>
+    <t>[[350, 506, 369, 260, 348, 185, 510, 482, 714, 439], [434, 167, 206, 345, 97, 449, 1988], [359, 67, 440, 403], [1374, 1881, 228, 209], [807], [464, 339, 371, 438, 687, 222], [85, 431, 376, 325, 467, 488, 1634], [312, 219, 145, 208, 17]]</t>
   </si>
   <si>
     <t>h128_ws8_idx32768_random_inbf16_outbf16_ID508</t>
   </si>
   <si>
-    <t>[[11333, 201, 315, 191, 11005, 95, 130, 23733, 90, 265, 402, 31565, 313, 350, 261, 4, 410, 205, 28326, 32279, 77, 38, 274, 337, 253, 466, 371, 940, 226, 445, 69], [481, 461, 103, 143, 84, 26065, 7536, 150, 365, 50, 298, 184, 69, 19443], [284, 27494, 29, 233], [6393, 51, 281, 468, 181, 10864, 394, 193, 14032, 251, 33, 487, 506, 45, 185, 5879, 391, 466, 353, 114, 235, 20, 168, 11125, 432], [25544, 6, 484], [436, 452, 341, 42, 24443, 25161, 194, 104, 357, 28082, 65, 13617, 386, 317, 83, 452, 492, 87, 496], [16, 117, 402, 395, 239, 136, 322, 29072, 406, 16978, 163, 24572, 191, 0, 27416, 258, 472, 298, 465, 73, 215, 496, 370, 241, 8, 223, 26067, 30844, 172, 101, 91, 5451], [63, 344, 26425, 25, 373, 358, 441, 452, 416, 13118, 31482]]</t>
+    <t>[[8, 209, 185], [1586], [110, 323], [16, 244, 502, 157, 93, 219, 286, 551, 329, 92], [194, 282, 364, 2024, 192, 290, 464], [239, 499, 35, 226, 408, 1350], [277, 751, 475, 298, 87, 139, 206, 112], [345, 331, 398, 96, 15, 190, 466]]</t>
   </si>
   <si>
     <t>h64_ws16_idx65536_random_infp16_outfp16_ID509</t>
   </si>
   <si>
-    <t>[[441, 56, 58939, 4856, 288, 37670, 176, 283, 370, 423, 53, 139, 215], [154, 283, 48476, 16, 242, 448, 433, 487, 11446], [41193, 113, 37886, 311, 50, 197, 43816, 471, 311, 29938, 54465, 269, 363, 205, 344, 144, 21, 16, 463, 271, 374, 227, 87, 123, 296, 215, 228, 29571, 25438, 440, 1, 114], [356, 106, 253, 202, 285, 275, 9508, 256, 487, 296, 16, 390, 12, 48578, 81, 42359, 42132, 149, 43, 167], [214, 29460, 443, 36503, 40100, 41160, 229, 268, 510, 10, 59, 478, 9007, 241, 49, 284, 218, 151, 354, 480, 501, 196, 258, 499], [469, 38, 76, 4494, 64146, 39507, 428, 24, 387, 53, 106, 59, 213, 99, 222, 35632, 140, 125, 231, 53713, 322, 39, 102, 348, 255, 30778, 140, 474], [34186, 6, 422, 364, 63, 25547, 112, 294, 13, 458], [39358, 386, 356, 22415, 206, 37, 393, 78, 427, 95, 19173, 468, 94, 94, 163, 259, 3194, 335, 101, 39041, 457, 80], [195, 377, 263, 44330, 164, 297, 30, 362, 61839, 254, 384, 469, 433, 134, 265, 261, 10, 336, 42268, 392, 63116, 189, 46, 199, 499, 16140, 4891, 6, 147], [432, 185, 337, 261, 400, 22, 44134, 37222, 284, 502, 480, 191, 75, 143, 434, 55013, 198, 8401, 170], [474, 41298, 482], [46266, 17, 28, 465, 794, 204, 201, 30926, 158, 47961, 251, 54, 42, 63441, 268, 13, 158, 62870, 380, 120, 33, 486, 73, 346, 318, 109], [428, 15458, 384, 359, 149, 42, 348, 422, 69, 139, 407, 42, 67, 28, 295, 112, 46005, 505, 20365, 18826, 51026, 29033, 311, 481, 374, 189, 268], [377, 352, 16288, 101, 128, 474, 29, 43271, 441, 195, 59, 222, 66, 415, 338, 485, 64706, 489, 334, 45007, 47, 6064, 430, 486, 94, 59449, 61, 118, 224, 140], [478, 9308, 480, 286, 51243, 99, 103, 89, 359, 219, 433, 389, 294, 15102, 198, 341, 25, 52078, 315, 15699, 240, 18, 206], [110, 20075, 341, 203, 236, 373, 413, 220, 285, 22038, 47318, 189]]</t>
+    <t>[[53, 10, 1016, 98, 256, 133, 392, 459], [422, 423, 410, 253, 1421, 467, 439, 443, 1108, 197], [1768, 662, 363, 56, 360, 66], [1616, 171, 386, 301, 243, 128, 476], [1285, 332, 112], [54, 40, 497, 485, 273, 444, 391], [373, 241, 215, 40, 266, 77, 33], [438, 1159, 337, 131], [22, 382, 209, 254, 1372, 274, 120], [62, 277, 966], [33], [43, 430, 92, 33, 186, 242, 369], [256, 293, 251], [365], [356, 229, 249, 122, 292, 445, 130], [223, 386, 230, 306, 161, 36, 185]]</t>
   </si>
   <si>
     <t>h256_ws8_idx32768_random_inbf16_outbf16_ID510</t>
   </si>
   <si>
-    <t>[[212, 253, 84, 279, 26631, 29607, 319, 19, 295, 481], [473, 107, 365, 8, 29454, 206, 398, 28385, 489, 66, 126, 109, 298, 18870, 7954, 362, 4, 233], [295, 255, 23293, 177, 71, 121, 482, 372, 169, 21951, 8360, 159], [228, 321, 25420, 170, 421, 29112, 256, 32354, 412, 239, 340, 130, 506, 152, 49, 19926, 364, 83, 411, 214, 481, 510, 349, 385, 250, 283, 375, 31219, 3168, 294, 3472], [495, 177, 15, 28335, 9048, 314, 246, 45], [343, 296, 289, 172, 6611, 2220, 412, 179, 352], [396, 139, 15472, 168, 121, 183, 159, 448, 315, 231, 206, 291, 281, 388, 340, 176, 410, 5994, 217, 149, 7932, 479, 8, 134, 32509, 2188, 25602], [163, 169, 167, 92, 238, 12684, 469, 17, 386, 343, 148, 19482, 499, 1512, 25806, 308, 12443, 64, 212, 496, 242, 188, 270]]</t>
+    <t>[[1597, 208, 181, 287, 88, 508, 4, 78, 386], [145, 85, 1576, 169, 167, 299, 448, 353, 53], [83, 4, 194, 180], [294, 74, 271, 1241, 245, 6, 199, 103, 424, 402], [392, 297, 31, 266, 285, 175, 415, 447], [1696, 254, 109], [255, 370, 189, 360, 656, 314, 444], [190]]</t>
   </si>
   <si>
     <t>h64_ws16_idx32768_random_infp16_outfp16_ID511</t>
   </si>
   <si>
-    <t>[[373, 285, 479, 13586, 15, 129, 121, 133, 187, 203, 141, 22637, 491, 459, 6179, 281, 444, 15654, 68, 159, 511, 22058, 16765, 220, 465, 98, 166, 188], [408, 12775, 850, 401, 364, 377, 448, 89, 28130, 311, 423, 202, 144], [29821, 443, 211, 17, 452, 338, 152, 238, 200, 381, 12, 102, 87, 452, 84, 17034, 1986, 226, 6783], [207, 330, 189, 315, 365, 185, 241, 2032, 298, 135, 401, 41, 29711, 14357, 406, 388, 279, 363, 35, 159, 103, 23676, 360, 11848, 16], [94, 434, 5321, 427, 443, 222, 281, 10628, 29775, 241, 160], [262, 95, 9480, 21478, 207, 137, 260, 131, 277, 120, 417, 221, 503, 319, 62, 1141, 15254, 235, 20453, 294, 76, 116], [358, 120, 38, 467, 395, 326, 443, 362, 195, 476, 25702, 364, 26699, 90, 411, 18076, 22359, 270, 32039, 368, 459, 261, 183, 49], [8052, 46, 344, 284, 14562, 121, 95, 284], [225, 341, 297, 3984, 12653, 25858, 477, 283, 318, 207, 351, 210, 458, 426], [29244], [15963, 349, 295, 390], [346, 13708, 254, 31155, 462, 341], [418, 30258, 282, 68, 12155, 266, 429, 221, 295, 438, 50, 0, 232, 13322, 97, 5508, 300], [439, 59, 13, 69, 384, 207, 406, 2570, 197, 18960, 380, 365, 464, 12877, 166], [419, 188, 121, 81, 26067, 157, 10380, 2819, 479, 168, 478, 6534, 431, 181, 20, 474, 435, 127], [61, 12000, 237, 359, 447]]</t>
+    <t>[[207, 112, 104, 89, 1475, 43, 112], [24, 450, 440, 47, 174, 1891, 1459, 1327], [35, 286, 264, 507, 1079, 887, 487], [42, 225, 202], [196, 221], [381, 173], [494, 731, 172, 422, 218, 192, 25], [353, 143], [21, 322, 399, 1922, 493, 373], [489, 439, 389], [236, 314, 267, 158, 471, 193, 406], [214, 19, 244, 135, 487, 334, 265, 1863], [377, 424, 1062, 436, 30, 50, 488, 130], [252, 240, 485, 61, 1920, 152, 290, 691, 80], [419, 436, 459, 187, 125, 362, 371, 221], [441]]</t>
   </si>
   <si>
     <t>h128_ws2_idx4096_random_inbf16_outbf16_ID512</t>
   </si>
   <si>
-    <t>[[370, 3372, 509, 269, 1168, 100, 157, 4020, 354, 294, 67, 294, 509, 306, 432, 1365, 217, 56, 509, 398], [136, 283, 3260, 60, 120, 63, 457, 219, 94, 8, 355, 759, 420, 1651, 238, 229, 3249, 240]]</t>
+    <t>[[287, 118], [1745, 333, 3, 325, 203, 169, 504, 368]]</t>
   </si>
   <si>
     <t>h128_ws8_idx4096_random_inbf16_outbf16_ID513</t>
   </si>
   <si>
-    <t>[[2922], [171, 509, 480, 970, 96, 7, 1825], [80, 23, 2642, 273, 3246, 329], [116, 77, 237, 3821, 3391, 399, 3817, 373, 338, 16, 172, 46], [326, 3312, 259, 21, 506], [18, 228, 187, 3784, 3784, 182, 166, 107, 4042, 185, 340, 220, 412, 183, 2026, 352, 235], [432, 292, 3723, 3911, 147, 348, 324, 207, 247, 463, 296, 2256, 817, 484, 2269, 438, 497, 457, 213, 236, 481], [797, 154, 154, 264, 260, 155, 238, 106, 1975, 377, 26, 471, 3927, 77, 464]]</t>
+    <t>[[401, 454, 119, 193, 498, 13], [59, 236, 864, 104, 446, 68, 324, 376, 374], [4, 114, 489, 41, 291, 330, 43], [471, 390, 914, 470, 1421, 227, 383, 382], [68, 366, 1419, 84, 327], [238, 73, 128, 9, 709, 287, 278, 1146], [103, 443], [15, 1285, 244, 292, 372, 50, 157, 420, 525, 479]]</t>
   </si>
   <si>
     <t>h512_ws4_idx8192_random_infp16_outfp16_ID514</t>
   </si>
   <si>
-    <t>[[3367, 2951, 7003, 31, 3455, 410, 215, 334, 148, 294, 74, 222, 481, 59, 312, 261, 1477, 406, 481, 366, 4591, 63, 482, 134, 16, 125, 5], [1, 492, 85, 268, 6903, 187, 501, 1601, 29, 509, 30, 2447, 151, 511, 153, 489, 357, 76, 419, 271, 602, 4319, 284, 56, 234, 74, 104, 246, 6790, 95, 1039], [31, 2276, 121, 447, 1843, 89], [441, 481, 337, 443, 4385, 292, 153, 107, 6748, 497]]</t>
+    <t>[[102, 286], [244, 398, 1040, 211, 276, 474, 1077, 237], [354], [747, 1704, 66, 448]]</t>
   </si>
   <si>
     <t>h512_ws4_idx4096_random_infp32_outfp32_ID515</t>
   </si>
   <si>
-    <t>[[72, 335, 1784, 304, 369, 234, 1187, 2700, 108, 411, 28, 1629, 334, 99, 430, 247], [1711, 472, 25, 371, 215], [178, 382, 169, 151, 261, 87, 361, 2913, 579, 174], [671, 37, 151]]</t>
+    <t>[[31, 357, 161, 276, 215, 484, 143, 464, 338, 350], [1], [367, 729, 10, 484], [457, 88, 545, 1860, 357, 1361, 471]]</t>
   </si>
   <si>
     <t>h64_ws16_idx16384_random_infp32_outfp32_ID516</t>
   </si>
   <si>
-    <t>[[109, 353, 394, 51, 403, 11232, 411, 4241, 281, 11880, 419, 290, 577, 214, 115, 440, 4], [153, 140, 294, 2162, 33, 461, 5935, 59], [74, 6493], [400, 7990, 21], [4807, 1616, 165, 394, 201, 377, 499], [123, 14738, 6284, 51, 8516, 14, 294, 210, 459, 49, 289, 136, 210, 16263, 80, 404, 502, 331, 443, 467, 2321, 77, 448, 390], [13278, 39, 50, 258, 284, 197, 2272, 286, 317, 1, 486, 426, 164, 441, 12, 33, 165, 13, 154, 12537, 424, 8058, 4514, 25, 203, 129, 497, 4800, 68, 88, 75, 9870], [12328, 379, 303, 363, 230, 365, 391, 347, 332, 9132, 121, 2015, 137, 355, 214, 7682, 270, 146, 459, 473], [382, 52, 3659, 66, 1189, 122, 293, 425, 168, 10872, 348, 131, 444, 487, 180, 388, 108, 9968, 321], [508, 74, 40, 507, 5431, 236, 13080, 129, 14641, 62, 188, 164, 203, 441, 4, 3732], [11927], [127, 105, 188, 12822, 432], [55, 144, 198, 7183, 224, 334, 5919, 2364, 385, 143, 175, 196], [422, 459, 4626, 5787, 107, 326, 238, 373, 7, 14735, 184, 411, 219, 7848, 109, 48, 249, 245, 7024, 139, 175, 46, 21], [276, 31, 8318, 387, 1512, 65], [476, 138, 483, 14368, 1, 23, 16206, 5027, 412, 144, 231, 140, 348, 273]]</t>
+    <t>[[380, 104, 43, 70, 1278, 1603], [126, 151, 307, 155, 1430, 172, 237], [433, 482, 220, 368, 168, 313], [324, 84, 69, 107, 16], [328, 472, 1854, 79], [77, 147, 55, 327, 267, 496], [187, 43, 95, 384, 645, 53, 433, 378, 190], [380, 298, 324, 210, 251, 886, 301, 346, 409, 173], [259, 79, 11, 95, 247, 124, 122, 260], [1302], [274, 1754, 327, 25, 417, 287, 93, 410, 372, 217], [6], [246], [15, 70, 426, 119, 437], [453, 264, 430, 179, 208, 424, 264], [175, 72, 173, 346, 557, 218, 133]]</t>
   </si>
   <si>
     <t>h256_ws4_idx16384_random_infp32_outfp32_ID517</t>
   </si>
   <si>
-    <t>[[426, 1680, 112, 500, 129, 298, 176, 5363, 36, 89, 9158, 324, 434], [216, 138, 342, 222, 132, 474, 413, 7911, 54, 502, 412, 432, 24, 5984, 4310, 1327, 295], [338, 225, 14016, 110, 183, 297, 306, 18, 418, 10065, 231, 149, 302, 6101, 438], [95, 327, 125, 111, 1235, 286, 191, 287, 101, 10287, 123, 426, 258, 14494, 123, 383, 62, 249, 127, 267, 319, 398, 424, 8768, 4659, 12219]]</t>
+    <t>[[503, 97, 1754, 239], [1836, 481, 431, 474, 17, 275, 377, 120], [126, 389, 451, 506, 302], [483, 269, 498, 258, 7, 184, 30, 607, 73, 137]]</t>
   </si>
   <si>
     <t>h64_ws4_idx16384_random_infp32_outfp32_ID518</t>
   </si>
   <si>
-    <t>[[449, 39, 12, 500, 2008, 176, 53, 15178, 445, 4559, 184], [67, 401, 238, 67, 193, 6080, 121, 200, 405, 8611, 440, 12360, 44, 234, 507, 229, 255, 6452, 15, 451, 312, 243, 29, 9217], [20, 349, 311, 141, 355, 236, 11825, 15935, 476, 860, 131, 351, 140, 128, 8390, 13986, 222, 342, 485, 485, 62, 111], [306, 450, 26, 416, 394, 142, 214, 3540, 202, 203, 372, 297, 3814, 46, 397, 297, 485, 509, 10749, 435, 994, 80, 14, 1395, 92, 499, 14336, 4, 392, 425, 12440]]</t>
+    <t>[[428, 292, 485, 471, 294, 291, 435], [1111], [442], [211, 1148, 17]]</t>
   </si>
   <si>
     <t>h512_ws2_idx4096_random_infp32_outfp32_ID519</t>
   </si>
   <si>
-    <t>[[92, 1575, 3563, 154, 165, 512, 294, 371, 297, 500, 339, 509, 285, 882, 238], [7, 105, 368, 2326, 2527, 321, 82, 1608, 66, 42, 517, 410, 484, 52, 480, 314]]</t>
+    <t>[[322], [380, 401, 990, 311, 40, 375]]</t>
   </si>
   <si>
     <t>h256_ws16_idx8192_random_inbf16_outbf16_ID520</t>
   </si>
   <si>
-    <t>[[114, 342, 110, 122, 8, 441, 371, 223, 2478, 189, 318, 3534, 7524, 494, 7242, 184, 409, 0, 297], [446, 37, 3556, 325, 100, 5675, 181, 4363, 492, 109, 613, 401, 287, 479, 163, 5, 277, 5773, 120, 219, 5677, 0, 238, 117, 86, 368], [65, 472, 388, 218, 5466, 317, 175, 105, 3503, 40, 110, 271, 33, 430, 1830, 226, 429, 5048], [7459], [174, 140, 4718, 163, 420, 326, 325, 3897, 190, 7590, 190, 273, 508, 193, 262, 312, 173, 421, 6836, 467, 478, 5149, 190, 458, 217, 116, 3377, 160, 439], [242, 289, 110, 431, 7267], [264, 4728, 172, 506, 322, 459, 109, 147, 2796, 259, 349, 7458], [360, 6758, 488, 468, 43, 424, 221, 318, 2581], [79, 500, 740, 295, 350, 486, 59, 68, 486, 7072, 457, 5766, 88, 3276, 402, 427, 54, 211, 293, 1273, 64, 80, 24, 19], [253, 324, 105, 427, 280, 5349, 116, 4435, 194, 325], [321, 483, 18, 346, 454, 4600, 227, 127, 457, 355, 266, 190, 2764, 67, 385, 2098, 275, 274, 213, 362, 7685, 455, 490, 448, 6901, 336, 4719], [478, 7289, 232, 77, 1603, 287, 458, 79], [443, 3559, 5376, 57, 191, 270, 124, 269, 208, 504, 403, 281, 320, 355, 364, 105, 314, 148, 3330, 88, 3903, 426, 4842], [427, 2061, 448], [3320, 90, 243, 409, 257, 7716, 128, 5943, 317, 433, 115, 148, 501, 501, 61, 12, 328, 31, 449, 7832, 86, 334, 43, 245, 1540, 7921, 188, 374, 311, 459], [14, 432, 445, 2738, 418, 279, 221, 389, 2885, 8011, 284]]</t>
+    <t>[[91, 335, 367, 205, 377, 95, 461, 52, 208], [199, 417, 178, 254, 1718], [942, 1789, 2033, 27, 149, 254, 124], [402, 474, 424, 77, 11, 1362, 371, 56], [1907, 361], [335, 172, 383, 73, 444, 176, 343], [217, 115, 1062, 249, 783, 373], [364, 130, 156, 140], [335, 141, 302, 80, 279, 1374, 464], [173, 462, 503, 1925, 288], [447, 284, 568, 167, 441, 79, 1536, 357, 489, 146], [475, 400, 165, 504, 214, 149, 560], [1021, 23, 1703, 62], [631, 286, 394, 355, 432, 358, 230], [512, 182], [503, 11, 67, 279, 63]]</t>
   </si>
   <si>
     <t>h128_ws2_idx2048_random_inbf16_outbf16_ID521</t>
   </si>
   <si>
-    <t>[[1414, 277, 350, 1605, 302, 397, 1, 30, 72, 177, 359, 1389, 220, 39, 86, 224, 103, 1005, 411], [335, 129, 373, 491, 382, 1042, 307, 148, 27, 790, 14, 442, 157, 92, 329, 397, 197, 1664, 279, 617, 521]]</t>
+    <t>[[10, 124, 201, 348, 7], [127, 451, 441, 231, 141, 289, 342, 1246]]</t>
   </si>
   <si>
     <t>h128_ws4_idx2048_random_infp32_outfp32_ID522</t>
   </si>
   <si>
-    <t>[[161, 169, 1761, 193, 289, 25, 1944, 432, 241, 301], [1866, 293, 201, 913, 253, 97, 389, 1206, 1694, 440, 48, 477, 1747, 458, 9, 403, 4, 400, 130, 177, 489, 22, 987, 1064, 369, 168, 294, 155, 223, 478, 462, 421], [1, 62, 153, 149, 1655, 740, 1142, 461, 191, 305, 318, 115, 498, 200, 129, 187, 377, 142, 1972], [483, 545, 44, 674, 400, 392, 258]]</t>
+    <t>[[218, 96, 301, 1428, 473, 1240], [1605, 256, 326, 508, 1779], [1726, 442], [49, 85, 188, 246, 494, 355, 218, 315, 7, 218]]</t>
   </si>
   <si>
     <t>h64_ws8_idx16384_random_inbf16_outbf16_ID523</t>
   </si>
   <si>
-    <t>[[449, 4334, 487, 494, 127, 9702, 450, 150, 141, 325, 13567, 142, 27, 4, 506, 224, 192, 5907, 10568, 91, 61], [110, 372, 291, 10, 3401, 17, 4084, 472, 225, 204], [33, 170, 161, 258, 168, 4249, 458, 9, 14404, 405, 8245, 313, 28, 81, 99, 226, 174, 387, 126, 165, 502, 457, 15, 12431, 322, 1178, 78, 355, 6008], [148, 9518, 112, 316, 8011, 109, 283, 279, 6383, 342, 178], [214, 456, 118, 12644, 204, 330, 418, 752, 415, 146, 75, 326, 486, 398, 467, 14558, 8502, 93, 94, 110, 409, 5882, 75, 506, 8320, 317], [347, 247, 9213, 452, 491, 59, 3652, 276, 13742, 400, 437, 7, 868, 129, 410, 482, 305, 11, 201, 8099, 8721, 59, 216, 398, 334, 258, 119, 1185, 330, 288, 79], [511, 75, 183, 457, 452, 352, 8263, 103, 359, 13080, 345, 193, 137, 2202, 55, 191, 5210], [2748, 223, 12405, 63, 218, 13683, 1876, 317, 193, 11927, 86, 465, 414, 451, 423, 204, 11, 29, 293, 430, 25, 395, 70]]</t>
+    <t>[[375, 360], [26, 458], [9, 13, 416, 672, 306, 200, 477, 347, 1312], [360, 80, 1077], [380], [6, 166, 321, 155, 699, 196, 1809, 205, 145], [405, 483, 781, 1171, 251, 177, 338, 1, 322, 983], [42, 417, 402, 90]]</t>
   </si>
   <si>
     <t>h64_ws8_idx8192_random_infp16_outfp16_ID524</t>
   </si>
   <si>
-    <t>[[173, 319, 439, 59, 146, 264, 486, 81, 133, 94, 6710, 3284, 84, 1499, 474, 471, 226, 260, 5300, 244, 108, 1695, 330, 450, 21, 343, 7070, 9, 172, 311, 4802], [181, 643, 6006, 114, 175, 364, 76, 19, 324, 240, 27, 2989, 97, 454, 421], [374, 91, 390, 6244, 403], [463, 5221, 3508, 317, 179, 341, 79, 164, 728, 1, 272], [4248, 184, 273, 85, 6739, 152, 4579, 225, 443, 381, 240, 7, 7461, 19, 279, 51, 408, 254, 104, 7538, 453, 271, 434], [7114, 163], [12, 412, 468, 324, 415, 6251, 7112, 159, 38], [6686, 38, 172, 436]]</t>
+    <t>[[134, 400], [89, 508, 1623], [168], [12, 379, 407], [184, 455, 489, 294, 211, 1251, 174, 216], [160, 454], [432, 1446, 77], [191]]</t>
   </si>
   <si>
     <t>exception_indices_range_exceed_ID901</t>
@@ -2396,7 +2396,7 @@
     <t>['int8']</t>
   </si>
   <si>
-    <t>[[10000, 20000], [30000, 40000], [50000, 60000], [70000, 80000]]</t>
+    <t>[[37, 339, 284, 423, 367, 460, 494, 263, 498, 36], [414, 168, 151, 89], [70, 103, 1014], [446, 72, 311, 44, 216, 504, 147]]</t>
   </si>
   <si>
     <t>exception_fetch_num_exceed_32_ID902</t>
@@ -2405,13 +2405,13 @@
     <t>[[10240000000, 128]]</t>
   </si>
   <si>
-    <t>[[2016, 2707, 400, 3897, 1164, 209, 2225, 1964, 509, 3554, 3621, 1012, 1340, 2609, 1636, 2594, 2367, 4088, 3724, 379, 4089, 1820, 738, 3837, 1539, 2350, 2638, 1690, 1748, 2926, 3293, 1647, 3130, 831, 639, 952, 1981, 116, 748, 3210, 3163, 3741, 224, 1152, 976, 1283, 1058, 2547, 3659, 3150], [2025, 1266, 1543, 2750, 3671, 110, 1895, 3864, 2004, 2933, 2634, 3869, 3088, 627, 1237, 3307, 881, 575, 3352, 1582, 1916, 3091, 1016, 258, 36, 3954, 1905, 3424, 1804, 2298, 2352, 2810, 1102, 473, 2468, 785, 2955, 3964, 2595, 263, 2689, 512, 2095, 728, 107, 3768, 537, 1058, 953, 2289], [548, 1410, 3016, 2248, 1625, 2555, 3147, 3472, 3254, 218, 1027, 870, 537, 2405, 1065, 3487, 201, 3077, 2889, 3288, 130, 32, 1703, 1525, 2472, 2963, 3414, 2963, 1547, 3987, 2250, 2182, 2139, 1163, 3331, 4031, 1638, 122, 324, 4036, 79, 2689, 3130, 755, 3762, 2818, 1318, 176, 4070, 357], [3386, 1024, 3658, 2997, 2545, 785, 915, 756, 2974, 2096, 1615, 3065, 2608, 2151, 1389, 1850, 98, 846, 750, 1160, 3699, 2534, 1264, 2882, 199, 2335, 123, 979, 3616, 2693, 2751, 1010, 3697, 1425, 3630, 3855, 1883, 2799, 2752, 1103, 2260, 151, 120, 2137, 1708, 1421, 930, 924, 113, 3350]]</t>
+    <t>[[783, 433, 352, 65, 81], [505, 1677, 1729, 42, 462, 173, 641, 508, 397], [88, 511, 1793, 994], [376, 420, 249, 209, 27, 234]]</t>
   </si>
   <si>
     <t>exception_indices_count_mismatch_ID903</t>
   </si>
   <si>
-    <t>[[10, 20], [30, 40], [50, 60]]</t>
+    <t>[[54, 349, 20], [250, 164, 191, 446, 49], [471], [381, 1592, 214, 74]]</t>
   </si>
   <si>
     <t>exception_storage_dtype_int32_ID904</t>
@@ -2420,7 +2420,7 @@
     <t>['int32']</t>
   </si>
   <si>
-    <t>[[2995, 369, 475, 1455, 370, 501], [3098, 340, 495, 497, 5, 354, 321, 1553, 501, 2726, 466, 372, 85, 461, 66, 2486], [3922], [3180, 376, 308, 4095, 220, 44, 893, 329, 110, 328, 2373, 195, 364, 223, 62, 423, 374, 230, 54, 88, 716, 300, 68, 89]]</t>
+    <t>[[1822, 457, 34, 402, 3, 340, 427], [452, 19, 1872, 202, 379, 235], [1377, 93, 1585, 482, 50, 480], [49, 47, 69]]</t>
   </si>
   <si>
     <t>exception_hidden_zero_ID905</t>
@@ -2429,7 +2429,7 @@
     <t>[[1024, 0]]</t>
   </si>
   <si>
-    <t>[[1012], [358, 36, 436, 1621, 219, 57, 376, 138, 161, 3181, 398, 3, 436, 175, 2861, 252, 325, 326, 324, 118, 182, 432, 364, 203, 1813, 365, 193, 2630, 3952, 66], [3388, 429, 20, 95, 3740, 159, 423, 2218, 373, 28, 35, 341, 437, 185, 2498, 117, 460, 476, 62, 112, 2221, 505, 182, 335, 489], [2673, 632, 196, 474, 494, 433, 269, 427, 221, 75, 1634, 309]]</t>
+    <t>[[243, 88, 1956, 454, 442, 293, 309, 278], [1186, 490, 175, 494, 21, 296, 462, 392], [17, 91], [502, 84, 462, 915, 88, 187, 391, 83, 181]]</t>
   </si>
   <si>
     <t>exception_world_size_zero_ID906</t>
@@ -2444,25 +2444,25 @@
     <t>[[0, 128]]</t>
   </si>
   <si>
-    <t>[[0, 0, 0, 0]]</t>
+    <t>[[461, 88, 160, 12, 283, 149, 409], [352, 292, 306, 254, 29, 424, 220], [365, 309, 412, 195, 1956, 55, 463, 326, 424], [387, 445, 7, 75, 354, 306, 333, 73, 388]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h512_ws4_inbf16_outbf16_ID1001</t>
   </si>
   <si>
-    <t>[[498, 430, 351, 342, 401, 81, 342, 432, 299, 3250, 313, 361, 2433, 508, 3744], [77, 68, 437, 910, 245, 486, 2264, 257, 412], [106, 81, 3084, 352, 2581, 102, 425, 170, 0, 449, 507, 859, 160, 242, 360, 112, 44, 0, 72, 3014, 1057, 2460, 186, 92, 494, 423, 154, 3, 166, 220, 90, 1286], [96, 411, 25, 18, 15, 432, 10, 2750, 211, 809, 1917, 231, 192, 279, 207, 1654, 382, 366, 506, 406, 129, 245, 3648, 271, 491, 1502]]</t>
+    <t>[[492, 115, 292, 15], [14, 435, 491], [21, 352, 147, 455], [1561]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h512_ws8_inbf16_outbf16_ID1002</t>
   </si>
   <si>
-    <t>[[7835, 218, 190, 240, 214], [473, 462, 27, 77, 112, 289, 176, 211, 3847, 1439, 96, 19, 2285, 113, 479, 4577, 164, 316, 3997, 17, 331], [396, 330, 6724, 411, 203, 238, 308, 409, 2055, 396, 61, 392, 181, 325, 76, 3444, 63, 2950], [57, 507, 3550, 152, 247, 244, 505, 237, 500, 326, 295, 453, 600, 287, 4719, 25, 253, 2072, 115, 477, 2075, 289, 396], [452, 382, 318, 395, 4465, 255, 1372, 433, 87, 193, 7987, 188, 104, 77, 157, 7971, 132, 401, 166], [366, 380, 225, 379, 250, 476, 2623, 5020, 3359, 391, 311, 1288, 487, 137, 295, 403, 354, 380, 511, 4812, 367, 276, 5792, 80, 238, 107, 488, 93], [264, 562, 16, 104, 309, 6508, 6084, 124, 50, 58, 91, 354, 42, 412, 304], [566, 267]]</t>
+    <t>[[476, 290, 303, 381, 360, 273], [281, 281], [356, 475, 1, 460, 179, 468, 395, 231, 314, 282], [393], [1709, 465, 280, 20, 470, 378], [384, 125, 1922, 500, 286, 80, 242, 242], [1289, 159, 430, 462, 248, 17, 58, 441, 118, 189], [593]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h512_ws16_inbf16_outbf16_ID1003</t>
   </si>
   <si>
-    <t>[[120, 492, 14015, 476, 5120, 72, 509, 305, 417, 110], [364, 5470, 294, 374, 9, 16222], [410, 14352, 170, 11005, 952, 420, 303, 130, 360, 278, 365, 176, 374, 16, 282, 136, 264, 493, 321, 141, 395, 393, 107, 503, 4889, 5250, 220, 15938, 7710, 50, 368], [7919, 292, 122, 184], [473, 8070, 225, 130, 46], [4830, 259, 310, 453, 367, 152, 347, 791, 415, 129, 12604, 436], [6202, 4284, 159, 14071, 138, 485, 210, 313, 777, 117, 474, 470, 444, 16109, 86, 112, 293, 205, 159, 458, 14, 173, 61, 8050, 225, 501, 397, 250, 124, 358], [160, 90, 413, 190, 156, 211, 419, 39, 97, 95, 5400, 220, 7445, 266, 12203, 369, 193, 2, 286, 96, 217, 3, 46, 10428, 8792], [222, 10359, 502, 230, 249, 123, 152, 1746, 7, 1127, 419], [507, 80, 168, 304, 88, 1475, 246, 506, 508, 75, 473, 16257, 389, 5037, 102], [119, 4, 55, 397, 3330, 432, 279, 16304, 248, 13840, 403, 5276, 338, 208, 285, 510, 431, 261, 464, 383], [108, 6221, 52, 313, 169, 163, 165, 62, 257, 353, 15075, 8314, 150, 172, 11103, 70, 74], [184, 357, 9764], [195, 128, 4269, 8699, 121, 299, 347, 5925, 49, 139, 93, 123, 406, 390, 297, 40, 11392, 202, 212, 193, 3624], [325, 469, 245, 220, 104, 352, 15326, 456, 480, 456, 6408, 0, 15728], [4938, 425, 5, 81, 499, 316, 492, 6886]]</t>
+    <t>[[231, 207], [89, 439, 428, 276, 236, 317, 436, 1112], [47, 73, 430, 221, 1740], [106, 446, 510, 156], [380, 1244, 1189, 224, 355, 244], [395, 496, 240, 375, 765, 423, 312, 321, 251, 439], [205], [259], [1135, 1622, 38, 336, 130, 873, 511, 231], [441, 11, 49], [493, 463, 60, 2037, 445, 58, 84, 373, 87, 1372], [72, 175, 282, 1569, 196, 443], [132, 324, 71, 505, 144, 385], [449, 88, 238, 146, 464, 357, 182], [980, 2045, 478, 185, 1470, 226, 159, 231, 506, 258], [336, 150, 337, 1, 670, 793]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h1024_ws4_inbf16_outbf16_ID1004</t>
@@ -2471,67 +2471,67 @@
     <t>[[1024, 1024]]</t>
   </si>
   <si>
-    <t>[[5, 121, 431, 104, 2769, 230, 245, 428, 164, 332, 2800, 455, 220, 3809, 98], [107, 66, 187, 486, 69, 494, 2816, 1932, 1118, 345, 495, 1272, 2792, 234, 122, 310, 265, 1860, 239, 105, 481, 99, 254, 213, 350, 83, 123, 472], [3, 2662, 138, 180, 327, 121, 451, 497, 1188], [1411, 279, 114, 95, 234]]</t>
+    <t>[[497], [2019], [703, 320, 209, 191, 303, 404, 242, 271], [571, 375, 150, 268, 302, 198, 377]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h1024_ws8_inbf16_outbf16_ID1005</t>
   </si>
   <si>
-    <t>[[262, 209, 4028, 403, 142, 406, 5870, 2909, 8005, 5037, 6787, 369, 667, 251, 31, 495, 188, 428, 270, 4, 499, 379, 45, 86, 2, 318, 130, 76, 75, 331, 68], [367, 312, 162, 84, 156, 127, 2673, 1621, 424, 295, 132, 482, 8, 511, 1313, 6794, 101, 355, 6980, 106, 0, 199, 4244, 353, 468, 205, 37, 151, 181], [381, 120, 5486, 370, 920, 309], [36, 387, 4720, 228, 86, 230, 360, 5594, 6969, 254, 52, 386, 328, 318], [242, 77, 6265], [163, 117, 1723, 281, 7141, 81, 342, 911, 472, 82, 3591, 328, 37, 2644, 401, 182, 25, 51, 485, 23, 294, 253, 398], [247, 5760, 467, 354, 53, 553, 324, 42, 7655, 177, 323, 97, 36], [203, 1708, 6886, 259, 503, 60, 482, 381, 346, 433, 357, 460, 283, 5158, 2115, 283, 457, 469, 6623, 537, 362, 481, 237, 361, 383, 193]]</t>
+    <t>[[400, 482, 473, 289, 1777, 343, 284, 394, 339], [376, 490, 464, 390, 445, 113, 1406, 147, 318, 1936], [414], [42, 156, 504, 142, 281, 340, 309, 225, 4, 120], [42, 62, 259, 338, 1328, 360, 408], [141], [60, 181, 475], [323]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h1024_ws16_inbf16_outbf16_ID1006</t>
   </si>
   <si>
-    <t>[[14, 83, 305, 6328, 225, 11631, 83, 4598, 476, 420, 271, 200, 13, 432, 448, 14529, 341, 147, 482, 1425, 170, 402, 5209, 7460, 406, 11, 204, 350, 75, 206, 357, 185], [142, 7715, 482, 509, 49, 493, 14437, 303, 342, 351, 5153, 243, 144, 129], [267, 453, 9881, 12290, 66, 422, 195, 120, 5089, 296, 365, 497, 328, 16338, 475, 5397, 188, 381, 441, 350, 81, 389, 343, 54, 133], [177, 80, 297, 8916, 87, 3329, 386, 72, 327, 407, 7, 9, 79, 106, 260, 4877, 107, 2710, 399, 2580, 29, 148, 491, 6097, 186, 69], [462, 460, 338, 106, 158, 150, 5081, 396, 416, 390, 440, 413, 184, 99, 14474, 14839, 400, 441, 2895], [251, 272, 1983, 72, 473, 63, 304, 6615, 466, 129, 12306], [367, 430, 341, 10509, 83], [364, 43, 447, 2147], [9470, 234], [460, 455, 360, 492, 7056, 200, 1, 448, 314, 4129], [16096, 182, 175, 40, 12708, 364, 371, 39], [178, 168, 414, 9432, 339, 14292, 166], [275, 13678, 45, 189, 86, 24, 481, 498, 324, 15, 476, 380, 14385, 180, 402, 471, 155, 500, 1213, 3333, 111, 256, 376, 301, 71, 345, 844, 12553], [12111, 159, 239, 3565, 115, 334, 248, 402, 49, 55, 49, 143, 5766, 482, 142, 289, 50, 14367, 512, 171], [485, 1517, 169, 6482, 67, 246, 186, 436, 468, 13895, 453, 153, 81, 8302, 463, 25, 164, 332, 12394, 206, 162, 438, 15121, 280, 311, 57, 246, 158, 191, 66, 11291], [218, 10250, 217, 326, 12, 508, 10249, 267, 289, 14, 8076, 509, 3771, 255, 307, 95, 116, 252]]</t>
+    <t>[[82, 220, 74, 129, 1217], [261, 229, 308, 379, 829, 504, 313, 509], [196, 79, 35, 156, 296, 268, 43, 317, 1920], [339, 324, 277, 1473, 459, 433, 1239, 392], [1043, 405, 214, 157, 213, 227, 370, 264, 406], [459, 262, 370, 82, 240, 490, 154], [406, 128], [490, 168, 311, 51, 42, 502, 68, 585, 280], [77], [338, 203, 340], [368, 549, 734, 72, 76, 2010], [350, 122, 505, 88, 386], [476, 336, 352, 53, 11, 216, 224, 313, 341], [113], [236, 384, 441, 392, 235, 234, 95, 135, 304], [1064, 337, 1972, 299, 454, 456]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h512_ws4_infp16_outfp16_ID1007</t>
   </si>
   <si>
-    <t>[[201, 3660, 9, 410, 149, 61, 374, 452, 486, 162, 3241, 493, 411, 2303], [1212, 427, 96, 462, 59, 357, 1687, 225, 168, 267, 223, 3332], [77, 205, 3791], [332, 425, 213, 317, 172, 166, 509, 1454, 326, 194, 2260, 231, 1280, 340, 1222, 2912, 476, 245, 223, 240, 460, 181]]</t>
+    <t>[[160, 191, 412, 205, 11, 94], [117, 334, 754, 475, 310, 110, 386, 290, 116], [364, 193, 1684, 12], [500, 156, 306, 463, 528, 204, 166]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h512_ws8_infp16_outfp16_ID1008</t>
   </si>
   <si>
-    <t>[[381, 447, 160, 445, 477, 342, 127, 306, 193, 261, 5797, 1228, 8083, 160, 485, 356, 429, 1178], [339, 106, 320, 5735, 403, 169, 67, 34, 508, 487, 152, 1669, 6625, 1755, 428, 461, 427, 116, 155, 5214, 127, 105], [4989, 151, 171, 3087, 135, 395, 394, 511, 372, 471, 103, 133, 140, 5330], [467, 4117, 287, 38, 88, 442, 48, 6467], [132, 1, 252, 213, 4084, 7905, 1690, 429, 430, 6, 275, 290, 218, 410, 2364, 351], [166, 3610, 48, 248, 446, 5332, 189], [20, 151, 8186, 90, 7523, 6356, 360, 426, 252, 271, 16, 508, 38], [157, 440, 50, 394, 3156, 319, 285, 5482, 133, 211, 627, 5]]</t>
+    <t>[[197, 7, 115, 424, 457, 441, 425], [280, 218, 289, 180, 104, 269, 1073, 63], [4, 368, 183, 234, 285, 1246, 403], [227, 1153, 330, 1083, 290], [1249, 31], [220, 308, 117, 547, 60, 117, 229, 56, 455, 504], [1030, 46, 1246], [460, 1564, 1855, 115, 267, 200, 247, 839]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h512_ws16_infp16_outfp16_ID1009</t>
   </si>
   <si>
-    <t>[[372, 282, 96, 163, 388, 12603, 28, 408, 455, 16298, 12549, 365, 434, 9238, 8797, 200, 167, 251, 3622, 37, 8693, 483, 113, 152, 266, 154, 115, 419, 326, 272, 340, 199], [27, 505, 127, 198, 982, 111, 127, 193, 434, 225, 9963, 123, 289, 7253, 6051, 246], [9270, 361], [172, 14469, 257, 9698, 394, 257, 281, 320, 275], [15345, 76, 312, 138, 271, 377, 278, 9889, 181, 2168, 29, 314, 65, 256, 250, 378, 204, 7659], [210, 2997, 186, 8177, 245, 429, 261, 10968, 501, 182, 390, 150, 225, 90, 305, 8401, 277, 359, 293, 114, 10679, 320, 251, 501, 368], [372, 238, 3436, 352, 415, 175, 2438, 124, 4, 98, 10832, 430], [307, 485, 398, 93, 15685, 8013, 127, 81, 278, 6737, 14448, 421, 40, 56, 400, 259, 292], [425, 9, 367, 286, 8, 55, 16233, 501, 355, 84, 109, 355, 87, 13955, 14657, 2420, 504, 469, 468, 286, 440, 10276, 423, 476], [397, 335, 484, 200, 341, 326, 55, 400, 386, 353, 451, 7878, 412, 6198, 40, 15875, 326, 16187, 136], [423, 76, 23, 11352, 39], [387, 507, 427, 499, 8408, 249, 152, 9827, 400, 14398, 284, 291, 11864, 425, 3962, 267, 277, 507, 310, 236, 271], [7479, 493, 424, 499, 423, 239, 332, 13, 1738, 184, 41, 448, 4905, 189], [407, 312, 10666], [494, 213, 342, 15290, 5265, 259, 337, 15133, 58, 479, 16380, 462, 463, 270, 335, 304, 14244, 180, 33, 356, 177, 120, 70, 6, 11327, 141, 121, 258, 237, 113], [421, 11879, 204, 506, 409, 446, 194, 310, 332, 212, 110, 34, 8382, 294, 432, 211, 247, 12974, 450, 656, 204, 10565, 11911, 100, 388, 448, 370, 254, 137]]</t>
+    <t>[[306, 133], [280, 285, 283, 103], [104], [485, 349, 360, 489, 1078], [94], [359, 37, 142, 236, 74, 287, 19, 506, 143], [63, 330, 218, 98, 1655], [7, 1787, 580, 33, 284], [402, 402, 15], [38, 369, 1129, 1834], [398], [494, 455, 474, 1710, 290, 70], [26, 48, 444, 390], [154, 184, 129, 341, 324, 390, 379, 38, 691, 209], [16, 166, 267, 1265], [162, 344, 206]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h1024_ws4_infp16_outfp16_ID1010</t>
   </si>
   <si>
-    <t>[[276, 315, 504, 60, 207, 494, 3225, 504, 2123, 203, 138, 262, 376, 986, 167, 510, 111, 440, 3313, 257, 506, 278, 473, 2804, 71, 27, 409, 460, 2820, 186], [229, 3174, 194, 818, 443, 479, 157, 365], [2742, 220, 339, 190, 115, 42, 90, 194, 444, 3281, 106, 49, 1163, 39, 5, 85, 123, 132, 109, 502, 431, 3731, 2256, 2136, 271, 0, 421, 380, 179, 288, 925], [350, 298, 23, 439, 391, 313, 75, 86, 1163, 1976, 263, 4, 420, 467, 418, 2225, 7, 179, 437, 1078, 287, 561, 115, 343, 194, 2008, 379, 220, 28]]</t>
+    <t>[[1118, 427, 473, 136, 247, 788, 485], [1261, 272, 55, 343, 198, 845, 421], [410, 463, 443, 68], [327]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h1024_ws8_infp16_outfp16_ID1011</t>
   </si>
   <si>
-    <t>[[187, 189, 227, 6602, 8027, 243], [263, 8085, 6271, 194, 510, 4537, 5032, 223, 19, 423, 109, 5267, 329, 494, 273, 451, 320, 131, 231, 165, 377, 455, 449], [99, 74, 96, 435, 12, 26, 294, 71, 197, 286, 473, 483, 3355, 305, 132, 178, 413, 3202, 932, 2315], [311, 23, 498, 243, 381, 414, 492, 223, 30, 531, 285, 221, 7901, 239, 171, 406, 714, 8029, 401], [404, 361, 85, 4838, 89, 440, 395, 6655, 273, 456, 4645, 16, 228, 5448, 196, 3309, 509, 267, 430, 422, 44], [6569, 389], [6089, 457, 334, 53, 185, 220, 158, 182, 114, 162, 6303, 480, 429, 7920, 22, 451, 137, 246, 442, 223, 449, 5339, 156, 211, 317, 487, 34, 310, 2236, 2792, 7080], [300, 4106, 4, 375, 137, 432, 133, 4334, 182, 247]]</t>
+    <t>[[79, 372, 418, 1310, 247], [2043, 90, 312, 104, 47, 759, 159, 462], [123, 413, 309, 420, 149, 97], [187, 318, 385, 316, 481, 331, 855, 240, 389], [429, 86, 269, 46, 255, 310, 257, 404, 505, 126], [715, 277, 330, 101, 344, 47, 52], [1381, 432, 60, 722, 301, 391, 252, 1550, 442, 201], [237, 208, 210, 95]]</t>
   </si>
   <si>
     <t>perf_large_hidden_h1024_ws16_infp16_outfp16_ID1012</t>
   </si>
   <si>
-    <t>[[438, 13242], [287, 13484, 3158, 127, 259, 508, 156, 330, 85, 112, 122, 447, 241, 429, 7260, 63, 7485, 501, 369, 5357, 106, 474, 252, 262], [7664, 350, 86, 9346, 9603, 415, 135, 18, 121, 143, 229, 447, 15, 193, 267, 9709, 324, 172, 5090, 347, 64, 495], [304, 123, 293, 11788, 347, 172, 2856], [452, 483, 277, 309, 14523, 346, 21, 14103, 397, 7338, 253, 415, 511], [456, 15792, 494, 211], [349, 379, 9858, 115, 133, 52, 10767, 424, 96, 355, 176, 52, 466, 113, 142, 32, 62, 144, 177, 316, 10569, 1493, 15447, 332, 5059, 307], [173, 385, 303, 461, 240, 103, 155, 13, 128, 2395, 427, 370, 68, 201, 184, 48, 128, 117, 173, 27, 9778, 466, 6222, 20, 10943, 2814, 139, 50, 4857], [276, 14924, 10658, 490, 185, 8472, 88, 133, 445, 210, 124, 309, 425, 217, 193, 64, 12946, 97, 258, 178, 159, 12237, 88], [359, 3617, 64, 99, 139, 10281, 15, 135, 175, 80, 105, 122, 9758, 86, 221, 463, 460, 8269, 107, 88], [474, 257, 6, 15272, 9725, 219, 3, 10348, 346, 303, 166, 363, 137, 3, 88, 190, 7426, 179, 6674, 4767, 194, 431, 232, 319, 386, 10354, 372, 56, 30, 75, 346], [9515, 262, 188, 4058, 17, 174, 81, 258, 237, 13184, 340], [359, 10997, 316, 6368, 6239, 258, 508, 283, 80, 459, 367, 311, 55, 249, 234, 452, 219, 6274, 280, 214, 310, 4975, 475, 490, 316], [507, 9508, 193, 139, 43], [9105, 11104, 380, 287, 174, 260, 140, 22, 12, 190, 98, 139, 13267, 204, 161, 243, 69, 146, 39, 262, 456, 466, 383, 9544, 477, 52, 6187, 58, 490, 5995, 13362, 14], [484, 242, 104, 453, 181, 47, 423, 480, 16024, 228, 158, 283, 377, 9898, 6988, 389, 89, 4929, 429, 334, 6571, 85, 1, 10208, 461, 472, 502]]</t>
+    <t>[[31, 43, 451, 833], [370, 401, 365, 97, 370, 456, 262, 155, 270, 21], [346, 36, 93, 287], [497, 336, 406, 203, 327, 12, 344], [366, 29], [185], [1429, 312, 229, 2027, 157, 6], [196, 416, 236], [405, 163, 250, 256], [39, 7], [58, 338, 40, 400, 65, 218, 287, 62, 259, 349], [413], [210, 131, 1704, 348], [24, 471, 190, 298, 48, 216, 72, 329, 80], [15, 419], [72, 156, 97]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne4096_ws4_inbf16_outbf16_ID1013</t>
   </si>
   <si>
-    <t>[[7251, 177], [218, 229, 357, 497, 15473, 183, 485, 478, 256, 125, 5014, 16363, 355, 14403, 6167, 501, 427, 228, 152, 320, 40, 33], [343, 132, 4239, 490, 38, 11457, 377, 422, 27, 6706, 152, 112, 493, 236, 35, 221, 363, 423, 360, 3606], [14048, 41, 351, 7003, 265, 399, 194, 121, 136]]</t>
+    <t>[[480, 463, 1091], [379, 110, 1291, 287, 703, 269, 353, 354], [147, 687, 1423, 1882, 328, 352, 385, 1910, 218], [86, 177, 818, 98, 74]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne8192_ws4_inbf16_outbf16_ID1014</t>
   </si>
   <si>
-    <t>[[412, 347, 120, 12924, 93, 93, 318, 489, 21886, 395, 478, 3301, 427, 45, 247], [796, 111, 418, 481, 20, 379, 385, 444, 60, 334, 20596, 26714, 6750, 41, 243, 423, 146, 9, 98, 201], [239, 15926, 75, 20554, 131, 495, 162, 226, 642, 416, 416], [309, 83, 472, 151, 340, 22257, 395, 392, 488, 107, 275, 33, 80, 364, 35, 22349, 24602, 30882, 401, 1980, 196, 323, 494, 282, 20833, 476, 165, 98, 1749, 228, 334, 201]]</t>
+    <t>[[1705, 444, 485, 62], [435, 459, 445, 302, 963, 25, 72, 561], [269, 1725], [1871, 445, 82, 349]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne16384_ws4_inbf16_outbf16_ID1015</t>
@@ -2540,37 +2540,37 @@
     <t>[[16384, 128]]</t>
   </si>
   <si>
-    <t>[[368, 5974, 23, 5, 86, 420, 100, 269, 398, 215, 398, 352, 44, 45716, 306, 241, 39236, 501, 470, 326, 354, 148, 56926, 299, 1956, 132, 31119], [18840, 27531, 423, 249, 117, 1, 403, 242, 60, 87, 427, 293, 57057], [240, 107, 60351, 163, 139, 17, 20798, 436, 93], [31, 244, 25, 154, 843, 358, 113, 11030, 365, 446, 197, 3269, 157, 202, 28593, 458, 464, 464, 7, 48579, 7440, 164, 43, 266, 67, 279, 273, 109, 466, 372, 159, 45478]]</t>
+    <t>[[455, 463, 470, 197, 16, 58], [107, 101, 317, 233, 1928, 298], [24, 1312, 112], [438, 370, 426]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne4096_ws8_inbf16_outbf16_ID1016</t>
   </si>
   <si>
-    <t>[[171, 8453], [105, 46, 215, 269, 29248, 11219, 245, 468, 28959, 97, 89, 243, 4591, 38, 435, 484, 328, 17, 214, 465, 223, 148, 472, 10177, 154, 470, 231, 6400, 46, 457], [63, 296, 183, 411, 21584, 248, 30314, 10, 100, 301, 117, 383, 21636, 82], [223, 226, 54, 315, 26132, 4330, 148, 31954, 126, 380, 144], [76, 20006, 174, 187, 284, 29914, 254, 425, 344], [505, 5967, 443, 4, 254, 437, 135, 30287, 388, 20308, 145, 15698, 16, 272, 354, 120, 229, 106, 341, 47], [317, 270, 389, 195, 252, 412, 108, 20320, 236, 430, 201, 30352, 369, 22979, 288, 14652], [223, 265, 41, 247, 17277, 2537, 130, 293, 30815, 33, 269, 261, 194, 12985, 120, 19377, 247, 421, 27912, 59, 267, 12, 496, 241, 83, 299]]</t>
+    <t>[[303, 257, 160], [1843, 382, 623, 314], [508, 482, 325], [333, 284, 189, 3, 312], [941, 236, 469, 147, 189, 489, 115, 348, 282], [998, 1616, 1297, 118, 170, 1728, 434, 690, 98, 689], [235, 1212, 227, 273, 212, 418], [42]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne8192_ws8_inbf16_outbf16_ID1017</t>
   </si>
   <si>
-    <t>[[298, 461, 271, 181, 39, 166, 31, 50357, 232, 332, 33863, 478, 476, 154, 325, 506, 64488, 11848], [30003, 344, 335, 51024, 288, 496, 161, 227, 268, 44, 220, 96, 73, 32103, 393, 372, 150, 393, 99, 36703, 55100, 59], [385, 110, 162, 55335, 12101, 115, 332, 381], [291, 54, 291, 1388, 57, 347, 24786, 209, 1], [51, 4007, 234], [235, 431, 489, 472, 497, 28895, 396, 235, 87, 184, 220, 157, 276, 50, 296, 12809, 394, 265, 25015, 21683, 163, 188, 107, 43606, 306, 34084], [135, 25092, 376, 281, 37134, 309, 114, 278, 13, 465, 153, 48069, 23131, 370, 235, 396, 162], [314, 112, 54, 47756, 40501, 9, 60, 281, 493, 509]]</t>
+    <t>[[319, 469, 479, 116, 389, 434, 419, 1230, 312, 374], [1561, 490, 9, 1489], [400, 197, 2019, 436, 34], [252, 406, 506, 168, 9, 183, 391], [238], [314, 261, 1564, 77, 422, 114, 159, 410, 308, 464], [1903], [246, 255]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne16384_ws8_inbf16_outbf16_ID1018</t>
   </si>
   <si>
-    <t>[[105339, 175, 172, 276, 36, 134, 191, 456, 313, 153, 11049, 329, 126391, 176, 101, 50, 165, 323, 120368, 472, 23, 505, 69, 22084, 327, 463, 120619, 423, 160], [42, 469, 278, 257, 82, 126, 2892, 282, 337, 18649, 230, 235, 350, 1, 20, 122709, 54710, 341], [482, 328, 412, 74, 3, 77, 58212, 103694, 181, 54, 266, 146, 325, 266, 295, 198, 159, 375, 165, 488, 347, 499, 29885, 46758, 355, 47221, 358, 50, 10680, 115917, 78, 300], [113545, 93690, 87507, 127, 387, 497, 503, 325, 318, 8, 106896, 6398, 128, 423, 203, 242, 507, 16, 351, 279, 64], [426, 55974, 71797, 196, 173, 195, 331, 5, 425, 349, 428, 23, 484, 298, 20034], [388, 282, 65776, 96458, 409, 354], [241, 210, 328, 368, 162, 443, 101, 360, 294, 14502, 448, 321, 398, 192, 376, 89247, 337, 476, 65, 469, 384, 409, 90813, 68273, 355, 88109, 94, 63209, 54, 93, 75460], [55, 129, 125, 448, 481, 49977, 33, 363, 75698, 467, 111013, 77, 77464, 458, 292, 476]]</t>
+    <t>[[1904, 312, 362, 441, 724, 683, 143], [352, 230, 664], [510, 148, 38, 234], [322, 287, 92], [378, 130, 365, 192, 75, 316, 336, 266], [237, 151, 469, 456, 63, 783, 168, 351, 470], [291, 111], [50, 253, 365, 140]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne4096_ws4_inbf16_outbf16_ID1019</t>
   </si>
   <si>
-    <t>[[192, 161, 12046, 332, 2334, 311], [745, 234, 43, 256, 365], [450, 275, 512, 478, 375, 448, 465, 4575, 296, 385, 391, 6994, 192, 13444, 440, 5159], [129, 193, 92, 187, 185, 20, 417, 153, 230, 13003, 425, 6406, 292, 117, 64, 13271, 141, 14211, 260, 7739, 252, 100, 98, 378, 276, 14820, 274, 123, 250, 3]]</t>
+    <t>[[228, 830, 1341], [120], [1826, 331, 1315, 242, 1258, 425], [266]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne8192_ws4_inbf16_outbf16_ID1020</t>
   </si>
   <si>
-    <t>[[283, 7519, 6296, 291, 2198, 4306, 22, 429, 447, 6, 438, 364, 320, 111, 12, 505, 391, 462, 376, 96, 5226], [415, 83, 387, 96, 5580, 42, 417, 27304, 415, 268, 174, 72, 325, 251, 328, 790, 443, 218, 30588, 102, 343, 113, 12116, 250], [486, 184, 41, 129, 49, 15405, 464, 332, 383, 24936, 449, 12520, 31382, 285, 266, 182, 103, 76, 53, 4955, 333, 14, 217], [331, 50, 221, 31992, 304, 322, 21333]]</t>
+    <t>[[1847, 481, 477, 505, 48, 365, 153], [505, 507, 200], [496, 996, 108, 42, 300, 393, 431, 117, 150], [1542]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne16384_ws4_inbf16_outbf16_ID1021</t>
@@ -2579,145 +2579,145 @@
     <t>[[16384, 256]]</t>
   </si>
   <si>
-    <t>[[354, 60052, 56860, 454, 105, 235, 288, 506], [12, 76, 278, 29431, 64, 123, 184, 57, 68, 427, 65062, 29925, 127, 59266, 172, 343, 71, 447, 359, 20029, 306, 214], [117, 374, 512, 109, 175, 61, 341, 6012, 130, 35434, 141, 50398], [353, 23306, 509, 379, 325, 496, 6220]]</t>
+    <t>[[159, 416, 439, 232, 58, 23, 7], [1207, 127, 133, 458, 1021, 47, 125, 453, 56, 193], [336, 338], [498, 75, 271, 383, 166]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne4096_ws8_inbf16_outbf16_ID1022</t>
   </si>
   <si>
-    <t>[[389, 225, 23492, 10967, 38, 100], [439, 3712, 285, 30220, 23, 5642, 25780, 22627, 49, 34, 2163, 97, 210, 206, 175, 254, 373, 465, 384, 50, 265, 487, 204, 206, 85, 91, 180, 35, 206, 22883, 342], [164, 415, 345, 4579, 134, 17800, 25665, 40, 109, 295, 238, 84], [356, 263, 71, 405, 380, 222, 158, 5530, 493, 230, 11383, 375, 162, 106, 147, 3598, 43, 19460, 420, 385, 342, 445, 448, 8, 5076, 28660], [225, 23, 204, 8404, 253, 420, 231, 269, 428, 15580, 6381, 286, 142, 192, 19464, 478], [420, 235, 30502, 290, 9, 14727, 197, 497, 72, 453, 16133], [443, 79, 140, 417, 48, 31148, 20686, 250, 258, 2804, 349, 489, 85, 186, 459], [126, 4728, 84, 278, 398, 308, 79, 379, 451, 363, 302, 29762, 23375, 18, 212, 390, 11475, 132, 271, 629, 381, 243, 193, 495, 143, 31695, 142]]</t>
+    <t>[[119, 392, 401, 244], [318, 390, 310, 350, 209, 454, 89, 307, 355], [286, 127, 212], [453, 821, 989, 230, 195], [121, 1119, 1144, 281, 25, 137, 654, 394, 300], [295, 43, 313, 536, 292, 343, 349, 161, 79, 234], [239, 44, 440, 405], [320, 156]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne8192_ws8_inbf16_outbf16_ID1023</t>
   </si>
   <si>
-    <t>[[59890, 285, 276, 494, 48173, 266], [78, 5377, 367, 52157, 332, 347, 447, 63749, 67, 210, 33183, 486, 199, 285, 461, 361, 512, 50], [172, 19956], [64, 35, 140, 27196, 352, 7865, 91], [96, 27557, 449, 124, 105, 2182, 213, 220, 64452, 74, 72, 430, 180, 72, 273, 299, 52, 40190, 222, 31908, 256], [49181, 368, 173, 26, 431], [5078, 278, 112, 38189, 392, 54, 346, 473, 103, 255, 62, 180, 394, 63849, 157, 29524, 489, 132, 8739, 154, 373, 74], [41910, 268, 65335, 261, 59076, 467, 131, 310, 34, 412, 99, 507, 323, 453, 349, 182, 383, 100, 282, 34128]]</t>
+    <t>[[14, 298, 415, 482], [1921, 264, 385, 427, 352], [289, 142, 54, 188, 273, 131, 292, 378, 20], [1541, 370, 1946], [297, 1449, 250, 74, 438, 191], [27], [1363, 419, 232], [256]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne16384_ws8_inbf16_outbf16_ID1024</t>
   </si>
   <si>
-    <t>[[49365, 15, 378, 27, 48, 430, 306, 39677, 80775, 137, 47, 181], [122359, 130, 1, 129, 218, 230, 213, 189, 298, 17, 141, 70, 101091, 116989, 17801, 343], [267, 50877], [103471, 356, 4, 340, 181], [479, 265, 242, 192, 3, 322, 344, 92947, 354, 123, 479, 78, 40, 114326, 398, 108120, 131, 35640, 116836, 399, 452, 432, 301, 285, 464], [94742, 356, 112194, 91, 376, 33, 71330, 374, 398, 254, 335, 126, 361, 16, 491, 297, 214, 147, 240, 11836, 66004, 196, 210, 58, 160, 305, 349, 115250, 75], [26, 454, 35, 501, 209, 438, 371, 214, 34, 117, 20430, 12859, 60412, 290, 507], [77223, 380, 71044, 217, 206, 47, 293, 87172, 411, 112, 104890, 318, 114895, 462, 388, 220, 87, 41, 82, 368, 87, 419, 127, 110307, 337, 279, 307]]</t>
+    <t>[[1987, 232, 413], [61], [5, 235, 130, 422, 276], [337], [355, 258, 406, 1736, 429, 49, 411, 479, 478], [66, 29, 397, 186, 152, 97], [432, 501], [1911, 89, 2, 1379, 245, 378, 175]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne4096_ws4_infp16_outfp16_ID1025</t>
   </si>
   <si>
-    <t>[[475, 186, 14, 314, 6982, 2113], [45, 58, 500, 15412, 9835, 464, 206, 11955, 282, 427, 36, 422, 5674, 272, 9752, 497, 407, 141, 88, 499, 15534, 498, 113, 245, 156, 15382, 147, 84, 152, 274, 303], [129, 168, 292, 84, 70, 88, 394, 291, 483, 7831, 8979, 272, 298, 503, 1, 4047, 65, 60, 14569, 16316, 382, 3264, 94, 111, 405, 379, 426], [475, 75, 104, 249, 175, 479, 203, 322, 474, 317, 67, 139, 355, 111, 437, 14585, 10647, 5753, 321, 862, 6913, 0, 53, 505, 498, 7422, 358, 150]]</t>
+    <t>[[264, 508, 9, 44, 160], [1321, 94, 205, 347, 485, 441, 61, 308, 285, 455], [63, 217, 13, 134, 139, 537, 292], [97, 437, 125, 280, 169, 13, 56, 66, 23]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne8192_ws4_infp16_outfp16_ID1026</t>
   </si>
   <si>
-    <t>[[470, 8524, 441, 29210, 345, 415, 162, 5], [303, 5885], [321, 464, 217, 283, 180, 21069, 47, 16380, 72, 51, 465, 19215, 221, 7112, 271, 168, 10, 293, 132, 25373, 135, 307, 259, 508, 27801, 429], [358, 7, 243, 10, 474, 10, 22, 3, 440, 180, 18834, 291, 450, 22313, 110, 165, 17661, 1, 361, 13, 162, 195, 128, 27063, 20, 5132, 49, 8038, 257]]</t>
+    <t>[[106, 388], [362, 195, 420, 422, 153, 503, 81, 25], [165, 247, 440, 45], [355, 1335]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne16384_ws4_infp16_outfp16_ID1027</t>
   </si>
   <si>
-    <t>[[346, 44, 199, 273, 8348, 467, 386, 144, 460, 130, 32494, 245, 25516, 43836, 296, 58267, 142, 59, 431, 130, 359, 363, 137, 479, 446, 59756, 123, 320, 298, 46], [57, 144, 351, 304, 121, 331, 19273, 65, 355, 10568], [10860, 241, 112, 409, 60247, 30, 22, 8, 57444, 156, 41839, 466, 462, 293, 468, 305, 251, 59576, 183, 168, 108, 344], [464, 176, 76, 34373, 204, 166, 230, 13531, 29035, 392, 248, 103]]</t>
+    <t>[[742, 483, 136, 296, 259, 128, 333], [201, 534], [84, 42, 100, 282, 28], [314, 124, 17, 396, 42, 351, 496, 138, 1050]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne4096_ws8_infp16_outfp16_ID1028</t>
   </si>
   <si>
-    <t>[[14685, 89, 234, 416, 235, 277, 158, 442, 408, 6432, 318, 6120, 12501, 267, 319, 226, 97], [18822, 357, 146, 39, 260], [15990, 354, 499, 453, 441, 286, 268, 5024, 2], [432, 8532, 162, 34, 218, 444, 23, 292, 177, 8917, 14846, 385, 250, 368, 25, 355, 390, 205, 29488], [11117, 35, 95, 414, 315, 79, 237, 335, 136, 174, 1271, 164, 28066, 126, 27354, 500, 18675, 462, 158, 182, 421, 144, 84, 32, 157], [182, 258, 435, 116, 479, 18086, 18583, 448, 129, 247], [241, 21440, 254, 28126, 79, 319, 330, 190, 27786, 910, 371, 77, 508, 26630, 205, 32078, 170, 367, 170, 436, 433, 197, 387, 187, 184, 81, 408, 343], [34, 41, 185, 207, 320, 301, 302, 11558, 337, 236, 200, 451, 261, 22682, 26224]]</t>
+    <t>[[280], [186, 246, 358, 430, 153, 263], [208, 95, 264, 503, 1179, 357, 268, 89], [8, 445, 56, 1971, 390, 34, 285], [1878, 153, 295, 130, 383, 482, 452, 361, 377, 319], [447, 26], [367, 256, 15, 59, 511, 1033, 175], [13, 446, 118, 378, 11, 433, 137]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne8192_ws8_infp16_outfp16_ID1029</t>
   </si>
   <si>
-    <t>[[495, 290, 19382, 507, 51074, 33, 33, 147, 440, 66, 54123, 296, 795, 508, 27, 102, 436, 189], [160, 0, 332, 487, 402, 291, 42, 103, 51838, 471, 20, 35768, 29, 5, 231, 155, 35, 55582, 212, 41685, 5255, 53, 385, 452], [43, 116, 28853, 192, 270, 32630, 24, 425, 195, 370, 398, 11467, 399, 234, 211, 100, 294, 16460, 124, 19, 465, 17, 460, 321, 3374, 454, 382, 8421, 62839, 469, 18, 83], [11, 305, 169, 41819, 35], [244, 6, 43174, 4412, 59117, 292, 237, 484, 295, 424, 392, 255, 317], [388, 189, 385, 117, 9, 106, 350, 345, 369, 8692, 27, 193, 372, 61, 413, 12298, 14996, 28998, 451, 308, 33356, 306, 305, 213, 45803, 65], [125, 20929, 440, 274, 131, 27630, 7, 388, 89, 508, 74, 7675], [443, 10669, 222, 40, 97, 14, 31841, 65, 303, 464, 20733]]</t>
+    <t>[[16, 12, 182], [16, 75, 132, 90, 1528], [276, 42, 405, 316, 1673, 112, 94, 305], [236, 119, 225], [391, 165, 418, 1888, 1145, 1665, 385, 27, 324], [873, 163, 492, 433, 333, 116, 496, 1026, 78], [209], [454, 388, 178, 386, 980]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne16384_ws8_infp16_outfp16_ID1030</t>
   </si>
   <si>
-    <t>[[109, 437, 345, 443, 94120, 372, 293, 76108, 359, 227, 310, 119768, 356, 72384, 414, 27, 13], [119, 286, 187, 82, 111726, 343, 87, 116, 292, 108664, 183, 93537], [505, 467, 506, 101284, 115, 359, 232, 287, 43035, 115026, 368, 292, 512], [17305, 334, 233, 453, 18369, 259, 271, 423, 422, 258, 73, 318, 119, 97087, 72568, 38, 311, 9], [96367, 435, 166, 338, 379, 343, 73, 505, 211, 81, 305, 93682, 163, 212, 471, 506, 185, 54554, 98, 48, 502, 57, 101383, 6371, 68974, 162, 426, 146], [121, 170, 75314, 34686, 502, 484], [15576, 446, 56851, 483, 43, 66156, 158, 41, 113, 491, 501, 46926, 113, 349, 92583, 96, 30, 407, 145, 88, 454, 299, 427, 430, 399, 101511, 51809, 446, 505, 214, 419], [346, 100795, 280, 445, 405, 31380, 225, 198]]</t>
+    <t>[[83, 63, 792, 350, 153, 77, 45, 63, 36, 128], [372, 1671, 394, 108, 44, 392, 461, 80], [185, 56, 184, 1024, 224, 298], [932, 112, 6, 254], [200, 217, 238, 1190, 336, 213, 292, 417, 35], [52, 334, 16], [359], [356, 424, 71, 209]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne4096_ws4_infp16_outfp16_ID1031</t>
   </si>
   <si>
-    <t>[[257, 277, 12, 158, 400, 1, 418, 401, 2488, 8083, 1628, 167, 10158, 145, 58, 4637, 248, 416, 69, 258, 43, 78, 129], [261, 137, 323, 15436, 51, 347, 164, 405, 11186, 199, 46, 223, 334, 158, 178, 226, 219, 9969, 7638, 29], [482, 471, 11052, 7640, 11676, 119, 12, 165, 113, 176, 8625, 138, 128, 424, 99, 201], [369, 253, 103, 511, 412, 14326, 72, 11645, 215]]</t>
+    <t>[[188, 95, 277, 489, 102, 1510, 155], [320, 432, 233, 512, 473, 345], [372, 946, 140, 301, 1501, 49, 467, 282, 272, 489], [286, 471, 339, 496, 384, 149, 139, 538, 131, 365]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne8192_ws4_infp16_outfp16_ID1032</t>
   </si>
   <si>
-    <t>[[385, 91, 19113, 89, 393], [247, 29547, 188, 376], [77, 14025, 29, 352, 62, 74, 9187, 255], [368, 302, 397, 8, 399, 49, 106, 5407, 81, 23143, 359, 188, 27074, 37, 175, 11734, 179, 466, 28340, 338, 464, 139, 373, 45, 147, 218, 21254, 386, 251, 362, 309, 31103]]</t>
+    <t>[[88, 493, 363, 372, 313, 115, 180, 1864], [172, 657, 155, 73, 365, 25, 386, 1140], [384, 451, 24, 176, 42, 369, 127], [33, 1172, 471, 461, 65, 378, 628, 547, 447, 1892]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne16384_ws4_infp16_outfp16_ID1033</t>
   </si>
   <si>
-    <t>[[114, 8411, 403, 119, 409, 27, 2, 172, 1326], [421, 437, 375, 115, 253, 34375, 18856, 152, 190, 68, 305, 502, 7468, 185, 317, 510, 370, 441, 397, 25, 26293, 485, 345, 417, 52051], [200, 36950, 54891, 260, 105, 93, 57969, 48, 355, 480, 252, 239, 313, 475, 390], [92, 37478, 68, 495, 384, 199, 216, 6856, 154, 182, 492, 250, 512, 8084, 16075, 51764, 56, 387, 6, 46585, 69, 328, 42, 441, 81, 225, 145, 175]]</t>
+    <t>[[193, 336], [17, 194, 133, 394, 348, 449, 154, 104, 314, 364], [200], [161, 430, 463, 463, 42, 337, 1616, 268]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne4096_ws8_infp16_outfp16_ID1034</t>
   </si>
   <si>
-    <t>[[22332, 4000, 51, 86, 469, 443, 288, 26352, 17561, 421, 398, 341, 317, 27474, 470, 372, 145, 106, 369, 456, 74, 352], [172, 11639, 4], [507, 88, 477, 354, 10426, 234, 218, 281, 114, 140, 134, 32645, 86, 12265, 17752, 457, 33, 23, 455, 384, 440, 25284, 20531, 313, 473, 80, 58, 42, 68, 40], [460, 1, 18546, 223, 427, 28547], [441, 477, 349, 434, 1886, 178, 106, 10497, 61], [378, 491, 8445, 242, 196, 215, 110, 423, 114, 210, 28985, 115, 459, 21307], [38, 15040, 243, 21, 11124, 12, 79, 507, 426, 87, 25, 127, 500, 292, 30690, 393, 106, 29522, 476, 249], [19786, 452, 158, 445, 294, 306, 8524, 321, 476, 291, 16017, 198, 404, 128, 512, 165, 111, 21500, 245]]</t>
+    <t>[[160, 250, 397], [801], [508, 178, 1553], [190, 367], [145], [183, 445, 434, 325, 18, 43, 996, 1669, 507, 260], [356, 54, 492, 174, 1543, 739, 354, 207], [53, 33, 349, 484]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne8192_ws8_infp16_outfp16_ID1035</t>
   </si>
   <si>
-    <t>[[34671, 455, 220, 64, 44, 394, 42598, 130, 36494, 56, 83, 507, 114, 76, 364], [8175, 412, 52586, 331, 37, 17454, 385, 507, 372, 181, 153, 62, 58046, 98, 89, 234, 277, 304, 116, 360], [195, 5, 412, 349, 52798, 339, 81, 64411], [380, 42942, 54, 299, 178, 80, 388, 427, 242, 94, 339, 52491, 44782], [454, 213, 480, 243, 6110, 59, 103, 374, 60759, 420, 239, 466, 232, 473, 0, 22, 49, 50676, 505, 35, 410, 349, 41, 164, 44697, 37334, 307, 33785, 5], [188, 22398, 377, 45132, 84, 124, 35977, 424, 136, 365, 63, 281, 4, 79, 67, 58232, 470, 33921, 140, 474, 286, 92], [92, 442, 152, 49, 18902], [219, 458, 32522, 38, 307, 193, 210, 157, 135, 26508, 154, 57518, 134, 348, 63, 456, 116, 32420, 14]]</t>
+    <t>[[27, 48, 8, 221], [636, 90, 147], [43, 496, 221, 100, 434, 315], [390, 44, 445, 370, 304, 409, 761, 341, 213, 186], [236, 217, 176, 405, 430, 1100, 386], [260, 187, 8], [273, 404, 464, 258, 80], [196, 847, 264, 149, 356, 151]]</t>
   </si>
   <si>
     <t>perf_large_entries_ne16384_ws8_infp16_outfp16_ID1036</t>
   </si>
   <si>
-    <t>[[217, 188, 169, 82, 116900, 333, 187, 26, 67668, 124, 993, 11, 91, 37764, 481, 107450, 330, 127274, 373, 135, 489, 328, 400, 327, 347, 215, 20, 242, 59, 123], [262, 132, 4, 437, 43575, 360, 6770, 399, 458, 448, 474, 105875], [392, 89, 141, 160, 23829], [0, 236, 106841, 47694, 228, 486, 332, 113, 126177, 241, 59], [236, 493, 3, 285, 59141, 121, 142, 75033, 431, 52438, 28643, 77, 342, 507, 222, 387, 136, 122, 402, 113142, 121, 19, 149, 134, 76, 89410, 57], [127, 511, 122167, 11, 338, 119515, 155, 51800, 156, 53, 36, 159, 492], [51922, 488, 74, 203, 501, 301, 130556], [445, 43222, 2, 512, 250, 14, 325, 273, 30523, 205, 170, 404, 472, 503, 95, 65563, 41, 407, 191, 78803, 92, 103, 115539, 443, 273, 390, 210, 60549]]</t>
+    <t>[[12, 305, 56], [443, 1960, 459, 331], [67, 427, 117], [146, 391, 210, 378, 222, 389, 210], [485, 1582, 372], [183, 386, 486], [419, 478], [64]]</t>
   </si>
   <si>
     <t>perf_large_world_ws32_inbf16_outbf16_ID1037</t>
   </si>
   <si>
-    <t>[[386, 21134, 393, 289, 17776, 322, 270, 36, 394], [3127, 438, 381, 7518, 270, 98, 175, 273, 122, 206, 34, 158, 382, 282, 482, 45, 209, 6530, 9527, 500, 7600, 353], [357, 3153], [13, 261, 146, 140, 8759, 222, 28063, 285, 475, 9407, 370, 10309, 300, 159, 194, 459, 116, 374, 330, 21939, 110, 194, 2900, 400, 469, 68, 24], [274, 85, 175, 265, 132, 11, 285, 19505, 3989, 18, 120, 12093, 439, 245], [20, 30277, 13895, 1756, 233, 30561, 378, 199, 344, 354, 235, 67, 41, 511, 396, 37, 442, 402, 5826, 357, 179], [340, 213, 3222, 10152, 94, 453], [195, 148, 308, 437, 97, 207, 475, 11, 335, 18305, 331, 55, 4690, 14, 22459], [398, 175, 14818, 492, 32113, 411, 26, 28253, 229, 423, 2242, 28, 399, 405, 58, 134, 128, 437, 208, 27937, 367, 291, 496, 510], [41, 116, 25705, 138, 478, 293, 414, 257, 392, 20941], [29738, 264, 416, 303, 270, 211, 4046, 252], [460, 294, 19301], [5018], [65, 299, 276, 426, 184, 368, 7809, 14973, 11174, 374, 437, 11339, 166, 115, 332, 178, 320, 228, 379, 177], [380, 318, 100, 413, 111, 302, 371, 487, 179, 9199, 472, 310, 11, 13563, 450, 21183, 19456], [487, 323, 7, 202, 12, 6368, 21987, 16050, 344, 189, 401], [112, 255, 392, 121, 431, 12384, 64, 26635, 202, 4990, 145, 164], [422, 11098, 355, 255, 203], [151, 451, 313, 7090, 503, 222, 452, 228, 36, 140, 267, 5400, 5, 58, 113, 192, 335, 36, 32424, 228, 25449, 265, 352, 223, 17145, 12166, 104, 341], [390, 42, 6291, 239, 174, 346, 16491], [114, 32343, 254, 197, 242, 341, 191, 375, 158, 32, 417, 308, 14550, 31998, 292, 197, 14799, 368, 264], [168, 97, 7403, 139, 363, 128, 89, 31246, 67, 238, 275, 260, 315, 464, 274, 331, 326, 497, 219, 17431, 19374, 11, 7806], [17491, 282, 450, 462, 271, 369, 427, 18869, 8339, 499, 315, 316, 292, 285, 229, 458, 312, 23263, 271, 315, 130, 25511, 157, 179, 244], [114, 21611, 91, 433, 77, 511, 269, 7, 313, 21191, 68, 480, 14697, 4167, 13, 390, 263, 459, 148, 182, 29959, 7640, 234, 80, 236, 345], [487, 510, 260, 381, 42, 11285, 42, 278, 454, 7646, 312, 482, 121, 13289, 15671, 268], [74, 444, 3635, 0, 31348, 252, 4247, 501, 9, 192, 217, 398, 501, 184, 129, 23013, 17398, 5490, 413, 145, 109, 7, 57, 211, 8267, 279, 414, 225, 328, 488, 159], [142, 16, 11909, 485, 82, 405, 271, 212, 30608, 457, 216, 402, 13475, 229, 506, 366, 214, 108, 251, 457, 21056, 453, 26389, 170, 47, 270, 407, 15678, 116], [285, 184, 297, 154, 239, 509, 448, 457, 445, 502, 266, 364, 131, 103, 11127, 133, 3299, 253, 355, 23425, 271, 362, 13453, 209, 37, 323, 371, 14438, 6825, 324], [5372, 181, 181, 160, 16504, 276, 225, 507, 29662, 127, 245, 300, 478], [506, 207, 20968, 327, 71, 19632, 218, 107, 281, 29887, 345, 159, 72, 57, 424, 289, 308, 25570], [73, 31852, 357, 437], [135, 247, 241, 20, 6082, 7567, 110, 426, 275, 257, 465, 21, 492, 260, 330, 31464, 242, 437, 216, 18504, 12379, 28382, 110, 246, 7, 200, 18, 128, 22665, 421, 22, 425]]</t>
+    <t>[[426, 1066, 191, 443, 60, 116, 204, 741], [59, 213, 26, 367, 496, 149, 139, 472, 92, 137], [78, 219, 456, 165, 133], [338, 420, 259, 118, 314, 368, 117, 199, 499], [1587, 190], [62, 434, 1733, 108, 1652, 82, 457, 1199], [1008, 306, 209, 138, 368, 1920, 507, 229], [183, 464], [418, 146, 1319, 1865], [375, 156, 291, 1970, 200, 459, 1113, 358, 59, 276], [145, 199, 338, 190, 228], [499, 92, 439, 194, 366], [198, 473, 11, 1620, 109, 237, 84, 1351], [334, 336, 303, 461], [143, 295, 102], [263, 306], [500, 1150, 456, 8, 401, 157], [462, 185, 1513], [235, 156, 369, 246, 1880, 350, 138, 256], [1417, 38, 472], [438, 421, 134, 46, 155, 274, 291, 355, 94, 1193], [117, 248, 170, 198, 133, 180, 409, 346, 1407], [301, 172], [235, 271, 410, 1996, 65, 20, 486, 1076], [1311, 541, 314, 226, 186, 28, 429, 764, 414], [463, 497, 394, 405, 223, 178, 1], [382, 471, 378, 457], [74, 112, 313, 101, 1470, 399, 495, 200], [306, 282], [96, 2018, 1532, 199, 325, 308, 336, 62, 138], [158, 339, 438, 1852, 479], [188, 175, 433, 1127, 2001, 17, 214, 2, 91]]</t>
   </si>
   <si>
     <t>perf_large_world_ws64_inbf16_outbf16_ID1038</t>
   </si>
   <si>
-    <t>[[8219], [6, 27230], [368, 31868, 498], [315, 48, 14472, 421], [38915, 114, 214, 229, 251], [295, 62503, 36364, 478, 120, 51], [291, 477, 318, 101, 47553, 340, 26575], [465, 3195, 209, 281, 308, 293, 22454, 429], [28574, 434, 170, 339, 263, 18220, 106, 316, 321], [290, 37622, 5055, 119, 52, 288, 299, 413, 75, 255], [109, 372, 42304, 18479, 24, 75, 479, 326, 85, 416, 9603], [81, 54504, 24287, 297, 480, 154, 228, 226, 297, 311, 31518, 390], [329, 15292, 41260, 239, 162, 246, 19735, 254, 164, 173, 300, 251, 469], [310, 249, 101, 395, 368, 34, 283, 29124, 28950, 450, 38204, 193, 149, 245], [150, 316, 361, 186, 228, 319, 18252, 182, 162, 57166, 461, 282, 4695, 103, 37], [486, 460, 9560, 39586, 436, 263, 69, 234, 943, 329, 34, 464, 58829, 321, 486, 62], [26, 509, 318, 46341, 416, 47, 373, 486, 32450, 277, 204, 53, 12485, 428, 60106, 176, 226], [91, 20869, 377, 333, 245, 78, 184, 296, 28080, 20178, 389, 101, 470, 369, 39, 355, 427, 35135], [317, 12914, 487, 78, 13880, 443, 8, 8, 397, 335, 134, 175, 363, 9917, 256, 352, 56142, 165, 445], [248, 376, 64827, 489, 170, 41146, 107, 288, 117, 52198, 448, 239, 53856, 336, 361, 198, 493, 399, 380, 323], [478, 258, 444, 9272, 19595, 43190, 59699, 121, 347, 243, 228, 422, 490, 131, 403, 402, 408, 311, 376, 443, 49158], [478, 50, 58345, 143, 266, 11, 41, 188, 484, 33, 228, 163, 122, 1752, 14348, 512, 120, 512, 84, 50875, 37133, 254], [115, 235, 463, 292, 314, 11, 92, 470, 136, 45, 140, 503, 18563, 268, 302, 12942, 135, 435, 339, 0, 57397, 5269, 54932], [78, 115, 42, 33975, 35032, 386, 344, 398, 366, 75, 172, 182, 260, 273, 414, 408, 21482, 51234, 4636, 121, 256, 4, 485, 230], [88, 63, 134, 220, 70, 161, 336, 324, 163, 106, 13, 12618, 168, 187, 5980, 48916, 76, 60993, 437, 324, 466, 207, 397, 59297, 125], [373, 429, 194, 224, 229, 842, 45825, 254, 29197, 133, 19, 23974, 384, 87, 389, 187, 58302, 44, 67, 129, 13184, 371, 474, 446, 282, 476], [509, 233, 111, 150, 65, 61261, 16708, 43165, 306, 346, 342, 22, 390, 154, 483, 43364, 108, 28688, 71, 65, 33, 66, 212, 109, 141, 52266, 265], [291, 213, 459, 48791, 176, 511, 430, 161, 162, 387, 37, 396, 248, 353, 311, 55675, 45294, 39576, 395, 34, 444, 234, 4, 267, 62012, 56, 495, 57838], [3, 6, 307, 237, 441, 311, 357, 34568, 115, 49, 6178, 222, 37, 360, 429, 382, 409, 232, 16809, 42396, 254, 64398, 154, 197, 303, 243, 50, 359, 13779], [45231, 11407, 79, 86, 245, 221, 95, 242, 188, 184, 408, 452, 49, 358, 329, 441, 60989, 21779, 112, 20, 308, 255, 3205, 98, 52071, 224, 385, 279, 386, 184], [326, 172, 54492, 45, 312, 341, 424, 291, 34, 6, 36057, 15263, 401, 24392, 300, 162, 337, 61790, 450, 78, 35290, 210, 30, 124, 340, 421, 178, 51573, 116, 330, 429], [145, 2834, 28547, 168, 37402, 311, 165, 484, 237, 12732, 126, 30, 244, 142, 339, 260, 351, 156, 144, 18, 456, 265, 22764, 348, 60636, 385, 496, 161, 372, 220, 11872, 414], [339, 176, 472, 150, 174, 29, 54, 112, 53013, 32877, 349, 154, 1024, 424, 219, 471, 342, 414, 171, 60303, 44376, 239, 64, 127, 197, 5, 49409, 32, 218, 474, 107, 59751, 304], [355, 506, 297, 28982, 433, 39102, 59460, 250, 42265, 13876, 229, 201, 350, 410, 35483, 383, 190, 167, 411, 163, 138, 125, 251, 109, 282, 233, 40604, 205, 156, 249, 164, 232, 347, 487], [413, 129, 32559, 178, 410, 141, 48, 11028, 78, 279, 255, 93, 334, 11, 40, 433, 172, 60, 414, 2525, 82, 135, 325, 172, 155, 431, 69, 96, 23653, 256, 53793, 472, 24386, 41392, 245], [369, 313, 161, 473, 195, 427, 453, 264, 17860, 10, 337, 303, 165, 206, 12403, 14220, 61031, 425, 90, 7049, 61804, 32, 367, 54489, 488, 470, 44, 271, 384, 309, 156, 46528, 279, 425, 77, 328], [468, 154, 33827, 55222, 333, 65286, 315, 317, 138, 158, 413, 409, 278, 261, 63, 36901, 276, 310, 38, 76, 374, 160, 355, 125, 503, 290, 181, 80, 15013, 218, 343, 168, 69, 18515, 24606, 32687, 199], [45988, 1161, 111, 153, 207, 447, 31902, 394, 424, 167, 91, 191, 432, 380, 399, 245, 65, 133, 200, 320, 68, 164, 63248, 224, 79, 348, 31870, 78, 405, 19281, 373, 64, 247, 325, 6041, 27507, 463, 439], [398, 8401, 292, 69, 12962, 48999, 423, 162, 445, 238, 462, 126, 504, 275, 186, 436, 391, 64644, 35926, 33008, 419, 297, 484, 388, 364, 35569, 15, 139, 177, 229, 223, 61, 262, 474, 404, 115, 147, 328, 34364], [357, 438, 111, 254, 185, 9569, 371, 363, 463, 398, 97, 301, 436, 175, 351, 157, 466, 32087, 235, 420, 301, 17161, 31513, 262, 318, 504, 346, 38, 41687, 163, 252, 392, 160, 57236, 398, 55759, 58, 64149, 476, 24], [73, 26664, 463, 1947, 182, 357, 311, 369, 60179, 428, 118, 165, 345, 18, 42860, 392, 472, 151, 402, 12169, 301, 434, 38243, 82, 212, 179, 294, 215, 416, 28654, 30024, 211, 503, 51821, 14, 265, 152, 340, 168, 55, 308], [26817, 469, 115, 276, 53835, 221, 45, 476, 266, 48, 33824, 43609, 350, 486, 475, 332, 38, 40, 390, 43907, 476, 108, 23, 389, 108, 427, 314, 504, 254, 324, 398, 196, 296, 366, 2295, 29633, 10997, 221, 153, 326, 381, 55330], [43760, 327, 258, 63647, 485, 456, 213, 507, 247, 276, 17, 174, 21, 102, 57, 456, 183, 495, 102, 314, 380, 325, 393, 479, 390, 19169, 506, 444, 27898, 57602, 474, 62172, 64013, 137, 247, 182, 12170, 33574, 60, 355, 303, 253, 188], [335, 10136, 248, 4220, 329, 338, 461, 61901, 236, 473, 273, 390, 506, 489, 324, 274, 54779, 210, 61175, 20, 137, 489, 254, 454, 397, 113, 62575, 64272, 64625, 78, 258, 56, 56894, 137, 232, 141, 193, 161, 46, 401, 217, 320, 68, 465], [90, 272, 237, 493, 35746, 49926, 73, 140, 508, 12, 227, 397, 35374, 474, 283, 92, 97, 4797, 25016, 256, 345, 38837, 358, 226, 423, 488, 209, 361, 41, 79, 54435, 487, 59, 336, 40, 391, 21600, 13, 389, 154, 497, 400, 173, 37485, 317], [193, 300, 73, 436, 176, 184, 97, 277, 448, 197, 464, 100, 63, 363, 286, 495, 45045, 315, 140, 18691, 11426, 386, 320, 48092, 341, 49934, 39401, 60109, 313, 153, 445, 184, 442, 120, 246, 55488, 213, 12, 41, 214, 19652, 46, 270, 49938, 188, 501], [236, 1, 203, 35, 74, 295, 41858, 171, 289, 60908, 29867, 34766, 168, 86, 78, 221, 210, 15, 5343, 13, 207, 33, 25, 416, 418, 499, 38146, 506, 11639, 15057, 484, 497, 217, 101, 31112, 362, 59402, 132, 454, 312, 503, 184, 189, 152, 278, 380, 41], [49, 14, 420, 273, 430, 273, 61, 163, 11127, 218, 47245, 511, 459, 16156, 34996, 11783, 49139, 274, 34, 289, 284, 414, 61791, 337, 353, 507, 18533, 20592, 427, 493, 262, 333, 65, 498, 464, 23, 487, 227, 39597, 119, 408, 427, 278, 32, 277, 391, 234, 94], [138, 239, 48569, 433, 46, 177, 230, 0, 217, 12315, 280, 480, 260, 252, 83, 283, 57972, 42, 133, 21, 349, 218, 221, 396, 511, 76, 175, 38622, 63619, 331, 251, 177, 23430, 182, 58084, 15, 292, 336, 419, 60, 388, 508, 20333, 486, 60681, 421, 43, 456, 7299], [285, 305, 26546, 85, 314, 403, 344, 330, 2257, 25123, 159, 299, 348, 26777, 188, 416, 275, 129, 32458, 122, 32, 24, 320, 312, 171, 480, 49355, 396, 343, 39, 178, 422, 101, 227, 48629, 86, 148, 504, 445, 57504, 51, 42642, 383, 11, 242, 55, 41, 510, 46169, 120], [26910, 459, 58665, 89, 73, 299, 48, 132, 29, 362, 60631, 2, 72, 351, 11968, 24, 341, 409, 334, 251, 60097, 62012, 27, 267, 121, 102, 473, 495, 59, 21504, 471, 308, 48918, 131, 41811, 401, 234, 75, 34, 499, 432, 214, 95, 326, 12761, 111, 50188, 226, 357, 429, 280], [315, 29692, 208, 20, 17, 72, 224, 34201, 311, 347, 190, 346, 55075, 33199, 235, 63057, 292, 505, 263, 65, 280, 76, 283, 248, 40160, 303, 36, 37953, 290, 360, 474, 59469, 463, 414, 66, 38436, 6869, 508, 20286, 69, 88, 268, 430, 228, 465, 311, 6, 483, 153, 291, 246, 485], [308, 85, 94, 173, 454, 25, 458, 29550, 394, 40301, 1344, 472, 426, 121, 443, 174, 268, 441, 193, 19534, 503, 34247, 212, 425, 492, 418, 310, 229, 380, 159, 262, 364, 28554, 325, 262, 25166, 19, 233, 17600, 5331, 45529, 81, 149, 301, 511, 33301, 260, 30, 136, 438, 270, 430, 121], [504, 203, 164, 51248, 5717, 436, 24699, 120, 231, 273, 285, 483, 439, 34653, 64204, 187, 149, 460, 43925, 404, 60102, 464, 21726, 63304, 62, 136, 450, 265, 27178, 362, 421, 51, 121, 505, 367, 149, 135, 8, 163, 57850, 259, 236, 148, 36, 89, 318, 191, 510, 285, 413, 262, 218, 405, 173], [108, 272, 341, 371, 211, 149, 394, 48029, 435, 45841, 34, 46, 369, 510, 28800, 420, 26526, 53940, 406, 277, 37373, 27968, 229, 14, 43, 125, 127, 483, 179, 179, 9421, 421, 339, 54548, 140, 98, 163, 449, 218, 394, 15, 190, 251, 461, 302, 118, 58365, 96, 337, 63055, 173, 374, 147, 493, 104], [12, 233, 423, 244, 245, 449, 429, 440, 296, 266, 61, 332, 179, 410, 136, 363, 49825, 14596, 383, 67, 61472, 13867, 427, 60198, 8267, 482, 496, 28660, 356, 283, 153, 191, 414, 242, 146, 86, 28, 336, 353, 381, 7056, 242, 71, 69, 56413, 442, 387, 161, 497, 237, 65, 211, 472, 51788, 63546, 49900], [372, 217, 263, 409, 415, 19082, 507, 259, 235, 9553, 284, 625, 34, 204, 393, 81, 81, 62321, 375, 39983, 263, 54, 63675, 289, 239, 214, 62, 5, 44, 264, 4581, 118, 45, 12074, 53302, 164, 170, 457, 300, 273, 276, 500, 406, 439, 71, 209, 12, 298, 45713, 280, 270, 228, 12, 5478, 500, 10675, 493], [164, 202, 446, 417, 284, 55, 216, 133, 322, 25844, 387, 476, 502, 484, 111, 25245, 10, 21819, 218, 486, 155, 400, 447, 15, 37348, 72, 5540, 470, 404, 88, 408, 390, 320, 432, 354, 436, 282, 43222, 0, 391, 51850, 66, 47063, 373, 12344, 96, 16295, 218, 81, 205, 44315, 65, 381, 12842, 322, 108, 344, 327], [216, 250, 128, 317, 128, 481, 38781, 165, 214, 382, 236, 428, 266, 383, 259, 95, 418, 179, 164, 293, 37886, 418, 50, 16608, 57855, 170, 42788, 3659, 33, 11821, 224, 279, 29695, 143, 33674, 2249, 138, 342, 202, 15, 211, 329, 310, 346, 75, 487, 393, 467, 0, 326, 53088, 506, 287, 480, 272, 119, 259, 459, 11750], [47751, 213, 17355, 174, 285, 459, 358, 374, 430, 264, 279, 57719, 295, 204, 183, 21467, 140, 49, 466, 301, 338, 46, 226, 55761, 65, 81, 448, 276, 0, 202, 73, 340, 90, 325, 496, 57284, 65, 459, 455, 67, 53414, 402, 208, 231, 119, 40966, 242, 19021, 344, 17181, 75, 225, 26752, 136, 191, 34286, 414, 470, 257, 110], [348, 275, 61, 4597, 124, 21217, 489, 235, 192, 37219, 48746, 90, 27776, 64501, 165, 35426, 63368, 38, 19, 511, 85, 18, 235, 266, 273, 440, 258, 248, 485, 198, 140, 1064, 348, 3, 328, 494, 229, 366, 358, 51210, 58563, 291, 203, 432, 466, 234, 30726, 40, 274, 411, 264, 467, 305, 488, 468, 103, 434, 487, 40934, 512, 393], [52, 48, 51274, 137, 301, 308, 213, 331, 87, 53128, 456, 25702, 26092, 229, 501, 31373, 495, 14, 39572, 59, 167, 379, 326, 478, 80, 63456, 26490, 333, 359, 436, 284, 470, 257, 59720, 459, 7233, 140, 54381, 10, 182, 351, 87, 64283, 75, 368, 139, 177, 76, 469, 77, 15, 4035, 326, 265, 351, 2, 95, 274, 316, 431, 2, 165], [140, 65460, 277, 283, 419, 77, 186, 24145, 330, 12, 51112, 98, 96, 31599, 9, 335, 92, 367, 470, 248, 256, 115, 59253, 503, 328, 8782, 15, 45, 83, 393, 193, 419, 470, 299, 171, 8850, 32136, 213, 176, 255, 7524, 78, 167, 239, 59785, 45, 69, 200, 26842, 32, 41721, 130, 167, 13, 341, 9152, 348, 418, 236, 77, 245, 77, 100], [131, 204, 490, 130, 401, 500, 329, 54824, 148, 55034, 319, 19, 47, 101, 109, 208, 239, 31441, 46629, 45, 371, 79, 355, 374, 279, 331, 281, 243, 424, 431, 45196, 108, 210, 83, 112, 606, 165, 299, 111, 6145, 265, 397, 59157, 438, 29, 66, 269, 440, 419, 27547, 53547, 1443, 333, 44, 85, 110, 102, 166, 144, 33, 31983, 132, 464, 56867]]</t>
+    <t>[[298, 329], [116, 233, 98, 426, 1878, 1467], [52, 464, 489, 1464, 277, 159, 21, 128, 399], [255, 81, 61, 73, 897, 250, 1805, 313], [91, 437, 320, 49, 430, 263, 456, 344], [431, 125, 336, 120, 357, 368, 163, 383, 352], [330, 416, 402], [31, 23, 31, 1936, 481], [448, 240, 239, 265, 476, 455, 66, 428, 286], [22, 142, 4, 340, 249, 222], [162, 190, 1385, 174, 72, 901, 172, 251, 237, 228], [456, 339, 382], [490, 319, 1107, 316, 269, 339], [174, 71, 256], [462, 357, 444, 125, 342, 304, 348, 49], [334, 1868, 460, 1414, 425, 987, 41], [344, 293], [295, 1075, 284, 485, 6, 310, 194], [65, 428, 327, 440, 19, 326, 1009, 673, 435, 758], [285, 22, 198, 74, 70, 331, 488, 191, 840, 199], [1852, 348], [189, 325, 333, 1799], [436, 407, 27], [274, 116, 250, 535, 1626, 195, 85, 330], [196, 293, 338, 2048], [119, 248, 269, 28, 312, 319, 308, 442, 429], [480, 344, 382, 392, 112, 231, 1308], [1808, 503, 211, 329, 432, 48, 244], [430], [177, 281, 381, 4, 222, 12, 411, 130], [147, 213], [300, 580, 255, 497, 445, 77, 255, 266, 1242, 286], [14, 307, 18], [1275], [107, 449, 434, 478, 178, 287], [466, 69, 210, 214, 469, 1381, 273], [147, 317, 216, 238, 146, 439, 715, 409], [372, 1379, 1888], [350, 414, 508, 357, 254, 224, 1332, 182, 99], [1444, 82, 508, 154, 1731, 497], [121, 322, 475], [72, 1098, 327, 498, 317, 356], [236, 246, 10, 192], [252, 26, 322, 520, 419, 213, 885, 141, 1357, 239], [397, 504, 178, 372, 1426, 265, 66, 332, 1379], [483, 415, 361, 461, 345, 1652, 288, 5, 468], [72, 364, 58, 213, 19, 24, 260], [433, 1871, 220, 458, 834, 388, 416], [401, 416, 816, 97, 375, 299, 29, 396, 175], [394, 12, 471, 143, 432, 197, 257, 54], [410], [211, 230, 382, 171, 253, 1897], [481, 1512, 835, 58, 1053, 251, 49], [57, 447, 1487, 66, 120], [921, 71], [474], [31, 946, 276, 374, 356, 392, 199], [283, 389, 1977, 318], [403], [23, 471, 242, 277, 379], [312, 254, 1542, 1681, 408, 81, 496, 55, 230, 379], [406, 169, 1284], [175, 341, 1694, 410, 417, 941], [494, 420, 1061, 132, 360, 317, 1965, 444]]</t>
   </si>
   <si>
     <t>perf_large_world_ws32_inbf16_outbf16_ID1039</t>
   </si>
   <si>
-    <t>[[177, 310, 9, 429, 11677, 312, 113, 467, 19712, 437, 25282, 18095, 509, 200, 325, 8770, 235, 166, 31313, 98, 25053, 40, 296, 322, 170, 292, 490, 211, 117, 500, 155], [179, 199, 22222, 162, 101, 281, 32612, 416, 9800, 366, 260, 466, 288, 31075, 37, 203, 472, 111, 288, 23135, 479, 460, 36, 97, 393], [27023, 352, 167, 242, 279, 26142, 474, 511, 13896, 6346, 24506, 255, 496, 315, 334, 468, 366, 311, 464, 296, 137], [7526, 25365, 261, 455, 9, 15898, 163, 201, 107, 433, 12, 16, 30116, 219, 282, 1, 471, 471], [5617], [94, 166, 20102, 431, 314, 287, 27452, 266, 479, 20844, 501, 482], [393, 2781, 439, 14348, 344, 79], [3008, 491, 131, 201, 27960, 499, 63, 9847, 201, 47, 376, 118, 101, 7984, 31, 80, 399, 136, 448], [233, 20221, 278, 182, 32, 16964, 115], [12383, 420, 92, 40, 9017, 402, 171, 238, 346, 3454, 335, 67, 413, 44], [214, 60, 17619, 5140, 482, 31443, 3770, 394, 367, 415, 25, 187, 410, 480, 70, 201, 117], [136, 180, 29429, 293], [180, 78, 135, 9824, 314, 371, 7845, 88, 472, 351, 18294, 180, 248, 125, 49, 23234, 8681, 473, 509, 6, 102, 19091, 438, 79, 281, 366, 255, 443, 11, 293], [179, 375, 127, 161, 9904, 5587, 102, 399, 240, 7, 370, 379, 292, 14872, 408, 466, 229, 271, 156, 459, 500, 12307, 375, 14456], [355, 322, 362, 337, 314, 23525, 228, 435, 14519, 156, 31, 146, 28, 734, 14940, 20, 277, 351, 414, 131], [26, 297, 232, 10, 32227, 77, 26535, 217, 477, 306, 25752, 127, 304], [420, 109, 12929, 291, 7156, 317, 109, 379, 427, 502, 159, 110, 348, 6295, 459, 14576, 5837, 414, 243, 272, 384, 251, 496], [451, 37, 6, 458, 4321, 21611, 21387, 66, 69, 316, 441], [21493, 336, 8130, 47, 92, 317, 78, 407, 349, 75, 289, 295, 500, 489, 12971, 299, 1072, 257, 500, 3436, 29388, 387, 24, 41, 164, 189], [31230, 493], [353, 66, 108, 412, 422, 273, 7672, 26932, 324, 187, 4772, 489, 32745, 453, 84, 82], [33, 410, 30811, 202, 427], [28305, 41, 365], [347, 288, 47, 1510, 467, 34, 12746, 361, 460, 280, 453, 503, 26384, 22649, 488, 9, 226, 425, 347, 45, 444, 23276], [397, 304, 5, 24714, 82, 49, 14528, 384, 47, 370, 120, 14592, 245, 495, 31575, 1307, 140, 202, 14, 374, 32, 499, 9804, 357, 58, 34, 149, 191], [109, 144, 348, 864, 14107, 42, 16267, 432, 31517, 282, 23208, 449, 245, 252, 8439, 148, 370, 106, 193, 331, 492, 445, 279, 459, 342, 172, 314], [479, 267, 4819, 8468, 505, 147, 244, 236, 1023, 210, 4, 18, 205, 252, 15], [323, 131, 231, 387, 415, 26409, 170, 495, 16909], [477, 5, 32230, 365, 84, 12980, 182, 432, 355, 306, 432, 2135, 151, 215, 483, 478, 111, 12190, 433, 143, 405, 18068, 423, 422, 353, 503, 203, 32745, 371], [198, 13877, 181, 339, 403, 11406, 117, 283, 410, 314], [504, 12381, 362, 357, 109, 65, 41, 19170], [177, 153, 44, 297, 26160, 104, 8296, 100, 8876, 339, 1831, 144, 373, 405, 106, 12553, 17190, 135, 444, 446, 115, 9686, 300, 149, 418, 364, 312, 39, 507, 418, 263, 180]]</t>
+    <t>[[102, 263, 253, 495, 478, 15, 482, 481], [221, 287, 145, 97, 332, 371, 1304, 356], [36, 249, 442], [422, 460, 387, 52, 368, 941, 431, 1191, 441], [90, 479, 195], [392, 162, 333, 1207, 367], [437], [66], [473, 270, 39, 12, 1062, 266, 556], [479, 259, 173, 354, 428, 314, 78, 3, 217], [86, 131, 468, 182, 1552, 101, 174, 468, 369], [270, 150, 1735, 289], [244, 130, 1159, 315, 387, 327, 506, 207, 506], [120, 252, 305, 186, 372, 167, 12, 62, 45], [841, 62, 813, 488, 319, 151, 73, 270, 693], [161, 381, 45, 427, 184], [244, 12, 274, 374, 204, 1538, 273, 435, 14, 403], [238, 13, 248, 71, 198, 1517], [90, 489], [174, 450, 146, 392, 467, 8, 288], [1691, 250, 152, 681, 1863, 240, 316, 39, 389], [26, 301, 496, 355, 105, 86, 263, 1888, 224, 396], [13, 6, 33, 428], [1633, 195], [460, 1602, 39, 114, 194], [5, 299, 59, 157, 586], [257], [1084, 342], [8, 162, 895, 1539, 416, 1857, 85, 163, 443, 1130], [62, 495, 738, 198, 144, 770, 62, 1318, 234, 106], [162, 62, 357, 46, 436, 957, 439, 278, 80, 374], [317, 117, 377, 471, 459, 99]]</t>
   </si>
   <si>
     <t>perf_large_world_ws64_inbf16_outbf16_ID1040</t>
   </si>
   <si>
-    <t>[[55795], [69, 30544], [155, 45881, 436], [263, 336, 422, 33241], [411, 409, 66, 28129, 221], [100, 53367, 359, 15327, 99, 231], [111, 19, 63, 10975, 41359, 506, 179], [391, 27247, 374, 132, 462, 718, 118, 463], [120, 34444, 495, 11819, 113, 140, 120, 254, 497], [40, 7844, 69, 423, 167, 22606, 74, 444, 449, 31], [393, 355, 24230, 423, 276, 24080, 430, 112, 277, 438, 30011], [13575, 26, 270, 475, 503, 46, 502, 240, 16494, 20742, 446, 73], [419, 213, 236, 1371, 259, 128, 17498, 446, 166, 3, 59899, 475, 183], [461, 446, 100, 17, 43, 42483, 63482, 54, 392, 346, 42562, 115, 179, 19], [55055, 167, 406, 255, 77, 71, 440, 132, 7789, 500, 2450, 120, 21, 393, 181], [276, 97, 376, 35, 11046, 32923, 122, 282, 382, 6477, 109, 362, 403, 18064, 50, 262], [287, 39365, 38692, 272, 37770, 294, 510, 349, 29125, 37, 257, 303, 29, 32, 205, 462, 227], [499, 250, 48, 183, 171, 159, 15361, 465, 61052, 2412, 442, 178, 374, 156, 121, 267, 64667, 188], [153, 211, 136, 154, 23309, 237, 411, 36, 151, 4960, 240, 334, 2816, 328, 67, 180, 42437, 94, 332], [251, 343, 305, 303, 29281, 31464, 61490, 69, 9766, 410, 178, 512, 166, 117, 118, 158, 277, 255, 491, 310], [140, 50822, 118, 259, 302, 221, 426, 122, 417, 298, 441, 68, 59031, 48892, 63, 508, 61762, 341, 8027, 299, 394], [26622, 102, 420, 201, 471, 189, 6513, 108, 34440, 404, 215, 33512, 300, 272, 390, 390, 185, 282, 452, 196, 56679, 301], [55, 247, 124, 185, 23, 60567, 214, 23, 377, 373, 10290, 316, 291, 3038, 1, 13, 41927, 129, 395, 52993, 249, 8, 349], [331, 107, 266, 46, 299, 31476, 473, 113, 25595, 15759, 241, 377, 221, 63, 254, 6, 19944, 156, 441, 9, 440, 64170, 247, 302], [16, 270, 463, 156, 346, 97, 46, 14, 46916, 13, 111, 213, 41875, 436, 19534, 359, 35, 479, 59210, 146, 15810, 53, 312, 28, 29], [59758, 60, 12328, 4520, 260, 204, 438, 56, 3, 84, 272, 19093, 248, 222, 490, 52411, 59, 252, 75, 137, 188, 33, 51256, 471, 379, 92], [157, 482, 506, 53475, 44983, 386, 255, 497, 290, 144, 270, 202, 98, 1, 37, 128, 29, 59373, 43483, 90, 88, 488, 271, 4, 80, 41068, 15265], [436, 50, 51900, 9, 54, 19944, 418, 19, 479, 441, 479, 5411, 39768, 199, 194, 424, 429, 97, 131, 59, 175, 80, 63137, 13, 250, 201, 41514, 35], [158, 21, 322, 268, 396, 352, 249, 18740, 213, 80, 360, 49633, 10611, 408, 10955, 58730, 322, 443, 51, 419, 446, 185, 467, 357, 91, 370, 49324, 377, 427], [413, 283, 682, 181, 151, 37178, 272, 5364, 316, 144, 140, 384, 416, 119, 91, 11737, 8114, 20446, 307, 379, 388, 479, 29, 185, 235, 119, 184, 210, 330, 42], [492, 343, 350, 61, 4523, 377, 332, 395, 369, 43, 27233, 54, 432, 218, 5, 147, 180, 315, 67, 13, 41197, 335, 467, 28830, 93, 12582, 24073, 406, 91, 101, 64129], [109, 7173, 60932, 271, 455, 399, 2420, 412, 15313, 284, 62861, 398, 208, 140, 171, 61254, 52, 23, 439, 412, 420, 500, 159, 424, 90, 130, 443, 359, 128, 293, 58345, 20], [361, 24722, 145, 207, 8332, 21615, 320, 468, 245, 147, 332, 6784, 43, 37, 323, 5, 10860, 461, 491, 433, 267, 37, 451, 33077, 100, 445, 459, 54, 220, 55802, 263, 58, 273], [57504, 40, 246, 406, 56, 8115, 184, 32917, 231, 351, 66, 238, 478, 389, 206, 379, 134, 4122, 120, 41, 88, 190, 11438, 452, 365, 361, 507, 459, 137, 461, 484, 15, 625, 9016], [299, 2, 25805, 363, 496, 508, 235, 5296, 60, 323, 176, 285, 48305, 13, 18638, 425, 489, 495, 448, 113, 196, 357, 67, 203, 87, 63776, 69, 15, 468, 143, 33877, 113, 394, 41, 19500], [491, 318, 392, 278, 61045, 225, 193, 262, 467, 403, 213, 508, 221, 120, 423, 4, 37543, 337, 275, 320, 1439, 450, 134, 282, 24341, 52067, 110, 342, 23, 65, 64023, 90, 280, 695, 65, 2698], [437, 40, 50790, 442, 26804, 353, 409, 314, 310, 6, 216, 274, 23530, 24970, 153, 371, 405, 207, 110, 196, 115, 36253, 112, 420, 292, 431, 388, 470, 83, 64116, 238, 28161, 8305, 162, 232, 396, 70], [417, 12720, 144, 29399, 80, 371, 241, 288, 60, 389, 353, 20, 489, 108, 37465, 19, 19693, 478, 51275, 117, 483, 51839, 207, 67, 49428, 381, 206, 100, 213, 220, 3882, 290, 107, 270, 372, 380, 37, 4], [234, 19721, 17691, 497, 22, 274, 376, 3870, 492, 302, 218, 233, 15, 33935, 323, 17276, 310, 255, 335, 327, 507, 200, 53272, 312, 272, 40, 3866, 126, 304, 20, 156, 32876, 173, 382, 200, 401, 184, 281, 202], [330, 94, 475, 159, 93, 490, 165, 343, 332, 366, 224, 18, 117, 63417, 302, 39, 43072, 353, 434, 370, 28001, 466, 26, 37, 326, 226, 375, 417, 436, 11715, 409, 4480, 423, 30863, 35763, 176, 111, 389, 42271, 327], [235, 106, 52323, 443, 55075, 226, 421, 55935, 107, 451, 435, 491, 327, 27, 262, 227, 29805, 172, 13230, 94, 406, 46, 498, 1761, 324, 195, 49681, 213, 114, 6, 483, 31185, 195, 233, 276, 290, 476, 121, 120, 187, 1478], [170, 350, 40212, 414, 198, 252, 3462, 457, 13, 45572, 481, 37, 477, 155, 278, 282, 168, 258, 430, 57, 495, 108, 440, 26367, 360, 205, 305, 35407, 50, 59, 483, 4, 432, 16, 53272, 181, 58419, 215, 496, 34541, 63369, 338], [131, 65, 218, 172, 199, 449, 458, 73, 181, 59653, 305, 40212, 43264, 55, 185, 332, 64, 442, 369, 58, 509, 223, 57128, 158, 472, 13823, 269, 34233, 378, 123, 144, 175, 15, 45995, 7, 16689, 250, 505, 33737, 152, 272, 52, 70], [491, 333, 55, 289, 397, 247, 323, 76, 44363, 55864, 309, 104, 61, 14607, 163, 503, 273, 302, 94, 359, 291, 61893, 14950, 13695, 47, 459, 199, 211, 468, 14482, 170, 257, 501, 27078, 50182, 162, 7, 338, 7, 8, 422, 278, 331, 365], [386, 339, 2055, 127, 25, 37650, 5983, 301, 483, 254, 447, 116, 3, 96, 441, 37954, 451, 318, 11164, 103, 17547, 362, 432, 328, 37, 74, 28, 487, 501, 350, 442, 231, 297, 209, 428, 12, 272, 57332, 379, 181, 54350, 62549, 254, 189, 34], [1343, 325, 333, 439, 122, 131, 158, 155, 43161, 436, 257, 391, 65362, 348, 15823, 260, 430, 28889, 452, 8, 63513, 443, 507, 485, 419, 280, 441, 404, 34, 269, 312, 178, 5197, 126, 442, 151, 64129, 211, 77, 379, 93, 43988, 247, 9902, 301, 229], [401, 200, 772, 7, 59, 1918, 406, 47713, 483, 36586, 282, 34719, 172, 248, 412, 121, 14, 262, 446, 52491, 402, 41, 391, 319, 289, 42333, 38, 226, 208, 257, 379, 258, 155, 232, 21068, 323, 225, 48873, 428, 90, 62845, 174, 414, 119, 321, 314, 259], [448, 383, 145, 10633, 306, 228, 119, 432, 446, 213, 183, 410, 66, 365, 192, 50077, 43130, 387, 467, 278, 293, 475, 50170, 49285, 463, 43, 20324, 14396, 59322, 449, 40309, 343, 124, 41, 27553, 431, 108, 353, 334, 343, 349, 89, 22, 341, 249, 134, 201, 87], [455, 567, 36, 301, 312, 14375, 142, 31, 450, 56581, 44, 119, 259, 153, 435, 163, 267, 33, 35, 18703, 221, 94, 38, 51462, 170, 275, 15883, 24, 298, 324, 510, 56, 496, 25863, 83, 325, 232, 201, 288, 48521, 397, 313, 31604, 235, 331, 430, 8256, 300, 120], [304, 461, 400, 99, 218, 290, 6180, 37897, 24, 115, 117, 50909, 126, 2, 295, 26861, 60525, 473, 20582, 154, 485, 283, 52, 270, 232, 478, 18059, 398, 121, 463, 212, 460, 231, 4076, 389, 160, 280, 464, 32, 268, 430, 367, 25648, 77, 108, 159, 260, 109, 61598, 381], [510, 437, 308, 427, 468, 376, 32746, 465, 11793, 187, 10172, 503, 286, 144, 24, 315, 3, 775, 269, 343, 104, 396, 24714, 455, 46, 239, 320, 501, 58075, 195, 52, 427, 433, 219, 60545, 298, 147, 325, 75, 402, 36778, 246, 270, 204, 305, 302, 101, 106, 46820, 14586, 63794], [379, 100, 11, 55526, 269, 330, 468, 13387, 385, 4050, 347, 274, 143, 315, 384, 103, 432, 13909, 261, 47, 85, 125, 149, 431, 138, 60990, 443, 29, 139, 178, 505, 79, 459, 40, 130, 38726, 182, 43, 37, 44920, 5993, 157, 59244, 431, 124, 32595, 58741, 210, 437, 501, 108, 458], [4, 237, 34788, 433, 281, 59783, 476, 0, 274, 19903, 158, 295, 456, 474, 201, 24, 50, 414, 201, 62126, 450, 146, 187, 46, 102, 278, 55347, 498, 273, 174, 38196, 33, 29, 137, 244, 242, 511, 214, 251, 152, 446, 30403, 279, 45228, 116, 9783, 62521, 32003, 91, 319, 62, 172, 105], [238, 322, 243, 6031, 203, 207, 168, 316, 241, 93, 132, 405, 180, 391, 183, 413, 215, 55628, 17300, 304, 42, 183, 30988, 114, 472, 476, 59, 60, 191, 427, 61278, 24327, 50521, 357, 205, 176, 487, 362, 360, 308, 46751, 32, 38768, 220, 5, 260, 15637, 102, 437, 15, 356, 249, 49220, 185], [25359, 512, 117, 133, 383, 52585, 124, 388, 329, 276, 3789, 98, 258, 5119, 298, 58390, 52432, 120, 452, 279, 21, 74, 237, 191, 367, 8536, 255, 46499, 308, 432, 7119, 72, 427, 485, 387, 318, 119, 146, 345, 362, 512, 62498, 34, 273, 73, 488, 1470, 484, 227, 41, 449, 260, 162, 233, 151], [150, 94, 107, 103, 301, 439, 8, 21675, 263, 127, 323, 46170, 102, 21, 56, 40, 486, 29, 75, 176, 79, 65535, 3534, 100, 220, 386, 2190, 59229, 43, 325, 23396, 383, 151, 307, 288, 41, 5500, 58, 187, 7906, 276, 192, 45465, 305, 0, 57560, 384, 219, 449, 33702, 124, 13, 345, 267, 442, 153], [112, 207, 381, 7822, 268, 118, 4441, 37, 45477, 143, 25972, 113, 472, 428, 221, 174, 173, 464, 471, 251, 46, 106, 357, 11, 409, 3363, 495, 44224, 165, 298, 311, 356, 26, 492, 59, 283, 68, 109, 385, 50088, 19067, 73, 117, 280, 89, 407, 176, 11817, 80, 64681, 13173, 197, 405, 17909, 185, 452, 407], [73, 35979, 35, 505, 203, 285, 111, 292, 7016, 408, 510, 397, 470, 155, 123, 221, 10650, 60059, 414, 138, 37, 13097, 17405, 10, 235, 192, 132, 69, 80, 80, 11674, 112, 176, 350, 414, 399, 38, 354, 510, 49285, 64984, 35444, 184, 82, 440, 348, 448, 236, 255, 197, 414, 9695, 49326, 51, 152, 29, 243, 224], [346, 235, 303, 67, 199, 9321, 9654, 158, 315, 45047, 212, 277, 151, 128, 314, 161, 231, 456, 281, 319, 361, 449, 465, 195, 110, 132, 42978, 85, 245, 381, 218, 15982, 348, 135, 419, 34618, 56793, 61, 230, 21342, 52859, 486, 60330, 352, 471, 382, 506, 49, 244, 8963, 30, 34, 29204, 176, 413, 315, 184, 192, 362], [36, 54923, 160, 451, 50300, 505, 159, 171, 238, 108, 376, 446, 223, 278, 62, 453, 262, 148, 462, 441, 340, 65516, 52755, 59352, 168, 475, 45447, 361, 3441, 116, 432, 196, 132, 103, 44304, 238, 376, 445, 65, 382, 117, 250, 504, 371, 501, 47736, 144, 115, 39342, 312, 275, 76, 7, 491, 265, 18150, 292, 7459, 351, 92], [241, 52021, 342, 111, 325, 235, 90, 328, 423, 448, 37111, 418, 8532, 32, 40464, 322, 290, 330, 411, 34652, 43851, 301, 268, 452, 190, 67, 311, 61497, 306, 323, 11, 229, 460, 485, 283, 40789, 329, 429, 301, 423, 2484, 362, 144, 249, 254, 219, 196, 6, 53401, 387, 25, 12552, 8, 903, 23989, 288, 384, 101, 391, 363, 9], [392, 11230, 270, 1, 102, 203, 205, 401, 16313, 10140, 310, 384, 88, 51, 60, 225, 352, 42, 82, 7237, 43, 39746, 393, 42, 465, 434, 458, 428, 367, 267, 138, 297, 482, 63, 222, 458, 363, 256, 493, 179, 116, 227, 257, 445, 53556, 17205, 55, 158, 171, 120, 208, 8360, 57, 455, 34, 30699, 39043, 495, 154, 19748, 18596, 578], [98, 195, 331, 243, 144, 412, 451, 391, 365, 501, 39489, 15645, 318, 59159, 395, 155, 348, 43545, 270, 167, 408, 264, 255, 501, 230, 156, 1261, 275, 121, 35, 63138, 114, 42707, 452, 73, 91, 49, 470, 415, 221, 463, 176, 278, 427, 2960, 38045, 420, 123, 397, 311, 122, 206, 51, 203, 12616, 44435, 431, 93, 9996, 392, 85, 55866, 135], [19, 460, 153, 39920, 281, 340, 481, 489, 8537, 465, 378, 52024, 5, 15, 166, 359, 347, 18, 283, 43221, 131, 313, 18505, 488, 333, 137, 170, 467, 7, 432, 147, 10247, 223, 127, 58, 282, 147, 22, 306, 256, 45361, 205, 353, 151, 300, 319, 164, 48949, 15853, 16485, 338, 439, 64402, 260, 56361, 132, 257, 407, 294, 74, 39344, 207, 238, 175]]</t>
+    <t>[[270, 57, 236, 1651, 193, 234, 71, 86, 337], [346, 374, 109, 318, 340, 295, 96, 228, 470], [870, 415, 180, 452, 51, 1647, 291, 15], [206, 280, 415, 172, 31, 261, 109, 413, 296, 1269], [382, 879, 1786, 366, 738, 308, 474], [459, 1234, 369, 2031, 334], [214, 1107], [460, 207], [460, 508, 1695, 242, 405, 495, 102, 306, 192, 232], [339, 426, 252, 321, 1828, 365], [43, 481, 249, 14, 336, 453, 46], [492, 422, 206], [270, 109, 528, 302, 94, 291, 292], [421, 311], [439, 198, 1788, 34], [1154, 245, 17, 198, 6, 413, 349, 246, 335], [1970, 227, 501, 463], [101, 334, 929, 384, 787, 381], [149, 212, 278, 478, 318, 890, 291, 178, 475, 289], [423, 52, 58, 396, 670, 178], [583, 328], [94, 188, 285, 48, 50, 242, 398, 190, 197], [36, 738, 494, 66, 2, 59], [2, 165, 1727], [109, 181, 254, 36, 1437, 451, 1664, 315, 120, 330], [1672, 48, 532], [435, 50, 505, 442, 333, 414, 236, 916, 419, 348], [78, 81, 437, 163, 140, 436, 56, 68, 270], [77, 690, 196, 145, 476, 60], [290, 123], [246, 184, 475, 57, 232], [204, 31, 145, 199, 135, 466, 334, 504], [12, 118], [37, 469, 468, 286, 787], [2, 306, 469, 14, 348, 156, 949, 59, 253, 123], [259, 147, 334, 142], [388, 407, 228, 51, 131], [58, 78, 1396, 482], [276], [116, 1832, 332, 444, 151, 364, 487], [247, 192, 345, 187, 163], [437, 212], [465, 531, 2016, 398, 488, 498, 19, 173, 335, 10], [44, 39, 92, 315, 109, 726], [423, 154, 380, 378, 358, 450], [44, 401, 221, 326, 396, 344, 506], [415, 127, 991, 450], [260, 84, 1294], [143, 107, 5, 1523, 341], [384, 1668, 305, 201], [434, 298, 97, 909, 258, 260], [1694, 251], [217, 1094, 184, 191, 501, 122], [66, 318, 65], [197, 107, 600, 344], [159, 303, 342, 6, 79], [122, 1664, 631, 225], [79, 103, 290, 121, 398, 220, 74, 168, 116, 993], [416, 331, 357, 349, 470, 586, 11], [393, 105, 509, 402, 397, 1432], [312, 323, 319, 1881, 349], [391], [411], [457]]</t>
   </si>
   <si>
     <t>perf_large_world_ws32_infp16_outfp16_ID1041</t>
   </si>
   <si>
-    <t>[[255, 7335, 262, 635, 326, 486, 8094, 144, 241, 485, 308, 27520, 42, 185, 320, 240, 299, 337], [21932, 244, 312, 6670, 11, 150, 82, 10968, 180, 452, 346], [490, 149, 1825, 5, 53, 496, 1403], [304, 149, 10317, 132, 312, 127, 263, 27149, 433, 21792, 456, 503, 141, 91, 398, 312, 125, 29195, 341, 326, 379, 559], [214, 418, 7, 15904, 76, 14632, 444, 61, 27786, 23248, 366, 358, 36, 249, 249, 94, 180], [35, 26, 116, 2, 366, 148, 431, 33, 21474, 288, 26476, 475, 490, 429, 37, 528, 22638, 1837, 125, 372, 507, 121, 319, 375], [132, 287, 18036, 377, 198, 467, 287, 352, 207, 21802, 28, 483, 21129, 93, 324, 452, 236, 412, 11981, 118, 20429, 298, 397, 60, 8554, 449], [1246, 8, 76, 208, 469, 32608, 392, 465, 118, 30, 219, 17667, 7818, 280, 60, 505, 264, 352, 24, 31261, 245, 23654, 5480, 430, 474, 459, 435, 363, 6, 239, 418], [329, 76, 301, 321, 68, 11677, 70, 503, 307, 89, 11920, 507, 337, 442, 411, 43, 14678, 23096, 327, 8371, 355], [44, 18038, 143], [15315], [227, 497, 277, 169, 48, 30997, 84, 330, 353, 365, 428, 424, 270, 393, 16437, 60, 336, 10280, 19903, 251, 432, 193, 82, 24598, 25344, 186, 388, 137], [127, 489, 160, 163, 3110, 371, 10825, 260, 4077, 128, 336, 452, 192, 370, 388], [299, 444, 201, 161, 24494, 3889, 147, 372, 20561, 507, 481, 252], [112, 221, 488, 436, 302, 338, 13300, 206, 445, 23057, 260, 483, 138, 279, 1021, 22487], [47, 30096, 396, 105, 278, 439, 423, 153, 28454, 118, 282, 264, 31747, 323, 20758, 21, 145, 334, 26, 208, 55, 132, 263, 8862, 241], [385, 430, 25645, 182, 92, 84, 20578, 366, 116, 341, 406, 249, 2022], [303, 180, 253, 83, 161, 135, 957, 109, 236, 25174, 83, 476, 498, 311, 22656, 491, 29076, 362, 180, 85, 10294, 111, 92, 29, 350, 64, 27688, 56, 266, 487], [12679, 5, 293, 236, 10, 328, 13867, 419, 450], [3860, 8], [23751, 176, 451, 2118, 457, 43, 439, 182], [8585, 279, 271, 395, 134, 101, 305, 207, 250, 31149, 245, 351, 336, 40, 38, 10, 170, 332, 92, 14698, 1264, 39, 431, 247, 65, 79, 28, 25207, 24366], [128, 107, 54, 448, 482, 25753, 220, 107, 258, 16284, 323, 250, 7347, 13806, 475, 359, 121, 9419, 295, 165, 28327, 201, 396, 78, 431, 284, 216], [187, 13458, 262, 460, 352], [229, 6511, 311, 12517, 73, 337, 421, 249, 3, 24490, 348, 40, 373, 11, 50, 76, 294, 472, 501, 370, 205, 69, 11374, 51, 195, 22230, 68, 25911, 102, 6976, 89, 24], [294, 438, 16, 196, 217, 5147, 276, 12827, 294, 429], [311, 7151, 10792, 421, 293, 152, 8, 334, 378, 326, 437, 237, 16912, 117], [31103, 435, 262, 7, 75, 75, 254, 7723, 31030, 250, 62, 312, 444, 281, 7136, 204, 208, 293, 4943, 13, 90, 85, 248], [491, 390, 185, 108, 353, 45, 419, 11450, 14033, 509, 20496, 59, 100, 22765, 55, 497, 236, 510, 344], [18571, 348, 391, 41, 22452, 83], [240, 377, 55, 288, 211, 450, 362, 25175, 442, 288, 378, 300, 318, 236, 33, 153, 27612, 20749, 329, 27118], [7835, 5, 71, 230]]</t>
+    <t>[[1198, 831, 427, 501, 243, 91, 421, 351, 324, 436], [105, 885, 228, 1783, 43, 960, 297, 102], [450, 331, 83, 227, 422, 968], [325, 1270, 21, 78, 465, 166, 2029, 294, 332, 344], [259, 1959, 271, 132, 382, 311, 363, 1276], [482, 66, 234, 10], [273, 205, 1941], [321, 284, 73, 58, 384, 1940], [94, 172, 116, 246, 406], [253, 336, 188, 439, 211, 175, 155], [243, 260, 118, 321, 1717, 472, 433], [155, 324, 449], [333, 86, 62, 127], [409, 467, 1645, 647, 362], [797, 104, 171, 163, 251, 335], [252, 465, 68, 465], [40, 138], [191, 147, 115, 363, 324], [193, 162, 211, 419, 737, 20, 1339, 82], [508, 271, 85, 206, 394], [97, 427, 474, 33, 37, 162, 142], [399, 132, 113, 46], [135, 1881, 67, 414, 467, 1962, 100, 488, 108], [153, 156, 171], [20, 1892, 152], [146, 1068, 331, 402, 253, 1932], [219, 213, 450, 375, 16], [66, 151, 1188, 50, 466, 504, 232, 285, 158, 438], [193, 210, 319, 95, 992], [489, 225, 306, 424, 107], [334, 83, 44, 254, 203, 391, 202, 508, 1422], [137, 463, 137, 428]]</t>
   </si>
   <si>
     <t>perf_large_world_ws64_infp16_outfp16_ID1042</t>
   </si>
   <si>
-    <t>[[30425], [283, 56281], [309, 401, 48025], [7619, 10, 409, 96], [508, 19, 38945, 284, 250], [5760, 156, 194, 190, 55243, 240], [65, 202, 472, 458, 22979, 12, 64586], [218, 26247, 6054, 366, 188, 141, 383, 311], [444, 13, 52, 270, 210, 500, 247, 59556, 15552], [4255, 49, 304, 74, 468, 229, 244, 299, 48, 63967], [149, 381, 35783, 314, 36, 153, 36601, 403, 351, 41229, 241], [39, 459, 192, 477, 4, 319, 347, 14263, 14971, 275, 169, 8213], [50247, 54322, 37987, 138, 411, 494, 203, 363, 461, 64, 508, 267, 72], [52150, 323, 10936, 349, 478, 10, 226, 498, 138, 46645, 47, 175, 431, 93], [377, 137, 25812, 269, 380, 472, 113, 38, 374, 239, 28178, 53785, 396, 277, 505], [178, 8981, 61111, 6703, 4, 135, 371, 243, 288, 469, 142, 165, 16, 377, 248, 42911], [65267, 186, 180, 508, 7, 413, 97, 132, 67, 387, 22458, 497, 25121, 390, 502, 273, 21561], [213, 411, 82, 284, 36, 305, 22, 25496, 286, 176, 174, 51013, 57808, 379, 510, 508, 412, 26757], [38, 279, 30, 512, 317, 37, 416, 103, 499, 23644, 288, 510, 175, 28219, 239, 502, 788, 38788, 70], [27846, 416, 88, 19, 411, 55, 49102, 18448, 15, 207, 266, 85, 442, 478, 173, 141, 239, 4989, 17, 465], [445, 58, 147, 1450, 184, 28500, 65514, 375, 103, 107, 255, 169, 28749, 225, 346, 10041, 64, 105, 139, 216, 138], [186, 359, 290, 57300, 327, 492, 507, 13812, 21487, 400, 439, 232, 505, 216, 90, 54230, 220, 457, 90, 10094, 437, 295], [118, 216, 297, 32207, 45110, 330, 146, 372, 107, 484, 339, 454, 27126, 57, 72, 502, 349, 13440, 34, 473, 162, 174, 60366], [270, 20, 195, 47320, 1379, 468, 32660, 61310, 487, 52087, 39, 50, 36, 393, 427, 37, 312, 462, 269, 361, 308, 218, 16, 393], [16, 60, 202, 26903, 78, 472, 362, 25121, 44, 26822, 496, 365, 103, 3, 253, 318, 7448, 102, 16, 436, 369, 446, 138, 76, 3780], [47, 439, 49, 12506, 506, 138, 265, 159, 149, 96, 257, 8089, 369, 55357, 324, 90, 299, 110, 52932, 8, 60516, 495, 34739, 405, 239, 153], [248, 63026, 245, 40186, 510, 237, 15144, 60502, 216, 244, 299, 470, 422, 96, 387, 62200, 22, 64941, 113, 64, 40, 48, 336, 96, 255, 402, 453], [27713, 7, 27, 334, 23254, 82, 61, 510, 38395, 101, 77, 163, 14433, 176, 433, 12, 82, 87, 20395, 452, 327, 462, 55, 129, 59589, 512, 272, 485], [104, 363, 251, 47, 450, 235, 449, 8573, 289, 141, 450, 315, 273, 198, 239, 354, 14624, 49973, 9201, 282, 163, 78, 68, 164, 293, 46474, 361, 11099, 490], [187, 303, 59, 419, 216, 469, 244, 330, 41, 160, 283, 16232, 50415, 319, 2467, 419, 387, 23, 54, 400, 9295, 411, 219, 113, 383, 409, 216, 19141, 34586, 468], [430, 11801, 158, 8352, 167, 39775, 67, 455, 306, 393, 483, 61520, 50398, 205, 34897, 195, 29, 225, 405, 340, 150, 289, 179, 400, 339, 105, 182, 267, 215, 52973, 512], [426, 229, 27, 277, 142, 152, 21, 220, 130, 63964, 258, 362, 172, 58394, 310, 76, 423, 462, 6, 505, 279, 339, 5895, 51743, 467, 404, 363, 54286, 348, 364, 56271, 59802], [239, 42, 236, 471, 38423, 213, 499, 303, 41717, 278, 41, 388, 475, 257, 33924, 234, 342, 367, 49923, 222, 467, 368, 128, 334, 327, 185, 37158, 312, 38546, 197, 384, 57447, 147], [60499, 458, 179, 472, 53505, 246, 491, 20858, 288, 239, 219, 36, 362, 229, 426, 294, 72, 30228, 309, 270, 323, 39454, 27, 324, 70, 35592, 13116, 247, 255, 369, 186, 125, 429, 278], [340, 271, 406, 132, 55138, 436, 178, 425, 498, 402, 180, 56172, 199, 279, 376, 159, 43436, 462, 22366, 47169, 261, 259, 352, 41, 172, 487, 151, 11072, 285, 503, 140, 91, 29619, 22, 255], [417, 283, 60468, 249, 14, 425, 14, 275, 31581, 332, 464, 56121, 466, 200, 141, 318, 58778, 416, 45, 77, 225, 7715, 305, 487, 183, 60614, 133, 423, 53027, 174, 188, 466, 79, 42954, 278, 320], [124, 311, 235, 317, 130, 229, 20355, 489, 170, 384, 442, 392, 358, 493, 290, 363, 5284, 48, 47299, 440, 3894, 295, 55830, 211, 110, 4445, 60412, 292, 24534, 47, 464, 362, 137, 482, 118, 496, 385], [377, 171, 30, 503, 190, 327, 203, 445, 15842, 1860, 235, 502, 59697, 9, 322, 184, 212, 170, 165, 164, 261, 317, 292, 140, 346, 58994, 10, 46394, 100, 410, 58, 212, 9541, 290, 51836, 44057, 296, 28], [3751, 39, 485, 369, 365, 353, 417, 28945, 150, 59, 63, 398, 27, 179, 499, 50640, 393, 25603, 226, 303, 461, 438, 396, 1, 107, 52052, 242, 344, 401, 39325, 322, 253, 265, 31654, 121, 385, 332, 346, 14637], [342, 153, 381, 52671, 29899, 256, 33288, 282, 12, 331, 9082, 491, 120, 378, 45597, 210, 69, 17, 2937, 311, 80, 167, 13985, 434, 92, 149, 278, 192, 98, 386, 4223, 200, 464, 498, 209, 469, 33, 245, 288, 347], [267, 26, 416, 66, 299, 158, 99, 10, 429, 21304, 8, 479, 120, 420, 329, 229, 267, 7, 328, 31110, 275, 470, 379, 4, 54981, 299, 28, 26242, 55591, 59881, 407, 162, 32955, 249, 421, 269, 42408, 4461, 146, 409, 160], [475, 442, 390, 64344, 47233, 359, 414, 258, 417, 10584, 398, 81, 36528, 49922, 132, 370, 102, 91, 61144, 28, 468, 183, 144, 257, 78, 159, 24, 224, 222, 434, 317, 102, 55, 219, 362, 165, 469, 46169, 46131, 739, 177, 73], [14564, 75, 59232, 360, 510, 48, 497, 23340, 53529, 215, 241, 223, 419, 300, 158, 318, 468, 12, 338, 29366, 492, 9717, 316, 401, 231, 455, 16224, 166, 399, 492, 252, 459, 421, 45, 182, 63892, 50736, 372, 469, 268, 499, 251, 291], [239, 460, 35, 296, 415, 246, 99, 339, 141, 21403, 143, 53116, 457, 503, 55363, 162, 390, 189, 41, 183, 386, 230, 483, 12115, 482, 174, 212, 57703, 120, 63, 417, 386, 46, 51816, 511, 278, 65279, 31368, 365, 47, 322, 390, 55923, 459], [319, 53132, 197, 133, 154, 11423, 31295, 261, 179, 336, 483, 154, 28770, 41292, 466, 24421, 107, 424, 445, 34, 185, 53888, 287, 292, 385, 58788, 331, 343, 353, 34460, 260, 234, 487, 301, 229, 415, 65, 501, 255, 51, 1, 132, 498, 352, 480], [311, 27213, 362, 99, 457, 417, 457, 378, 100, 58859, 490, 54566, 450, 286, 20, 465, 83, 29584, 413, 169, 495, 512, 15847, 61115, 130, 18139, 72, 358, 240, 257, 362, 306, 48228, 30064, 56356, 250, 50, 130, 162, 485, 369, 48, 143, 317, 149, 57], [406, 36501, 258, 64122, 391, 423, 347, 143, 61, 104, 427, 59133, 168, 388, 13684, 141, 0, 156, 219, 72, 309, 31480, 61, 52, 345, 469, 174, 243, 233, 61355, 511, 211, 59545, 28588, 248, 18657, 431, 262, 470, 209, 224, 50657, 93, 338, 52, 375, 348], [263, 320, 128, 472, 380, 249, 190, 35927, 71, 92, 126, 477, 32744, 20743, 483, 331, 52510, 151, 308, 240, 388, 348, 212, 292, 233, 70, 370, 311, 25877, 140, 52292, 45, 28309, 201, 478, 28494, 217, 324, 109, 172, 38709, 451, 24995, 300, 487, 496, 495, 511], [248, 34286, 67, 187, 419, 491, 38611, 449, 207, 208, 112, 357, 45462, 273, 213, 257, 44, 347, 69, 56030, 502, 492, 51062, 443, 492, 324, 324, 16395, 445, 452, 241, 13336, 90, 465, 382, 171, 4419, 165, 332, 30369, 2854, 51, 18, 298, 268, 417, 105, 168, 260], [469, 144, 168, 472, 99, 20935, 316, 45040, 385, 35742, 234, 432, 403, 161, 318, 276, 511, 412, 282, 39466, 176, 18985, 469, 230, 162, 63686, 406, 318, 36227, 132, 59420, 288, 460, 490, 263, 40, 136, 24, 424, 440, 344, 458, 209, 248, 4129, 468, 152, 109, 352, 23354], [64, 463, 285, 494, 17127, 231, 6974, 56, 925, 478, 52313, 474, 121, 266, 32086, 452, 325, 81, 159, 158, 169, 27421, 84, 379, 21, 486, 54457, 489, 90, 483, 329, 243, 257, 48072, 196, 453, 181, 292, 288, 510, 27319, 108, 9304, 335, 134, 488, 341, 240, 7592, 48, 384], [341, 9556, 48, 451, 199, 300, 318, 437, 269, 3986, 310, 83, 226, 504, 34, 30185, 343, 391, 74, 422, 420, 181, 207, 57, 2758, 36152, 126, 65262, 165, 236, 4, 216, 357, 73, 4389, 59, 258, 13, 504, 6022, 306, 87, 218, 214, 183, 88, 65499, 365, 27535, 19, 14185, 505], [464, 363, 97, 9717, 41075, 7968, 39, 185, 366, 326, 396, 115, 179, 26, 61581, 41089, 2811, 234, 1, 131, 159, 54, 75, 378, 453, 285, 419, 401, 1711, 350, 57, 229, 53, 387, 140, 500, 416, 39, 25, 413, 503, 28334, 20, 25614, 315, 290, 231, 41886, 303, 509, 52431, 146, 395], [195, 272, 17992, 484, 84, 439, 356, 54639, 426, 268, 167, 281, 461, 55780, 179, 368, 52, 160, 58, 508, 498, 371, 104, 219, 170, 431, 56920, 25238, 5, 184, 18, 303, 143, 310, 94, 53195, 143, 45342, 344, 27944, 46, 170, 45017, 285, 37245, 46, 376, 283, 463, 460, 14000, 197, 216, 283], [179, 244, 136, 498, 57599, 450, 212, 502, 47173, 51671, 209, 214, 18237, 300, 226, 427, 420, 10317, 8329, 142, 197, 248, 58275, 25974, 155, 276, 479, 159, 371, 43, 306, 472, 379, 128, 30, 155, 237, 402, 19781, 383, 11, 27, 208, 41, 44639, 265, 271, 435, 437, 496, 314, 3558, 149, 159, 60], [60605, 412, 187, 267, 50, 104, 433, 289, 240, 63831, 79, 290, 397, 226, 350, 294, 83, 253, 232, 386, 437, 2364, 246, 22242, 255, 43971, 335, 486, 108, 337, 506, 12511, 36, 390, 54499, 15511, 390, 505, 381, 358, 352, 248, 30, 27399, 489, 362, 462, 294, 322, 383, 413, 31470, 30174, 106, 155, 65383], [31580, 498, 33669, 375, 15, 402, 44, 168, 133, 357, 52, 398, 5791, 149, 176, 260, 500, 369, 211, 408, 25184, 106, 437, 192, 223, 202, 56633, 2114, 401, 63329, 360, 443, 90, 9, 252, 65283, 18511, 502, 241, 102, 458, 207, 222, 246, 313, 358, 20868, 404, 236, 10492, 140, 210, 339, 140, 438, 144, 11618], [2, 350, 462, 165, 6, 28373, 40, 323, 21783, 450, 124, 219, 218, 437, 62998, 232, 319, 419, 10910, 495, 53980, 413, 234, 425, 125, 202, 14577, 45210, 266, 299, 343, 273, 425, 121, 203, 40552, 204, 436, 139, 192, 286, 45, 17129, 64554, 295, 424, 14742, 270, 176, 103, 407, 223, 337, 17032, 175, 316, 94, 378], [191, 384, 194, 52851, 503, 298, 292, 169, 75, 422, 360, 64345, 508, 243, 132, 59081, 53365, 17332, 36, 196, 1, 359, 17, 4, 295, 200, 218, 187, 403, 442, 274, 73, 210, 139, 42805, 28563, 49691, 145, 26492, 239, 94, 102, 23543, 168, 409, 470, 112, 113, 362, 484, 137, 432, 253, 353, 7374, 239, 224, 255, 3369], [419, 261, 321, 60711, 403, 504, 37, 409, 10, 342, 24357, 379, 473, 30781, 7, 293, 232, 339, 50291, 259, 10817, 255, 147, 233, 286, 285, 437, 54, 254, 55740, 263, 291, 32869, 98, 209, 366, 356, 22, 325, 4435, 268, 54778, 436, 108, 82, 352, 26, 326, 420, 301, 12499, 9274, 377, 181, 451, 452, 415, 26766, 346, 466], [254, 161, 199, 35343, 304, 76, 61735, 443, 47070, 44707, 439, 369, 79, 218, 333, 351, 503, 225, 11606, 235, 286, 249, 140, 182, 114, 189, 276, 2659, 164, 381, 425, 42449, 221, 11424, 305, 357, 16, 340, 33581, 57, 52976, 273, 466, 304, 365, 11483, 340, 155, 301, 3514, 32, 426, 338, 332, 45507, 506, 19, 288, 18, 58, 373], [68, 48, 418, 35176, 220, 21227, 228, 50914, 442, 4631, 101, 435, 346, 393, 465, 85, 366, 366, 33033, 511, 85, 257, 124, 365, 46414, 248, 135, 442, 269, 135, 117, 14429, 65152, 211, 16, 25, 420, 146, 51759, 192, 206, 287, 279, 228, 74, 63, 338, 445, 36346, 25007, 24, 52, 480, 49, 497, 307, 379, 64, 39995, 37, 61608, 216], [17, 201, 60709, 31740, 5127, 470, 153, 350, 167, 131, 374, 476, 43163, 291, 7621, 365, 93, 195, 63569, 335, 17, 192, 302, 508, 309, 24200, 442, 293, 310, 8173, 220, 296, 408, 0, 506, 204, 222, 12143, 163, 6787, 142, 142, 67, 349, 391, 47, 398, 61530, 44, 197, 384, 17, 241, 137, 115, 504, 392, 27, 153, 64453, 228, 218, 2083], [43, 486, 377, 4, 42826, 507, 97, 326, 265, 413, 189, 280, 55998, 186, 57363, 347, 435, 15, 401, 264, 445, 367, 130, 377, 23167, 196, 366, 287, 26, 213, 63408, 444, 416, 101, 457, 159, 469, 19627, 450, 223, 492, 328, 489, 58916, 21122, 48, 415, 328, 165, 52, 148, 120, 371, 58535, 53406, 98, 325, 16107, 284, 46126, 79, 7, 504, 28215]]</t>
+    <t>[[267, 236, 33, 162, 88, 145, 417, 290], [325, 1679, 233, 132, 452, 389, 298, 417, 51, 441], [211, 261, 447, 108, 44, 342, 66, 382, 121, 198], [210, 171, 143, 423, 403, 483], [134, 227], [328, 1122, 25, 125, 104, 86, 87, 251], [313, 1210, 77, 335, 259, 148], [88, 147, 214, 507, 368, 190, 122, 1370, 165], [129, 19, 59, 327, 1631, 225, 370, 10, 156], [242, 405, 190, 457, 972, 196, 109], [7, 369, 207, 320, 90, 292, 268, 418, 375], [399, 1178, 503, 76, 292, 103], [1996, 413, 479, 3, 667, 462, 1004, 278, 3, 465], [76, 188, 17], [274, 461, 224, 1766, 812, 1379, 11], [365, 377, 455, 147, 251, 60], [168, 250, 1191, 240, 163, 478, 509], [124, 352, 308, 29, 482, 287, 1692, 372], [237, 358, 99], [434, 353, 230, 865, 55, 420, 297], [275, 153, 286, 76, 326, 396, 186, 1593], [204, 337, 502, 1681, 443], [444, 386, 231, 1440], [194, 244, 154, 436, 447, 346, 332, 476], [498, 154, 153, 370, 457, 147, 138], [308], [505, 210, 464, 262, 149, 158, 95], [371, 57, 315, 859], [1289, 145], [1522, 1099, 433, 37, 919, 134, 177], [379], [424, 79], [405, 275, 201, 148, 621], [872], [201], [390, 1315, 333, 792, 457, 120, 498], [276, 108], [1949, 373, 281, 141, 175, 416, 498, 1803, 319, 184], [91, 441], [273, 1031, 251], [131, 504, 258, 704], [220], [127, 301, 246, 1426, 406, 73, 512], [450, 221, 603, 358, 454, 470, 13, 436, 124], [13, 135, 318], [182], [856, 392, 313, 78, 200, 907, 198, 254, 512, 29], [249, 218, 152], [323, 120, 991, 65, 407, 325, 1289, 248, 222, 340], [30, 224, 375, 148, 253, 212], [313, 462, 232, 257, 96], [1640, 166, 15, 165, 902, 1119, 60, 1151, 154, 999], [311, 208, 200], [214, 167], [157, 356, 1673, 251, 1542, 1879, 55, 417, 47, 136], [294, 27, 182, 282, 720, 1503], [126, 451, 63, 474], [303, 477, 177, 122, 108, 488, 496, 433, 389], [20], [141, 321, 247, 145, 240, 170, 113, 96], [490, 476, 500, 216, 167, 418, 415], [415, 323, 125, 389, 898, 46, 169, 44, 114], [156, 233, 461], [265, 304, 291, 449, 15]]</t>
   </si>
   <si>
     <t>perf_large_world_ws32_infp16_outfp16_ID1043</t>
   </si>
   <si>
-    <t>[[17180, 314, 499, 411, 16874, 149, 165, 54, 478, 416, 18, 383, 8359, 363, 386], [21707, 21873, 136, 487, 184, 323, 228], [56, 138, 302, 498, 171, 242, 10071, 438, 362, 309, 97, 505, 22620, 366, 138, 30291, 275, 186, 93, 195, 9094, 123, 167, 398, 15368, 22353, 114, 183, 195, 177, 19940], [402, 474, 406, 620, 473, 192, 102, 32383, 61, 400, 138, 18098, 3], [16110, 138, 15569, 171, 60, 396, 306, 198, 194, 182], [420, 25717], [215, 272, 85, 32310, 219, 485, 407, 499, 24610, 19302, 3, 471, 28, 258, 192, 335, 293, 406, 5, 5, 1950, 246, 375, 3889], [15451, 22078, 25659, 264, 369, 235, 362, 159, 351, 272, 399, 220, 289, 15265, 202, 430, 365, 511], [483, 21144, 359, 208, 23510, 250, 336, 486, 294, 17341, 252], [20335], [6851, 4, 342, 378], [31614, 27, 66, 258, 76, 11219, 459, 18, 408, 289, 390, 694, 265, 307, 236, 189, 238, 8456, 230, 431, 199, 343, 16224, 433, 32703, 322, 199, 413, 21915, 415, 510, 444], [226, 29710, 15, 9828, 463, 331, 23080, 199, 384, 114, 101, 138, 72, 412, 22, 381, 21856], [18333, 329, 316], [156, 488, 136, 1462, 12, 15036, 144, 224], [112, 97, 122, 361, 20025, 32391, 57, 197, 259, 15094, 5384, 7, 25992, 321, 496, 8, 397, 74, 245, 462, 205, 2], [28585, 16577, 434, 361, 151, 198, 65, 467, 337, 18639, 31116, 370, 16, 227, 105, 278, 22384, 293, 314, 219, 171, 426, 961, 359, 35, 439], [422, 436, 240, 9551, 9007, 357, 375, 498, 289, 302, 191, 475, 393, 3828, 324, 429, 19069, 381, 378], [80, 101, 162, 428, 10105, 425, 23, 28456, 2782, 443, 288, 420, 22189, 508, 48, 299], [128, 17932, 49, 338, 210, 111, 20921, 193, 426, 462, 372, 409, 339, 393, 24918, 185, 435, 156, 350, 14114, 221, 16010, 285, 30587, 239, 79, 214, 216], [18, 326, 8115, 28868, 329, 4655, 496, 45, 442, 478, 236, 429], [18093, 16234, 26834, 99, 139, 237, 343, 328, 456, 420, 333, 261, 431, 46, 405, 182, 214, 95, 309, 23249, 302, 24927, 42, 31057, 47, 333, 211], [21079, 400, 41, 397, 447], [83, 359, 243, 11933, 51, 112, 347, 27535, 426, 176, 3559, 180, 318, 492], [156, 31259, 17124, 309, 445, 259, 243, 323, 202, 486, 134, 4, 311, 126, 309, 484, 83, 17978, 432, 218, 30632, 23106, 415, 216, 83, 384, 48, 28328, 311], [20711, 204, 231, 396, 453, 465, 318, 510, 226, 14426, 109, 27190, 357, 12, 292, 133, 27709, 120, 320, 229, 3226], [69, 5084, 441, 34, 424, 384, 2680, 2868, 499, 430, 362, 415, 371, 235, 64, 5, 373, 39, 168, 261, 103, 21316, 25476], [386, 219, 24404, 2477, 142, 25750, 497, 243, 285, 79, 506, 220, 454, 336, 262, 375, 6463, 447, 369, 195, 22, 25803, 54, 136, 402, 13710, 333, 405, 156, 498], [203, 235, 420, 417, 415, 421, 113, 168, 244, 324, 3, 19516, 278, 73, 404, 5016, 416, 282, 21046, 54, 17568, 483, 301, 20697, 252], [313, 295, 3829, 372, 8439, 326], [239, 408, 407, 482, 16693, 384, 22091, 446, 248], [29504, 199, 485, 61, 392, 440, 13, 479, 40, 467, 8977, 93, 334, 185, 106, 20640, 51, 5284, 241, 433]]</t>
+    <t>[[32, 100], [282, 718, 147, 327, 1508], [17, 484, 316, 171], [506, 1255, 78, 155, 319, 1211, 239, 1452, 311], [438, 21, 188, 379, 3, 119], [98, 292, 253, 1237, 301, 365, 340, 1431, 464], [1017, 678, 339, 1498, 1638, 33, 245, 12, 284, 23], [610, 60, 345, 324, 434, 228], [314, 107, 273, 133, 105, 324, 278, 183, 224], [204, 510, 489, 1900], [119, 41, 191], [361, 749, 500, 184, 89], [181, 319], [1046, 207], [101, 182, 1868, 481, 94, 1212, 140, 127, 326], [1913, 42, 258, 182, 1584, 227], [53, 47, 498, 458, 18, 11, 395], [1540], [50, 8, 244, 489, 163, 154], [264, 57], [245, 177, 121, 18, 384, 463, 1158, 34, 351, 334], [1193, 192, 48, 1798, 400], [83, 148], [319, 346, 422, 418, 216, 136, 429, 644, 496], [824, 510], [471, 82, 486, 142, 140, 490, 165, 40, 98, 363], [402, 806, 412, 384, 383], [243, 228, 102, 68, 1864, 11, 97, 265, 346], [401, 372, 182, 339, 485, 581, 1314, 1791], [1913, 504, 920, 1781, 35, 2022], [1564, 313, 44, 84, 202, 107, 57, 73, 795], [235, 165, 428, 1017]]</t>
   </si>
   <si>
     <t>perf_large_world_ws64_infp16_outfp16_ID1044</t>
   </si>
   <si>
-    <t>[[42766], [65008, 412], [298, 51898, 253], [121, 401, 475, 4574], [281, 503, 325, 303, 20348], [430, 15075, 330, 207, 35295, 22], [20269, 36, 97, 252, 332, 25368, 509], [238, 59502, 147, 196, 472, 158, 62733, 391], [234, 147, 344, 58901, 13709, 168, 170, 247, 74], [282, 192, 52087, 445, 28673, 435, 123, 58, 204, 336], [120, 97, 287, 30, 38, 3178, 1, 378, 318, 19735, 49411], [21730, 470, 220, 259, 460, 79, 26, 326, 31023, 443, 241, 10421], [5014, 247, 94, 51, 310, 11320, 163, 12, 211, 85, 14, 340, 56702], [387, 509, 102, 431, 391, 347, 29051, 169, 405, 283, 37080, 177, 348, 32231], [18, 362, 269, 157, 276, 25967, 37966, 240, 151, 62621, 261, 113, 445, 162, 501], [18704, 22815, 275, 303, 428, 435, 168, 269, 19, 123, 428, 40044, 319, 186, 17684, 511], [109, 47504, 194, 52082, 244, 104, 128, 104, 46, 56, 348, 302, 25775, 484, 74, 31656, 419], [388, 421, 91, 17, 473, 122, 318, 7446, 77, 124, 39496, 475, 113, 415, 5410, 15600, 448, 142], [59, 16366, 219, 128, 473, 498, 372, 446, 1777, 140, 113, 203, 11, 338, 301, 6577, 244, 5089, 60], [358, 7774, 376, 216, 131, 431, 412, 453, 28391, 96, 220, 65, 253, 16876, 471, 320, 52937, 54, 44, 292], [44647, 172, 489, 142, 2, 33035, 42, 149, 34, 272, 505, 30, 222, 32526, 232, 55768, 364, 479, 35381, 448, 496], [34850, 10206, 451, 297, 32477, 232, 254, 433, 468, 477, 371, 60, 142, 44048, 228, 174, 15332, 58, 316, 40, 145, 240], [506, 48, 225, 4772, 21763, 465, 479, 418, 216, 51642, 11833, 196, 193, 129, 259, 45, 53275, 212, 45, 80, 292, 190, 150], [15743, 32477, 489, 475, 442, 449, 51, 100, 37, 37, 429, 7, 285, 258, 151, 440, 27, 187, 222, 173, 48367, 27065, 58, 1224], [374, 37673, 273, 83, 39121, 169, 366, 493, 272, 49431, 434, 163, 485, 17804, 243, 39112, 320, 224, 116, 180, 135, 430, 294, 384, 116], [253, 136, 267, 296, 7124, 10053, 108, 45822, 50, 104, 164, 171, 3, 270, 379, 16799, 61660, 469, 115, 51, 63, 206, 508, 448, 53981, 66], [50715, 470, 112, 180, 119, 482, 101, 217, 40636, 287, 0, 344, 201, 206, 129, 86, 397, 17369, 420, 20537, 408, 173, 392, 44002, 1046, 333, 504], [12140, 469, 456, 211, 157, 220, 96, 469, 147, 404, 152, 51518, 259, 467, 59097, 383, 46, 474, 274, 41, 506, 499, 19877, 59609, 351, 198, 384, 25730], [70, 31542, 426, 503, 8449, 107, 36433, 416, 452, 320, 232, 298, 309, 431, 393, 131, 10568, 246, 127, 6, 183, 82, 16017, 63, 18112, 210, 210, 485, 97], [61, 180, 155, 378, 46512, 505, 3270, 14373, 74, 369, 204, 196, 30271, 33, 4791, 319, 123, 450, 97, 464, 107, 192, 63079, 416, 452, 266, 418, 238, 447, 396], [184, 2023, 338, 336, 252, 13623, 190, 326, 53, 472, 406, 86, 491, 340, 376, 9694, 118, 54642, 431, 65344, 411, 35073, 28416, 241, 38, 483, 165, 412, 156, 104, 50], [130, 103, 246, 179, 25589, 511, 138, 453, 305, 246, 22, 49, 99, 99, 17108, 412, 62542, 139, 28, 443, 490, 258, 0, 306, 383, 278, 8101, 8961, 21142, 41661, 422, 51], [436, 39075, 498, 438, 22, 109, 488, 105, 49246, 7, 19938, 584, 99, 214, 436, 144, 302, 163, 48, 19755, 21370, 45531, 369, 285, 339, 6, 256, 356, 269, 35, 221, 52, 129], [151, 348, 465, 124, 225, 31792, 2, 495, 29495, 453, 50169, 6254, 222, 43732, 362, 491, 344, 122, 441, 18237, 105, 225, 28, 240, 323, 497, 416, 41192, 94, 147, 60, 382, 74, 500], [110, 222, 272, 284, 499, 432, 171, 53881, 226, 48371, 39, 357, 38, 37691, 170, 261, 342, 9, 176, 188, 357, 875, 219, 358, 50, 9438, 446, 95, 167, 12089, 379, 317, 426, 10894, 286], [334, 82, 33736, 1628, 37657, 40826, 26525, 434, 189, 200, 194, 170, 115, 95, 215, 35438, 373, 288, 52583, 328, 18504, 361, 3, 198, 309, 487, 374, 2, 432, 316, 180, 56, 377, 166, 40, 481], [252, 274, 343, 171, 6, 82, 40, 78, 225, 20, 39622, 60970, 42, 396, 132, 502, 399, 19, 359, 59, 41935, 409, 449, 278, 504, 510, 8712, 129, 285, 503, 13, 57058, 40, 63211, 397, 23887, 62133], [299, 10, 239, 287, 27, 405, 375, 239, 18431, 60088, 330, 18983, 494, 182, 255, 443, 19, 434, 244, 16, 166, 58698, 10500, 266, 43185, 52, 37, 65011, 200, 81, 142, 511, 403, 8, 484, 185, 214, 60850], [22, 206, 187, 52323, 27395, 32522, 64073, 292, 10447, 328, 477, 361, 491, 222, 135, 111, 405, 44, 485, 7219, 80, 353, 306, 486, 466, 35, 328, 449, 16179, 248, 255, 158, 24, 79, 182, 57102, 400, 436, 399], [78, 3, 389, 120, 3709, 13545, 346, 431, 172, 108, 18831, 24649, 109, 8654, 482, 184, 219, 64170, 65, 357, 420, 367, 364, 30570, 506, 301, 214, 398, 321, 295, 267, 18029, 18, 110, 362, 308, 19, 447, 199, 117], [46370, 342, 387, 388, 20, 188, 26237, 176, 257, 28, 108, 15083, 431, 102, 8807, 28, 57434, 369, 394, 417, 26, 86, 207, 10695, 319, 330, 205, 410, 40, 43, 14965, 489, 154, 28882, 74, 29973, 316, 200, 390, 255, 75], [73, 177, 476, 244, 367, 69, 508, 384, 75, 60, 483, 104, 46401, 211, 241, 482, 433, 280, 244, 34, 325, 30542, 62239, 29243, 296, 24, 167, 314, 25090, 446, 421, 43339, 115, 127, 224, 36, 384, 40833, 431, 183, 27017, 2864], [279, 207, 353, 481, 207, 380, 359, 54, 3331, 318, 173, 409, 502, 388, 424, 14, 194, 33069, 145, 3691, 220, 305, 495, 316, 117, 313, 362, 42283, 11249, 290, 115, 272, 388, 48882, 88, 32, 343, 2636, 288, 13, 21319, 12761, 339], [484, 55945, 122, 225, 477, 441, 356, 13949, 38, 384, 18, 320, 245, 25455, 480, 460, 177, 398, 84, 416, 422, 37995, 8, 324, 391, 153, 485, 488, 41294, 396, 19778, 171, 445, 64277, 86, 201, 277, 18649, 235, 206, 246, 460, 65, 57957], [379, 346, 271, 335, 32604, 29, 373, 19934, 34, 119, 445, 214, 32339, 397, 387, 325, 505, 98, 34749, 399, 54042, 65, 88, 397, 312, 141, 333, 145, 3848, 97, 408, 173, 173, 248, 28800, 114, 427, 7731, 449, 62, 5053, 155, 295, 62, 405], [11597, 4, 5, 189, 292, 372, 96, 163, 299, 40420, 336, 159, 469, 52581, 161, 116, 313, 45569, 56661, 329, 75, 409, 272, 32888, 359, 425, 42998, 44101, 21, 456, 287, 405, 412, 63624, 410, 94, 23194, 105, 76, 12, 149, 239, 75, 283, 305, 260], [448, 14337, 362, 114, 86, 19, 357, 417, 72, 375, 44, 199, 141, 144, 381, 10022, 241, 402, 64263, 476, 221, 49, 210, 5, 416, 279, 23, 55847, 464, 6, 51, 130, 365, 33989, 187, 205, 29513, 370, 27806, 107, 12916, 60290, 194, 56586, 214, 78, 20], [203, 382, 345, 49485, 235, 60716, 19102, 420, 110, 0, 66, 60776, 48991, 447, 320, 397, 74, 313, 478, 102, 237, 367, 65, 466, 85, 417, 376, 188, 57, 120, 56120, 110, 180, 403, 51128, 26440, 80, 393, 78, 448, 155, 470, 26, 9210, 34669, 281, 438, 32], [376, 30374, 5654, 133, 56722, 83, 341, 178, 38648, 326, 198, 428, 108, 496, 65265, 190, 329, 266, 381, 33886, 310, 59848, 307, 388, 122, 499, 311, 275, 47746, 478, 8, 215, 474, 390, 75, 297, 495, 465, 222, 7038, 345, 470, 502, 403, 342, 13039, 38, 410, 347], [2100, 506, 324, 23168, 414, 387, 146, 97, 12410, 358, 353, 53288, 128, 43, 19, 339, 123, 11005, 232, 129, 192, 478, 370, 411, 424, 207, 329, 146, 448, 7756, 54754, 217, 431, 349, 288, 445, 12854, 270, 211, 30626, 322, 29432, 89, 272, 394, 432, 371, 372, 248, 401], [296, 220, 103, 33340, 121, 373, 26517, 7, 290, 497, 295, 166, 85, 23385, 92, 211, 55420, 21707, 47905, 29399, 176, 22, 445, 481, 395, 791, 18368, 167, 64000, 379, 213, 288, 263, 179, 175, 314, 354, 89, 293, 255, 54, 465, 319, 292, 147, 400, 447, 18139, 385, 383, 171], [66, 151, 4873, 29430, 61480, 479, 48013, 58992, 101, 378, 189, 163, 17951, 440, 251, 387, 149, 291, 109, 108, 444, 218, 301, 141, 98, 52534, 480, 375, 455, 226, 59422, 421, 414, 246, 443, 248, 24447, 54, 39, 11501, 288, 7, 232, 46247, 29, 234, 45, 66, 181, 68, 455, 51], [272, 270, 51, 67, 474, 31, 377, 434, 64933, 509, 300, 350, 500, 15137, 5, 19515, 418, 360, 33, 404, 147, 348, 258, 48485, 41243, 54288, 64, 300, 42137, 390, 44388, 32532, 84, 280, 238, 475, 29, 158, 44820, 39700, 355, 512, 367, 120, 364, 435, 125, 288, 122, 422, 176, 132, 484], [71, 19344, 376, 121, 311, 10082, 217, 512, 345, 145, 171, 33, 361, 488, 81, 69, 218, 356, 2123, 357, 298, 295, 436, 48508, 505, 466, 339, 312, 295, 7955, 360, 317, 23497, 20374, 4169, 374, 342, 335, 18447, 24661, 305, 135, 4547, 293, 380, 4, 47, 63, 202, 332, 295, 447, 49, 3], [499, 320, 136, 247, 276, 50410, 345, 231, 337, 36766, 19175, 249, 50, 367, 44135, 33, 88, 132, 409, 176, 82, 10034, 154, 40654, 54495, 472, 443, 11, 61281, 383, 341, 303, 221, 60301, 338, 196, 27208, 1819, 35, 327, 462, 317, 431, 154, 389, 326, 232, 239, 285, 423, 244, 183, 274, 55, 446], [373, 354, 474, 90, 4224, 179, 256, 138, 166, 36851, 476, 160, 25, 477, 412, 432, 467, 413, 183, 503, 292, 131, 382, 475, 59289, 452, 358, 230, 320, 94, 28, 145, 372, 30729, 440, 11867, 53638, 19056, 54253, 400, 376, 40806, 363, 126, 213, 447, 195, 57528, 9234, 188, 102, 115, 27608, 496, 452, 293], [282, 17472, 48355, 50184, 275, 233, 459, 59, 48670, 540, 198, 285, 456, 28, 81, 313, 367, 416, 510, 6420, 32871, 470, 327, 155, 231, 231, 1229, 106, 391, 38, 272, 153, 61502, 503, 143, 2213, 205, 416, 149, 5836, 369, 256, 249, 400, 351, 314, 493, 311, 339, 109, 467, 334, 373, 494, 254, 435, 15010], [66, 326, 188, 432, 39751, 63425, 60774, 484, 218, 55225, 251, 361, 169, 256, 214, 416, 483, 404, 56, 165, 18570, 103, 53, 21, 45, 126, 368, 199, 365, 8269, 33, 174, 326, 266, 321, 30508, 258, 32330, 169, 490, 64, 22467, 492, 130, 164, 258, 5031, 117, 493, 323, 119, 12258, 44023, 291, 435, 225, 198, 210], [189, 31, 82, 61648, 60, 279, 205, 464, 49, 70, 59526, 388, 14773, 2509, 45232, 173, 172, 143, 5, 338, 59562, 43003, 22916, 193, 353, 31, 132, 59, 324, 341, 8610, 229, 45224, 493, 181, 134, 12, 306, 42, 139, 146, 388, 188, 168, 330, 50, 249, 117, 208, 75, 345, 198, 484, 474, 466, 218, 22943, 45478, 21], [298, 213, 396, 47454, 134, 152, 189, 105, 227, 73, 502, 33, 343, 59754, 40741, 152, 25959, 14849, 450, 67, 292, 227, 249, 487, 67, 327, 148, 175, 364, 357, 263, 257, 113, 51989, 382, 3881, 328, 270, 29142, 242, 52198, 440, 180, 186, 386, 50667, 117, 512, 60, 474, 220, 53132, 511, 79, 491, 333, 393, 280, 64, 55157], [175, 328, 261, 427, 186, 31811, 468, 218, 3, 55009, 37, 399, 431, 46126, 25648, 200, 405, 312, 27737, 260, 291, 431, 63482, 306, 130, 27331, 164, 8, 41, 406, 52, 349, 32325, 166, 164, 3, 24, 327, 27, 509, 371, 492, 314, 20737, 423, 55578, 262, 170, 5651, 41, 481, 203, 272, 225, 39132, 129, 163, 20219, 339, 214, 480], [53494, 474, 64, 37663, 332, 339, 354, 205, 177, 471, 59668, 191, 63, 8, 75, 43084, 41, 437, 441, 16, 61, 183, 266, 9414, 439, 212, 11408, 286, 6433, 492, 58175, 377, 24, 136, 432, 422, 8126, 430, 30, 227, 233, 351, 20726, 125, 15015, 397, 86, 289, 114, 219, 2, 144, 139, 452, 14554, 23024, 364, 127, 190, 211, 112, 77], [299, 286, 64125, 393, 20007, 156, 55828, 25048, 243, 435, 80, 354, 90, 209, 250, 206, 424, 397, 26411, 273, 400, 210, 108, 61, 456, 198, 58013, 87, 497, 423, 216, 342, 504, 366, 29004, 290, 316, 272, 489, 2561, 120, 223, 91, 66, 398, 54921, 158, 38881, 481, 482, 339, 23, 29, 337, 206, 190, 51154, 362, 416, 5, 38848, 59064, 144], [171, 435, 327, 28374, 178, 348, 265, 61, 457, 69, 120, 492, 301, 36, 486, 409, 268, 313, 277, 202, 419, 459, 462, 29491, 457, 290, 18, 140, 16684, 153, 260, 58151, 121, 388, 35346, 28629, 81, 8336, 351, 240, 291, 497, 317, 488, 17, 326, 6395, 21, 12774, 94, 506, 18778, 203, 93, 55149, 394, 100, 64377, 37084, 389, 376, 268, 198, 422]]</t>
+    <t>[[468, 40, 224, 166, 463, 441], [394, 176, 425, 1516, 439, 75], [262, 290, 72, 325, 276, 152, 388, 200, 412, 251], [81, 5, 15, 1051, 115, 135, 259], [3, 372, 227, 474, 500, 143], [253, 400, 367], [160, 451, 25, 325], [412, 469, 110, 1981, 211], [457, 230, 482, 890, 1881, 138], [378, 238, 200, 179, 358, 1278, 546, 275], [199, 393, 279, 395, 269, 441, 443, 450, 297, 1053], [318, 338, 16, 992, 324], [148, 406, 1896], [1427, 254, 76, 40, 346, 472], [1884, 130, 438, 2, 139, 413], [116, 1007, 378], [443, 476, 376, 203], [288, 236, 512, 613], [67, 122, 233], [129, 81, 81, 357, 278, 140], [118, 374, 113, 1918, 366], [78, 381, 24, 241, 371, 1034, 90, 51, 208, 27], [189, 223, 852, 204, 136, 1536, 1171, 1779, 500], [232, 353, 56, 278, 206, 347], [187, 507, 82, 67, 317, 58, 1730, 262, 29, 223], [398], [256, 511, 61, 499, 110], [349, 389, 252, 203, 433, 446, 354], [254, 134, 325, 1280, 111, 349, 293, 141], [82], [1960, 257, 357, 466, 354, 217, 41, 85], [504, 59, 812, 96, 72], [1666, 424, 159, 340], [188, 509, 270, 108, 511, 246, 185, 250, 307], [94, 495, 309, 340, 207], [820, 287, 497, 473, 221, 1032, 86], [67, 376, 156, 2, 23], [84, 1864, 846], [339], [168, 352, 443, 10, 279, 405, 198, 1509], [220, 105, 174, 414, 59, 49, 72, 50], [88, 49, 16, 377, 1022, 185, 366], [106, 88, 127, 193, 1037, 319, 94, 1, 232], [184, 276, 245, 417], [1321, 182, 499, 66, 1491, 490, 48, 99], [330, 295, 139, 389, 235, 363, 374], [187, 474], [500, 358], [26, 68, 423, 47, 77, 201, 1035, 257, 1210], [58, 641], [93, 300], [407, 508, 12, 398, 251, 204, 338], [342], [359, 349, 924, 156, 114, 815, 32, 79, 317, 855], [6, 1052], [481, 35, 402, 314], [271, 272, 654, 190, 16, 700, 293, 34, 308], [131], [1747, 376, 35, 419, 117, 431, 511, 715, 70], [313, 371, 271, 113, 289, 350, 1058, 197, 102], [705, 390, 1591, 1038, 29, 455, 460, 465, 396, 1526], [425, 253, 147, 1398, 122, 407, 437], [315, 1461, 395, 498, 353], [1054, 147, 205, 441, 1133, 1908, 338, 488, 326, 1587]]</t>
   </si>
   <si>
     <t>perf_typical_h12288_ne1024_ws8_inbf16_outbf16_ID1045</t>
@@ -2726,7 +2726,7 @@
     <t>[[1024, 12288]]</t>
   </si>
   <si>
-    <t>[[106, 377, 951, 5178, 5426, 205, 497, 164, 182, 4, 205, 354, 334, 1847, 400, 26, 7400, 40, 357, 99, 280, 197, 30, 259, 455], [3745], [417, 387, 7724, 270, 3197, 236, 390, 324, 146, 390, 370, 474, 3457, 3145, 113, 308, 9, 5953, 195, 40, 459, 278, 253], [129, 340, 2201, 320, 36], [5369, 47], [148, 7513, 5, 402], [288, 371, 170, 7276, 60, 1817, 45, 352], [133, 4266, 457, 275, 434, 32, 369, 483, 277, 135, 434, 37, 30, 508, 483, 7811, 510, 1789, 42, 143, 102, 286, 4972, 368, 4466, 443, 165, 46, 7573]]</t>
+    <t>[[192, 1376, 1438, 335, 393, 156, 884], [264, 191, 379, 30], [92, 442], [1194, 235, 119, 153, 277, 474, 444, 115], [272, 98, 77, 205, 1302], [124, 1641, 396, 421, 41], [97, 472, 89], [351, 584, 359, 132, 45, 352]]</t>
   </si>
   <si>
     <t>perf_typical_h12288_ne2048_ws8_inbf16_outbf16_ID1046</t>
@@ -2735,7 +2735,7 @@
     <t>[[2048, 12288]]</t>
   </si>
   <si>
-    <t>[[31, 118, 345, 485, 43, 457, 52, 383, 10778, 1030], [9637, 4585, 12994, 510, 404, 353, 14904, 9426, 327, 366, 273, 14014, 208, 386, 327, 350, 101, 112, 423, 161, 488, 90, 410, 144, 269, 87, 196, 437, 6155, 29, 306, 1], [248, 11875, 227, 491], [469, 14847], [398, 11419, 3316, 419, 105, 88, 74, 454], [6589, 252, 308, 149, 342, 294, 184, 82, 294, 403, 349, 10341, 60, 294, 128, 781, 328, 2545, 295], [162, 303, 142, 291, 199, 258, 11096, 781, 7636, 226, 146], [12720]]</t>
+    <t>[[86, 427, 435, 470, 407, 367, 453, 490, 209], [273], [195, 416, 504, 432, 939, 37, 149, 194, 266, 633], [149, 258, 225, 108, 436, 146, 387, 1627], [288, 506, 128, 2042, 203, 325, 362], [149, 351, 4, 57, 493], [332, 1104, 255, 187, 165], [227, 222]]</t>
   </si>
   <si>
     <t>perf_typical_h4096_ne1024_ws4_inbf16_outbf16_ID1047</t>
@@ -2744,7 +2744,7 @@
     <t>[[1024, 4096]]</t>
   </si>
   <si>
-    <t>[[914, 129, 105, 240, 1703, 506, 500, 128, 67, 291], [203, 118, 186, 69, 182, 448, 281, 4, 1651, 398, 502, 445, 208, 1403, 16, 427, 1779, 472, 3407], [3880, 736, 455, 46, 314, 431], [103, 185, 20, 921, 283, 162, 3270, 157, 2192, 46, 725, 437, 42, 167, 257, 449, 183, 1608, 68, 445, 2429, 67, 52, 389, 62, 408, 230, 2561, 401, 99, 440]]</t>
+    <t>[[216, 1323, 350, 124, 1134, 23], [1068, 266, 163], [252, 113, 308, 83, 1690], [132, 232, 324, 445, 510, 316, 383]]</t>
   </si>
   <si>
     <t>perf_typical_h4096_ne2048_ws8_inbf16_outbf16_ID1048</t>
@@ -2753,19 +2753,19 @@
     <t>[[2048, 4096]]</t>
   </si>
   <si>
-    <t>[[26, 131, 140, 12192, 107, 4, 453, 3581, 106, 125, 3205, 247, 165, 483, 138], [444, 283, 1120, 487, 91, 238, 68, 162, 375, 7975, 247, 362, 383, 11384, 7055, 67], [21, 48, 98, 497, 167, 38, 26, 233, 155, 4013, 345, 224, 403, 9502, 290, 200, 355, 158, 397, 31, 9990, 4857, 411, 2587, 103, 202, 14610], [268, 495, 995, 76, 92, 34, 66, 3780, 3904, 16204, 408, 240, 389, 141, 3447, 220, 470, 103, 158, 11, 444, 4], [488, 14882, 458, 259, 423, 274, 259, 11563, 36, 402, 432, 6181, 113, 354, 221, 6, 422, 196, 186, 120, 426, 4343, 256, 182, 3682, 432, 3597, 211, 386, 288], [13467, 423], [267, 189, 476, 10637, 15433, 289, 29], [6688, 275, 5671, 453, 2647, 150, 5379, 483, 365, 103, 9448, 14949, 206, 276, 471, 31, 236, 401, 303, 193, 150, 404, 342, 14, 466, 92, 226, 351, 235, 6643, 473]]</t>
+    <t>[[159, 29, 363, 246, 209, 364, 465], [365, 267, 280], [462, 313, 251, 312, 209, 64, 475, 508], [391], [442, 1795, 465, 121], [58, 425, 135, 964, 376], [485, 206, 290, 423, 387, 326, 320, 359], [41, 119, 494, 1907]]</t>
   </si>
   <si>
     <t>perf_typical_h1024_ne1024_ws2_infp16_outfp16_ID1049</t>
   </si>
   <si>
-    <t>[[95, 998], [55, 356, 270, 210, 42, 369, 240, 937, 419, 1193, 226, 335, 410, 689, 337, 1710, 480, 267, 27, 1449, 293, 173, 31]]</t>
+    <t>[[124, 308, 1156, 45, 144], [493, 411, 194, 134, 457, 400, 349, 299]]</t>
   </si>
   <si>
     <t>perf_typical_h1024_ne1024_ws4_infp16_outfp16_ID1050</t>
   </si>
   <si>
-    <t>[[1872, 155, 290, 467, 40, 443, 2158, 490, 59, 4060, 81, 118, 3544, 91, 318, 320, 3230, 341, 24, 454, 141, 12, 342, 328, 158, 207, 476, 3992, 353, 396, 439, 2462], [483, 2529, 210], [402, 320, 441, 313, 293, 159, 2538, 414, 312, 250, 425, 161, 434, 55, 268, 211, 744, 3075, 359, 2633], [192, 3374, 104, 267, 1316, 314, 3894, 325, 462, 299, 212, 3940, 15, 26, 289, 269, 73, 207, 453]]</t>
+    <t>[[182], [1884, 339, 340, 326, 324, 193, 769, 316, 26, 408], [1659, 465], [56, 200, 718, 768, 435, 462, 294, 405, 374, 1746]]</t>
   </si>
 </sst>
 </file>
@@ -3241,148 +3241,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
